--- a/bancos/SISOR/BASE_DETALHAMENTO_OBRAS.xlsx
+++ b/bancos/SISOR/BASE_DETALHAMENTO_OBRAS.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x15 xr xr6 xr10">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25601"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25928"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\andre\OneDrive\SEPLAG\2022\SPLOR\DCPPN\LeiOrcamentariaAnual\LOA\bancos\SISOR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{72D73F02-82B8-4576-B7B8-54DEC71DE37A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{17E7E226-1BB7-442E-A82D-B32F9EC6D3EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="150" windowWidth="21600" windowHeight="11145"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="21600" windowHeight="10890"/>
   </bookViews>
   <sheets>
     <sheet name="BASE_DETALHAMENTO_OBRAS" sheetId="1" r:id="rId1"/>
@@ -2079,7 +2079,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme 2013 - 2022" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>

--- a/bancos/SISOR/BASE_DETALHAMENTO_OBRAS.xlsx
+++ b/bancos/SISOR/BASE_DETALHAMENTO_OBRAS.xlsx
@@ -2627,11 +2627,11 @@
         <v>111</v>
       </c>
       <c r="I26" t="n">
-        <v>12042</v>
+        <v>8657</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>PRESTACAO DE SERVICOS DE IMPLEMENTACAO OBRA DE CONTROLE DE CHEIAS DO CORREGORIACHO DA PEDRA PROJETO DE TRABALHO TECNICO SOCIAL PPS EM CONTAGEM</t>
+          <t>Exec. Obras do Complemento da Requalif. Urb. e Ambiental do Ribeirão Arrudas”, no trecho entre o Viaduto do Barreiro e a Av. Presidente Castelo Branco, em BH e Contagem/MG.</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -27629,19 +27629,19 @@
     </row>
     <row r="317">
       <c r="A317" t="n">
-        <v>5141</v>
+        <v>5081</v>
       </c>
       <c r="B317" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="C317" t="n">
-        <v>126</v>
+        <v>512</v>
       </c>
       <c r="D317" t="n">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="E317" t="n">
-        <v>6006</v>
+        <v>8009</v>
       </c>
       <c r="F317" t="n">
         <v>0</v>
@@ -27650,14 +27650,14 @@
         <v>0</v>
       </c>
       <c r="H317" t="n">
-        <v>50</v>
+        <v>498</v>
       </c>
       <c r="I317" t="n">
         <v>0</v>
       </c>
       <c r="J317" t="inlineStr">
         <is>
-          <t>ELABORAÇÃO E EXECUÇÃO DE PROJETOS RELACIONADOS À REFORMA, MODERNIZAÇÃO E ADEQUAÇÃO DAS INSTALAÇÕES PREDIAIS DA COMPANHIA</t>
+          <t>AMPLIAÇÃO REALIZADA, OPERAÇÃO, MANUTENÇÃO E CONSERVAÇÃO DAS UNIDADES DE ADUÇÃO DO SISTEMA PRODUTOR RIO MANSO; REVERSÃO DOS ATIVOS À COMPANHIA DE SANEAMENTO DE MINAS GERAIS.</t>
         </is>
       </c>
       <c r="K317" t="inlineStr">
@@ -27667,11 +27667,11 @@
       </c>
       <c r="L317" t="inlineStr">
         <is>
-          <t>PERCENTUAL</t>
+          <t>METRO CÚBICO P/ SEGUNDO</t>
         </is>
       </c>
       <c r="M317" t="n">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="N317" t="inlineStr">
         <is>
@@ -27680,54 +27680,54 @@
       </c>
       <c r="O317" t="inlineStr">
         <is>
-          <t>Estadual</t>
+          <t>Região Intermediária de Belo Horizonte</t>
         </is>
       </c>
       <c r="P317" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
+          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE BELO HORIZONTE</t>
         </is>
       </c>
       <c r="Q317" t="n">
         <v>0</v>
       </c>
       <c r="R317" t="n">
-        <v>3280000</v>
+        <v>45752420</v>
       </c>
       <c r="S317" t="n">
         <v>0</v>
       </c>
       <c r="T317" t="n">
-        <v>13250000</v>
+        <v>42380044</v>
       </c>
       <c r="U317" t="n">
         <v>0</v>
       </c>
       <c r="V317" t="n">
-        <v>6250000</v>
+        <v>42380044</v>
       </c>
       <c r="W317" t="n">
         <v>0</v>
       </c>
       <c r="X317" t="n">
-        <v>3250000</v>
+        <v>42380044</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="n">
-        <v>5251</v>
+        <v>5141</v>
       </c>
       <c r="B318" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="C318" t="n">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="D318" t="n">
-        <v>123</v>
+        <v>30</v>
       </c>
       <c r="E318" t="n">
-        <v>3013</v>
+        <v>6006</v>
       </c>
       <c r="F318" t="n">
         <v>0</v>
@@ -27736,14 +27736,14 @@
         <v>0</v>
       </c>
       <c r="H318" t="n">
-        <v>93</v>
+        <v>50</v>
       </c>
       <c r="I318" t="n">
         <v>0</v>
       </c>
       <c r="J318" t="inlineStr">
         <is>
-          <t>EXPANSÃO DA INFRAESTRUTURA DE DISTRIBUIÇÃO DE GÁS NATURAL, EM GASODUTOS VIRTUAIS E PRIMÁRIOS, EM MINAS GERAIS.</t>
+          <t>ELABORAÇÃO E EXECUÇÃO DE PROJETOS RELACIONADOS À REFORMA, MODERNIZAÇÃO E ADEQUAÇÃO DAS INSTALAÇÕES PREDIAIS DA COMPANHIA</t>
         </is>
       </c>
       <c r="K318" t="inlineStr">
@@ -27753,11 +27753,11 @@
       </c>
       <c r="L318" t="inlineStr">
         <is>
-          <t>AÇÃO</t>
+          <t>PERCENTUAL</t>
         </is>
       </c>
       <c r="M318" t="n">
-        <v>292</v>
+        <v>100</v>
       </c>
       <c r="N318" t="inlineStr">
         <is>
@@ -27766,54 +27766,54 @@
       </c>
       <c r="O318" t="inlineStr">
         <is>
-          <t>Região Intermediária de Belo Horizonte</t>
+          <t>Estadual</t>
         </is>
       </c>
       <c r="P318" t="inlineStr">
         <is>
-          <t>BELO HORIZONTE</t>
+          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
         </is>
       </c>
       <c r="Q318" t="n">
-        <v>409881263</v>
+        <v>0</v>
       </c>
       <c r="R318" t="n">
-        <v>409881263</v>
+        <v>3280000</v>
       </c>
       <c r="S318" t="n">
-        <v>416795211</v>
+        <v>0</v>
       </c>
       <c r="T318" t="n">
-        <v>416795211</v>
+        <v>13250000</v>
       </c>
       <c r="U318" t="n">
-        <v>433214634</v>
+        <v>0</v>
       </c>
       <c r="V318" t="n">
-        <v>433214634</v>
+        <v>6250000</v>
       </c>
       <c r="W318" t="n">
-        <v>285354938</v>
+        <v>0</v>
       </c>
       <c r="X318" t="n">
-        <v>285354938</v>
+        <v>3250000</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="n">
-        <v>5391</v>
+        <v>5251</v>
       </c>
       <c r="B319" t="n">
         <v>25</v>
       </c>
       <c r="C319" t="n">
-        <v>752</v>
+        <v>121</v>
       </c>
       <c r="D319" t="n">
-        <v>92</v>
+        <v>133</v>
       </c>
       <c r="E319" t="n">
-        <v>3004</v>
+        <v>3018</v>
       </c>
       <c r="F319" t="n">
         <v>0</v>
@@ -27822,28 +27822,28 @@
         <v>0</v>
       </c>
       <c r="H319" t="n">
-        <v>21</v>
+        <v>495</v>
       </c>
       <c r="I319" t="n">
         <v>0</v>
       </c>
       <c r="J319" t="inlineStr">
         <is>
-          <t>EXPANSÃO E AQUISIÇÃO DO SISTEMA DE TRANSMISSÃO</t>
+          <t>EXPANSÃO DA INFRAESTRUTURA DE DISTRIBUIÇÃO DE GÁS NATURAL, EM GASODUTOS VIRTUAIS E PRIMÁRIOS, EM MINAS GERAIS.</t>
         </is>
       </c>
       <c r="K319" t="inlineStr">
         <is>
-          <t>EXECUÇÃO</t>
+          <t>INICIANDO</t>
         </is>
       </c>
       <c r="L319" t="inlineStr">
         <is>
-          <t>UNIDADE</t>
+          <t>AÇÃO</t>
         </is>
       </c>
       <c r="M319" t="n">
-        <v>4</v>
+        <v>292</v>
       </c>
       <c r="N319" t="inlineStr">
         <is>
@@ -27857,32 +27857,32 @@
       </c>
       <c r="P319" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE BELO HORIZONTE</t>
+          <t>BELO HORIZONTE</t>
         </is>
       </c>
       <c r="Q319" t="n">
         <v>0</v>
       </c>
       <c r="R319" t="n">
-        <v>64463632</v>
+        <v>409881263</v>
       </c>
       <c r="S319" t="n">
         <v>0</v>
       </c>
       <c r="T319" t="n">
-        <v>67170650</v>
+        <v>416795211</v>
       </c>
       <c r="U319" t="n">
         <v>0</v>
       </c>
       <c r="V319" t="n">
-        <v>18488267</v>
+        <v>433214634</v>
       </c>
       <c r="W319" t="n">
         <v>0</v>
       </c>
       <c r="X319" t="n">
-        <v>0</v>
+        <v>285354938</v>
       </c>
     </row>
     <row r="320">
@@ -27908,7 +27908,7 @@
         <v>0</v>
       </c>
       <c r="H320" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I320" t="n">
         <v>0</v>
@@ -27929,7 +27929,7 @@
         </is>
       </c>
       <c r="M320" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="N320" t="inlineStr">
         <is>
@@ -27938,31 +27938,31 @@
       </c>
       <c r="O320" t="inlineStr">
         <is>
-          <t>Região Intermediária de Divinópolis</t>
+          <t>Região Intermediária de Belo Horizonte</t>
         </is>
       </c>
       <c r="P320" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE DIVINÓPOLIS</t>
+          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE BELO HORIZONTE</t>
         </is>
       </c>
       <c r="Q320" t="n">
         <v>0</v>
       </c>
       <c r="R320" t="n">
-        <v>18351371</v>
+        <v>64463632</v>
       </c>
       <c r="S320" t="n">
         <v>0</v>
       </c>
       <c r="T320" t="n">
-        <v>18186779</v>
+        <v>67170650</v>
       </c>
       <c r="U320" t="n">
         <v>0</v>
       </c>
       <c r="V320" t="n">
-        <v>0</v>
+        <v>18488267</v>
       </c>
       <c r="W320" t="n">
         <v>0</v>
@@ -27994,7 +27994,7 @@
         <v>0</v>
       </c>
       <c r="H321" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I321" t="n">
         <v>0</v>
@@ -28015,7 +28015,7 @@
         </is>
       </c>
       <c r="M321" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N321" t="inlineStr">
         <is>
@@ -28024,25 +28024,25 @@
       </c>
       <c r="O321" t="inlineStr">
         <is>
-          <t>Região Intermediária de Ipatinga</t>
+          <t>Região Intermediária de Divinópolis</t>
         </is>
       </c>
       <c r="P321" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE IPATINGA</t>
+          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE DIVINÓPOLIS</t>
         </is>
       </c>
       <c r="Q321" t="n">
         <v>0</v>
       </c>
       <c r="R321" t="n">
-        <v>12200672</v>
+        <v>18351371</v>
       </c>
       <c r="S321" t="n">
         <v>0</v>
       </c>
       <c r="T321" t="n">
-        <v>9039384</v>
+        <v>18186779</v>
       </c>
       <c r="U321" t="n">
         <v>0</v>
@@ -28080,7 +28080,7 @@
         <v>0</v>
       </c>
       <c r="H322" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I322" t="n">
         <v>0</v>
@@ -28101,7 +28101,7 @@
         </is>
       </c>
       <c r="M322" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N322" t="inlineStr">
         <is>
@@ -28110,25 +28110,25 @@
       </c>
       <c r="O322" t="inlineStr">
         <is>
-          <t>Região Intermediária de Juíz de Fora</t>
+          <t>Região Intermediária de Ipatinga</t>
         </is>
       </c>
       <c r="P322" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE JUÍZ DE FORA</t>
+          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE IPATINGA</t>
         </is>
       </c>
       <c r="Q322" t="n">
         <v>0</v>
       </c>
       <c r="R322" t="n">
-        <v>749073</v>
+        <v>12200672</v>
       </c>
       <c r="S322" t="n">
         <v>0</v>
       </c>
       <c r="T322" t="n">
-        <v>3644159</v>
+        <v>9039384</v>
       </c>
       <c r="U322" t="n">
         <v>0</v>
@@ -28166,7 +28166,7 @@
         <v>0</v>
       </c>
       <c r="H323" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I323" t="n">
         <v>0</v>
@@ -28196,37 +28196,37 @@
       </c>
       <c r="O323" t="inlineStr">
         <is>
-          <t>Região Intermediária de Montes Claros</t>
+          <t>Região Intermediária de Juíz de Fora</t>
         </is>
       </c>
       <c r="P323" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE MONTES CLAROS</t>
+          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE JUÍZ DE FORA</t>
         </is>
       </c>
       <c r="Q323" t="n">
         <v>0</v>
       </c>
       <c r="R323" t="n">
-        <v>15117086</v>
+        <v>749073</v>
       </c>
       <c r="S323" t="n">
         <v>0</v>
       </c>
       <c r="T323" t="n">
-        <v>73356054</v>
+        <v>3644159</v>
       </c>
       <c r="U323" t="n">
         <v>0</v>
       </c>
       <c r="V323" t="n">
-        <v>41670854</v>
+        <v>0</v>
       </c>
       <c r="W323" t="n">
         <v>0</v>
       </c>
       <c r="X323" t="n">
-        <v>13570642</v>
+        <v>0</v>
       </c>
     </row>
     <row r="324">
@@ -28252,7 +28252,7 @@
         <v>0</v>
       </c>
       <c r="H324" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I324" t="n">
         <v>0</v>
@@ -28282,37 +28282,37 @@
       </c>
       <c r="O324" t="inlineStr">
         <is>
-          <t>Região Intermediária de Pouso Alegre</t>
+          <t>Região Intermediária de Montes Claros</t>
         </is>
       </c>
       <c r="P324" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE POUSO ALEGRE</t>
+          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE MONTES CLAROS</t>
         </is>
       </c>
       <c r="Q324" t="n">
         <v>0</v>
       </c>
       <c r="R324" t="n">
-        <v>40701410</v>
+        <v>15117086</v>
       </c>
       <c r="S324" t="n">
         <v>0</v>
       </c>
       <c r="T324" t="n">
-        <v>277702</v>
+        <v>73356054</v>
       </c>
       <c r="U324" t="n">
         <v>0</v>
       </c>
       <c r="V324" t="n">
-        <v>0</v>
+        <v>41670854</v>
       </c>
       <c r="W324" t="n">
         <v>0</v>
       </c>
       <c r="X324" t="n">
-        <v>0</v>
+        <v>13570642</v>
       </c>
     </row>
     <row r="325">
@@ -28338,7 +28338,7 @@
         <v>0</v>
       </c>
       <c r="H325" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I325" t="n">
         <v>0</v>
@@ -28359,7 +28359,7 @@
         </is>
       </c>
       <c r="M325" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N325" t="inlineStr">
         <is>
@@ -28368,31 +28368,31 @@
       </c>
       <c r="O325" t="inlineStr">
         <is>
-          <t>Região Intermediária de Uberaba</t>
+          <t>Região Intermediária de Pouso Alegre</t>
         </is>
       </c>
       <c r="P325" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE UBERABA</t>
+          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE POUSO ALEGRE</t>
         </is>
       </c>
       <c r="Q325" t="n">
         <v>0</v>
       </c>
       <c r="R325" t="n">
-        <v>30960705</v>
+        <v>40701410</v>
       </c>
       <c r="S325" t="n">
         <v>0</v>
       </c>
       <c r="T325" t="n">
-        <v>33334550</v>
+        <v>277702</v>
       </c>
       <c r="U325" t="n">
         <v>0</v>
       </c>
       <c r="V325" t="n">
-        <v>31941527</v>
+        <v>0</v>
       </c>
       <c r="W325" t="n">
         <v>0</v>
@@ -28424,7 +28424,7 @@
         <v>0</v>
       </c>
       <c r="H326" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I326" t="n">
         <v>0</v>
@@ -28445,7 +28445,7 @@
         </is>
       </c>
       <c r="M326" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N326" t="inlineStr">
         <is>
@@ -28454,31 +28454,31 @@
       </c>
       <c r="O326" t="inlineStr">
         <is>
-          <t>Região Intermediária de Uberlândia</t>
+          <t>Região Intermediária de Uberaba</t>
         </is>
       </c>
       <c r="P326" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE UBERLÂNDIA</t>
+          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE UBERABA</t>
         </is>
       </c>
       <c r="Q326" t="n">
         <v>0</v>
       </c>
       <c r="R326" t="n">
-        <v>903230</v>
+        <v>30960705</v>
       </c>
       <c r="S326" t="n">
         <v>0</v>
       </c>
       <c r="T326" t="n">
-        <v>5310430</v>
+        <v>33334550</v>
       </c>
       <c r="U326" t="n">
         <v>0</v>
       </c>
       <c r="V326" t="n">
-        <v>0</v>
+        <v>31941527</v>
       </c>
       <c r="W326" t="n">
         <v>0</v>
@@ -28510,7 +28510,7 @@
         <v>0</v>
       </c>
       <c r="H327" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="I327" t="n">
         <v>0</v>
@@ -28540,25 +28540,25 @@
       </c>
       <c r="O327" t="inlineStr">
         <is>
-          <t>Estadual</t>
+          <t>Região Intermediária de Uberlândia</t>
         </is>
       </c>
       <c r="P327" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
+          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE UBERLÂNDIA</t>
         </is>
       </c>
       <c r="Q327" t="n">
         <v>0</v>
       </c>
       <c r="R327" t="n">
-        <v>15493024</v>
+        <v>903230</v>
       </c>
       <c r="S327" t="n">
         <v>0</v>
       </c>
       <c r="T327" t="n">
-        <v>14350000</v>
+        <v>5310430</v>
       </c>
       <c r="U327" t="n">
         <v>0</v>
@@ -28587,7 +28587,7 @@
         <v>92</v>
       </c>
       <c r="E328" t="n">
-        <v>3005</v>
+        <v>3004</v>
       </c>
       <c r="F328" t="n">
         <v>0</v>
@@ -28596,14 +28596,14 @@
         <v>0</v>
       </c>
       <c r="H328" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I328" t="n">
         <v>0</v>
       </c>
       <c r="J328" t="inlineStr">
         <is>
-          <t>REFORMAS DE SUBESTAÇÕES E LINHAS DE TRANSMISSÃO</t>
+          <t>EXPANSÃO E AQUISIÇÃO DO SISTEMA DE TRANSMISSÃO</t>
         </is>
       </c>
       <c r="K328" t="inlineStr">
@@ -28626,37 +28626,37 @@
       </c>
       <c r="O328" t="inlineStr">
         <is>
-          <t>Região Intermediária de Barbacena</t>
+          <t>Estadual</t>
         </is>
       </c>
       <c r="P328" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE BARBACENA</t>
+          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
         </is>
       </c>
       <c r="Q328" t="n">
         <v>0</v>
       </c>
       <c r="R328" t="n">
-        <v>4671650</v>
+        <v>15493024</v>
       </c>
       <c r="S328" t="n">
         <v>0</v>
       </c>
       <c r="T328" t="n">
-        <v>25457731</v>
+        <v>14350000</v>
       </c>
       <c r="U328" t="n">
         <v>0</v>
       </c>
       <c r="V328" t="n">
-        <v>4169945</v>
+        <v>0</v>
       </c>
       <c r="W328" t="n">
         <v>0</v>
       </c>
       <c r="X328" t="n">
-        <v>20660732</v>
+        <v>0</v>
       </c>
     </row>
     <row r="329">
@@ -28682,7 +28682,7 @@
         <v>0</v>
       </c>
       <c r="H329" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I329" t="n">
         <v>0</v>
@@ -28712,37 +28712,37 @@
       </c>
       <c r="O329" t="inlineStr">
         <is>
-          <t>Região Intermediária de Belo Horizonte</t>
+          <t>Região Intermediária de Barbacena</t>
         </is>
       </c>
       <c r="P329" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE BELO HORIZONTE</t>
+          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE BARBACENA</t>
         </is>
       </c>
       <c r="Q329" t="n">
         <v>0</v>
       </c>
       <c r="R329" t="n">
-        <v>46552654</v>
+        <v>4671650</v>
       </c>
       <c r="S329" t="n">
         <v>0</v>
       </c>
       <c r="T329" t="n">
-        <v>148470607</v>
+        <v>25457731</v>
       </c>
       <c r="U329" t="n">
         <v>0</v>
       </c>
       <c r="V329" t="n">
-        <v>202616016</v>
+        <v>4169945</v>
       </c>
       <c r="W329" t="n">
         <v>0</v>
       </c>
       <c r="X329" t="n">
-        <v>125656975</v>
+        <v>20660732</v>
       </c>
     </row>
     <row r="330">
@@ -28768,7 +28768,7 @@
         <v>0</v>
       </c>
       <c r="H330" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I330" t="n">
         <v>0</v>
@@ -28798,37 +28798,37 @@
       </c>
       <c r="O330" t="inlineStr">
         <is>
-          <t>Região Intermediária de Divinópolis</t>
+          <t>Região Intermediária de Belo Horizonte</t>
         </is>
       </c>
       <c r="P330" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE DIVINÓPOLIS</t>
+          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE BELO HORIZONTE</t>
         </is>
       </c>
       <c r="Q330" t="n">
         <v>0</v>
       </c>
       <c r="R330" t="n">
-        <v>13684605</v>
+        <v>46552654</v>
       </c>
       <c r="S330" t="n">
         <v>0</v>
       </c>
       <c r="T330" t="n">
-        <v>24101202</v>
+        <v>148470607</v>
       </c>
       <c r="U330" t="n">
         <v>0</v>
       </c>
       <c r="V330" t="n">
-        <v>10241872</v>
+        <v>202616016</v>
       </c>
       <c r="W330" t="n">
         <v>0</v>
       </c>
       <c r="X330" t="n">
-        <v>15576475</v>
+        <v>125656975</v>
       </c>
     </row>
     <row r="331">
@@ -28854,7 +28854,7 @@
         <v>0</v>
       </c>
       <c r="H331" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I331" t="n">
         <v>0</v>
@@ -28884,37 +28884,37 @@
       </c>
       <c r="O331" t="inlineStr">
         <is>
-          <t>Região Intermediária de Governador Valadares</t>
+          <t>Região Intermediária de Divinópolis</t>
         </is>
       </c>
       <c r="P331" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE GOVERNADOR VALADARES</t>
+          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE DIVINÓPOLIS</t>
         </is>
       </c>
       <c r="Q331" t="n">
         <v>0</v>
       </c>
       <c r="R331" t="n">
-        <v>1280000</v>
+        <v>13684605</v>
       </c>
       <c r="S331" t="n">
         <v>0</v>
       </c>
       <c r="T331" t="n">
-        <v>17349423</v>
+        <v>24101202</v>
       </c>
       <c r="U331" t="n">
         <v>0</v>
       </c>
       <c r="V331" t="n">
-        <v>29671909</v>
+        <v>10241872</v>
       </c>
       <c r="W331" t="n">
         <v>0</v>
       </c>
       <c r="X331" t="n">
-        <v>21352654</v>
+        <v>15576475</v>
       </c>
     </row>
     <row r="332">
@@ -28940,7 +28940,7 @@
         <v>0</v>
       </c>
       <c r="H332" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I332" t="n">
         <v>0</v>
@@ -28970,37 +28970,37 @@
       </c>
       <c r="O332" t="inlineStr">
         <is>
-          <t>Região Intermediária de Ipatinga</t>
+          <t>Região Intermediária de Governador Valadares</t>
         </is>
       </c>
       <c r="P332" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE IPATINGA</t>
+          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE GOVERNADOR VALADARES</t>
         </is>
       </c>
       <c r="Q332" t="n">
         <v>0</v>
       </c>
       <c r="R332" t="n">
-        <v>16177065</v>
+        <v>1280000</v>
       </c>
       <c r="S332" t="n">
         <v>0</v>
       </c>
       <c r="T332" t="n">
-        <v>50824821</v>
+        <v>17349423</v>
       </c>
       <c r="U332" t="n">
         <v>0</v>
       </c>
       <c r="V332" t="n">
-        <v>52951623</v>
+        <v>29671909</v>
       </c>
       <c r="W332" t="n">
         <v>0</v>
       </c>
       <c r="X332" t="n">
-        <v>30208222</v>
+        <v>21352654</v>
       </c>
     </row>
     <row r="333">
@@ -29026,7 +29026,7 @@
         <v>0</v>
       </c>
       <c r="H333" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I333" t="n">
         <v>0</v>
@@ -29056,37 +29056,37 @@
       </c>
       <c r="O333" t="inlineStr">
         <is>
-          <t>Região Intermediária de Juíz de Fora</t>
+          <t>Região Intermediária de Ipatinga</t>
         </is>
       </c>
       <c r="P333" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE JUÍZ DE FORA</t>
+          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE IPATINGA</t>
         </is>
       </c>
       <c r="Q333" t="n">
         <v>0</v>
       </c>
       <c r="R333" t="n">
-        <v>716368</v>
+        <v>16177065</v>
       </c>
       <c r="S333" t="n">
         <v>0</v>
       </c>
       <c r="T333" t="n">
-        <v>11724151</v>
+        <v>50824821</v>
       </c>
       <c r="U333" t="n">
         <v>0</v>
       </c>
       <c r="V333" t="n">
-        <v>669016</v>
+        <v>52951623</v>
       </c>
       <c r="W333" t="n">
         <v>0</v>
       </c>
       <c r="X333" t="n">
-        <v>23500746</v>
+        <v>30208222</v>
       </c>
     </row>
     <row r="334">
@@ -29112,7 +29112,7 @@
         <v>0</v>
       </c>
       <c r="H334" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="I334" t="n">
         <v>0</v>
@@ -29142,37 +29142,37 @@
       </c>
       <c r="O334" t="inlineStr">
         <is>
-          <t>Região Intermediária de Montes Claros</t>
+          <t>Região Intermediária de Juíz de Fora</t>
         </is>
       </c>
       <c r="P334" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE MONTES CLAROS</t>
+          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE JUÍZ DE FORA</t>
         </is>
       </c>
       <c r="Q334" t="n">
         <v>0</v>
       </c>
       <c r="R334" t="n">
-        <v>16689185</v>
+        <v>716368</v>
       </c>
       <c r="S334" t="n">
         <v>0</v>
       </c>
       <c r="T334" t="n">
-        <v>91854231</v>
+        <v>11724151</v>
       </c>
       <c r="U334" t="n">
         <v>0</v>
       </c>
       <c r="V334" t="n">
-        <v>76848075</v>
+        <v>669016</v>
       </c>
       <c r="W334" t="n">
         <v>0</v>
       </c>
       <c r="X334" t="n">
-        <v>46129193</v>
+        <v>23500746</v>
       </c>
     </row>
     <row r="335">
@@ -29198,7 +29198,7 @@
         <v>0</v>
       </c>
       <c r="H335" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I335" t="n">
         <v>0</v>
@@ -29228,37 +29228,37 @@
       </c>
       <c r="O335" t="inlineStr">
         <is>
-          <t>Região Intermediária de Pouso Alegre</t>
+          <t>Região Intermediária de Montes Claros</t>
         </is>
       </c>
       <c r="P335" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE POUSO ALEGRE</t>
+          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE MONTES CLAROS</t>
         </is>
       </c>
       <c r="Q335" t="n">
         <v>0</v>
       </c>
       <c r="R335" t="n">
-        <v>4804338</v>
+        <v>16689185</v>
       </c>
       <c r="S335" t="n">
         <v>0</v>
       </c>
       <c r="T335" t="n">
-        <v>1965000</v>
+        <v>91854231</v>
       </c>
       <c r="U335" t="n">
         <v>0</v>
       </c>
       <c r="V335" t="n">
-        <v>0</v>
+        <v>76848075</v>
       </c>
       <c r="W335" t="n">
         <v>0</v>
       </c>
       <c r="X335" t="n">
-        <v>0</v>
+        <v>46129193</v>
       </c>
     </row>
     <row r="336">
@@ -29284,7 +29284,7 @@
         <v>0</v>
       </c>
       <c r="H336" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="I336" t="n">
         <v>0</v>
@@ -29314,37 +29314,37 @@
       </c>
       <c r="O336" t="inlineStr">
         <is>
-          <t>Região Intermediária de Uberaba</t>
+          <t>Região Intermediária de Pouso Alegre</t>
         </is>
       </c>
       <c r="P336" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE UBERABA</t>
+          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE POUSO ALEGRE</t>
         </is>
       </c>
       <c r="Q336" t="n">
         <v>0</v>
       </c>
       <c r="R336" t="n">
-        <v>73431695</v>
+        <v>4804338</v>
       </c>
       <c r="S336" t="n">
         <v>0</v>
       </c>
       <c r="T336" t="n">
-        <v>90525277</v>
+        <v>1965000</v>
       </c>
       <c r="U336" t="n">
         <v>0</v>
       </c>
       <c r="V336" t="n">
-        <v>87502566</v>
+        <v>0</v>
       </c>
       <c r="W336" t="n">
         <v>0</v>
       </c>
       <c r="X336" t="n">
-        <v>91741380</v>
+        <v>0</v>
       </c>
     </row>
     <row r="337">
@@ -29370,7 +29370,7 @@
         <v>0</v>
       </c>
       <c r="H337" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I337" t="n">
         <v>0</v>
@@ -29400,37 +29400,37 @@
       </c>
       <c r="O337" t="inlineStr">
         <is>
-          <t>Região Intermediária de Uberlândia</t>
+          <t>Região Intermediária de Uberaba</t>
         </is>
       </c>
       <c r="P337" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE UBERLÂNDIA</t>
+          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE UBERABA</t>
         </is>
       </c>
       <c r="Q337" t="n">
         <v>0</v>
       </c>
       <c r="R337" t="n">
-        <v>41440409</v>
+        <v>73431695</v>
       </c>
       <c r="S337" t="n">
         <v>0</v>
       </c>
       <c r="T337" t="n">
-        <v>11615612</v>
+        <v>90525277</v>
       </c>
       <c r="U337" t="n">
         <v>0</v>
       </c>
       <c r="V337" t="n">
-        <v>12854837</v>
+        <v>87502566</v>
       </c>
       <c r="W337" t="n">
         <v>0</v>
       </c>
       <c r="X337" t="n">
-        <v>51737981</v>
+        <v>91741380</v>
       </c>
     </row>
     <row r="338">
@@ -29456,7 +29456,7 @@
         <v>0</v>
       </c>
       <c r="H338" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I338" t="n">
         <v>0</v>
@@ -29486,37 +29486,37 @@
       </c>
       <c r="O338" t="inlineStr">
         <is>
-          <t>Região Intermediária de Varginha</t>
+          <t>Região Intermediária de Uberlândia</t>
         </is>
       </c>
       <c r="P338" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE VARGINHA</t>
+          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE UBERLÂNDIA</t>
         </is>
       </c>
       <c r="Q338" t="n">
         <v>0</v>
       </c>
       <c r="R338" t="n">
-        <v>817866</v>
+        <v>41440409</v>
       </c>
       <c r="S338" t="n">
         <v>0</v>
       </c>
       <c r="T338" t="n">
-        <v>9725528</v>
+        <v>11615612</v>
       </c>
       <c r="U338" t="n">
         <v>0</v>
       </c>
       <c r="V338" t="n">
-        <v>22285802</v>
+        <v>12854837</v>
       </c>
       <c r="W338" t="n">
         <v>0</v>
       </c>
       <c r="X338" t="n">
-        <v>21166631</v>
+        <v>51737981</v>
       </c>
     </row>
     <row r="339">
@@ -29542,7 +29542,7 @@
         <v>0</v>
       </c>
       <c r="H339" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I339" t="n">
         <v>0</v>
@@ -29572,37 +29572,37 @@
       </c>
       <c r="O339" t="inlineStr">
         <is>
-          <t>Estadual</t>
+          <t>Região Intermediária de Varginha</t>
         </is>
       </c>
       <c r="P339" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
+          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE VARGINHA</t>
         </is>
       </c>
       <c r="Q339" t="n">
         <v>0</v>
       </c>
       <c r="R339" t="n">
-        <v>21556074</v>
+        <v>817866</v>
       </c>
       <c r="S339" t="n">
         <v>0</v>
       </c>
       <c r="T339" t="n">
-        <v>32249383</v>
+        <v>9725528</v>
       </c>
       <c r="U339" t="n">
         <v>0</v>
       </c>
       <c r="V339" t="n">
-        <v>37593579</v>
+        <v>22285802</v>
       </c>
       <c r="W339" t="n">
         <v>0</v>
       </c>
       <c r="X339" t="n">
-        <v>32622214</v>
+        <v>21166631</v>
       </c>
     </row>
     <row r="340">
@@ -29616,10 +29616,10 @@
         <v>752</v>
       </c>
       <c r="D340" t="n">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E340" t="n">
-        <v>3001</v>
+        <v>3005</v>
       </c>
       <c r="F340" t="n">
         <v>0</v>
@@ -29628,14 +29628,14 @@
         <v>0</v>
       </c>
       <c r="H340" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I340" t="n">
         <v>0</v>
       </c>
       <c r="J340" t="inlineStr">
         <is>
-          <t>EXPANSÃO DO SISTEMA DE GERAÇÃO</t>
+          <t>REFORMAS DE SUBESTAÇÕES E LINHAS DE TRANSMISSÃO</t>
         </is>
       </c>
       <c r="K340" t="inlineStr">
@@ -29658,37 +29658,37 @@
       </c>
       <c r="O340" t="inlineStr">
         <is>
-          <t>Região Intermediária de Montes Claros</t>
+          <t>Estadual</t>
         </is>
       </c>
       <c r="P340" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE MONTES CLAROS</t>
+          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
         </is>
       </c>
       <c r="Q340" t="n">
         <v>0</v>
       </c>
       <c r="R340" t="n">
-        <v>24673817</v>
+        <v>21556074</v>
       </c>
       <c r="S340" t="n">
         <v>0</v>
       </c>
       <c r="T340" t="n">
-        <v>0</v>
+        <v>32249383</v>
       </c>
       <c r="U340" t="n">
         <v>0</v>
       </c>
       <c r="V340" t="n">
-        <v>0</v>
+        <v>37593579</v>
       </c>
       <c r="W340" t="n">
         <v>0</v>
       </c>
       <c r="X340" t="n">
-        <v>0</v>
+        <v>32622214</v>
       </c>
     </row>
     <row r="341">
@@ -29714,7 +29714,7 @@
         <v>0</v>
       </c>
       <c r="H341" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="I341" t="n">
         <v>0</v>
@@ -29744,19 +29744,19 @@
       </c>
       <c r="O341" t="inlineStr">
         <is>
-          <t>Região Intermediária de Patos de Minas</t>
+          <t>Região Intermediária de Montes Claros</t>
         </is>
       </c>
       <c r="P341" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE PATOS DE MINAS</t>
+          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE MONTES CLAROS</t>
         </is>
       </c>
       <c r="Q341" t="n">
         <v>0</v>
       </c>
       <c r="R341" t="n">
-        <v>24423146</v>
+        <v>24673817</v>
       </c>
       <c r="S341" t="n">
         <v>0</v>
@@ -29779,7 +29779,7 @@
     </row>
     <row r="342">
       <c r="A342" t="n">
-        <v>5401</v>
+        <v>5391</v>
       </c>
       <c r="B342" t="n">
         <v>25</v>
@@ -29788,10 +29788,10 @@
         <v>752</v>
       </c>
       <c r="D342" t="n">
-        <v>72</v>
+        <v>94</v>
       </c>
       <c r="E342" t="n">
-        <v>3002</v>
+        <v>3001</v>
       </c>
       <c r="F342" t="n">
         <v>0</v>
@@ -29800,14 +29800,14 @@
         <v>0</v>
       </c>
       <c r="H342" t="n">
-        <v>7</v>
+        <v>43</v>
       </c>
       <c r="I342" t="n">
         <v>0</v>
       </c>
       <c r="J342" t="inlineStr">
         <is>
-          <t>EXECUÇÃO DO PLANO DE DESENVOLVIMENTO DA DISTRIBUIDORA (PDD)</t>
+          <t>EXPANSÃO DO SISTEMA DE GERAÇÃO</t>
         </is>
       </c>
       <c r="K342" t="inlineStr">
@@ -29821,7 +29821,7 @@
         </is>
       </c>
       <c r="M342" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="N342" t="inlineStr">
         <is>
@@ -29830,37 +29830,37 @@
       </c>
       <c r="O342" t="inlineStr">
         <is>
-          <t>Região Intermediária de Barbacena</t>
+          <t>Região Intermediária de Patos de Minas</t>
         </is>
       </c>
       <c r="P342" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE BARBACENA</t>
+          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE PATOS DE MINAS</t>
         </is>
       </c>
       <c r="Q342" t="n">
         <v>0</v>
       </c>
       <c r="R342" t="n">
-        <v>110105088</v>
+        <v>24423146</v>
       </c>
       <c r="S342" t="n">
         <v>0</v>
       </c>
       <c r="T342" t="n">
-        <v>122825942</v>
+        <v>0</v>
       </c>
       <c r="U342" t="n">
         <v>0</v>
       </c>
       <c r="V342" t="n">
-        <v>154836385</v>
+        <v>0</v>
       </c>
       <c r="W342" t="n">
         <v>0</v>
       </c>
       <c r="X342" t="n">
-        <v>142258628</v>
+        <v>0</v>
       </c>
     </row>
     <row r="343">
@@ -29886,7 +29886,7 @@
         <v>0</v>
       </c>
       <c r="H343" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I343" t="n">
         <v>0</v>
@@ -29907,7 +29907,7 @@
         </is>
       </c>
       <c r="M343" t="n">
-        <v>80</v>
+        <v>15</v>
       </c>
       <c r="N343" t="inlineStr">
         <is>
@@ -29916,37 +29916,37 @@
       </c>
       <c r="O343" t="inlineStr">
         <is>
-          <t>Região Intermediária de Belo Horizonte</t>
+          <t>Região Intermediária de Barbacena</t>
         </is>
       </c>
       <c r="P343" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE BELO HORIZONTE</t>
+          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE BARBACENA</t>
         </is>
       </c>
       <c r="Q343" t="n">
         <v>0</v>
       </c>
       <c r="R343" t="n">
-        <v>726324680</v>
+        <v>110105088</v>
       </c>
       <c r="S343" t="n">
         <v>0</v>
       </c>
       <c r="T343" t="n">
-        <v>859831029</v>
+        <v>122825942</v>
       </c>
       <c r="U343" t="n">
         <v>0</v>
       </c>
       <c r="V343" t="n">
-        <v>863237653</v>
+        <v>154836385</v>
       </c>
       <c r="W343" t="n">
         <v>0</v>
       </c>
       <c r="X343" t="n">
-        <v>527976420</v>
+        <v>142258628</v>
       </c>
     </row>
     <row r="344">
@@ -29972,7 +29972,7 @@
         <v>0</v>
       </c>
       <c r="H344" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I344" t="n">
         <v>0</v>
@@ -29993,7 +29993,7 @@
         </is>
       </c>
       <c r="M344" t="n">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="N344" t="inlineStr">
         <is>
@@ -30002,37 +30002,37 @@
       </c>
       <c r="O344" t="inlineStr">
         <is>
-          <t>Região Intermediária de Divinópolis</t>
+          <t>Região Intermediária de Belo Horizonte</t>
         </is>
       </c>
       <c r="P344" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE DIVINÓPOLIS</t>
+          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE BELO HORIZONTE</t>
         </is>
       </c>
       <c r="Q344" t="n">
         <v>0</v>
       </c>
       <c r="R344" t="n">
-        <v>353806722</v>
+        <v>726324680</v>
       </c>
       <c r="S344" t="n">
         <v>0</v>
       </c>
       <c r="T344" t="n">
-        <v>344167183</v>
+        <v>859831029</v>
       </c>
       <c r="U344" t="n">
         <v>0</v>
       </c>
       <c r="V344" t="n">
-        <v>401499310</v>
+        <v>863237653</v>
       </c>
       <c r="W344" t="n">
         <v>0</v>
       </c>
       <c r="X344" t="n">
-        <v>342915468</v>
+        <v>527976420</v>
       </c>
     </row>
     <row r="345">
@@ -30058,7 +30058,7 @@
         <v>0</v>
       </c>
       <c r="H345" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I345" t="n">
         <v>0</v>
@@ -30079,7 +30079,7 @@
         </is>
       </c>
       <c r="M345" t="n">
-        <v>1</v>
+        <v>83</v>
       </c>
       <c r="N345" t="inlineStr">
         <is>
@@ -30088,37 +30088,37 @@
       </c>
       <c r="O345" t="inlineStr">
         <is>
-          <t>Região Intermediária de Governador Valadares</t>
+          <t>Região Intermediária de Divinópolis</t>
         </is>
       </c>
       <c r="P345" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE GOVERNADOR VALADARES</t>
+          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE DIVINÓPOLIS</t>
         </is>
       </c>
       <c r="Q345" t="n">
         <v>0</v>
       </c>
       <c r="R345" t="n">
-        <v>120100570</v>
+        <v>353806722</v>
       </c>
       <c r="S345" t="n">
         <v>0</v>
       </c>
       <c r="T345" t="n">
-        <v>287268604</v>
+        <v>344167183</v>
       </c>
       <c r="U345" t="n">
         <v>0</v>
       </c>
       <c r="V345" t="n">
-        <v>182151414</v>
+        <v>401499310</v>
       </c>
       <c r="W345" t="n">
         <v>0</v>
       </c>
       <c r="X345" t="n">
-        <v>153489073</v>
+        <v>342915468</v>
       </c>
     </row>
     <row r="346">
@@ -30144,7 +30144,7 @@
         <v>0</v>
       </c>
       <c r="H346" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I346" t="n">
         <v>0</v>
@@ -30165,7 +30165,7 @@
         </is>
       </c>
       <c r="M346" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="N346" t="inlineStr">
         <is>
@@ -30174,37 +30174,37 @@
       </c>
       <c r="O346" t="inlineStr">
         <is>
-          <t>Região Intermediária de Ipatinga</t>
+          <t>Região Intermediária de Governador Valadares</t>
         </is>
       </c>
       <c r="P346" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE IPATINGA</t>
+          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE GOVERNADOR VALADARES</t>
         </is>
       </c>
       <c r="Q346" t="n">
         <v>0</v>
       </c>
       <c r="R346" t="n">
-        <v>98230858</v>
+        <v>120100570</v>
       </c>
       <c r="S346" t="n">
         <v>0</v>
       </c>
       <c r="T346" t="n">
-        <v>144051956</v>
+        <v>287268604</v>
       </c>
       <c r="U346" t="n">
         <v>0</v>
       </c>
       <c r="V346" t="n">
-        <v>178681504</v>
+        <v>182151414</v>
       </c>
       <c r="W346" t="n">
         <v>0</v>
       </c>
       <c r="X346" t="n">
-        <v>186607380</v>
+        <v>153489073</v>
       </c>
     </row>
     <row r="347">
@@ -30230,7 +30230,7 @@
         <v>0</v>
       </c>
       <c r="H347" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I347" t="n">
         <v>0</v>
@@ -30251,7 +30251,7 @@
         </is>
       </c>
       <c r="M347" t="n">
-        <v>65</v>
+        <v>25</v>
       </c>
       <c r="N347" t="inlineStr">
         <is>
@@ -30260,37 +30260,37 @@
       </c>
       <c r="O347" t="inlineStr">
         <is>
-          <t>Região Intermediária de Juíz de Fora</t>
+          <t>Região Intermediária de Ipatinga</t>
         </is>
       </c>
       <c r="P347" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE JUÍZ DE FORA</t>
+          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE IPATINGA</t>
         </is>
       </c>
       <c r="Q347" t="n">
         <v>0</v>
       </c>
       <c r="R347" t="n">
-        <v>370862856</v>
+        <v>98230858</v>
       </c>
       <c r="S347" t="n">
         <v>0</v>
       </c>
       <c r="T347" t="n">
-        <v>352372357</v>
+        <v>144051956</v>
       </c>
       <c r="U347" t="n">
         <v>0</v>
       </c>
       <c r="V347" t="n">
-        <v>412953428</v>
+        <v>178681504</v>
       </c>
       <c r="W347" t="n">
         <v>0</v>
       </c>
       <c r="X347" t="n">
-        <v>420297410</v>
+        <v>186607380</v>
       </c>
     </row>
     <row r="348">
@@ -30316,7 +30316,7 @@
         <v>0</v>
       </c>
       <c r="H348" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I348" t="n">
         <v>0</v>
@@ -30337,7 +30337,7 @@
         </is>
       </c>
       <c r="M348" t="n">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="N348" t="inlineStr">
         <is>
@@ -30346,37 +30346,37 @@
       </c>
       <c r="O348" t="inlineStr">
         <is>
-          <t>Região Intermediária de Montes Claros</t>
+          <t>Região Intermediária de Juíz de Fora</t>
         </is>
       </c>
       <c r="P348" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE MONTES CLAROS</t>
+          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE JUÍZ DE FORA</t>
         </is>
       </c>
       <c r="Q348" t="n">
         <v>0</v>
       </c>
       <c r="R348" t="n">
-        <v>421204358</v>
+        <v>370862856</v>
       </c>
       <c r="S348" t="n">
         <v>0</v>
       </c>
       <c r="T348" t="n">
-        <v>489659419</v>
+        <v>352372357</v>
       </c>
       <c r="U348" t="n">
         <v>0</v>
       </c>
       <c r="V348" t="n">
-        <v>526822948</v>
+        <v>412953428</v>
       </c>
       <c r="W348" t="n">
         <v>0</v>
       </c>
       <c r="X348" t="n">
-        <v>506261509</v>
+        <v>420297410</v>
       </c>
     </row>
     <row r="349">
@@ -30402,7 +30402,7 @@
         <v>0</v>
       </c>
       <c r="H349" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="I349" t="n">
         <v>0</v>
@@ -30423,7 +30423,7 @@
         </is>
       </c>
       <c r="M349" t="n">
-        <v>145</v>
+        <v>80</v>
       </c>
       <c r="N349" t="inlineStr">
         <is>
@@ -30432,37 +30432,37 @@
       </c>
       <c r="O349" t="inlineStr">
         <is>
-          <t>Região Intermediária de Patos de Minas</t>
+          <t>Região Intermediária de Montes Claros</t>
         </is>
       </c>
       <c r="P349" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE PATOS DE MINAS</t>
+          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE MONTES CLAROS</t>
         </is>
       </c>
       <c r="Q349" t="n">
         <v>0</v>
       </c>
       <c r="R349" t="n">
-        <v>323743010</v>
+        <v>421204358</v>
       </c>
       <c r="S349" t="n">
         <v>0</v>
       </c>
       <c r="T349" t="n">
-        <v>220962542</v>
+        <v>489659419</v>
       </c>
       <c r="U349" t="n">
         <v>0</v>
       </c>
       <c r="V349" t="n">
-        <v>264145839</v>
+        <v>526822948</v>
       </c>
       <c r="W349" t="n">
         <v>0</v>
       </c>
       <c r="X349" t="n">
-        <v>226401320</v>
+        <v>506261509</v>
       </c>
     </row>
     <row r="350">
@@ -30488,7 +30488,7 @@
         <v>0</v>
       </c>
       <c r="H350" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I350" t="n">
         <v>0</v>
@@ -30509,7 +30509,7 @@
         </is>
       </c>
       <c r="M350" t="n">
-        <v>40</v>
+        <v>145</v>
       </c>
       <c r="N350" t="inlineStr">
         <is>
@@ -30518,37 +30518,37 @@
       </c>
       <c r="O350" t="inlineStr">
         <is>
-          <t>Região Intermediária de Pouso Alegre</t>
+          <t>Região Intermediária de Patos de Minas</t>
         </is>
       </c>
       <c r="P350" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE POUSO ALEGRE</t>
+          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE PATOS DE MINAS</t>
         </is>
       </c>
       <c r="Q350" t="n">
         <v>0</v>
       </c>
       <c r="R350" t="n">
-        <v>173871149</v>
+        <v>323743010</v>
       </c>
       <c r="S350" t="n">
         <v>0</v>
       </c>
       <c r="T350" t="n">
-        <v>175688647</v>
+        <v>220962542</v>
       </c>
       <c r="U350" t="n">
         <v>0</v>
       </c>
       <c r="V350" t="n">
-        <v>199716376</v>
+        <v>264145839</v>
       </c>
       <c r="W350" t="n">
         <v>0</v>
       </c>
       <c r="X350" t="n">
-        <v>185023098</v>
+        <v>226401320</v>
       </c>
     </row>
     <row r="351">
@@ -30574,7 +30574,7 @@
         <v>0</v>
       </c>
       <c r="H351" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I351" t="n">
         <v>0</v>
@@ -30595,7 +30595,7 @@
         </is>
       </c>
       <c r="M351" t="n">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="N351" t="inlineStr">
         <is>
@@ -30604,37 +30604,37 @@
       </c>
       <c r="O351" t="inlineStr">
         <is>
-          <t>Região Intermediária de Teófilo Otoni</t>
+          <t>Região Intermediária de Pouso Alegre</t>
         </is>
       </c>
       <c r="P351" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE TEÓFILO OTONI</t>
+          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE POUSO ALEGRE</t>
         </is>
       </c>
       <c r="Q351" t="n">
         <v>0</v>
       </c>
       <c r="R351" t="n">
-        <v>215436922</v>
+        <v>173871149</v>
       </c>
       <c r="S351" t="n">
         <v>0</v>
       </c>
       <c r="T351" t="n">
-        <v>276033928</v>
+        <v>175688647</v>
       </c>
       <c r="U351" t="n">
         <v>0</v>
       </c>
       <c r="V351" t="n">
-        <v>270093200</v>
+        <v>199716376</v>
       </c>
       <c r="W351" t="n">
         <v>0</v>
       </c>
       <c r="X351" t="n">
-        <v>242950628</v>
+        <v>185023098</v>
       </c>
     </row>
     <row r="352">
@@ -30660,7 +30660,7 @@
         <v>0</v>
       </c>
       <c r="H352" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I352" t="n">
         <v>0</v>
@@ -30681,7 +30681,7 @@
         </is>
       </c>
       <c r="M352" t="n">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="N352" t="inlineStr">
         <is>
@@ -30690,37 +30690,37 @@
       </c>
       <c r="O352" t="inlineStr">
         <is>
-          <t>Região Intermediária de Uberaba</t>
+          <t>Região Intermediária de Teófilo Otoni</t>
         </is>
       </c>
       <c r="P352" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE UBERABA</t>
+          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE TEÓFILO OTONI</t>
         </is>
       </c>
       <c r="Q352" t="n">
         <v>0</v>
       </c>
       <c r="R352" t="n">
-        <v>110565893</v>
+        <v>215436922</v>
       </c>
       <c r="S352" t="n">
         <v>0</v>
       </c>
       <c r="T352" t="n">
-        <v>155093520</v>
+        <v>276033928</v>
       </c>
       <c r="U352" t="n">
         <v>0</v>
       </c>
       <c r="V352" t="n">
-        <v>235966080</v>
+        <v>270093200</v>
       </c>
       <c r="W352" t="n">
         <v>0</v>
       </c>
       <c r="X352" t="n">
-        <v>198983124</v>
+        <v>242950628</v>
       </c>
     </row>
     <row r="353">
@@ -30746,7 +30746,7 @@
         <v>0</v>
       </c>
       <c r="H353" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I353" t="n">
         <v>0</v>
@@ -30767,7 +30767,7 @@
         </is>
       </c>
       <c r="M353" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="N353" t="inlineStr">
         <is>
@@ -30776,37 +30776,37 @@
       </c>
       <c r="O353" t="inlineStr">
         <is>
-          <t>Região Intermediária de Uberlândia</t>
+          <t>Região Intermediária de Uberaba</t>
         </is>
       </c>
       <c r="P353" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE UBERLÂNDIA</t>
+          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE UBERABA</t>
         </is>
       </c>
       <c r="Q353" t="n">
         <v>0</v>
       </c>
       <c r="R353" t="n">
-        <v>134543898</v>
+        <v>110565893</v>
       </c>
       <c r="S353" t="n">
         <v>0</v>
       </c>
       <c r="T353" t="n">
-        <v>153874367</v>
+        <v>155093520</v>
       </c>
       <c r="U353" t="n">
         <v>0</v>
       </c>
       <c r="V353" t="n">
-        <v>233587134</v>
+        <v>235966080</v>
       </c>
       <c r="W353" t="n">
         <v>0</v>
       </c>
       <c r="X353" t="n">
-        <v>186906495</v>
+        <v>198983124</v>
       </c>
     </row>
     <row r="354">
@@ -30832,7 +30832,7 @@
         <v>0</v>
       </c>
       <c r="H354" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I354" t="n">
         <v>0</v>
@@ -30853,7 +30853,7 @@
         </is>
       </c>
       <c r="M354" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="N354" t="inlineStr">
         <is>
@@ -30862,37 +30862,37 @@
       </c>
       <c r="O354" t="inlineStr">
         <is>
-          <t>Região Intermediária de Varginha</t>
+          <t>Região Intermediária de Uberlândia</t>
         </is>
       </c>
       <c r="P354" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE VARGINHA</t>
+          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE UBERLÂNDIA</t>
         </is>
       </c>
       <c r="Q354" t="n">
         <v>0</v>
       </c>
       <c r="R354" t="n">
-        <v>193964617</v>
+        <v>134543898</v>
       </c>
       <c r="S354" t="n">
         <v>0</v>
       </c>
       <c r="T354" t="n">
-        <v>195427106</v>
+        <v>153874367</v>
       </c>
       <c r="U354" t="n">
         <v>0</v>
       </c>
       <c r="V354" t="n">
-        <v>245125024</v>
+        <v>233587134</v>
       </c>
       <c r="W354" t="n">
         <v>0</v>
       </c>
       <c r="X354" t="n">
-        <v>226089618</v>
+        <v>186906495</v>
       </c>
     </row>
     <row r="355">
@@ -30918,67 +30918,239 @@
         <v>0</v>
       </c>
       <c r="H355" t="n">
+        <v>19</v>
+      </c>
+      <c r="I355" t="n">
+        <v>0</v>
+      </c>
+      <c r="J355" t="inlineStr">
+        <is>
+          <t>EXECUÇÃO DO PLANO DE DESENVOLVIMENTO DA DISTRIBUIDORA (PDD)</t>
+        </is>
+      </c>
+      <c r="K355" t="inlineStr">
+        <is>
+          <t>EXECUÇÃO</t>
+        </is>
+      </c>
+      <c r="L355" t="inlineStr">
+        <is>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="M355" t="n">
+        <v>30</v>
+      </c>
+      <c r="N355" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="O355" t="inlineStr">
+        <is>
+          <t>Região Intermediária de Varginha</t>
+        </is>
+      </c>
+      <c r="P355" t="inlineStr">
+        <is>
+          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE VARGINHA</t>
+        </is>
+      </c>
+      <c r="Q355" t="n">
+        <v>0</v>
+      </c>
+      <c r="R355" t="n">
+        <v>193964617</v>
+      </c>
+      <c r="S355" t="n">
+        <v>0</v>
+      </c>
+      <c r="T355" t="n">
+        <v>195427106</v>
+      </c>
+      <c r="U355" t="n">
+        <v>0</v>
+      </c>
+      <c r="V355" t="n">
+        <v>245125024</v>
+      </c>
+      <c r="W355" t="n">
+        <v>0</v>
+      </c>
+      <c r="X355" t="n">
+        <v>226089618</v>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="n">
+        <v>5401</v>
+      </c>
+      <c r="B356" t="n">
+        <v>25</v>
+      </c>
+      <c r="C356" t="n">
+        <v>752</v>
+      </c>
+      <c r="D356" t="n">
+        <v>72</v>
+      </c>
+      <c r="E356" t="n">
+        <v>3002</v>
+      </c>
+      <c r="F356" t="n">
+        <v>0</v>
+      </c>
+      <c r="G356" t="n">
+        <v>0</v>
+      </c>
+      <c r="H356" t="n">
         <v>20</v>
       </c>
-      <c r="I355" t="n">
-        <v>0</v>
-      </c>
-      <c r="J355" t="inlineStr">
+      <c r="I356" t="n">
+        <v>0</v>
+      </c>
+      <c r="J356" t="inlineStr">
         <is>
           <t>EXECUÇÃO DO PLANO DE DESENVOLVIMENTO DA DISTRIBUIDORA (PDD)</t>
         </is>
       </c>
-      <c r="K355" t="inlineStr">
+      <c r="K356" t="inlineStr">
         <is>
           <t>EXECUÇÃO</t>
         </is>
       </c>
-      <c r="L355" t="inlineStr">
+      <c r="L356" t="inlineStr">
         <is>
           <t>UNIDADE</t>
         </is>
       </c>
-      <c r="M355" t="n">
-        <v>1</v>
-      </c>
-      <c r="N355" t="inlineStr">
+      <c r="M356" t="n">
+        <v>1</v>
+      </c>
+      <c r="N356" t="inlineStr">
         <is>
           <t>Não</t>
         </is>
       </c>
-      <c r="O355" t="inlineStr">
+      <c r="O356" t="inlineStr">
         <is>
           <t>Estadual</t>
         </is>
       </c>
-      <c r="P355" t="inlineStr">
+      <c r="P356" t="inlineStr">
         <is>
           <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
         </is>
       </c>
-      <c r="Q355" t="n">
-        <v>0</v>
-      </c>
-      <c r="R355" t="n">
+      <c r="Q356" t="n">
+        <v>0</v>
+      </c>
+      <c r="R356" t="n">
         <v>134672413</v>
       </c>
-      <c r="S355" t="n">
-        <v>0</v>
-      </c>
-      <c r="T355" t="n">
+      <c r="S356" t="n">
+        <v>0</v>
+      </c>
+      <c r="T356" t="n">
         <v>153467750</v>
       </c>
-      <c r="U355" t="n">
-        <v>0</v>
-      </c>
-      <c r="V355" t="n">
+      <c r="U356" t="n">
+        <v>0</v>
+      </c>
+      <c r="V356" t="n">
         <v>160742426</v>
       </c>
-      <c r="W355" t="n">
-        <v>0</v>
-      </c>
-      <c r="X355" t="n">
+      <c r="W356" t="n">
+        <v>0</v>
+      </c>
+      <c r="X356" t="n">
         <v>157438322</v>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="n">
+        <v>5511</v>
+      </c>
+      <c r="B357" t="n">
+        <v>17</v>
+      </c>
+      <c r="C357" t="n">
+        <v>512</v>
+      </c>
+      <c r="D357" t="n">
+        <v>21</v>
+      </c>
+      <c r="E357" t="n">
+        <v>8012</v>
+      </c>
+      <c r="F357" t="n">
+        <v>0</v>
+      </c>
+      <c r="G357" t="n">
+        <v>0</v>
+      </c>
+      <c r="H357" t="n">
+        <v>393</v>
+      </c>
+      <c r="I357" t="n">
+        <v>0</v>
+      </c>
+      <c r="J357" t="inlineStr">
+        <is>
+          <t>IMPLANTAÇÃO OU AMPLIAÇÃO REALIZADA EM SISTEMAS DE ABASTECIMENTO DE ÁGUA QUE PODEM CONTEMPLAR SISTEMA PRODUTOR QUE PODE SER ATRAVÉS DE POÇO PROFUNDO OU CAPTAÇÃO SUPERFICIAL, ESTAÇÃO DE TRATAMENTO DE ÁGUA, ADUTORAS, ESTAÇÕES ELEVATÓRIAS, RESERVATÓRIOS E REDES DE DISTRIBUIÇÃO DE ÁGUA PARA OPERAÇÃO DAS UNIDADES DE TRATAMENTO E DISTRIBUIÇÃO DE ÁGUA TRATADA EM LOCALIDADES QUE A COPASA TENHA OU VENHA A TER A CONCESSÃO PARA O SERVIÇO DE ABASTECIMENTO DE ÁGUA. IMPLANTAÇÃO OU AMPLIAÇÃO REALIZADA EM SISTEMAS DE ESGOTAMENTO SANITÁRIO QUE PODEM CONTEMPLAR ESTAÇÃO DE TRATAMENTO DE ESGOTO, ESTAÇÕES ELEVATÓRIAS, INTERCEPTORES E REDES COLETORAS PARA OPERAÇÃO DAS UNIDADES DE COLETA E TRATAMENTO DE ESGOTO EM LOCALIDADES QUE A COPANOR TENHA OU VENHA A TER A CONCESSÃO PARA O SERVIÇO DE ESGOTAMENTO SANITÁRIO.</t>
+        </is>
+      </c>
+      <c r="K357" t="inlineStr">
+        <is>
+          <t>INICIANDO</t>
+        </is>
+      </c>
+      <c r="L357" t="inlineStr">
+        <is>
+          <t>ECONOMIA RESIDENCIAL</t>
+        </is>
+      </c>
+      <c r="M357" t="n">
+        <v>2000</v>
+      </c>
+      <c r="N357" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="O357" t="inlineStr">
+        <is>
+          <t>Região Intermediária de Teófilo Otoni</t>
+        </is>
+      </c>
+      <c r="P357" t="inlineStr">
+        <is>
+          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE TEÓFILO OTONI</t>
+        </is>
+      </c>
+      <c r="Q357" t="n">
+        <v>0</v>
+      </c>
+      <c r="R357" t="n">
+        <v>45000000</v>
+      </c>
+      <c r="S357" t="n">
+        <v>0</v>
+      </c>
+      <c r="T357" t="n">
+        <v>45000000</v>
+      </c>
+      <c r="U357" t="n">
+        <v>0</v>
+      </c>
+      <c r="V357" t="n">
+        <v>45000000</v>
+      </c>
+      <c r="W357" t="n">
+        <v>0</v>
+      </c>
+      <c r="X357" t="n">
+        <v>45000000</v>
       </c>
     </row>
   </sheetData>

--- a/bancos/SISOR/BASE_DETALHAMENTO_OBRAS.xlsx
+++ b/bancos/SISOR/BASE_DETALHAMENTO_OBRAS.xlsx
@@ -562,9 +562,6 @@
       <c r="H2" t="n">
         <v>407</v>
       </c>
-      <c r="I2" t="n">
-        <v>0</v>
-      </c>
       <c r="J2" t="inlineStr">
         <is>
           <t>CONSTRUÇÃO DE SEDES PROPRIAS</t>
@@ -648,9 +645,6 @@
       <c r="H3" t="n">
         <v>360</v>
       </c>
-      <c r="I3" t="n">
-        <v>0</v>
-      </c>
       <c r="J3" t="inlineStr">
         <is>
           <t>REFORMA DA EE PROFESSOR CAETANO AZEREDO</t>
@@ -734,9 +728,6 @@
       <c r="H4" t="n">
         <v>361</v>
       </c>
-      <c r="I4" t="n">
-        <v>0</v>
-      </c>
       <c r="J4" t="inlineStr">
         <is>
           <t>PROJETO PSCIP E ADEQUAÇÃO ACESSIBILIDADE PLUGMINAS</t>
@@ -820,9 +811,6 @@
       <c r="H5" t="n">
         <v>362</v>
       </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
       <c r="J5" t="inlineStr">
         <is>
           <t>PROJETO REFORMA E REESTRUTURAÇÃO - INSTITUTO DE EDUCAÇÃO DE MINAS GERAIS</t>
@@ -906,9 +894,6 @@
       <c r="H6" t="n">
         <v>363</v>
       </c>
-      <c r="I6" t="n">
-        <v>0</v>
-      </c>
       <c r="J6" t="inlineStr">
         <is>
           <t>REFORMA E RESTAURAÇÃO DA EE WENCESLAU BRAZ</t>
@@ -992,9 +977,6 @@
       <c r="H7" t="n">
         <v>364</v>
       </c>
-      <c r="I7" t="n">
-        <v>0</v>
-      </c>
       <c r="J7" t="inlineStr">
         <is>
           <t>REFORMA E RESTAURAÇÃO DA EE DUQUE DE CAXIAS</t>
@@ -1078,9 +1060,6 @@
       <c r="H8" t="n">
         <v>365</v>
       </c>
-      <c r="I8" t="n">
-        <v>0</v>
-      </c>
       <c r="J8" t="inlineStr">
         <is>
           <t>REFORMA, RESTAURAÇÃO E AMPLIAÇÃO - EE AFONSO PENA</t>
@@ -1164,9 +1143,6 @@
       <c r="H9" t="n">
         <v>366</v>
       </c>
-      <c r="I9" t="n">
-        <v>0</v>
-      </c>
       <c r="J9" t="inlineStr">
         <is>
           <t>REFORMA E RESTAURAÇÃO - INSTITUTO DE EDUCAÇÃO DE MINAS GERAIS</t>
@@ -1250,9 +1226,6 @@
       <c r="H10" t="n">
         <v>367</v>
       </c>
-      <c r="I10" t="n">
-        <v>0</v>
-      </c>
       <c r="J10" t="inlineStr">
         <is>
           <t>CONTENÇÃO DE TALUDE EE ANTONIO MARINHO CAMPOS</t>
@@ -1336,9 +1309,6 @@
       <c r="H11" t="n">
         <v>368</v>
       </c>
-      <c r="I11" t="n">
-        <v>0</v>
-      </c>
       <c r="J11" t="inlineStr">
         <is>
           <t>REFORMA - ESCOLAS INDÍGENAS TÉOFILO OTONI, LADAINHA, SANTA HELENA, BERTÓPOLIS</t>
@@ -1422,9 +1392,6 @@
       <c r="H12" t="n">
         <v>369</v>
       </c>
-      <c r="I12" t="n">
-        <v>0</v>
-      </c>
       <c r="J12" t="inlineStr">
         <is>
           <t>OBRA REFORMA E RESTAURAÇÃO EE PROFESSOR ANTONIO DIAS MACIEL</t>
@@ -3486,9 +3453,6 @@
       <c r="H36" t="n">
         <v>87</v>
       </c>
-      <c r="I36" t="n">
-        <v>0</v>
-      </c>
       <c r="J36" t="inlineStr">
         <is>
           <t>Obras de contenção de encostas em Sabará - Intervenção em setores de risco alto e muito alto, no âmbito do Programa PAC Gestão de Riscos e Resposta a Desastres.</t>
@@ -5206,9 +5170,6 @@
       <c r="H56" t="n">
         <v>159</v>
       </c>
-      <c r="I56" t="n">
-        <v>0</v>
-      </c>
       <c r="J56" t="inlineStr">
         <is>
           <t>Restauração dos dois prédios do 1° Batalhão de Bombeiros Militar tombados pelo patrimônio histórico.</t>
@@ -5292,9 +5253,6 @@
       <c r="H57" t="n">
         <v>160</v>
       </c>
-      <c r="I57" t="n">
-        <v>0</v>
-      </c>
       <c r="J57" t="inlineStr">
         <is>
           <t>Obtenção de AVCB para as edificações do CBMMG por meio da contratação da elaboração de PSCIP e/ou execução desses</t>
@@ -5378,9 +5336,6 @@
       <c r="H58" t="n">
         <v>344</v>
       </c>
-      <c r="I58" t="n">
-        <v>0</v>
-      </c>
       <c r="J58" t="inlineStr">
         <is>
           <t>DIVERSAS OBRAS REFERENTES A RECURSO VALE</t>
@@ -5636,9 +5591,6 @@
       <c r="H61" t="n">
         <v>155</v>
       </c>
-      <c r="I61" t="n">
-        <v>0</v>
-      </c>
       <c r="J61" t="inlineStr">
         <is>
           <t>OBRA DE REFORMA DE UM PRÉDIO EM BELO HORIZONTE PARA OCUPAÇÃO DA SCPMSO</t>
@@ -5722,9 +5674,6 @@
       <c r="H62" t="n">
         <v>158</v>
       </c>
-      <c r="I62" t="n">
-        <v>0</v>
-      </c>
       <c r="J62" t="inlineStr">
         <is>
           <t>OBRA DE REFORMA NA UNIDADE REGIONAL DE PERÍCIA MÉDICA DE UBERLÂNDIA</t>
@@ -5808,9 +5757,6 @@
       <c r="H63" t="n">
         <v>156</v>
       </c>
-      <c r="I63" t="n">
-        <v>0</v>
-      </c>
       <c r="J63" t="inlineStr">
         <is>
           <t>OBRA PARA ABRIGOS E CAMINHOS NA CIDADE ADMINISTRATA</t>
@@ -5894,9 +5840,6 @@
       <c r="H64" t="n">
         <v>157</v>
       </c>
-      <c r="I64" t="n">
-        <v>0</v>
-      </c>
       <c r="J64" t="inlineStr">
         <is>
           <t>OBRA PARA PROJETO DE USINA FOTOVOLTAICA NA CIDADE ADMINISTRATIVA</t>
@@ -5980,9 +5923,6 @@
       <c r="H65" t="n">
         <v>329</v>
       </c>
-      <c r="I65" t="n">
-        <v>0</v>
-      </c>
       <c r="J65" t="inlineStr">
         <is>
           <t>Reforma e adequação para instalação do complexo para atendimento à mulher vítima de violência no prédio anexo ao imóvel localizado na Av. João de Deus Costa, nº 42, Bairro Centro, Contagem/MG</t>
@@ -6066,9 +6006,6 @@
       <c r="H66" t="n">
         <v>330</v>
       </c>
-      <c r="I66" t="n">
-        <v>0</v>
-      </c>
       <c r="J66" t="inlineStr">
         <is>
           <t>Reforma e adequação no imóvel situado na Avenida Faria Pereira, 3517, Bairro Marciano Brandão, Patrocínio MG.</t>
@@ -6152,9 +6089,6 @@
       <c r="H67" t="n">
         <v>331</v>
       </c>
-      <c r="I67" t="n">
-        <v>0</v>
-      </c>
       <c r="J67" t="inlineStr">
         <is>
           <t>Fornecimento e instalação de rede elétrica exclusiva para os equipamentos, fornecimento e instalação de rede frigorígena e rede de dreno em 02 (duas) salas da Delegacia de Polícia Civil do Município de Lagoa Santa/MG, situada na R. Santos Dumont, 55 - Lindolfo do C Viana, Lagoa Santa - MG</t>
@@ -6238,9 +6172,6 @@
       <c r="H68" t="n">
         <v>332</v>
       </c>
-      <c r="I68" t="n">
-        <v>0</v>
-      </c>
       <c r="J68" t="inlineStr">
         <is>
           <t>Fornecimento e instalação de rede elétrica exclusiva para os equipamentos, fornecimento e instalação de rede frigorígena e rede de dreno em 02 (duas) salas da Delegacia de Polícia Civil do Município de Andradas/MG, situada na R. Erico Buzato, 234, Vila Buzato, Andradas / MG, CEP: 37795-000</t>
@@ -6324,9 +6255,6 @@
       <c r="H69" t="n">
         <v>333</v>
       </c>
-      <c r="I69" t="n">
-        <v>0</v>
-      </c>
       <c r="J69" t="inlineStr">
         <is>
           <t>Fornecimento e instalação de rede elétrica exclusiva para os equipamentos de ar condicionado e instalação de rede frigorígena e rede de dreno em 02 (duas) salas da Delegacia de Polícia Civil do Município de Conceição das Alagoas/MG, situada na Rua Wady Nassif, 79, Centro, Conceição das Alagoas/MG</t>
@@ -6410,9 +6338,6 @@
       <c r="H70" t="n">
         <v>334</v>
       </c>
-      <c r="I70" t="n">
-        <v>0</v>
-      </c>
       <c r="J70" t="inlineStr">
         <is>
           <t>reforma e adequação no imóvel que abriga o Hospital da Polícia Civil - HPC, localizado na Rua Bernardo Guimarães nº 1.280, Funcionários, Belo Horizonte/MG</t>
@@ -6496,9 +6421,6 @@
       <c r="H71" t="n">
         <v>335</v>
       </c>
-      <c r="I71" t="n">
-        <v>0</v>
-      </c>
       <c r="J71" t="inlineStr">
         <is>
           <t>ESTRUTURAÇÃO OPERACIONAL DA PCMG</t>
@@ -6582,9 +6504,6 @@
       <c r="H72" t="n">
         <v>154</v>
       </c>
-      <c r="I72" t="n">
-        <v>0</v>
-      </c>
       <c r="J72" t="inlineStr">
         <is>
           <t>CONSTRUÇÃO DO NÚCLEO INTEGRADO DE PERÍCIAS DA PCMG</t>
@@ -6668,9 +6587,6 @@
       <c r="H73" t="n">
         <v>149</v>
       </c>
-      <c r="I73" t="n">
-        <v>0</v>
-      </c>
       <c r="J73" t="inlineStr">
         <is>
           <t>Execução de serviços de demolição e limpeza fazenda Contagem</t>
@@ -6754,9 +6670,6 @@
       <c r="H74" t="n">
         <v>150</v>
       </c>
-      <c r="I74" t="n">
-        <v>0</v>
-      </c>
       <c r="J74" t="inlineStr">
         <is>
           <t>Reforma e adaptação do imóvel do DER para instalação da Agência regional do Ipsemg.</t>
@@ -6840,9 +6753,6 @@
       <c r="H75" t="n">
         <v>151</v>
       </c>
-      <c r="I75" t="n">
-        <v>0</v>
-      </c>
       <c r="J75" t="inlineStr">
         <is>
           <t>Reforma de manutenção do imóvel do Centro Regional - 80%</t>
@@ -6926,9 +6836,6 @@
       <c r="H76" t="n">
         <v>152</v>
       </c>
-      <c r="I76" t="n">
-        <v>0</v>
-      </c>
       <c r="J76" t="inlineStr">
         <is>
           <t>Reforma geral no imóvel do Centro Regional de Teófilo Otôni - 90%</t>
@@ -7012,9 +6919,6 @@
       <c r="H77" t="n">
         <v>130</v>
       </c>
-      <c r="I77" t="n">
-        <v>0</v>
-      </c>
       <c r="J77" t="inlineStr">
         <is>
           <t>Reformas ala B do HGIP - 40%</t>
@@ -7098,9 +7002,6 @@
       <c r="H78" t="n">
         <v>131</v>
       </c>
-      <c r="I78" t="n">
-        <v>0</v>
-      </c>
       <c r="J78" t="inlineStr">
         <is>
           <t>Reforma-manutenção das fachadas do HGIP - 25%</t>
@@ -7184,9 +7085,6 @@
       <c r="H79" t="n">
         <v>132</v>
       </c>
-      <c r="I79" t="n">
-        <v>0</v>
-      </c>
       <c r="J79" t="inlineStr">
         <is>
           <t>Reforma da Endoscopia - HGIP - 70%</t>
@@ -7270,9 +7168,6 @@
       <c r="H80" t="n">
         <v>133</v>
       </c>
-      <c r="I80" t="n">
-        <v>0</v>
-      </c>
       <c r="J80" t="inlineStr">
         <is>
           <t>Reforma da Quimioterapia - HGIP Projeto</t>
@@ -7356,9 +7251,6 @@
       <c r="H81" t="n">
         <v>328</v>
       </c>
-      <c r="I81" t="n">
-        <v>0</v>
-      </c>
       <c r="J81" t="inlineStr">
         <is>
           <t>OBRA DESCOMTAMINAÇÃO POR MERCURIO</t>
@@ -7442,9 +7334,6 @@
       <c r="H82" t="n">
         <v>336</v>
       </c>
-      <c r="I82" t="n">
-        <v>0</v>
-      </c>
       <c r="J82" t="inlineStr">
         <is>
           <t>CETRAS UBERLÂNDIA</t>
@@ -7528,9 +7417,6 @@
       <c r="H83" t="n">
         <v>337</v>
       </c>
-      <c r="I83" t="n">
-        <v>0</v>
-      </c>
       <c r="J83" t="inlineStr">
         <is>
           <t>CETRAS GOVERNADOR VALADARES</t>
@@ -7614,9 +7500,6 @@
       <c r="H84" t="n">
         <v>338</v>
       </c>
-      <c r="I84" t="n">
-        <v>0</v>
-      </c>
       <c r="J84" t="inlineStr">
         <is>
           <t>OBRAS DE ESTRUTURAÇÃO DO PE PICO DO ITAMBÉ</t>
@@ -7700,9 +7583,6 @@
       <c r="H85" t="n">
         <v>340</v>
       </c>
-      <c r="I85" t="n">
-        <v>0</v>
-      </c>
       <c r="J85" t="inlineStr">
         <is>
           <t>PROJETO E OBRA APA PARQUE FERNÃO DIAS</t>
@@ -7786,9 +7666,6 @@
       <c r="H86" t="n">
         <v>341</v>
       </c>
-      <c r="I86" t="n">
-        <v>0</v>
-      </c>
       <c r="J86" t="inlineStr">
         <is>
           <t>OBRAS PE SERRA NEGRA DA MANTIQUEIRA</t>
@@ -7872,9 +7749,6 @@
       <c r="H87" t="n">
         <v>125</v>
       </c>
-      <c r="I87" t="n">
-        <v>0</v>
-      </c>
       <c r="J87" t="inlineStr">
         <is>
           <t>CRIAÇÃO DO CENTRO DE REFERENCIA</t>
@@ -8818,9 +8692,6 @@
       <c r="H98" t="n">
         <v>164</v>
       </c>
-      <c r="I98" t="n">
-        <v>0</v>
-      </c>
       <c r="J98" t="inlineStr">
         <is>
           <t>REESTABELECIMENTO TRAFEGABILIDADE</t>
@@ -8904,9 +8775,6 @@
       <c r="H99" t="n">
         <v>370</v>
       </c>
-      <c r="I99" t="n">
-        <v>0</v>
-      </c>
       <c r="J99" t="inlineStr">
         <is>
           <t>MITIGAÇÃO DE DANOS CAUSADOS PELAS CHUVAS</t>
@@ -8990,9 +8858,6 @@
       <c r="H100" t="n">
         <v>232</v>
       </c>
-      <c r="I100" t="n">
-        <v>0</v>
-      </c>
       <c r="J100" t="inlineStr">
         <is>
           <t>AMPLIAÇÃO DE CAPACIDADE DA MALHA VIÁRIA</t>
@@ -9076,9 +8941,6 @@
       <c r="H101" t="n">
         <v>233</v>
       </c>
-      <c r="I101" t="n">
-        <v>0</v>
-      </c>
       <c r="J101" t="inlineStr">
         <is>
           <t>AMPLIAÇÃO DE CAPACIDADE DA MALHA VIÁRIA</t>
@@ -9162,9 +9024,6 @@
       <c r="H102" t="n">
         <v>234</v>
       </c>
-      <c r="I102" t="n">
-        <v>0</v>
-      </c>
       <c r="J102" t="inlineStr">
         <is>
           <t>AMPLIAÇÃO DE CAPACIDADE DA MALHA VIÁRIA</t>
@@ -9248,9 +9107,6 @@
       <c r="H103" t="n">
         <v>235</v>
       </c>
-      <c r="I103" t="n">
-        <v>0</v>
-      </c>
       <c r="J103" t="inlineStr">
         <is>
           <t>AMPLIAÇÃO DE CAPACIDADE DA MALHA VIÁRIA</t>
@@ -9334,9 +9190,6 @@
       <c r="H104" t="n">
         <v>236</v>
       </c>
-      <c r="I104" t="n">
-        <v>0</v>
-      </c>
       <c r="J104" t="inlineStr">
         <is>
           <t>AMPLIAÇÃO DE CAPACIDADE DA MALHA VIÁRIA</t>
@@ -9420,9 +9273,6 @@
       <c r="H105" t="n">
         <v>237</v>
       </c>
-      <c r="I105" t="n">
-        <v>0</v>
-      </c>
       <c r="J105" t="inlineStr">
         <is>
           <t>AMPLIAÇÃO DE CAPACIDADE DA MALHA VIÁRIA</t>
@@ -9506,9 +9356,6 @@
       <c r="H106" t="n">
         <v>238</v>
       </c>
-      <c r="I106" t="n">
-        <v>0</v>
-      </c>
       <c r="J106" t="inlineStr">
         <is>
           <t>IMPLANTAÇÃO E MANUTENÇÃO DE OAE´S</t>
@@ -9592,9 +9439,6 @@
       <c r="H107" t="n">
         <v>239</v>
       </c>
-      <c r="I107" t="n">
-        <v>0</v>
-      </c>
       <c r="J107" t="inlineStr">
         <is>
           <t>IMPLANTAÇÃO E MANUTENÇÃO DE OAE´S</t>
@@ -9678,9 +9522,6 @@
       <c r="H108" t="n">
         <v>240</v>
       </c>
-      <c r="I108" t="n">
-        <v>0</v>
-      </c>
       <c r="J108" t="inlineStr">
         <is>
           <t>IMPLANTAÇÃO E MANUTENÇÃO DE OAE´S</t>
@@ -9764,9 +9605,6 @@
       <c r="H109" t="n">
         <v>241</v>
       </c>
-      <c r="I109" t="n">
-        <v>0</v>
-      </c>
       <c r="J109" t="inlineStr">
         <is>
           <t>IMPLANTAÇÃO E MANUTENÇÃO DE OAE´S</t>
@@ -9850,9 +9688,6 @@
       <c r="H110" t="n">
         <v>242</v>
       </c>
-      <c r="I110" t="n">
-        <v>0</v>
-      </c>
       <c r="J110" t="inlineStr">
         <is>
           <t>IMPLANTAÇÃO E MANUTENÇÃO DE OAE´S</t>
@@ -9936,9 +9771,6 @@
       <c r="H111" t="n">
         <v>243</v>
       </c>
-      <c r="I111" t="n">
-        <v>0</v>
-      </c>
       <c r="J111" t="inlineStr">
         <is>
           <t>IMPLANTAÇÃO E MANUTENÇÃO DE OAE´S</t>
@@ -10022,9 +9854,6 @@
       <c r="H112" t="n">
         <v>244</v>
       </c>
-      <c r="I112" t="n">
-        <v>0</v>
-      </c>
       <c r="J112" t="inlineStr">
         <is>
           <t>IMPLANTAÇÃO E MANUTENÇÃO DE OAE´S</t>
@@ -10108,9 +9937,6 @@
       <c r="H113" t="n">
         <v>245</v>
       </c>
-      <c r="I113" t="n">
-        <v>0</v>
-      </c>
       <c r="J113" t="inlineStr">
         <is>
           <t>IMPLANTAÇÃO E MANUTENÇÃO DE OAE´S</t>
@@ -10194,9 +10020,6 @@
       <c r="H114" t="n">
         <v>246</v>
       </c>
-      <c r="I114" t="n">
-        <v>0</v>
-      </c>
       <c r="J114" t="inlineStr">
         <is>
           <t>IMPLANTAÇÃO E MANUTENÇÃO DE OAE´S</t>
@@ -10280,9 +10103,6 @@
       <c r="H115" t="n">
         <v>260</v>
       </c>
-      <c r="I115" t="n">
-        <v>0</v>
-      </c>
       <c r="J115" t="inlineStr">
         <is>
           <t>IMPLANTAÇÃO/PAVIMENTAÇÃO DA MALHA</t>
@@ -10366,9 +10186,6 @@
       <c r="H116" t="n">
         <v>261</v>
       </c>
-      <c r="I116" t="n">
-        <v>0</v>
-      </c>
       <c r="J116" t="inlineStr">
         <is>
           <t>IMPLANTAÇÃO/PAVIMENTAÇÃO DA MALHA</t>
@@ -10452,9 +10269,6 @@
       <c r="H117" t="n">
         <v>262</v>
       </c>
-      <c r="I117" t="n">
-        <v>0</v>
-      </c>
       <c r="J117" t="inlineStr">
         <is>
           <t>IMPLANTAÇÃO/PAVIMENTAÇÃO DA MALHA</t>
@@ -10538,9 +10352,6 @@
       <c r="H118" t="n">
         <v>263</v>
       </c>
-      <c r="I118" t="n">
-        <v>0</v>
-      </c>
       <c r="J118" t="inlineStr">
         <is>
           <t>IMPLANTAÇÃO/PAVIMENTAÇÃO DA MALHA</t>
@@ -10624,9 +10435,6 @@
       <c r="H119" t="n">
         <v>264</v>
       </c>
-      <c r="I119" t="n">
-        <v>0</v>
-      </c>
       <c r="J119" t="inlineStr">
         <is>
           <t>IMPLANTAÇÃO/PAVIMENTAÇÃO DA MALHA</t>
@@ -10710,9 +10518,6 @@
       <c r="H120" t="n">
         <v>265</v>
       </c>
-      <c r="I120" t="n">
-        <v>0</v>
-      </c>
       <c r="J120" t="inlineStr">
         <is>
           <t>IMPLANTAÇÃO/PAVIMENTAÇÃO DA MALHA</t>
@@ -10796,9 +10601,6 @@
       <c r="H121" t="n">
         <v>266</v>
       </c>
-      <c r="I121" t="n">
-        <v>0</v>
-      </c>
       <c r="J121" t="inlineStr">
         <is>
           <t>IMPLANTAÇÃO/PAVIMENTAÇÃO DA MALHA</t>
@@ -10882,9 +10684,6 @@
       <c r="H122" t="n">
         <v>267</v>
       </c>
-      <c r="I122" t="n">
-        <v>0</v>
-      </c>
       <c r="J122" t="inlineStr">
         <is>
           <t>IMPLANTAÇÃO/PAVIMENTAÇÃO DA MALHA</t>
@@ -10968,9 +10767,6 @@
       <c r="H123" t="n">
         <v>268</v>
       </c>
-      <c r="I123" t="n">
-        <v>0</v>
-      </c>
       <c r="J123" t="inlineStr">
         <is>
           <t>IMPLANTAÇÃO/PAVIMENTAÇÃO DA MALHA</t>
@@ -11054,9 +10850,6 @@
       <c r="H124" t="n">
         <v>269</v>
       </c>
-      <c r="I124" t="n">
-        <v>0</v>
-      </c>
       <c r="J124" t="inlineStr">
         <is>
           <t>IMPLANTAÇÃO/PAVIMENTAÇÃO DA MALHA</t>
@@ -11140,9 +10933,6 @@
       <c r="H125" t="n">
         <v>270</v>
       </c>
-      <c r="I125" t="n">
-        <v>0</v>
-      </c>
       <c r="J125" t="inlineStr">
         <is>
           <t>IMPLANTAÇÃO/PAVIMENTAÇÃO DA MALHA</t>
@@ -11226,9 +11016,6 @@
       <c r="H126" t="n">
         <v>271</v>
       </c>
-      <c r="I126" t="n">
-        <v>0</v>
-      </c>
       <c r="J126" t="inlineStr">
         <is>
           <t>IMPLANTAÇÃO/PAVIMENTAÇÃO DA MALHA</t>
@@ -11312,9 +11099,6 @@
       <c r="H127" t="n">
         <v>272</v>
       </c>
-      <c r="I127" t="n">
-        <v>0</v>
-      </c>
       <c r="J127" t="inlineStr">
         <is>
           <t>IMPLANTAÇÃO/PAVIMENTAÇÃO DA MALHA</t>
@@ -11398,9 +11182,6 @@
       <c r="H128" t="n">
         <v>273</v>
       </c>
-      <c r="I128" t="n">
-        <v>0</v>
-      </c>
       <c r="J128" t="inlineStr">
         <is>
           <t>IMPLANTAÇÃO/PAVIMENTAÇÃO DA MALHA</t>
@@ -11484,9 +11265,6 @@
       <c r="H129" t="n">
         <v>274</v>
       </c>
-      <c r="I129" t="n">
-        <v>0</v>
-      </c>
       <c r="J129" t="inlineStr">
         <is>
           <t>IMPLANTAÇÃO/PAVIMENTAÇÃO DA MALHA</t>
@@ -11570,9 +11348,6 @@
       <c r="H130" t="n">
         <v>275</v>
       </c>
-      <c r="I130" t="n">
-        <v>0</v>
-      </c>
       <c r="J130" t="inlineStr">
         <is>
           <t>IMPLANTAÇÃO/PAVIMENTAÇÃO DA MALHA</t>
@@ -11656,9 +11431,6 @@
       <c r="H131" t="n">
         <v>276</v>
       </c>
-      <c r="I131" t="n">
-        <v>0</v>
-      </c>
       <c r="J131" t="inlineStr">
         <is>
           <t>IMPLANTAÇÃO/PAVIMENTAÇÃO DA MALHA</t>
@@ -11742,9 +11514,6 @@
       <c r="H132" t="n">
         <v>277</v>
       </c>
-      <c r="I132" t="n">
-        <v>0</v>
-      </c>
       <c r="J132" t="inlineStr">
         <is>
           <t>IMPLANTAÇÃO/PAVIMENTAÇÃO DA MALHA</t>
@@ -11828,9 +11597,6 @@
       <c r="H133" t="n">
         <v>278</v>
       </c>
-      <c r="I133" t="n">
-        <v>0</v>
-      </c>
       <c r="J133" t="inlineStr">
         <is>
           <t>IMPLANTAÇÃO/PAVIMENTAÇÃO DA MALHA</t>
@@ -11914,9 +11680,6 @@
       <c r="H134" t="n">
         <v>279</v>
       </c>
-      <c r="I134" t="n">
-        <v>0</v>
-      </c>
       <c r="J134" t="inlineStr">
         <is>
           <t>IMPLANTAÇÃO/PAVIMENTAÇÃO DA MALHA</t>
@@ -12000,9 +11763,6 @@
       <c r="H135" t="n">
         <v>280</v>
       </c>
-      <c r="I135" t="n">
-        <v>0</v>
-      </c>
       <c r="J135" t="inlineStr">
         <is>
           <t>IMPLANTAÇÃO/PAVIMENTAÇÃO DA MALHA</t>
@@ -12086,9 +11846,6 @@
       <c r="H136" t="n">
         <v>281</v>
       </c>
-      <c r="I136" t="n">
-        <v>0</v>
-      </c>
       <c r="J136" t="inlineStr">
         <is>
           <t>IMPLANTAÇÃO/PAVIMENTAÇÃO DA MALHA</t>
@@ -12172,9 +11929,6 @@
       <c r="H137" t="n">
         <v>283</v>
       </c>
-      <c r="I137" t="n">
-        <v>0</v>
-      </c>
       <c r="J137" t="inlineStr">
         <is>
           <t>IMPLANTAÇÃO/PAVIMENTAÇÃO DA MALHA</t>
@@ -12258,9 +12012,6 @@
       <c r="H138" t="n">
         <v>284</v>
       </c>
-      <c r="I138" t="n">
-        <v>0</v>
-      </c>
       <c r="J138" t="inlineStr">
         <is>
           <t>IMPLANTAÇÃO/PAVIMENTAÇÃO DA MALHA</t>
@@ -12344,9 +12095,6 @@
       <c r="H139" t="n">
         <v>285</v>
       </c>
-      <c r="I139" t="n">
-        <v>0</v>
-      </c>
       <c r="J139" t="inlineStr">
         <is>
           <t>IMPLANTAÇÃO/PAVIMENTAÇÃO DA MALHA</t>
@@ -12430,9 +12178,6 @@
       <c r="H140" t="n">
         <v>286</v>
       </c>
-      <c r="I140" t="n">
-        <v>0</v>
-      </c>
       <c r="J140" t="inlineStr">
         <is>
           <t>IMPLANTAÇÃO/PAVIMENTAÇÃO DA MALHA</t>
@@ -12516,9 +12261,6 @@
       <c r="H141" t="n">
         <v>327</v>
       </c>
-      <c r="I141" t="n">
-        <v>0</v>
-      </c>
       <c r="J141" t="inlineStr">
         <is>
           <t>IMPLANTAÇÃO/PAVIMENTAÇÃO DA MALHA</t>
@@ -12602,9 +12344,6 @@
       <c r="H142" t="n">
         <v>213</v>
       </c>
-      <c r="I142" t="n">
-        <v>0</v>
-      </c>
       <c r="J142" t="inlineStr">
         <is>
           <t>CONSTRUÇÃO E ADEQUAÇÃO DE RODOVIAS</t>
@@ -12688,9 +12427,6 @@
       <c r="H143" t="n">
         <v>214</v>
       </c>
-      <c r="I143" t="n">
-        <v>0</v>
-      </c>
       <c r="J143" t="inlineStr">
         <is>
           <t>RECUPERAÇÃO E MANUTENÇÃO DA MALHA VIÁRIA</t>
@@ -12774,9 +12510,6 @@
       <c r="H144" t="n">
         <v>215</v>
       </c>
-      <c r="I144" t="n">
-        <v>0</v>
-      </c>
       <c r="J144" t="inlineStr">
         <is>
           <t>CONSTRUÇÃO E ADEQUAÇÃO DE RODOVIAS</t>
@@ -12860,9 +12593,6 @@
       <c r="H145" t="n">
         <v>287</v>
       </c>
-      <c r="I145" t="n">
-        <v>0</v>
-      </c>
       <c r="J145" t="inlineStr">
         <is>
           <t>CONSERVAÇÃO ROTINEIRA DA MALHA VIÁRIA</t>
@@ -12946,9 +12676,6 @@
       <c r="H146" t="n">
         <v>288</v>
       </c>
-      <c r="I146" t="n">
-        <v>0</v>
-      </c>
       <c r="J146" t="inlineStr">
         <is>
           <t>CONSERVAÇÃO ROTINEIRA DA MALHA VIÁRIA</t>
@@ -13032,9 +12759,6 @@
       <c r="H147" t="n">
         <v>289</v>
       </c>
-      <c r="I147" t="n">
-        <v>0</v>
-      </c>
       <c r="J147" t="inlineStr">
         <is>
           <t>CONSERVAÇÃO ROTINEIRA DA MALHA VIÁRIA</t>
@@ -13118,9 +12842,6 @@
       <c r="H148" t="n">
         <v>290</v>
       </c>
-      <c r="I148" t="n">
-        <v>0</v>
-      </c>
       <c r="J148" t="inlineStr">
         <is>
           <t>CONSERVAÇÃO ROTINEIRA DA MALHA VIÁRIA</t>
@@ -13204,9 +12925,6 @@
       <c r="H149" t="n">
         <v>291</v>
       </c>
-      <c r="I149" t="n">
-        <v>0</v>
-      </c>
       <c r="J149" t="inlineStr">
         <is>
           <t>CONSERVAÇÃO ROTINEIRA DA MALHA VIÁRIA</t>
@@ -13290,9 +13008,6 @@
       <c r="H150" t="n">
         <v>292</v>
       </c>
-      <c r="I150" t="n">
-        <v>0</v>
-      </c>
       <c r="J150" t="inlineStr">
         <is>
           <t>CONSERVAÇÃO ROTINEIRA DA MALHA VIÁRIA</t>
@@ -13376,9 +13091,6 @@
       <c r="H151" t="n">
         <v>293</v>
       </c>
-      <c r="I151" t="n">
-        <v>0</v>
-      </c>
       <c r="J151" t="inlineStr">
         <is>
           <t>CONSERVAÇÃO ROTINEIRA DA MALHA VIÁRIA</t>
@@ -13462,9 +13174,6 @@
       <c r="H152" t="n">
         <v>294</v>
       </c>
-      <c r="I152" t="n">
-        <v>0</v>
-      </c>
       <c r="J152" t="inlineStr">
         <is>
           <t>CONSERVAÇÃO ROTINEIRA DA MALHA VIÁRIA</t>
@@ -13548,9 +13257,6 @@
       <c r="H153" t="n">
         <v>295</v>
       </c>
-      <c r="I153" t="n">
-        <v>0</v>
-      </c>
       <c r="J153" t="inlineStr">
         <is>
           <t>CONSERVAÇÃO ROTINEIRA DA MALHA VIÁRIA</t>
@@ -13634,9 +13340,6 @@
       <c r="H154" t="n">
         <v>296</v>
       </c>
-      <c r="I154" t="n">
-        <v>0</v>
-      </c>
       <c r="J154" t="inlineStr">
         <is>
           <t>CONSERVAÇÃO ROTINEIRA DA MALHA VIÁRIA</t>
@@ -13720,9 +13423,6 @@
       <c r="H155" t="n">
         <v>297</v>
       </c>
-      <c r="I155" t="n">
-        <v>0</v>
-      </c>
       <c r="J155" t="inlineStr">
         <is>
           <t>CONSERVAÇÃO ROTINEIRA DA MALHA VIÁRIA</t>
@@ -13806,9 +13506,6 @@
       <c r="H156" t="n">
         <v>298</v>
       </c>
-      <c r="I156" t="n">
-        <v>0</v>
-      </c>
       <c r="J156" t="inlineStr">
         <is>
           <t>CONSERVAÇÃO ROTINEIRA DA MALHA VIÁRIA</t>
@@ -13892,9 +13589,6 @@
       <c r="H157" t="n">
         <v>299</v>
       </c>
-      <c r="I157" t="n">
-        <v>0</v>
-      </c>
       <c r="J157" t="inlineStr">
         <is>
           <t>CONSERVAÇÃO ROTINEIRA DA MALHA VIÁRIA</t>
@@ -13978,9 +13672,6 @@
       <c r="H158" t="n">
         <v>300</v>
       </c>
-      <c r="I158" t="n">
-        <v>0</v>
-      </c>
       <c r="J158" t="inlineStr">
         <is>
           <t>CONSERVAÇÃO ROTINEIRA DA MALHA VIÁRIA</t>
@@ -14064,9 +13755,6 @@
       <c r="H159" t="n">
         <v>301</v>
       </c>
-      <c r="I159" t="n">
-        <v>0</v>
-      </c>
       <c r="J159" t="inlineStr">
         <is>
           <t>CONSERVAÇÃO ROTINEIRA DA MALHA VIÁRIA</t>
@@ -14150,9 +13838,6 @@
       <c r="H160" t="n">
         <v>302</v>
       </c>
-      <c r="I160" t="n">
-        <v>0</v>
-      </c>
       <c r="J160" t="inlineStr">
         <is>
           <t>CONSERVAÇÃO ROTINEIRA DA MALHA VIÁRIA</t>
@@ -14236,9 +13921,6 @@
       <c r="H161" t="n">
         <v>303</v>
       </c>
-      <c r="I161" t="n">
-        <v>0</v>
-      </c>
       <c r="J161" t="inlineStr">
         <is>
           <t>CONSERVAÇÃO ROTINEIRA DA MALHA VIÁRIA</t>
@@ -14322,9 +14004,6 @@
       <c r="H162" t="n">
         <v>304</v>
       </c>
-      <c r="I162" t="n">
-        <v>0</v>
-      </c>
       <c r="J162" t="inlineStr">
         <is>
           <t>CONSERVAÇÃO ROTINEIRA DA MALHA VIÁRIA</t>
@@ -14408,9 +14087,6 @@
       <c r="H163" t="n">
         <v>305</v>
       </c>
-      <c r="I163" t="n">
-        <v>0</v>
-      </c>
       <c r="J163" t="inlineStr">
         <is>
           <t>CONSERVAÇÃO ROTINEIRA DA MALHA VIÁRIA</t>
@@ -14494,9 +14170,6 @@
       <c r="H164" t="n">
         <v>306</v>
       </c>
-      <c r="I164" t="n">
-        <v>0</v>
-      </c>
       <c r="J164" t="inlineStr">
         <is>
           <t>CONSERVAÇÃO ROTINEIRA DA MALHA VIÁRIA</t>
@@ -14580,9 +14253,6 @@
       <c r="H165" t="n">
         <v>307</v>
       </c>
-      <c r="I165" t="n">
-        <v>0</v>
-      </c>
       <c r="J165" t="inlineStr">
         <is>
           <t>CONSERVAÇÃO ROTINEIRA DA MALHA VIÁRIA</t>
@@ -14666,9 +14336,6 @@
       <c r="H166" t="n">
         <v>308</v>
       </c>
-      <c r="I166" t="n">
-        <v>0</v>
-      </c>
       <c r="J166" t="inlineStr">
         <is>
           <t>CONSERVAÇÃO ROTINEIRA DA MALHA VIÁRIA</t>
@@ -14752,9 +14419,6 @@
       <c r="H167" t="n">
         <v>309</v>
       </c>
-      <c r="I167" t="n">
-        <v>0</v>
-      </c>
       <c r="J167" t="inlineStr">
         <is>
           <t>CONSERVAÇÃO ROTINEIRA DA MALHA VIÁRIA</t>
@@ -14838,9 +14502,6 @@
       <c r="H168" t="n">
         <v>310</v>
       </c>
-      <c r="I168" t="n">
-        <v>0</v>
-      </c>
       <c r="J168" t="inlineStr">
         <is>
           <t>CONSERVAÇÃO ROTINEIRA DA MALHA VIÁRIA</t>
@@ -14924,9 +14585,6 @@
       <c r="H169" t="n">
         <v>311</v>
       </c>
-      <c r="I169" t="n">
-        <v>0</v>
-      </c>
       <c r="J169" t="inlineStr">
         <is>
           <t>CONSERVAÇÃO ROTINEIRA DA MALHA VIÁRIA</t>
@@ -15010,9 +14668,6 @@
       <c r="H170" t="n">
         <v>312</v>
       </c>
-      <c r="I170" t="n">
-        <v>0</v>
-      </c>
       <c r="J170" t="inlineStr">
         <is>
           <t>CONSERVAÇÃO ROTINEIRA DA MALHA VIÁRIA</t>
@@ -15096,9 +14751,6 @@
       <c r="H171" t="n">
         <v>313</v>
       </c>
-      <c r="I171" t="n">
-        <v>0</v>
-      </c>
       <c r="J171" t="inlineStr">
         <is>
           <t>CONSERVAÇÃO ROTINEIRA DA MALHA VIÁRIA</t>
@@ -15182,9 +14834,6 @@
       <c r="H172" t="n">
         <v>314</v>
       </c>
-      <c r="I172" t="n">
-        <v>0</v>
-      </c>
       <c r="J172" t="inlineStr">
         <is>
           <t>CONSERVAÇÃO ROTINEIRA DA MALHA VIÁRIA</t>
@@ -15268,9 +14917,6 @@
       <c r="H173" t="n">
         <v>315</v>
       </c>
-      <c r="I173" t="n">
-        <v>0</v>
-      </c>
       <c r="J173" t="inlineStr">
         <is>
           <t>CONSERVAÇÃO ROTINEIRA DA MALHA VIÁRIA</t>
@@ -15354,9 +15000,6 @@
       <c r="H174" t="n">
         <v>316</v>
       </c>
-      <c r="I174" t="n">
-        <v>0</v>
-      </c>
       <c r="J174" t="inlineStr">
         <is>
           <t>CONSERVAÇÃO ROTINEIRA DA MALHA VIÁRIA</t>
@@ -15440,9 +15083,6 @@
       <c r="H175" t="n">
         <v>317</v>
       </c>
-      <c r="I175" t="n">
-        <v>0</v>
-      </c>
       <c r="J175" t="inlineStr">
         <is>
           <t>CONSERVAÇÃO ROTINEIRA DA MALHA VIÁRIA</t>
@@ -15526,9 +15166,6 @@
       <c r="H176" t="n">
         <v>318</v>
       </c>
-      <c r="I176" t="n">
-        <v>0</v>
-      </c>
       <c r="J176" t="inlineStr">
         <is>
           <t>CONSERVAÇÃO ROTINEIRA DA MALHA VIÁRIA</t>
@@ -15612,9 +15249,6 @@
       <c r="H177" t="n">
         <v>319</v>
       </c>
-      <c r="I177" t="n">
-        <v>0</v>
-      </c>
       <c r="J177" t="inlineStr">
         <is>
           <t>CONSERVAÇÃO ROTINEIRA DA MALHA VIÁRIA</t>
@@ -15698,9 +15332,6 @@
       <c r="H178" t="n">
         <v>320</v>
       </c>
-      <c r="I178" t="n">
-        <v>0</v>
-      </c>
       <c r="J178" t="inlineStr">
         <is>
           <t>CONSERVAÇÃO ROTINEIRA DA MALHA VIÁRIA</t>
@@ -15784,9 +15415,6 @@
       <c r="H179" t="n">
         <v>321</v>
       </c>
-      <c r="I179" t="n">
-        <v>0</v>
-      </c>
       <c r="J179" t="inlineStr">
         <is>
           <t>CONSERVAÇÃO ROTINEIRA DA MALHA VIÁRIA</t>
@@ -15870,9 +15498,6 @@
       <c r="H180" t="n">
         <v>322</v>
       </c>
-      <c r="I180" t="n">
-        <v>0</v>
-      </c>
       <c r="J180" t="inlineStr">
         <is>
           <t>CONSERVAÇÃO ROTINEIRA DA MALHA VIÁRIA</t>
@@ -15956,9 +15581,6 @@
       <c r="H181" t="n">
         <v>323</v>
       </c>
-      <c r="I181" t="n">
-        <v>0</v>
-      </c>
       <c r="J181" t="inlineStr">
         <is>
           <t>CONSERVAÇÃO ROTINEIRA DA MALHA VIÁRIA</t>
@@ -16042,9 +15664,6 @@
       <c r="H182" t="n">
         <v>324</v>
       </c>
-      <c r="I182" t="n">
-        <v>0</v>
-      </c>
       <c r="J182" t="inlineStr">
         <is>
           <t>CONSERVAÇÃO ROTINEIRA DA MALHA VIÁRIA</t>
@@ -16128,9 +15747,6 @@
       <c r="H183" t="n">
         <v>325</v>
       </c>
-      <c r="I183" t="n">
-        <v>0</v>
-      </c>
       <c r="J183" t="inlineStr">
         <is>
           <t>CONSERVAÇÃO ROTINEIRA DA MALHA VIÁRIA</t>
@@ -16214,9 +15830,6 @@
       <c r="H184" t="n">
         <v>326</v>
       </c>
-      <c r="I184" t="n">
-        <v>0</v>
-      </c>
       <c r="J184" t="inlineStr">
         <is>
           <t>CONSERVAÇÃO ROTINEIRA DA MALHA VIÁRIA</t>
@@ -16300,9 +15913,6 @@
       <c r="H185" t="n">
         <v>371</v>
       </c>
-      <c r="I185" t="n">
-        <v>0</v>
-      </c>
       <c r="J185" t="inlineStr">
         <is>
           <t>RECUPERAÇÃO MALHA VIÁRIA</t>
@@ -16386,9 +15996,6 @@
       <c r="H186" t="n">
         <v>372</v>
       </c>
-      <c r="I186" t="n">
-        <v>0</v>
-      </c>
       <c r="J186" t="inlineStr">
         <is>
           <t>RE</t>
@@ -16472,9 +16079,6 @@
       <c r="H187" t="n">
         <v>373</v>
       </c>
-      <c r="I187" t="n">
-        <v>0</v>
-      </c>
       <c r="J187" t="inlineStr">
         <is>
           <t>RECUPERAÇÃO MALHA VIÁRIA</t>
@@ -16558,9 +16162,6 @@
       <c r="H188" t="n">
         <v>374</v>
       </c>
-      <c r="I188" t="n">
-        <v>0</v>
-      </c>
       <c r="J188" t="inlineStr">
         <is>
           <t>RECUPERAÇÃO MALHA VIÁRIA</t>
@@ -16644,9 +16245,6 @@
       <c r="H189" t="n">
         <v>375</v>
       </c>
-      <c r="I189" t="n">
-        <v>0</v>
-      </c>
       <c r="J189" t="inlineStr">
         <is>
           <t>RECUPERAÇÃO MALHA VIÁRIA</t>
@@ -16730,9 +16328,6 @@
       <c r="H190" t="n">
         <v>376</v>
       </c>
-      <c r="I190" t="n">
-        <v>0</v>
-      </c>
       <c r="J190" t="inlineStr">
         <is>
           <t>RECUPERAÇÃO MALHA VIÁRIA</t>
@@ -16816,9 +16411,6 @@
       <c r="H191" t="n">
         <v>377</v>
       </c>
-      <c r="I191" t="n">
-        <v>0</v>
-      </c>
       <c r="J191" t="inlineStr">
         <is>
           <t>RECUPERAÇÃO MALHA VIÁRIA</t>
@@ -16902,9 +16494,6 @@
       <c r="H192" t="n">
         <v>378</v>
       </c>
-      <c r="I192" t="n">
-        <v>0</v>
-      </c>
       <c r="J192" t="inlineStr">
         <is>
           <t>RECUPERAÇÃO MALHA VIÁRIA</t>
@@ -16988,9 +16577,6 @@
       <c r="H193" t="n">
         <v>379</v>
       </c>
-      <c r="I193" t="n">
-        <v>0</v>
-      </c>
       <c r="J193" t="inlineStr">
         <is>
           <t>REABILITAÇÃO DA MALHA VIÁRIA</t>
@@ -17074,9 +16660,6 @@
       <c r="H194" t="n">
         <v>380</v>
       </c>
-      <c r="I194" t="n">
-        <v>0</v>
-      </c>
       <c r="J194" t="inlineStr">
         <is>
           <t>REABILITAÇÃO DA MALHA VIÁRIA</t>
@@ -17160,9 +16743,6 @@
       <c r="H195" t="n">
         <v>381</v>
       </c>
-      <c r="I195" t="n">
-        <v>0</v>
-      </c>
       <c r="J195" t="inlineStr">
         <is>
           <t>REABILITAÇÃO DA MALHA VIÁRIA</t>
@@ -17246,9 +16826,6 @@
       <c r="H196" t="n">
         <v>382</v>
       </c>
-      <c r="I196" t="n">
-        <v>0</v>
-      </c>
       <c r="J196" t="inlineStr">
         <is>
           <t>RECUPERAÇÃO MALHA VIÁRIA</t>
@@ -17332,9 +16909,6 @@
       <c r="H197" t="n">
         <v>383</v>
       </c>
-      <c r="I197" t="n">
-        <v>0</v>
-      </c>
       <c r="J197" t="inlineStr">
         <is>
           <t>REABILITAÇÃO DA MALHA VIÁRIA</t>
@@ -17418,9 +16992,6 @@
       <c r="H198" t="n">
         <v>396</v>
       </c>
-      <c r="I198" t="n">
-        <v>0</v>
-      </c>
       <c r="J198" t="inlineStr">
         <is>
           <t>REABILITAÇÃO DA MALHA VIÁRIA</t>
@@ -18020,9 +17591,6 @@
       <c r="H205" t="n">
         <v>471</v>
       </c>
-      <c r="I205" t="n">
-        <v>0</v>
-      </c>
       <c r="J205" t="inlineStr">
         <is>
           <t>CONSTRUÇÃO DE SEDE PRÓPRIA</t>
@@ -18106,9 +17674,6 @@
       <c r="H206" t="n">
         <v>96</v>
       </c>
-      <c r="I206" t="n">
-        <v>0</v>
-      </c>
       <c r="J206" t="inlineStr">
         <is>
           <t>OBRAS PARA ATENDER O ENSINO SUPERIOR NO ILCT</t>
@@ -18192,9 +17757,6 @@
       <c r="H207" t="n">
         <v>97</v>
       </c>
-      <c r="I207" t="n">
-        <v>0</v>
-      </c>
       <c r="J207" t="inlineStr">
         <is>
           <t>OBRAS PARA ATENDER O ENSINO SUPERIOR NO ITAP</t>
@@ -18278,9 +17840,6 @@
       <c r="H208" t="n">
         <v>105</v>
       </c>
-      <c r="I208" t="n">
-        <v>0</v>
-      </c>
       <c r="J208" t="inlineStr">
         <is>
           <t>OBRA PARA MELHORIA DA INFRAESTRUTURA DA EPAMIG</t>
@@ -18364,9 +17923,6 @@
       <c r="H209" t="n">
         <v>106</v>
       </c>
-      <c r="I209" t="n">
-        <v>0</v>
-      </c>
       <c r="J209" t="inlineStr">
         <is>
           <t>OBRA MELHORIA DA INFRAESTRUTURA DA EPAMIG</t>
@@ -18576,7 +18132,7 @@
         <v>0</v>
       </c>
       <c r="R211" t="n">
-        <v>16800000</v>
+        <v>17000000</v>
       </c>
       <c r="S211" t="n">
         <v>0</v>
@@ -18748,7 +18304,7 @@
         <v>0</v>
       </c>
       <c r="R213" t="n">
-        <v>24000000</v>
+        <v>36040000</v>
       </c>
       <c r="S213" t="n">
         <v>0</v>
@@ -18794,9 +18350,6 @@
       <c r="H214" t="n">
         <v>402</v>
       </c>
-      <c r="I214" t="n">
-        <v>0</v>
-      </c>
       <c r="J214" t="inlineStr">
         <is>
           <t>Obra de restauração e adaptação predial do Palácio da Justiça, localizado na Avenida Afonso Pena, nº. 1.420, Centro, Belo Horizonte/MG</t>
@@ -18880,12 +18433,9 @@
       <c r="H215" t="n">
         <v>403</v>
       </c>
-      <c r="I215" t="n">
-        <v>0</v>
-      </c>
       <c r="J215" t="inlineStr">
         <is>
-          <t>Contrato a obra de reforma e ampliação</t>
+          <t>CONSTRUÇÃO NOVO FÓRUM PAD. P3 - RETOMADA - CT 280/2023</t>
         </is>
       </c>
       <c r="K215" t="inlineStr">
@@ -18920,7 +18470,7 @@
         <v>0</v>
       </c>
       <c r="R215" t="n">
-        <v>3000000</v>
+        <v>8671597</v>
       </c>
       <c r="S215" t="n">
         <v>0</v>
@@ -18966,12 +18516,9 @@
       <c r="H216" t="n">
         <v>404</v>
       </c>
-      <c r="I216" t="n">
-        <v>0</v>
-      </c>
       <c r="J216" t="inlineStr">
         <is>
-          <t>Construção do novo prédio do Fórum da Comarca de Bom Sucesso/MG</t>
+          <t>CONSTRUÇÃO NOVO FÓRUM PAD. BETA</t>
         </is>
       </c>
       <c r="K216" t="inlineStr">
@@ -19006,7 +18553,7 @@
         <v>0</v>
       </c>
       <c r="R216" t="n">
-        <v>4066270</v>
+        <v>8481045</v>
       </c>
       <c r="S216" t="n">
         <v>0</v>
@@ -19052,9 +18599,6 @@
       <c r="H217" t="n">
         <v>405</v>
       </c>
-      <c r="I217" t="n">
-        <v>0</v>
-      </c>
       <c r="J217" t="inlineStr">
         <is>
           <t>Retomada da obra de construção do novo prédio do Fórum da Comarca de Dores do Indaiá/MG.</t>
@@ -19092,7 +18636,7 @@
         <v>0</v>
       </c>
       <c r="R217" t="n">
-        <v>3012699</v>
+        <v>1943196</v>
       </c>
       <c r="S217" t="n">
         <v>0</v>
@@ -19138,12 +18682,9 @@
       <c r="H218" t="n">
         <v>406</v>
       </c>
-      <c r="I218" t="n">
-        <v>0</v>
-      </c>
       <c r="J218" t="inlineStr">
         <is>
-          <t>Contrato a obra de reforma e ampliação</t>
+          <t>FORMIGA – CONSTRUÇÃO NOVO FÓRUM PAD. NLN5 – RETOMADA DA OBRA</t>
         </is>
       </c>
       <c r="K218" t="inlineStr">
@@ -19178,7 +18719,7 @@
         <v>0</v>
       </c>
       <c r="R218" t="n">
-        <v>7000000</v>
+        <v>8406955</v>
       </c>
       <c r="S218" t="n">
         <v>0</v>
@@ -19224,9 +18765,6 @@
       <c r="H219" t="n">
         <v>408</v>
       </c>
-      <c r="I219" t="n">
-        <v>0</v>
-      </c>
       <c r="J219" t="inlineStr">
         <is>
           <t>Construção do novo prédio do Fórum da Comarca de Governador Valadares</t>
@@ -19264,7 +18802,7 @@
         <v>0</v>
       </c>
       <c r="R219" t="n">
-        <v>10800000</v>
+        <v>18000000</v>
       </c>
       <c r="S219" t="n">
         <v>0</v>
@@ -19310,9 +18848,6 @@
       <c r="H220" t="n">
         <v>409</v>
       </c>
-      <c r="I220" t="n">
-        <v>0</v>
-      </c>
       <c r="J220" t="inlineStr">
         <is>
           <t>Retomada da obra de construção do novo prédio do Fórum da Comarca de Guanhães/MG.</t>
@@ -19350,7 +18885,7 @@
         <v>0</v>
       </c>
       <c r="R220" t="n">
-        <v>7354637</v>
+        <v>5870448</v>
       </c>
       <c r="S220" t="n">
         <v>0</v>
@@ -19396,9 +18931,6 @@
       <c r="H221" t="n">
         <v>410</v>
       </c>
-      <c r="I221" t="n">
-        <v>0</v>
-      </c>
       <c r="J221" t="inlineStr">
         <is>
           <t>Contrato a execução de obras de reforma e ampliação do Fórum da Comarca de Igarapé/MG</t>
@@ -19436,7 +18968,7 @@
         <v>0</v>
       </c>
       <c r="R221" t="n">
-        <v>4800000</v>
+        <v>7000000</v>
       </c>
       <c r="S221" t="n">
         <v>0</v>
@@ -19482,9 +19014,6 @@
       <c r="H222" t="n">
         <v>411</v>
       </c>
-      <c r="I222" t="n">
-        <v>0</v>
-      </c>
       <c r="J222" t="inlineStr">
         <is>
           <t>Construção do novo prédio do Fórum da Comarca de Inhapim/MG</t>
@@ -19522,7 +19051,7 @@
         <v>0</v>
       </c>
       <c r="R222" t="n">
-        <v>4800000</v>
+        <v>7345086</v>
       </c>
       <c r="S222" t="n">
         <v>0</v>
@@ -19568,9 +19097,6 @@
       <c r="H223" t="n">
         <v>412</v>
       </c>
-      <c r="I223" t="n">
-        <v>0</v>
-      </c>
       <c r="J223" t="inlineStr">
         <is>
           <t>Reforma e ampliação do Fórum da Comarca de Ipanema/MG</t>
@@ -19608,7 +19134,7 @@
         <v>0</v>
       </c>
       <c r="R223" t="n">
-        <v>6459303</v>
+        <v>6000000</v>
       </c>
       <c r="S223" t="n">
         <v>0</v>
@@ -19654,12 +19180,9 @@
       <c r="H224" t="n">
         <v>413</v>
       </c>
-      <c r="I224" t="n">
-        <v>0</v>
-      </c>
       <c r="J224" t="inlineStr">
         <is>
-          <t>Contrato a obra de reforma e ampliação</t>
+          <t>CONSTRUÇÃO NOVO FÓRUM PAD. P9</t>
         </is>
       </c>
       <c r="K224" t="inlineStr">
@@ -19694,7 +19217,7 @@
         <v>0</v>
       </c>
       <c r="R224" t="n">
-        <v>18942767</v>
+        <v>15246330</v>
       </c>
       <c r="S224" t="n">
         <v>0</v>
@@ -19740,9 +19263,6 @@
       <c r="H225" t="n">
         <v>417</v>
       </c>
-      <c r="I225" t="n">
-        <v>0</v>
-      </c>
       <c r="J225" t="inlineStr">
         <is>
           <t>Contrato a obra de reforma e ampliação</t>
@@ -19780,7 +19300,7 @@
         <v>0</v>
       </c>
       <c r="R225" t="n">
-        <v>5588870</v>
+        <v>5147378</v>
       </c>
       <c r="S225" t="n">
         <v>0</v>
@@ -19826,9 +19346,6 @@
       <c r="H226" t="n">
         <v>418</v>
       </c>
-      <c r="I226" t="n">
-        <v>0</v>
-      </c>
       <c r="J226" t="inlineStr">
         <is>
           <t>Obra de construção do novo prédio do Fórum da Comarca de Juiz de Fora.</t>
@@ -19866,7 +19383,7 @@
         <v>0</v>
       </c>
       <c r="R226" t="n">
-        <v>12000000</v>
+        <v>16494637</v>
       </c>
       <c r="S226" t="n">
         <v>0</v>
@@ -19912,9 +19429,6 @@
       <c r="H227" t="n">
         <v>419</v>
       </c>
-      <c r="I227" t="n">
-        <v>0</v>
-      </c>
       <c r="J227" t="inlineStr">
         <is>
           <t>Retomada da obra de construção do novo prédio do Fórum</t>
@@ -19952,7 +19466,7 @@
         <v>0</v>
       </c>
       <c r="R227" t="n">
-        <v>12000000</v>
+        <v>19958308</v>
       </c>
       <c r="S227" t="n">
         <v>0</v>
@@ -19998,12 +19512,9 @@
       <c r="H228" t="n">
         <v>420</v>
       </c>
-      <c r="I228" t="n">
-        <v>0</v>
-      </c>
       <c r="J228" t="inlineStr">
         <is>
-          <t>Contrato a obra de reforma e ampliação</t>
+          <t>CONSTRUÇÃO NOVO FÓRUM PAD. 1V – RETOMADA DA OBRA</t>
         </is>
       </c>
       <c r="K228" t="inlineStr">
@@ -20038,7 +19549,7 @@
         <v>0</v>
       </c>
       <c r="R228" t="n">
-        <v>2726039</v>
+        <v>625934</v>
       </c>
       <c r="S228" t="n">
         <v>0</v>
@@ -20084,9 +19595,6 @@
       <c r="H229" t="n">
         <v>421</v>
       </c>
-      <c r="I229" t="n">
-        <v>0</v>
-      </c>
       <c r="J229" t="inlineStr">
         <is>
           <t>Retomada da obra de construção do novo prédio do Fórum da Comarca de Pará de Minas/MG</t>
@@ -20124,7 +19632,7 @@
         <v>0</v>
       </c>
       <c r="R229" t="n">
-        <v>9600000</v>
+        <v>12000000</v>
       </c>
       <c r="S229" t="n">
         <v>0</v>
@@ -20170,9 +19678,6 @@
       <c r="H230" t="n">
         <v>422</v>
       </c>
-      <c r="I230" t="n">
-        <v>0</v>
-      </c>
       <c r="J230" t="inlineStr">
         <is>
           <t>Retomada da obra de construção do novo prédio do Fórum</t>
@@ -20210,7 +19715,7 @@
         <v>0</v>
       </c>
       <c r="R230" t="n">
-        <v>7525674</v>
+        <v>5962058</v>
       </c>
       <c r="S230" t="n">
         <v>0</v>
@@ -20256,9 +19761,6 @@
       <c r="H231" t="n">
         <v>423</v>
       </c>
-      <c r="I231" t="n">
-        <v>0</v>
-      </c>
       <c r="J231" t="inlineStr">
         <is>
           <t>Construção do novo prédio do Fórum da Comarca de Pitangui/MG</t>
@@ -20296,7 +19798,7 @@
         <v>0</v>
       </c>
       <c r="R231" t="n">
-        <v>6704585</v>
+        <v>7000000</v>
       </c>
       <c r="S231" t="n">
         <v>0</v>
@@ -20342,12 +19844,9 @@
       <c r="H232" t="n">
         <v>424</v>
       </c>
-      <c r="I232" t="n">
-        <v>0</v>
-      </c>
       <c r="J232" t="inlineStr">
         <is>
-          <t>Contrato a obra de reforma e ampliação</t>
+          <t>CONSTRUÇÃO NOVO FÓRUM PAD. NLN6 – RETOMADA DA OBRA</t>
         </is>
       </c>
       <c r="K232" t="inlineStr">
@@ -20382,7 +19881,7 @@
         <v>0</v>
       </c>
       <c r="R232" t="n">
-        <v>13357938</v>
+        <v>12679547</v>
       </c>
       <c r="S232" t="n">
         <v>0</v>
@@ -20433,7 +19932,7 @@
       </c>
       <c r="J233" t="inlineStr">
         <is>
-          <t>Constitui objeto do presente Contrato a execução de obra de construção do novo prédio do Fórum da Comarca de São João da Ponte/MG</t>
+          <t>CONSTRUÇÃO DO NOVO PRÉDIO DO FÓRUM DA COMARCA DE SÃO JOÃO DA PONTE/MG</t>
         </is>
       </c>
       <c r="K233" t="inlineStr">
@@ -20468,7 +19967,7 @@
         <v>0</v>
       </c>
       <c r="R233" t="n">
-        <v>6415497</v>
+        <v>5302197</v>
       </c>
       <c r="S233" t="n">
         <v>0</v>
@@ -20514,9 +20013,6 @@
       <c r="H234" t="n">
         <v>426</v>
       </c>
-      <c r="I234" t="n">
-        <v>0</v>
-      </c>
       <c r="J234" t="inlineStr">
         <is>
           <t>Contrato a obra de reforma e ampliação do Fórum da Comarca de Teófilo Otoni/MG</t>
@@ -20554,7 +20050,7 @@
         <v>0</v>
       </c>
       <c r="R234" t="n">
-        <v>8400000</v>
+        <v>10845056</v>
       </c>
       <c r="S234" t="n">
         <v>0</v>
@@ -20600,9 +20096,6 @@
       <c r="H235" t="n">
         <v>427</v>
       </c>
-      <c r="I235" t="n">
-        <v>0</v>
-      </c>
       <c r="J235" t="inlineStr">
         <is>
           <t>Contrato a execução de obras de construção do novo prédio do Fórum da Comarca de Vespasiano/MG</t>
@@ -20640,7 +20133,7 @@
         <v>0</v>
       </c>
       <c r="R235" t="n">
-        <v>9600000</v>
+        <v>10000000</v>
       </c>
       <c r="S235" t="n">
         <v>0</v>
@@ -20686,9 +20179,6 @@
       <c r="H236" t="n">
         <v>428</v>
       </c>
-      <c r="I236" t="n">
-        <v>0</v>
-      </c>
       <c r="J236" t="inlineStr">
         <is>
           <t>Reforma parcial dos Anexos I e II do TRIBUNAL, para a substituição do sistema de ar condicionado central do Anexo II (Corregedoria), para pintura interna do Anexo I e para instalação do sistema de detecção e alarme de incêndio dos Anexos I e II</t>
@@ -20772,9 +20262,6 @@
       <c r="H237" t="n">
         <v>429</v>
       </c>
-      <c r="I237" t="n">
-        <v>0</v>
-      </c>
       <c r="J237" t="inlineStr">
         <is>
           <t>Reforma parcial do Edifício Liberdade</t>
@@ -20858,9 +20345,6 @@
       <c r="H238" t="n">
         <v>430</v>
       </c>
-      <c r="I238" t="n">
-        <v>0</v>
-      </c>
       <c r="J238" t="inlineStr">
         <is>
           <t>Reforma do 2º (segundo) pavimento do Edifício Sede do TRIBUNAL, localizado na Unidade Afonso Pena, nº. 4.001, Bairro Serra, Belo Horizonte/MG</t>
@@ -20898,7 +20382,7 @@
         <v>0</v>
       </c>
       <c r="R238" t="n">
-        <v>397813</v>
+        <v>942286</v>
       </c>
       <c r="S238" t="n">
         <v>0</v>
@@ -20944,9 +20428,6 @@
       <c r="H239" t="n">
         <v>431</v>
       </c>
-      <c r="I239" t="n">
-        <v>0</v>
-      </c>
       <c r="J239" t="inlineStr">
         <is>
           <t>Construção do Fórum e CEJUSC Digitais no município de Fronteira, integrante da Comarca de Frutal</t>
@@ -20984,7 +20465,7 @@
         <v>0</v>
       </c>
       <c r="R239" t="n">
-        <v>520524</v>
+        <v>706423</v>
       </c>
       <c r="S239" t="n">
         <v>0</v>
@@ -21030,9 +20511,6 @@
       <c r="H240" t="n">
         <v>432</v>
       </c>
-      <c r="I240" t="n">
-        <v>0</v>
-      </c>
       <c r="J240" t="inlineStr">
         <is>
           <t>Contrato a obra de reforma e ampliação</t>
@@ -21116,9 +20594,6 @@
       <c r="H241" t="n">
         <v>433</v>
       </c>
-      <c r="I241" t="n">
-        <v>0</v>
-      </c>
       <c r="J241" t="inlineStr">
         <is>
           <t>Execução de obra de reforma parcial para acessibilidade do Fórum da Comarca de Ouro Branco/MG</t>
@@ -21156,7 +20631,7 @@
         <v>0</v>
       </c>
       <c r="R241" t="n">
-        <v>507965</v>
+        <v>344687</v>
       </c>
       <c r="S241" t="n">
         <v>0</v>
@@ -21202,9 +20677,6 @@
       <c r="H242" t="n">
         <v>435</v>
       </c>
-      <c r="I242" t="n">
-        <v>0</v>
-      </c>
       <c r="J242" t="inlineStr">
         <is>
           <t>Retomada da obra de construção do novo prédio do Fórum</t>
@@ -21288,9 +20760,6 @@
       <c r="H243" t="n">
         <v>437</v>
       </c>
-      <c r="I243" t="n">
-        <v>0</v>
-      </c>
       <c r="J243" t="inlineStr">
         <is>
           <t>Retomada da obra de construção do novo prédio do Fórum</t>
@@ -21414,7 +20883,7 @@
         <v>0</v>
       </c>
       <c r="R244" t="n">
-        <v>7000000</v>
+        <v>15000000</v>
       </c>
       <c r="S244" t="n">
         <v>0</v>
@@ -21460,9 +20929,6 @@
       <c r="H245" t="n">
         <v>439</v>
       </c>
-      <c r="I245" t="n">
-        <v>0</v>
-      </c>
       <c r="J245" t="inlineStr">
         <is>
           <t>Contrato a obra de reforma e ampliação</t>
@@ -21546,9 +21012,6 @@
       <c r="H246" t="n">
         <v>440</v>
       </c>
-      <c r="I246" t="n">
-        <v>0</v>
-      </c>
       <c r="J246" t="inlineStr">
         <is>
           <t>Retomada da obra de construção do novo prédio do Fórum</t>
@@ -21632,9 +21095,6 @@
       <c r="H247" t="n">
         <v>441</v>
       </c>
-      <c r="I247" t="n">
-        <v>0</v>
-      </c>
       <c r="J247" t="inlineStr">
         <is>
           <t>REFORMA E AMPLIAÇÃO DO FÓRUM</t>
@@ -21672,7 +21132,7 @@
         <v>0</v>
       </c>
       <c r="R247" t="n">
-        <v>3000000</v>
+        <v>2273500</v>
       </c>
       <c r="S247" t="n">
         <v>0</v>
@@ -21718,9 +21178,6 @@
       <c r="H248" t="n">
         <v>442</v>
       </c>
-      <c r="I248" t="n">
-        <v>0</v>
-      </c>
       <c r="J248" t="inlineStr">
         <is>
           <t>CONSTRUÇÃO NOVO FÓRUM PAD. 1V</t>
@@ -21804,9 +21261,6 @@
       <c r="H249" t="n">
         <v>443</v>
       </c>
-      <c r="I249" t="n">
-        <v>0</v>
-      </c>
       <c r="J249" t="inlineStr">
         <is>
           <t>CONSTRUÇÃO NOVO FÓRUM PAD. M2</t>
@@ -21844,7 +21298,7 @@
         <v>0</v>
       </c>
       <c r="R249" t="n">
-        <v>3350000</v>
+        <v>6940618</v>
       </c>
       <c r="S249" t="n">
         <v>0</v>
@@ -21890,9 +21344,6 @@
       <c r="H250" t="n">
         <v>444</v>
       </c>
-      <c r="I250" t="n">
-        <v>0</v>
-      </c>
       <c r="J250" t="inlineStr">
         <is>
           <t>CONSTRUÇÃO NOVO FÓRUM PAD. M2</t>
@@ -21930,7 +21381,7 @@
         <v>0</v>
       </c>
       <c r="R250" t="n">
-        <v>3150000</v>
+        <v>5838079</v>
       </c>
       <c r="S250" t="n">
         <v>0</v>
@@ -21976,9 +21427,6 @@
       <c r="H251" t="n">
         <v>445</v>
       </c>
-      <c r="I251" t="n">
-        <v>0</v>
-      </c>
       <c r="J251" t="inlineStr">
         <is>
           <t>CONSTRUÇÃO NOVO FÓRUM PAD. M2</t>
@@ -22016,7 +21464,7 @@
         <v>0</v>
       </c>
       <c r="R251" t="n">
-        <v>3050000</v>
+        <v>5824727</v>
       </c>
       <c r="S251" t="n">
         <v>0</v>
@@ -22062,9 +21510,6 @@
       <c r="H252" t="n">
         <v>446</v>
       </c>
-      <c r="I252" t="n">
-        <v>0</v>
-      </c>
       <c r="J252" t="inlineStr">
         <is>
           <t>CONSTRUÇÃO NOVO FÓRUM PAD. BETA - RETOMADA</t>
@@ -22148,9 +21593,6 @@
       <c r="H253" t="n">
         <v>447</v>
       </c>
-      <c r="I253" t="n">
-        <v>0</v>
-      </c>
       <c r="J253" t="inlineStr">
         <is>
           <t>CONSTRUÇÃO NOVO FÓRUM PAD. P3</t>
@@ -22188,7 +21630,7 @@
         <v>0</v>
       </c>
       <c r="R253" t="n">
-        <v>1350000</v>
+        <v>4302244</v>
       </c>
       <c r="S253" t="n">
         <v>0</v>
@@ -22234,9 +21676,6 @@
       <c r="H254" t="n">
         <v>448</v>
       </c>
-      <c r="I254" t="n">
-        <v>0</v>
-      </c>
       <c r="J254" t="inlineStr">
         <is>
           <t>REFORMA E AMPLIAÇÃO DO FÓRUM - RETOMADA</t>
@@ -22320,9 +21759,6 @@
       <c r="H255" t="n">
         <v>449</v>
       </c>
-      <c r="I255" t="n">
-        <v>0</v>
-      </c>
       <c r="J255" t="inlineStr">
         <is>
           <t>CONSTRUÇÃO NOVO FÓRUM PAD. 1V</t>
@@ -22360,7 +21796,7 @@
         <v>0</v>
       </c>
       <c r="R255" t="n">
-        <v>2450000</v>
+        <v>3554023</v>
       </c>
       <c r="S255" t="n">
         <v>0</v>
@@ -22406,9 +21842,6 @@
       <c r="H256" t="n">
         <v>450</v>
       </c>
-      <c r="I256" t="n">
-        <v>0</v>
-      </c>
       <c r="J256" t="inlineStr">
         <is>
           <t>CONSTRUÇÃO NOVO FÓRUM PAD. 1V</t>
@@ -22446,7 +21879,7 @@
         <v>0</v>
       </c>
       <c r="R256" t="n">
-        <v>2430000</v>
+        <v>3554023</v>
       </c>
       <c r="S256" t="n">
         <v>0</v>
@@ -22492,9 +21925,6 @@
       <c r="H257" t="n">
         <v>451</v>
       </c>
-      <c r="I257" t="n">
-        <v>0</v>
-      </c>
       <c r="J257" t="inlineStr">
         <is>
           <t>CONSTRUÇÃO NOVO FÓRUM PAD. 1V</t>
@@ -22532,7 +21962,7 @@
         <v>0</v>
       </c>
       <c r="R257" t="n">
-        <v>1550000</v>
+        <v>2166465</v>
       </c>
       <c r="S257" t="n">
         <v>0</v>
@@ -22578,9 +22008,6 @@
       <c r="H258" t="n">
         <v>452</v>
       </c>
-      <c r="I258" t="n">
-        <v>0</v>
-      </c>
       <c r="J258" t="inlineStr">
         <is>
           <t>CONSTRUÇÃO NOVO FÓRUM PAD. M4</t>
@@ -22618,7 +22045,7 @@
         <v>0</v>
       </c>
       <c r="R258" t="n">
-        <v>2300000</v>
+        <v>2598700</v>
       </c>
       <c r="S258" t="n">
         <v>0</v>
@@ -22664,9 +22091,6 @@
       <c r="H259" t="n">
         <v>453</v>
       </c>
-      <c r="I259" t="n">
-        <v>0</v>
-      </c>
       <c r="J259" t="inlineStr">
         <is>
           <t>CONSTRUÇÃO NOVO FÓRUM PAD. M2</t>
@@ -22704,7 +22128,7 @@
         <v>0</v>
       </c>
       <c r="R259" t="n">
-        <v>1700000</v>
+        <v>1826378</v>
       </c>
       <c r="S259" t="n">
         <v>0</v>
@@ -22750,9 +22174,6 @@
       <c r="H260" t="n">
         <v>454</v>
       </c>
-      <c r="I260" t="n">
-        <v>0</v>
-      </c>
       <c r="J260" t="inlineStr">
         <is>
           <t>CONSTRUÇÃO NOVO FÓRUM PAD. M2</t>
@@ -22790,7 +22211,7 @@
         <v>0</v>
       </c>
       <c r="R260" t="n">
-        <v>1700000</v>
+        <v>1826378</v>
       </c>
       <c r="S260" t="n">
         <v>0</v>
@@ -22836,9 +22257,6 @@
       <c r="H261" t="n">
         <v>455</v>
       </c>
-      <c r="I261" t="n">
-        <v>0</v>
-      </c>
       <c r="J261" t="inlineStr">
         <is>
           <t>CONSTRUÇÃO NOVO FÓRUM PAD. M3</t>
@@ -22876,7 +22294,7 @@
         <v>0</v>
       </c>
       <c r="R261" t="n">
-        <v>2100000</v>
+        <v>2568492</v>
       </c>
       <c r="S261" t="n">
         <v>0</v>
@@ -22922,9 +22340,6 @@
       <c r="H262" t="n">
         <v>456</v>
       </c>
-      <c r="I262" t="n">
-        <v>0</v>
-      </c>
       <c r="J262" t="inlineStr">
         <is>
           <t>REFORMA E AMPLIAÇÃO DO FÓRUM</t>
@@ -23008,9 +22423,6 @@
       <c r="H263" t="n">
         <v>457</v>
       </c>
-      <c r="I263" t="n">
-        <v>0</v>
-      </c>
       <c r="J263" t="inlineStr">
         <is>
           <t>CONSTRUÇÃO NOVO FÓRUM PAD. M4</t>
@@ -23048,7 +22460,7 @@
         <v>0</v>
       </c>
       <c r="R263" t="n">
-        <v>2100000</v>
+        <v>2598700</v>
       </c>
       <c r="S263" t="n">
         <v>0</v>
@@ -23094,9 +22506,6 @@
       <c r="H264" t="n">
         <v>458</v>
       </c>
-      <c r="I264" t="n">
-        <v>0</v>
-      </c>
       <c r="J264" t="inlineStr">
         <is>
           <t>CONSTRUÇÃO NOVO FÓRUM PAD. M3</t>
@@ -23134,7 +22543,7 @@
         <v>0</v>
       </c>
       <c r="R264" t="n">
-        <v>1800000</v>
+        <v>2032013</v>
       </c>
       <c r="S264" t="n">
         <v>0</v>
@@ -23180,9 +22589,6 @@
       <c r="H265" t="n">
         <v>459</v>
       </c>
-      <c r="I265" t="n">
-        <v>0</v>
-      </c>
       <c r="J265" t="inlineStr">
         <is>
           <t>CONSTRUÇÃO NOVO FÓRUM PAD. 1+1V</t>
@@ -23220,7 +22626,7 @@
         <v>0</v>
       </c>
       <c r="R265" t="n">
-        <v>1250000</v>
+        <v>1456341</v>
       </c>
       <c r="S265" t="n">
         <v>0</v>
@@ -23266,9 +22672,6 @@
       <c r="H266" t="n">
         <v>460</v>
       </c>
-      <c r="I266" t="n">
-        <v>0</v>
-      </c>
       <c r="J266" t="inlineStr">
         <is>
           <t>CONSTRUÇÃO NOVO FÓRUM PAD. M2</t>
@@ -23306,7 +22709,7 @@
         <v>0</v>
       </c>
       <c r="R266" t="n">
-        <v>950000</v>
+        <v>657957</v>
       </c>
       <c r="S266" t="n">
         <v>0</v>
@@ -23352,9 +22755,6 @@
       <c r="H267" t="n">
         <v>461</v>
       </c>
-      <c r="I267" t="n">
-        <v>0</v>
-      </c>
       <c r="J267" t="inlineStr">
         <is>
           <t>CONSTRUÇÃO NOVO FÓRUM PAD. 1V</t>
@@ -23392,7 +22792,7 @@
         <v>0</v>
       </c>
       <c r="R267" t="n">
-        <v>600000</v>
+        <v>795357</v>
       </c>
       <c r="S267" t="n">
         <v>0</v>
@@ -23438,9 +22838,6 @@
       <c r="H268" t="n">
         <v>462</v>
       </c>
-      <c r="I268" t="n">
-        <v>0</v>
-      </c>
       <c r="J268" t="inlineStr">
         <is>
           <t>CONSTRUÇÃO NOVO FÓRUM PAD. 1V</t>
@@ -23478,7 +22875,7 @@
         <v>0</v>
       </c>
       <c r="R268" t="n">
-        <v>750000</v>
+        <v>795358</v>
       </c>
       <c r="S268" t="n">
         <v>0</v>
@@ -23524,9 +22921,6 @@
       <c r="H269" t="n">
         <v>463</v>
       </c>
-      <c r="I269" t="n">
-        <v>0</v>
-      </c>
       <c r="J269" t="inlineStr">
         <is>
           <t>REFORMA E AMPLIAÇÃO DO FÓRUM</t>
@@ -23610,9 +23004,6 @@
       <c r="H270" t="n">
         <v>464</v>
       </c>
-      <c r="I270" t="n">
-        <v>0</v>
-      </c>
       <c r="J270" t="inlineStr">
         <is>
           <t>CONSTRUÇÃO NOVO FÓRUM PAD. M5</t>
@@ -23650,7 +23041,7 @@
         <v>0</v>
       </c>
       <c r="R270" t="n">
-        <v>159808</v>
+        <v>330287</v>
       </c>
       <c r="S270" t="n">
         <v>0</v>
@@ -23696,9 +23087,6 @@
       <c r="H271" t="n">
         <v>465</v>
       </c>
-      <c r="I271" t="n">
-        <v>0</v>
-      </c>
       <c r="J271" t="inlineStr">
         <is>
           <t>REFORMA HELIPONTO</t>
@@ -23782,9 +23170,6 @@
       <c r="H272" t="n">
         <v>466</v>
       </c>
-      <c r="I272" t="n">
-        <v>0</v>
-      </c>
       <c r="J272" t="inlineStr">
         <is>
           <t>REFORMA PARCIAL (1ª PARCELA) UNIDADE FRANCISCO SALES (DEMOLIÇÃO CASAS, PAISAGISMO, IMPERMEABILIZAÇÃO, BRISES E ESQUADRIA DA FACHADA)</t>
@@ -23868,9 +23253,6 @@
       <c r="H273" t="n">
         <v>467</v>
       </c>
-      <c r="I273" t="n">
-        <v>0</v>
-      </c>
       <c r="J273" t="inlineStr">
         <is>
           <t>REFORMA ANEXO I E AUDITÓRIO (ACESSIBILIDADE)</t>
@@ -23954,9 +23336,6 @@
       <c r="H274" t="n">
         <v>468</v>
       </c>
-      <c r="I274" t="n">
-        <v>0</v>
-      </c>
       <c r="J274" t="inlineStr">
         <is>
           <t>REFORMA ED. SEDE 3ª PARCELA (2° SUBSOLO E DATA CENTER 3)</t>
@@ -24040,9 +23419,6 @@
       <c r="H275" t="n">
         <v>469</v>
       </c>
-      <c r="I275" t="n">
-        <v>0</v>
-      </c>
       <c r="J275" t="inlineStr">
         <is>
           <t>ED. SEDE - AMPLIAÇÃO - CONSTRUÇÃO DA TORRE SUL E NORTE</t>
@@ -24126,9 +23502,6 @@
       <c r="H276" t="n">
         <v>470</v>
       </c>
-      <c r="I276" t="n">
-        <v>0</v>
-      </c>
       <c r="J276" t="inlineStr">
         <is>
           <t>EJEF REFORMA GERAL</t>
@@ -24212,9 +23585,6 @@
       <c r="H277" t="n">
         <v>472</v>
       </c>
-      <c r="I277" t="n">
-        <v>0</v>
-      </c>
       <c r="J277" t="inlineStr">
         <is>
           <t>ED. SEDE E FRANCISCO SALES TJMG - CONTRATO DE MODERNIZAÇÃO AUDIOVISUAL</t>
@@ -24298,9 +23668,6 @@
       <c r="H278" t="n">
         <v>473</v>
       </c>
-      <c r="I278" t="n">
-        <v>0</v>
-      </c>
       <c r="J278" t="inlineStr">
         <is>
           <t>CEOP - INSTALAÇÕES DE NOVOS SISTEMAS DE AR CONDICIONADO PARA O DATA CENTER E PARA O 2° ANDAR. CT 296/2023</t>
@@ -24338,7 +23705,7 @@
         <v>0</v>
       </c>
       <c r="R278" t="n">
-        <v>600209</v>
+        <v>814654</v>
       </c>
       <c r="S278" t="n">
         <v>0</v>
@@ -24384,9 +23751,6 @@
       <c r="H279" t="n">
         <v>474</v>
       </c>
-      <c r="I279" t="n">
-        <v>0</v>
-      </c>
       <c r="J279" t="inlineStr">
         <is>
           <t>CORREGEDORIA - AR COND. E DETECÇÃO ANEXO I E II</t>
@@ -24470,9 +23834,6 @@
       <c r="H280" t="n">
         <v>475</v>
       </c>
-      <c r="I280" t="n">
-        <v>0</v>
-      </c>
       <c r="J280" t="inlineStr">
         <is>
           <t>DIVERSOS PRÉDIOS - OBRAS E SERVIÇOS EMERGENCIAIS E PEQUENAS INTEREVENÇÕES</t>
@@ -24556,9 +23917,6 @@
       <c r="H281" t="n">
         <v>476</v>
       </c>
-      <c r="I281" t="n">
-        <v>0</v>
-      </c>
       <c r="J281" t="inlineStr">
         <is>
           <t>ED. SEDE - 1º PARCELA DA REFORMA NO 2º PAVIMENTO DO PRÉDIO DO TJMG</t>
@@ -24596,7 +23954,7 @@
         <v>0</v>
       </c>
       <c r="R281" t="n">
-        <v>340476</v>
+        <v>1327187</v>
       </c>
       <c r="S281" t="n">
         <v>0</v>
@@ -24642,9 +24000,6 @@
       <c r="H282" t="n">
         <v>477</v>
       </c>
-      <c r="I282" t="n">
-        <v>0</v>
-      </c>
       <c r="J282" t="inlineStr">
         <is>
           <t>GUTIERREZ - REFORMA GERAL DO CEJUSC</t>
@@ -24682,7 +24037,7 @@
         <v>0</v>
       </c>
       <c r="R282" t="n">
-        <v>4442700</v>
+        <v>3458197</v>
       </c>
       <c r="S282" t="n">
         <v>0</v>
@@ -24728,9 +24083,6 @@
       <c r="H283" t="n">
         <v>478</v>
       </c>
-      <c r="I283" t="n">
-        <v>0</v>
-      </c>
       <c r="J283" t="inlineStr">
         <is>
           <t>Construção do Fórum e CEJUSC Digitais no Município de Coluna/MG</t>
@@ -24814,9 +24166,6 @@
       <c r="H284" t="n">
         <v>479</v>
       </c>
-      <c r="I284" t="n">
-        <v>0</v>
-      </c>
       <c r="J284" t="inlineStr">
         <is>
           <t>DIVERSAS COMARCA - PROJETOS - CONSTRUÇÕES, AMPLI. E REF. - LOTE 3</t>
@@ -24900,9 +24249,6 @@
       <c r="H285" t="n">
         <v>480</v>
       </c>
-      <c r="I285" t="n">
-        <v>0</v>
-      </c>
       <c r="J285" t="inlineStr">
         <is>
           <t>DIVERSAS COMARCAS - ACESSIBILIDADE - 7ª LICITAÇÃO -CURVELO, VÁRZEA DE PALMA E BUENÓPOLIS</t>
@@ -24986,9 +24332,6 @@
       <c r="H286" t="n">
         <v>481</v>
       </c>
-      <c r="I286" t="n">
-        <v>0</v>
-      </c>
       <c r="J286" t="inlineStr">
         <is>
           <t>DIVERSAS COMARCAS - ACESSIBILIDADE - RETOMADA - (CARANDAÍ, CARANGOLA, RIO CASCA, TOMBOS, BONFIM)</t>
@@ -25072,9 +24415,6 @@
       <c r="H287" t="n">
         <v>482</v>
       </c>
-      <c r="I287" t="n">
-        <v>0</v>
-      </c>
       <c r="J287" t="inlineStr">
         <is>
           <t>DIVERSAS COMARCAS - ACESSIBILIDADE - RETOMADA - (CARANGOLA, TOMBOS, RIO CASCA E BAMBUÍ)</t>
@@ -25158,9 +24498,6 @@
       <c r="H288" t="n">
         <v>483</v>
       </c>
-      <c r="I288" t="n">
-        <v>0</v>
-      </c>
       <c r="J288" t="inlineStr">
         <is>
           <t>DIVERSAS COMARCAS - CONTRATO DE SISTEMAS DE GERAÇÃO DE ENERGIA SOLAR FOTOVOLTAICA</t>
@@ -25198,7 +24535,7 @@
         <v>0</v>
       </c>
       <c r="R288" t="n">
-        <v>5900000</v>
+        <v>5899992</v>
       </c>
       <c r="S288" t="n">
         <v>0</v>
@@ -25244,9 +24581,6 @@
       <c r="H289" t="n">
         <v>484</v>
       </c>
-      <c r="I289" t="n">
-        <v>0</v>
-      </c>
       <c r="J289" t="inlineStr">
         <is>
           <t>DIVERSAS COMARCAS - FORNECIMENTO E INSTALAÇÃO DE ELEVADORES HIDRÁULICOS NOVOS TIPO “PLATAFORMA” BEM COMO A PRESTAÇÃO DE ASSISTÊNCIA TÉCNICA NO PERÍODO DE GARANTIA DAS INSTALAÇÕES, ESTANDO INCLUÍDAS AS DESINSTALAÇÕES DOS ELEVADORES ORIGINAIS</t>
@@ -25330,9 +24664,6 @@
       <c r="H290" t="n">
         <v>485</v>
       </c>
-      <c r="I290" t="n">
-        <v>0</v>
-      </c>
       <c r="J290" t="inlineStr">
         <is>
           <t>DIVERSAS COMARCAS - OBRAS E SERVIÇOS EMERGENCIAIS E PEQUENAS INTERVENÇÕES</t>
@@ -25416,9 +24747,6 @@
       <c r="H291" t="n">
         <v>486</v>
       </c>
-      <c r="I291" t="n">
-        <v>0</v>
-      </c>
       <c r="J291" t="inlineStr">
         <is>
           <t>DIVERSAS COMARCAS - PRESTAÇÃO DE SERVIÇO TÉCNICO DE ENGENHARIA DE MEMÓRIA DE CÁLCULO DOS AJUSTES E COORDENOGRAMA DO RELÉ DE PROTEÇÃO SECUNDÁRIO PARA AS SUBESTAÇÕES</t>
@@ -25502,9 +24830,6 @@
       <c r="H292" t="n">
         <v>487</v>
       </c>
-      <c r="I292" t="n">
-        <v>0</v>
-      </c>
       <c r="J292" t="inlineStr">
         <is>
           <t>DIVERSAS COMARCAS - PROJETOS - CONSTRUÇÕES, AMPLI. E REF. - LOTE 1</t>
@@ -25588,9 +24913,6 @@
       <c r="H293" t="n">
         <v>488</v>
       </c>
-      <c r="I293" t="n">
-        <v>0</v>
-      </c>
       <c r="J293" t="inlineStr">
         <is>
           <t>DIVERSAS COMARCAS - PROJETOS - CONSTRUÇÕES, AMPLI. E REF. - LOTE 2</t>
@@ -25674,9 +24996,6 @@
       <c r="H294" t="n">
         <v>489</v>
       </c>
-      <c r="I294" t="n">
-        <v>0</v>
-      </c>
       <c r="J294" t="inlineStr">
         <is>
           <t>DIVERSAS COMARCAS - PROJETOS DIVERSOS</t>
@@ -25760,9 +25079,6 @@
       <c r="H295" t="n">
         <v>490</v>
       </c>
-      <c r="I295" t="n">
-        <v>0</v>
-      </c>
       <c r="J295" t="inlineStr">
         <is>
           <t>ITAÚNA - CONSTRUÇÃO NOVO FÓRUM PAD. P9 - RETOMADA DA OBRA</t>
@@ -25800,7 +25116,7 @@
         <v>0</v>
       </c>
       <c r="R295" t="n">
-        <v>11000000</v>
+        <v>25779347</v>
       </c>
       <c r="S295" t="n">
         <v>0</v>
@@ -25846,9 +25162,6 @@
       <c r="H296" t="n">
         <v>491</v>
       </c>
-      <c r="I296" t="n">
-        <v>0</v>
-      </c>
       <c r="J296" t="inlineStr">
         <is>
           <t>OBRA DE CONSTRUÇÃO DO PRÉDIO DO FÓRUM DIGITAL</t>
@@ -25932,9 +25245,6 @@
       <c r="H297" t="n">
         <v>492</v>
       </c>
-      <c r="I297" t="n">
-        <v>0</v>
-      </c>
       <c r="J297" t="inlineStr">
         <is>
           <t>REFORMA AR CONDICIONADO CENTRAL</t>
@@ -25972,7 +25282,7 @@
         <v>0</v>
       </c>
       <c r="R297" t="n">
-        <v>960229</v>
+        <v>455960</v>
       </c>
       <c r="S297" t="n">
         <v>0</v>
@@ -26018,9 +25328,6 @@
       <c r="H298" t="n">
         <v>493</v>
       </c>
-      <c r="I298" t="n">
-        <v>0</v>
-      </c>
       <c r="J298" t="inlineStr">
         <is>
           <t>OBRA DE CONSTRUÇÃO DO PRÉDIO DO FÓRUM DIGITAL</t>
@@ -26104,9 +25411,6 @@
       <c r="H299" t="n">
         <v>494</v>
       </c>
-      <c r="I299" t="n">
-        <v>0</v>
-      </c>
       <c r="J299" t="inlineStr">
         <is>
           <t>Execução da instalação de ar condicionado central no Fórum da Comarca de Passos, localizado na Avenida Arlindo Figueiredo, nº. 850, Jardim Continental, Passos/MG</t>
@@ -26144,7 +25448,7 @@
         <v>0</v>
       </c>
       <c r="R299" t="n">
-        <v>311324</v>
+        <v>2592985</v>
       </c>
       <c r="S299" t="n">
         <v>0</v>
@@ -27136,9 +26440,6 @@
       <c r="H311" t="n">
         <v>45</v>
       </c>
-      <c r="I311" t="n">
-        <v>0</v>
-      </c>
       <c r="J311" t="inlineStr">
         <is>
           <t>EXPOMINAS BH</t>
@@ -27222,9 +26523,6 @@
       <c r="H312" t="n">
         <v>46</v>
       </c>
-      <c r="I312" t="n">
-        <v>0</v>
-      </c>
       <c r="J312" t="inlineStr">
         <is>
           <t>OBRAS ARAXÁ</t>
@@ -27308,9 +26606,6 @@
       <c r="H313" t="n">
         <v>47</v>
       </c>
-      <c r="I313" t="n">
-        <v>0</v>
-      </c>
       <c r="J313" t="inlineStr">
         <is>
           <t>VERTEDOURO BALNEÁRIO ÁGUAS SANTAS - TIRADENTES/MG</t>
@@ -27394,9 +26689,6 @@
       <c r="H314" t="n">
         <v>48</v>
       </c>
-      <c r="I314" t="n">
-        <v>0</v>
-      </c>
       <c r="J314" t="inlineStr">
         <is>
           <t>ADEQUAÇÃO LICENCIAMENTO MINASCENTRO</t>
@@ -27480,9 +26772,6 @@
       <c r="H315" t="n">
         <v>49</v>
       </c>
-      <c r="I315" t="n">
-        <v>0</v>
-      </c>
       <c r="J315" t="inlineStr">
         <is>
           <t>CONSORCIOS E SERVIDORES</t>
@@ -27566,9 +26855,6 @@
       <c r="H316" t="n">
         <v>397</v>
       </c>
-      <c r="I316" t="n">
-        <v>0</v>
-      </c>
       <c r="J316" t="inlineStr">
         <is>
           <t>IMPLANTAÇÃO OU AMPLIAÇÃO REALIZADA EM SISTEMAS DE ABASTECIMENTO DE ÁGUA QUE PODEM CONTEMPLAR SISTEMA PRODUTOR QUE PODE SER ATRAVÉS DE POÇO PROFUNDO OU CAPTAÇÃO SUPERFICIAL, ESTAÇÃO DE TRATAMENTO DE ÁGUA, ADUTORAS, ESTAÇÕES ELEVATÓRIAS, RESERVATÓRIOS E REDES DE DISTRIBUIÇÃO DE ÁGUA PARA OPERAÇÃO DAS UNIDADES DE TRATAMENTO E DISTRIBUIÇÃO DE ÁGUA TRATADA EM LOCALIDADES QUE A COPASA TENHA OU VENHA A TER A CONCESSÃO PARA O SERVIÇO DE ABASTECIMENTO DE ÁGUA. IMPLANTAÇÃO OU AMPLIAÇÃO REALIZADA EM SISTEMAS DE ESGOTAMENTO SANITÁRIO QUE PODEM CONTEMPLAR ESTAÇÃO DE TRATAMENTO DE ESGOTO, ESTAÇÕES ELEVATÓRIAS, INTERCEPTORES E REDES COLETORAS PARA OPERAÇÃO DAS UNIDADES DE COLETA E TRATAMENTO DE ESGOTO EM LOCALIDADES QUE A COPASA TENHA OU VENHA A TER A CONCESSÃO PARA O SERVIÇO DE ESGOTAMENTO SANITÁRIO</t>
@@ -27652,9 +26938,6 @@
       <c r="H317" t="n">
         <v>498</v>
       </c>
-      <c r="I317" t="n">
-        <v>0</v>
-      </c>
       <c r="J317" t="inlineStr">
         <is>
           <t>AMPLIAÇÃO REALIZADA, OPERAÇÃO, MANUTENÇÃO E CONSERVAÇÃO DAS UNIDADES DE ADUÇÃO DO SISTEMA PRODUTOR RIO MANSO; REVERSÃO DOS ATIVOS À COMPANHIA DE SANEAMENTO DE MINAS GERAIS.</t>
@@ -27738,9 +27021,6 @@
       <c r="H318" t="n">
         <v>50</v>
       </c>
-      <c r="I318" t="n">
-        <v>0</v>
-      </c>
       <c r="J318" t="inlineStr">
         <is>
           <t>ELABORAÇÃO E EXECUÇÃO DE PROJETOS RELACIONADOS À REFORMA, MODERNIZAÇÃO E ADEQUAÇÃO DAS INSTALAÇÕES PREDIAIS DA COMPANHIA</t>
@@ -27824,9 +27104,6 @@
       <c r="H319" t="n">
         <v>495</v>
       </c>
-      <c r="I319" t="n">
-        <v>0</v>
-      </c>
       <c r="J319" t="inlineStr">
         <is>
           <t>EXPANSÃO DA INFRAESTRUTURA DE DISTRIBUIÇÃO DE GÁS NATURAL, EM GASODUTOS VIRTUAIS E PRIMÁRIOS, EM MINAS GERAIS.</t>
@@ -27910,9 +27187,6 @@
       <c r="H320" t="n">
         <v>21</v>
       </c>
-      <c r="I320" t="n">
-        <v>0</v>
-      </c>
       <c r="J320" t="inlineStr">
         <is>
           <t>EXPANSÃO E AQUISIÇÃO DO SISTEMA DE TRANSMISSÃO</t>
@@ -27996,9 +27270,6 @@
       <c r="H321" t="n">
         <v>22</v>
       </c>
-      <c r="I321" t="n">
-        <v>0</v>
-      </c>
       <c r="J321" t="inlineStr">
         <is>
           <t>EXPANSÃO E AQUISIÇÃO DO SISTEMA DE TRANSMISSÃO</t>
@@ -28082,9 +27353,6 @@
       <c r="H322" t="n">
         <v>23</v>
       </c>
-      <c r="I322" t="n">
-        <v>0</v>
-      </c>
       <c r="J322" t="inlineStr">
         <is>
           <t>EXPANSÃO E AQUISIÇÃO DO SISTEMA DE TRANSMISSÃO</t>
@@ -28168,9 +27436,6 @@
       <c r="H323" t="n">
         <v>24</v>
       </c>
-      <c r="I323" t="n">
-        <v>0</v>
-      </c>
       <c r="J323" t="inlineStr">
         <is>
           <t>EXPANSÃO E AQUISIÇÃO DO SISTEMA DE TRANSMISSÃO</t>
@@ -28254,9 +27519,6 @@
       <c r="H324" t="n">
         <v>25</v>
       </c>
-      <c r="I324" t="n">
-        <v>0</v>
-      </c>
       <c r="J324" t="inlineStr">
         <is>
           <t>EXPANSÃO E AQUISIÇÃO DO SISTEMA DE TRANSMISSÃO</t>
@@ -28340,9 +27602,6 @@
       <c r="H325" t="n">
         <v>26</v>
       </c>
-      <c r="I325" t="n">
-        <v>0</v>
-      </c>
       <c r="J325" t="inlineStr">
         <is>
           <t>EXPANSÃO E AQUISIÇÃO DO SISTEMA DE TRANSMISSÃO</t>
@@ -28426,9 +27685,6 @@
       <c r="H326" t="n">
         <v>27</v>
       </c>
-      <c r="I326" t="n">
-        <v>0</v>
-      </c>
       <c r="J326" t="inlineStr">
         <is>
           <t>EXPANSÃO E AQUISIÇÃO DO SISTEMA DE TRANSMISSÃO</t>
@@ -28512,9 +27768,6 @@
       <c r="H327" t="n">
         <v>28</v>
       </c>
-      <c r="I327" t="n">
-        <v>0</v>
-      </c>
       <c r="J327" t="inlineStr">
         <is>
           <t>EXPANSÃO E AQUISIÇÃO DO SISTEMA DE TRANSMISSÃO</t>
@@ -28598,9 +27851,6 @@
       <c r="H328" t="n">
         <v>29</v>
       </c>
-      <c r="I328" t="n">
-        <v>0</v>
-      </c>
       <c r="J328" t="inlineStr">
         <is>
           <t>EXPANSÃO E AQUISIÇÃO DO SISTEMA DE TRANSMISSÃO</t>
@@ -28684,9 +27934,6 @@
       <c r="H329" t="n">
         <v>30</v>
       </c>
-      <c r="I329" t="n">
-        <v>0</v>
-      </c>
       <c r="J329" t="inlineStr">
         <is>
           <t>REFORMAS DE SUBESTAÇÕES E LINHAS DE TRANSMISSÃO</t>
@@ -28770,9 +28017,6 @@
       <c r="H330" t="n">
         <v>31</v>
       </c>
-      <c r="I330" t="n">
-        <v>0</v>
-      </c>
       <c r="J330" t="inlineStr">
         <is>
           <t>REFORMAS DE SUBESTAÇÕES E LINHAS DE TRANSMISSÃO</t>
@@ -28856,9 +28100,6 @@
       <c r="H331" t="n">
         <v>32</v>
       </c>
-      <c r="I331" t="n">
-        <v>0</v>
-      </c>
       <c r="J331" t="inlineStr">
         <is>
           <t>REFORMAS DE SUBESTAÇÕES E LINHAS DE TRANSMISSÃO</t>
@@ -28942,9 +28183,6 @@
       <c r="H332" t="n">
         <v>33</v>
       </c>
-      <c r="I332" t="n">
-        <v>0</v>
-      </c>
       <c r="J332" t="inlineStr">
         <is>
           <t>REFORMAS DE SUBESTAÇÕES E LINHAS DE TRANSMISSÃO</t>
@@ -29028,9 +28266,6 @@
       <c r="H333" t="n">
         <v>34</v>
       </c>
-      <c r="I333" t="n">
-        <v>0</v>
-      </c>
       <c r="J333" t="inlineStr">
         <is>
           <t>REFORMAS DE SUBESTAÇÕES E LINHAS DE TRANSMISSÃO</t>
@@ -29114,9 +28349,6 @@
       <c r="H334" t="n">
         <v>35</v>
       </c>
-      <c r="I334" t="n">
-        <v>0</v>
-      </c>
       <c r="J334" t="inlineStr">
         <is>
           <t>REFORMAS DE SUBESTAÇÕES E LINHAS DE TRANSMISSÃO</t>
@@ -29200,9 +28432,6 @@
       <c r="H335" t="n">
         <v>36</v>
       </c>
-      <c r="I335" t="n">
-        <v>0</v>
-      </c>
       <c r="J335" t="inlineStr">
         <is>
           <t>REFORMAS DE SUBESTAÇÕES E LINHAS DE TRANSMISSÃO</t>
@@ -29286,9 +28515,6 @@
       <c r="H336" t="n">
         <v>37</v>
       </c>
-      <c r="I336" t="n">
-        <v>0</v>
-      </c>
       <c r="J336" t="inlineStr">
         <is>
           <t>REFORMAS DE SUBESTAÇÕES E LINHAS DE TRANSMISSÃO</t>
@@ -29372,9 +28598,6 @@
       <c r="H337" t="n">
         <v>38</v>
       </c>
-      <c r="I337" t="n">
-        <v>0</v>
-      </c>
       <c r="J337" t="inlineStr">
         <is>
           <t>REFORMAS DE SUBESTAÇÕES E LINHAS DE TRANSMISSÃO</t>
@@ -29458,9 +28681,6 @@
       <c r="H338" t="n">
         <v>39</v>
       </c>
-      <c r="I338" t="n">
-        <v>0</v>
-      </c>
       <c r="J338" t="inlineStr">
         <is>
           <t>REFORMAS DE SUBESTAÇÕES E LINHAS DE TRANSMISSÃO</t>
@@ -29544,9 +28764,6 @@
       <c r="H339" t="n">
         <v>40</v>
       </c>
-      <c r="I339" t="n">
-        <v>0</v>
-      </c>
       <c r="J339" t="inlineStr">
         <is>
           <t>REFORMAS DE SUBESTAÇÕES E LINHAS DE TRANSMISSÃO</t>
@@ -29630,9 +28847,6 @@
       <c r="H340" t="n">
         <v>41</v>
       </c>
-      <c r="I340" t="n">
-        <v>0</v>
-      </c>
       <c r="J340" t="inlineStr">
         <is>
           <t>REFORMAS DE SUBESTAÇÕES E LINHAS DE TRANSMISSÃO</t>
@@ -29716,9 +28930,6 @@
       <c r="H341" t="n">
         <v>42</v>
       </c>
-      <c r="I341" t="n">
-        <v>0</v>
-      </c>
       <c r="J341" t="inlineStr">
         <is>
           <t>EXPANSÃO DO SISTEMA DE GERAÇÃO</t>
@@ -29802,9 +29013,6 @@
       <c r="H342" t="n">
         <v>43</v>
       </c>
-      <c r="I342" t="n">
-        <v>0</v>
-      </c>
       <c r="J342" t="inlineStr">
         <is>
           <t>EXPANSÃO DO SISTEMA DE GERAÇÃO</t>
@@ -29888,9 +29096,6 @@
       <c r="H343" t="n">
         <v>7</v>
       </c>
-      <c r="I343" t="n">
-        <v>0</v>
-      </c>
       <c r="J343" t="inlineStr">
         <is>
           <t>EXECUÇÃO DO PLANO DE DESENVOLVIMENTO DA DISTRIBUIDORA (PDD)</t>
@@ -29974,9 +29179,6 @@
       <c r="H344" t="n">
         <v>8</v>
       </c>
-      <c r="I344" t="n">
-        <v>0</v>
-      </c>
       <c r="J344" t="inlineStr">
         <is>
           <t>EXECUÇÃO DO PLANO DE DESENVOLVIMENTO DA DISTRIBUIDORA (PDD)</t>
@@ -30060,9 +29262,6 @@
       <c r="H345" t="n">
         <v>9</v>
       </c>
-      <c r="I345" t="n">
-        <v>0</v>
-      </c>
       <c r="J345" t="inlineStr">
         <is>
           <t>EXECUÇÃO DO PLANO DE DESENVOLVIMENTO DA DISTRIBUIDORA (PDD)</t>
@@ -30146,9 +29345,6 @@
       <c r="H346" t="n">
         <v>10</v>
       </c>
-      <c r="I346" t="n">
-        <v>0</v>
-      </c>
       <c r="J346" t="inlineStr">
         <is>
           <t>EXECUÇÃO DO PLANO DE DESENVOLVIMENTO DA DISTRIBUIDORA (PDD)</t>
@@ -30232,9 +29428,6 @@
       <c r="H347" t="n">
         <v>11</v>
       </c>
-      <c r="I347" t="n">
-        <v>0</v>
-      </c>
       <c r="J347" t="inlineStr">
         <is>
           <t>EXECUÇÃO DO PLANO DE DESENVOLVIMENTO DA DISTRIBUIDORA (PDD)</t>
@@ -30318,9 +29511,6 @@
       <c r="H348" t="n">
         <v>12</v>
       </c>
-      <c r="I348" t="n">
-        <v>0</v>
-      </c>
       <c r="J348" t="inlineStr">
         <is>
           <t>EXECUÇÃO DO PLANO DE DESENVOLVIMENTO DA DISTRIBUIDORA (PDD)</t>
@@ -30404,9 +29594,6 @@
       <c r="H349" t="n">
         <v>13</v>
       </c>
-      <c r="I349" t="n">
-        <v>0</v>
-      </c>
       <c r="J349" t="inlineStr">
         <is>
           <t>EXECUÇÃO DO PLANO DE DESENVOLVIMENTO DA DISTRIBUIDORA (PDD)</t>
@@ -30490,9 +29677,6 @@
       <c r="H350" t="n">
         <v>14</v>
       </c>
-      <c r="I350" t="n">
-        <v>0</v>
-      </c>
       <c r="J350" t="inlineStr">
         <is>
           <t>EXECUÇÃO DO PLANO DE DESENVOLVIMENTO DA DISTRIBUIDORA (PDD)</t>
@@ -30576,9 +29760,6 @@
       <c r="H351" t="n">
         <v>15</v>
       </c>
-      <c r="I351" t="n">
-        <v>0</v>
-      </c>
       <c r="J351" t="inlineStr">
         <is>
           <t>EXECUÇÃO DO PLANO DE DESENVOLVIMENTO DA DISTRIBUIDORA (PDD)</t>
@@ -30662,9 +29843,6 @@
       <c r="H352" t="n">
         <v>16</v>
       </c>
-      <c r="I352" t="n">
-        <v>0</v>
-      </c>
       <c r="J352" t="inlineStr">
         <is>
           <t>EXECUÇÃO DO PLANO DE DESENVOLVIMENTO DA DISTRIBUIDORA (PDD)</t>
@@ -30748,9 +29926,6 @@
       <c r="H353" t="n">
         <v>17</v>
       </c>
-      <c r="I353" t="n">
-        <v>0</v>
-      </c>
       <c r="J353" t="inlineStr">
         <is>
           <t>EXECUÇÃO DO PLANO DE DESENVOLVIMENTO DA DISTRIBUIDORA (PDD)</t>
@@ -30834,9 +30009,6 @@
       <c r="H354" t="n">
         <v>18</v>
       </c>
-      <c r="I354" t="n">
-        <v>0</v>
-      </c>
       <c r="J354" t="inlineStr">
         <is>
           <t>EXECUÇÃO DO PLANO DE DESENVOLVIMENTO DA DISTRIBUIDORA (PDD)</t>
@@ -30920,9 +30092,6 @@
       <c r="H355" t="n">
         <v>19</v>
       </c>
-      <c r="I355" t="n">
-        <v>0</v>
-      </c>
       <c r="J355" t="inlineStr">
         <is>
           <t>EXECUÇÃO DO PLANO DE DESENVOLVIMENTO DA DISTRIBUIDORA (PDD)</t>
@@ -31006,9 +30175,6 @@
       <c r="H356" t="n">
         <v>20</v>
       </c>
-      <c r="I356" t="n">
-        <v>0</v>
-      </c>
       <c r="J356" t="inlineStr">
         <is>
           <t>EXECUÇÃO DO PLANO DE DESENVOLVIMENTO DA DISTRIBUIDORA (PDD)</t>
@@ -31091,9 +30257,6 @@
       </c>
       <c r="H357" t="n">
         <v>393</v>
-      </c>
-      <c r="I357" t="n">
-        <v>0</v>
       </c>
       <c r="J357" t="inlineStr">
         <is>

--- a/bancos/SISOR/BASE_DETALHAMENTO_OBRAS.xlsx
+++ b/bancos/SISOR/BASE_DETALHAMENTO_OBRAS.xlsx
@@ -13253,19 +13253,19 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>2321</v>
+        <v>2311</v>
       </c>
       <c r="B155" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C155" t="n">
-        <v>302</v>
+        <v>363</v>
       </c>
       <c r="D155" t="n">
-        <v>87</v>
+        <v>7</v>
       </c>
       <c r="E155" t="n">
-        <v>4222</v>
+        <v>4006</v>
       </c>
       <c r="F155" t="n">
         <v>1</v>
@@ -13274,11 +13274,11 @@
         <v>0</v>
       </c>
       <c r="H155" t="n">
-        <v>113</v>
+        <v>71</v>
       </c>
       <c r="J155" t="inlineStr">
         <is>
-          <t>Execução de reforma da unidade de Ituiutaba</t>
+          <t>Construção de escolas em atendimento ao Plano de Ações Articuladas PAR na cidade de Unaí-MG</t>
         </is>
       </c>
       <c r="K155" t="inlineStr">
@@ -13288,32 +13288,32 @@
       </c>
       <c r="L155" t="inlineStr">
         <is>
-          <t>UNIDADE</t>
+          <t>ALUNO</t>
         </is>
       </c>
       <c r="M155" t="n">
-        <v>1</v>
+        <v>560</v>
       </c>
       <c r="N155" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="O155" t="inlineStr">
         <is>
-          <t>Região Intermediária de Uberlândia</t>
+          <t>Região Intermediária de Patos de Minas</t>
         </is>
       </c>
       <c r="P155" t="inlineStr">
         <is>
-          <t>ITUIUTABA</t>
+          <t>UNAÍ</t>
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>80539</v>
+        <v>0</v>
       </c>
       <c r="R155" t="n">
-        <v>309171</v>
+        <v>7311390</v>
       </c>
       <c r="S155" t="n">
         <v>0</v>
@@ -13357,16 +13357,16 @@
         <v>0</v>
       </c>
       <c r="H156" t="n">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="J156" t="inlineStr">
         <is>
-          <t>CONSTRUCAO DO HEMONUCLEO DE PONTE NOVA</t>
+          <t>Execução de reforma da unidade de Ituiutaba</t>
         </is>
       </c>
       <c r="K156" t="inlineStr">
         <is>
-          <t>EXECUÇÃO</t>
+          <t>INICIANDO</t>
         </is>
       </c>
       <c r="L156" t="inlineStr">
@@ -13384,19 +13384,19 @@
       </c>
       <c r="O156" t="inlineStr">
         <is>
-          <t>Região Intermediária de Juíz de Fora</t>
+          <t>Região Intermediária de Uberlândia</t>
         </is>
       </c>
       <c r="P156" t="inlineStr">
         <is>
-          <t>PONTE NOVA</t>
+          <t>ITUIUTABA</t>
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>5214112</v>
+        <v>80539</v>
       </c>
       <c r="R156" t="n">
-        <v>3180000</v>
+        <v>309171</v>
       </c>
       <c r="S156" t="n">
         <v>0</v>
@@ -13440,16 +13440,16 @@
         <v>0</v>
       </c>
       <c r="H157" t="n">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="J157" t="inlineStr">
         <is>
-          <t>REFORMA DE UNIDADE DE ATENÇÃO ESPECIALIZADA EM SAÚDE</t>
+          <t>CONSTRUCAO DO HEMONUCLEO DE PONTE NOVA</t>
         </is>
       </c>
       <c r="K157" t="inlineStr">
         <is>
-          <t>INICIANDO</t>
+          <t>EXECUÇÃO</t>
         </is>
       </c>
       <c r="L157" t="inlineStr">
@@ -13467,19 +13467,19 @@
       </c>
       <c r="O157" t="inlineStr">
         <is>
-          <t>Região Intermediária de Uberlândia</t>
+          <t>Região Intermediária de Juíz de Fora</t>
         </is>
       </c>
       <c r="P157" t="inlineStr">
         <is>
-          <t>UBERLÂNDIA</t>
+          <t>PONTE NOVA</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>0</v>
+        <v>5214112</v>
       </c>
       <c r="R157" t="n">
-        <v>501382</v>
+        <v>3180000</v>
       </c>
       <c r="S157" t="n">
         <v>0</v>
@@ -13502,19 +13502,19 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>2361</v>
+        <v>2321</v>
       </c>
       <c r="B158" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C158" t="n">
-        <v>274</v>
+        <v>302</v>
       </c>
       <c r="D158" t="n">
-        <v>767</v>
+        <v>87</v>
       </c>
       <c r="E158" t="n">
-        <v>2114</v>
+        <v>4222</v>
       </c>
       <c r="F158" t="n">
         <v>1</v>
@@ -13523,81 +13523,81 @@
         <v>0</v>
       </c>
       <c r="H158" t="n">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="J158" t="inlineStr">
         <is>
-          <t>REFORMA DA NOVA SEDE</t>
+          <t>REFORMA DE UNIDADE DE ATENÇÃO ESPECIALIZADA EM SAÚDE</t>
         </is>
       </c>
       <c r="K158" t="inlineStr">
         <is>
-          <t>EXECUÇÃO</t>
+          <t>INICIANDO</t>
         </is>
       </c>
       <c r="L158" t="inlineStr">
         <is>
-          <t>R$ MIL</t>
+          <t>UNIDADE</t>
         </is>
       </c>
       <c r="M158" t="n">
-        <v>2850</v>
+        <v>1</v>
       </c>
       <c r="N158" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="O158" t="inlineStr">
         <is>
-          <t>Região Intermediária de Belo Horizonte</t>
+          <t>Região Intermediária de Uberlândia</t>
         </is>
       </c>
       <c r="P158" t="inlineStr">
         <is>
-          <t>BELO HORIZONTE</t>
+          <t>UBERLÂNDIA</t>
         </is>
       </c>
       <c r="Q158" t="n">
         <v>0</v>
       </c>
       <c r="R158" t="n">
-        <v>4754406</v>
+        <v>501382</v>
       </c>
       <c r="S158" t="n">
         <v>0</v>
       </c>
       <c r="T158" t="n">
-        <v>4754406</v>
+        <v>0</v>
       </c>
       <c r="U158" t="n">
         <v>0</v>
       </c>
       <c r="V158" t="n">
-        <v>4754406</v>
+        <v>0</v>
       </c>
       <c r="W158" t="n">
         <v>0</v>
       </c>
       <c r="X158" t="n">
-        <v>4754406</v>
+        <v>0</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>3051</v>
+        <v>2321</v>
       </c>
       <c r="B159" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C159" t="n">
-        <v>364</v>
+        <v>302</v>
       </c>
       <c r="D159" t="n">
-        <v>15</v>
+        <v>87</v>
       </c>
       <c r="E159" t="n">
-        <v>4016</v>
+        <v>4222</v>
       </c>
       <c r="F159" t="n">
         <v>1</v>
@@ -13606,11 +13606,11 @@
         <v>0</v>
       </c>
       <c r="H159" t="n">
-        <v>99</v>
+        <v>119</v>
       </c>
       <c r="J159" t="inlineStr">
         <is>
-          <t>CONSTRUÇÃO E MODIFICAÇÕES NECESSÁRIAS À MANUTENÇÃO DA ATIVIDADE DE ENSINO SUPERIOR EM AGROPECUÁRIA DE PRECISÃO.</t>
+          <t>Pojetos executivos para várias unidades da Fundação Hemominas</t>
         </is>
       </c>
       <c r="K159" t="inlineStr">
@@ -13624,7 +13624,7 @@
         </is>
       </c>
       <c r="M159" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="N159" t="inlineStr">
         <is>
@@ -13633,16 +13633,16 @@
       </c>
       <c r="O159" t="inlineStr">
         <is>
-          <t>Região Intermediária de Divinópolis</t>
+          <t>Região Intermediária de Belo Horizonte</t>
         </is>
       </c>
       <c r="P159" t="inlineStr">
         <is>
-          <t>PITANGUI</t>
+          <t>BELO HORIZONTE</t>
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>8293093</v>
+        <v>4517798</v>
       </c>
       <c r="R159" t="n">
         <v>0</v>
@@ -13668,19 +13668,19 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>3051</v>
+        <v>2361</v>
       </c>
       <c r="B160" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C160" t="n">
-        <v>364</v>
+        <v>274</v>
       </c>
       <c r="D160" t="n">
-        <v>15</v>
+        <v>767</v>
       </c>
       <c r="E160" t="n">
-        <v>4016</v>
+        <v>2114</v>
       </c>
       <c r="F160" t="n">
         <v>1</v>
@@ -13689,64 +13689,64 @@
         <v>0</v>
       </c>
       <c r="H160" t="n">
-        <v>100</v>
+        <v>125</v>
       </c>
       <c r="J160" t="inlineStr">
         <is>
-          <t>CONSTRUÇÃO E MODIFICAÇÕES NECESSÁRIAS À MANUTENÇÃO DA ATIVIDADE DE ENSINO SUPERIOR EM LATICÍNIOS.</t>
+          <t>REFORMA DA NOVA SEDE</t>
         </is>
       </c>
       <c r="K160" t="inlineStr">
         <is>
-          <t>INICIANDO</t>
+          <t>EXECUÇÃO</t>
         </is>
       </c>
       <c r="L160" t="inlineStr">
         <is>
-          <t>UNIDADE</t>
+          <t>R$ MIL</t>
         </is>
       </c>
       <c r="M160" t="n">
-        <v>1</v>
+        <v>2850</v>
       </c>
       <c r="N160" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="O160" t="inlineStr">
         <is>
-          <t>Região Intermediária de Juíz de Fora</t>
+          <t>Região Intermediária de Belo Horizonte</t>
         </is>
       </c>
       <c r="P160" t="inlineStr">
         <is>
-          <t>JUIZ DE FORA</t>
+          <t>BELO HORIZONTE</t>
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>1418986</v>
+        <v>0</v>
       </c>
       <c r="R160" t="n">
-        <v>0</v>
+        <v>4754406</v>
       </c>
       <c r="S160" t="n">
         <v>0</v>
       </c>
       <c r="T160" t="n">
-        <v>0</v>
+        <v>4754406</v>
       </c>
       <c r="U160" t="n">
         <v>0</v>
       </c>
       <c r="V160" t="n">
-        <v>0</v>
+        <v>4754406</v>
       </c>
       <c r="W160" t="n">
         <v>0</v>
       </c>
       <c r="X160" t="n">
-        <v>0</v>
+        <v>4754406</v>
       </c>
     </row>
     <row r="161">
@@ -13754,16 +13754,16 @@
         <v>3051</v>
       </c>
       <c r="B161" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="C161" t="n">
-        <v>571</v>
+        <v>364</v>
       </c>
       <c r="D161" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E161" t="n">
-        <v>4018</v>
+        <v>4016</v>
       </c>
       <c r="F161" t="n">
         <v>1</v>
@@ -13772,11 +13772,11 @@
         <v>0</v>
       </c>
       <c r="H161" t="n">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="J161" t="inlineStr">
         <is>
-          <t>INVESTIMENTO EM MELHORIAS DA INFRAESTUTURA DE PESQUISA AGROPECUÁRIA.</t>
+          <t>CONSTRUÇÃO E MODIFICAÇÕES NECESSÁRIAS À MANUTENÇÃO DA ATIVIDADE DE ENSINO SUPERIOR EM AGROPECUÁRIA DE PRECISÃO.</t>
         </is>
       </c>
       <c r="K161" t="inlineStr">
@@ -13799,19 +13799,19 @@
       </c>
       <c r="O161" t="inlineStr">
         <is>
-          <t>Região Intermediária de Belo Horizonte</t>
+          <t>Região Intermediária de Divinópolis</t>
         </is>
       </c>
       <c r="P161" t="inlineStr">
         <is>
-          <t>BELO HORIZONTE</t>
+          <t>PITANGUI</t>
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>0</v>
+        <v>8293093</v>
       </c>
       <c r="R161" t="n">
-        <v>1365100</v>
+        <v>0</v>
       </c>
       <c r="S161" t="n">
         <v>0</v>
@@ -13837,16 +13837,16 @@
         <v>3051</v>
       </c>
       <c r="B162" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="C162" t="n">
-        <v>571</v>
+        <v>364</v>
       </c>
       <c r="D162" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E162" t="n">
-        <v>4018</v>
+        <v>4016</v>
       </c>
       <c r="F162" t="n">
         <v>1</v>
@@ -13855,11 +13855,11 @@
         <v>0</v>
       </c>
       <c r="H162" t="n">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="J162" t="inlineStr">
         <is>
-          <t>INVESTIMENTO EM MELHORIAS DA INFRAESTUTURA DE PESQUISA AGROPECUÁRIA.</t>
+          <t>CONSTRUÇÃO E MODIFICAÇÕES NECESSÁRIAS À MANUTENÇÃO DA ATIVIDADE DE ENSINO SUPERIOR EM LATICÍNIOS.</t>
         </is>
       </c>
       <c r="K162" t="inlineStr">
@@ -13882,19 +13882,19 @@
       </c>
       <c r="O162" t="inlineStr">
         <is>
-          <t>Região Intermediária de Pouso Alegre</t>
+          <t>Região Intermediária de Juíz de Fora</t>
         </is>
       </c>
       <c r="P162" t="inlineStr">
         <is>
-          <t>MARIA DA FÉ</t>
+          <t>JUIZ DE FORA</t>
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>0</v>
+        <v>1418986</v>
       </c>
       <c r="R162" t="n">
-        <v>393453</v>
+        <v>0</v>
       </c>
       <c r="S162" t="n">
         <v>0</v>
@@ -13938,7 +13938,7 @@
         <v>0</v>
       </c>
       <c r="H163" t="n">
-        <v>104</v>
+        <v>77</v>
       </c>
       <c r="J163" t="inlineStr">
         <is>
@@ -13965,19 +13965,19 @@
       </c>
       <c r="O163" t="inlineStr">
         <is>
-          <t>Região Intermediária de Pouso Alegre</t>
+          <t>Região Intermediária de Belo Horizonte</t>
         </is>
       </c>
       <c r="P163" t="inlineStr">
         <is>
-          <t>CALDAS</t>
+          <t>BELO HORIZONTE</t>
         </is>
       </c>
       <c r="Q163" t="n">
         <v>0</v>
       </c>
       <c r="R163" t="n">
-        <v>1362002</v>
+        <v>1365100</v>
       </c>
       <c r="S163" t="n">
         <v>0</v>
@@ -14000,19 +14000,19 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>4031</v>
+        <v>3051</v>
       </c>
       <c r="B164" t="n">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="C164" t="n">
-        <v>61</v>
+        <v>571</v>
       </c>
       <c r="D164" t="n">
-        <v>706</v>
+        <v>16</v>
       </c>
       <c r="E164" t="n">
-        <v>2091</v>
+        <v>4018</v>
       </c>
       <c r="F164" t="n">
         <v>1</v>
@@ -14021,16 +14021,16 @@
         <v>0</v>
       </c>
       <c r="H164" t="n">
-        <v>338</v>
+        <v>103</v>
       </c>
       <c r="J164" t="inlineStr">
         <is>
-          <t>Construção do novo prédio do Fórum da Comarca de Areado/MG</t>
+          <t>INVESTIMENTO EM MELHORIAS DA INFRAESTUTURA DE PESQUISA AGROPECUÁRIA.</t>
         </is>
       </c>
       <c r="K164" t="inlineStr">
         <is>
-          <t>EXECUÇÃO</t>
+          <t>INICIANDO</t>
         </is>
       </c>
       <c r="L164" t="inlineStr">
@@ -14048,19 +14048,19 @@
       </c>
       <c r="O164" t="inlineStr">
         <is>
-          <t>Região Intermediária de Varginha</t>
+          <t>Região Intermediária de Pouso Alegre</t>
         </is>
       </c>
       <c r="P164" t="inlineStr">
         <is>
-          <t>AREADO</t>
+          <t>MARIA DA FÉ</t>
         </is>
       </c>
       <c r="Q164" t="n">
         <v>0</v>
       </c>
       <c r="R164" t="n">
-        <v>5956080</v>
+        <v>393453</v>
       </c>
       <c r="S164" t="n">
         <v>0</v>
@@ -14083,19 +14083,19 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>4031</v>
+        <v>3051</v>
       </c>
       <c r="B165" t="n">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="C165" t="n">
-        <v>61</v>
+        <v>571</v>
       </c>
       <c r="D165" t="n">
-        <v>706</v>
+        <v>16</v>
       </c>
       <c r="E165" t="n">
-        <v>2091</v>
+        <v>4018</v>
       </c>
       <c r="F165" t="n">
         <v>1</v>
@@ -14104,16 +14104,16 @@
         <v>0</v>
       </c>
       <c r="H165" t="n">
-        <v>341</v>
+        <v>104</v>
       </c>
       <c r="J165" t="inlineStr">
         <is>
-          <t>Obra de construção do novo Fórum da Comarca de Andrelândia/MG.</t>
+          <t>INVESTIMENTO EM MELHORIAS DA INFRAESTUTURA DE PESQUISA AGROPECUÁRIA.</t>
         </is>
       </c>
       <c r="K165" t="inlineStr">
         <is>
-          <t>EXECUÇÃO</t>
+          <t>INICIANDO</t>
         </is>
       </c>
       <c r="L165" t="inlineStr">
@@ -14131,19 +14131,19 @@
       </c>
       <c r="O165" t="inlineStr">
         <is>
-          <t>Região Intermediária de Juíz de Fora</t>
+          <t>Região Intermediária de Pouso Alegre</t>
         </is>
       </c>
       <c r="P165" t="inlineStr">
         <is>
-          <t>ANDRELÂNDIA</t>
+          <t>CALDAS</t>
         </is>
       </c>
       <c r="Q165" t="n">
         <v>0</v>
       </c>
       <c r="R165" t="n">
-        <v>6243895</v>
+        <v>1362002</v>
       </c>
       <c r="S165" t="n">
         <v>0</v>
@@ -14187,11 +14187,11 @@
         <v>0</v>
       </c>
       <c r="H166" t="n">
-        <v>343</v>
+        <v>338</v>
       </c>
       <c r="J166" t="inlineStr">
         <is>
-          <t>Contrato a retomada da obra de construção do novo prédio do Fórum da Comarca de Barbacena/MG</t>
+          <t>Construção do novo prédio do Fórum da Comarca de Areado/MG</t>
         </is>
       </c>
       <c r="K166" t="inlineStr">
@@ -14214,19 +14214,19 @@
       </c>
       <c r="O166" t="inlineStr">
         <is>
-          <t>Região Intermediária de Barbacena</t>
+          <t>Região Intermediária de Varginha</t>
         </is>
       </c>
       <c r="P166" t="inlineStr">
         <is>
-          <t>BARBACENA</t>
+          <t>AREADO</t>
         </is>
       </c>
       <c r="Q166" t="n">
         <v>0</v>
       </c>
       <c r="R166" t="n">
-        <v>29647771</v>
+        <v>5956080</v>
       </c>
       <c r="S166" t="n">
         <v>0</v>
@@ -14270,11 +14270,11 @@
         <v>0</v>
       </c>
       <c r="H167" t="n">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="J167" t="inlineStr">
         <is>
-          <t>Construção do novo prédio do Fórum da Comarca de Betim/MG</t>
+          <t>Obra de construção do novo Fórum da Comarca de Andrelândia/MG.</t>
         </is>
       </c>
       <c r="K167" t="inlineStr">
@@ -14288,34 +14288,34 @@
         </is>
       </c>
       <c r="M167" t="n">
-        <v>28</v>
+        <v>1</v>
       </c>
       <c r="N167" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="O167" t="inlineStr">
         <is>
-          <t>Região Intermediária de Belo Horizonte</t>
+          <t>Região Intermediária de Juíz de Fora</t>
         </is>
       </c>
       <c r="P167" t="inlineStr">
         <is>
-          <t>BETIM</t>
+          <t>ANDRELÂNDIA</t>
         </is>
       </c>
       <c r="Q167" t="n">
         <v>0</v>
       </c>
       <c r="R167" t="n">
-        <v>29086632</v>
+        <v>6243895</v>
       </c>
       <c r="S167" t="n">
         <v>0</v>
       </c>
       <c r="T167" t="n">
-        <v>37354991</v>
+        <v>0</v>
       </c>
       <c r="U167" t="n">
         <v>0</v>
@@ -14353,11 +14353,11 @@
         <v>0</v>
       </c>
       <c r="H168" t="n">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="J168" t="inlineStr">
         <is>
-          <t>Reforma geral do Fórum Lafayette, em Belo Horizonte/MG</t>
+          <t>Contrato a retomada da obra de construção do novo prédio do Fórum da Comarca de Barbacena/MG</t>
         </is>
       </c>
       <c r="K168" t="inlineStr">
@@ -14380,25 +14380,25 @@
       </c>
       <c r="O168" t="inlineStr">
         <is>
-          <t>Região Intermediária de Belo Horizonte</t>
+          <t>Região Intermediária de Barbacena</t>
         </is>
       </c>
       <c r="P168" t="inlineStr">
         <is>
-          <t>BELO HORIZONTE</t>
+          <t>BARBACENA</t>
         </is>
       </c>
       <c r="Q168" t="n">
         <v>0</v>
       </c>
       <c r="R168" t="n">
-        <v>60595200</v>
+        <v>29647771</v>
       </c>
       <c r="S168" t="n">
         <v>0</v>
       </c>
       <c r="T168" t="n">
-        <v>28524747</v>
+        <v>0</v>
       </c>
       <c r="U168" t="n">
         <v>0</v>
@@ -14436,11 +14436,11 @@
         <v>0</v>
       </c>
       <c r="H169" t="n">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="J169" t="inlineStr">
         <is>
-          <t>Obra de restauração e adaptação predial do Palácio da Justiça, localizado na Avenida Afonso Pena, nº. 1.420, Centro, Belo Horizonte/MG</t>
+          <t>Construção do novo prédio do Fórum da Comarca de Betim/MG</t>
         </is>
       </c>
       <c r="K169" t="inlineStr">
@@ -14450,15 +14450,15 @@
       </c>
       <c r="L169" t="inlineStr">
         <is>
-          <t>PORCENTAGEM DE OBRA REALIZADA</t>
+          <t>UNIDADE</t>
         </is>
       </c>
       <c r="M169" t="n">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="N169" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="O169" t="inlineStr">
@@ -14468,20 +14468,20 @@
       </c>
       <c r="P169" t="inlineStr">
         <is>
-          <t>BELO HORIZONTE</t>
+          <t>BETIM</t>
         </is>
       </c>
       <c r="Q169" t="n">
         <v>0</v>
       </c>
       <c r="R169" t="n">
-        <v>15713441</v>
+        <v>29086632</v>
       </c>
       <c r="S169" t="n">
         <v>0</v>
       </c>
       <c r="T169" t="n">
-        <v>0</v>
+        <v>37354991</v>
       </c>
       <c r="U169" t="n">
         <v>0</v>
@@ -14519,11 +14519,11 @@
         <v>0</v>
       </c>
       <c r="H170" t="n">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="J170" t="inlineStr">
         <is>
-          <t>Construção do novo prédio do Fórum da Comarca de Camanducaia/MG</t>
+          <t>Reforma geral do Fórum Lafayette, em Belo Horizonte/MG</t>
         </is>
       </c>
       <c r="K170" t="inlineStr">
@@ -14546,25 +14546,25 @@
       </c>
       <c r="O170" t="inlineStr">
         <is>
-          <t>Região Intermediária de Pouso Alegre</t>
+          <t>Região Intermediária de Belo Horizonte</t>
         </is>
       </c>
       <c r="P170" t="inlineStr">
         <is>
-          <t>CAMANDUCAIA</t>
+          <t>BELO HORIZONTE</t>
         </is>
       </c>
       <c r="Q170" t="n">
         <v>0</v>
       </c>
       <c r="R170" t="n">
-        <v>6371627</v>
+        <v>60595200</v>
       </c>
       <c r="S170" t="n">
         <v>0</v>
       </c>
       <c r="T170" t="n">
-        <v>0</v>
+        <v>28524747</v>
       </c>
       <c r="U170" t="n">
         <v>0</v>
@@ -14602,11 +14602,11 @@
         <v>0</v>
       </c>
       <c r="H171" t="n">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="J171" t="inlineStr">
         <is>
-          <t>Contrato a construção do novo prédio do Fórum da Comarca de Coração de Jesus</t>
+          <t>Obra de restauração e adaptação predial do Palácio da Justiça, localizado na Avenida Afonso Pena, nº. 1.420, Centro, Belo Horizonte/MG</t>
         </is>
       </c>
       <c r="K171" t="inlineStr">
@@ -14616,11 +14616,11 @@
       </c>
       <c r="L171" t="inlineStr">
         <is>
-          <t>UNIDADE</t>
+          <t>PORCENTAGEM DE OBRA REALIZADA</t>
         </is>
       </c>
       <c r="M171" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="N171" t="inlineStr">
         <is>
@@ -14629,19 +14629,19 @@
       </c>
       <c r="O171" t="inlineStr">
         <is>
-          <t>Região Intermediária de Montes Claros</t>
+          <t>Região Intermediária de Belo Horizonte</t>
         </is>
       </c>
       <c r="P171" t="inlineStr">
         <is>
-          <t>CORAÇÃO DE JESUS</t>
+          <t>BELO HORIZONTE</t>
         </is>
       </c>
       <c r="Q171" t="n">
         <v>0</v>
       </c>
       <c r="R171" t="n">
-        <v>4888187</v>
+        <v>15713441</v>
       </c>
       <c r="S171" t="n">
         <v>0</v>
@@ -14685,11 +14685,11 @@
         <v>0</v>
       </c>
       <c r="H172" t="n">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="J172" t="inlineStr">
         <is>
-          <t>Construção do novo prédio do Fórum da Comarca de Governador Valadares</t>
+          <t>Construção do novo prédio do Fórum da Comarca de Camanducaia/MG</t>
         </is>
       </c>
       <c r="K172" t="inlineStr">
@@ -14712,19 +14712,19 @@
       </c>
       <c r="O172" t="inlineStr">
         <is>
-          <t>Região Intermediária de Governador Valadares</t>
+          <t>Região Intermediária de Pouso Alegre</t>
         </is>
       </c>
       <c r="P172" t="inlineStr">
         <is>
-          <t>GOVERNADOR VALADARES</t>
+          <t>CAMANDUCAIA</t>
         </is>
       </c>
       <c r="Q172" t="n">
         <v>0</v>
       </c>
       <c r="R172" t="n">
-        <v>30556619</v>
+        <v>6371627</v>
       </c>
       <c r="S172" t="n">
         <v>0</v>
@@ -14768,11 +14768,11 @@
         <v>0</v>
       </c>
       <c r="H173" t="n">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="J173" t="inlineStr">
         <is>
-          <t>Contrato a construção do novo prédio do Fórum da Comarca de Guarani/MG</t>
+          <t>Contrato a construção do novo prédio do Fórum da Comarca de Coração de Jesus</t>
         </is>
       </c>
       <c r="K173" t="inlineStr">
@@ -14795,19 +14795,19 @@
       </c>
       <c r="O173" t="inlineStr">
         <is>
-          <t>Região Intermediária de Juíz de Fora</t>
+          <t>Região Intermediária de Montes Claros</t>
         </is>
       </c>
       <c r="P173" t="inlineStr">
         <is>
-          <t>GUARANI</t>
+          <t>CORAÇÃO DE JESUS</t>
         </is>
       </c>
       <c r="Q173" t="n">
         <v>0</v>
       </c>
       <c r="R173" t="n">
-        <v>1413076</v>
+        <v>4888187</v>
       </c>
       <c r="S173" t="n">
         <v>0</v>
@@ -14851,11 +14851,11 @@
         <v>0</v>
       </c>
       <c r="H174" t="n">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="J174" t="inlineStr">
         <is>
-          <t>Contrato a retomada da construção do novo Fórum da Comarca de Ibirité/MG</t>
+          <t>Construção do novo prédio do Fórum da Comarca de Governador Valadares</t>
         </is>
       </c>
       <c r="K174" t="inlineStr">
@@ -14878,19 +14878,19 @@
       </c>
       <c r="O174" t="inlineStr">
         <is>
-          <t>Região Intermediária de Belo Horizonte</t>
+          <t>Região Intermediária de Governador Valadares</t>
         </is>
       </c>
       <c r="P174" t="inlineStr">
         <is>
-          <t>IBIRITÉ</t>
+          <t>GOVERNADOR VALADARES</t>
         </is>
       </c>
       <c r="Q174" t="n">
         <v>0</v>
       </c>
       <c r="R174" t="n">
-        <v>12445680</v>
+        <v>30556619</v>
       </c>
       <c r="S174" t="n">
         <v>0</v>
@@ -14934,11 +14934,11 @@
         <v>0</v>
       </c>
       <c r="H175" t="n">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="J175" t="inlineStr">
         <is>
-          <t>Contrato a execução de obras de reforma e ampliação do Fórum da Comarca de Igarapé/MG</t>
+          <t>Contrato a construção do novo prédio do Fórum da Comarca de Guarani/MG</t>
         </is>
       </c>
       <c r="K175" t="inlineStr">
@@ -14961,19 +14961,19 @@
       </c>
       <c r="O175" t="inlineStr">
         <is>
-          <t>Região Intermediária de Belo Horizonte</t>
+          <t>Região Intermediária de Juíz de Fora</t>
         </is>
       </c>
       <c r="P175" t="inlineStr">
         <is>
-          <t>IGARAPÉ</t>
+          <t>GUARANI</t>
         </is>
       </c>
       <c r="Q175" t="n">
         <v>0</v>
       </c>
       <c r="R175" t="n">
-        <v>8883525</v>
+        <v>1413076</v>
       </c>
       <c r="S175" t="n">
         <v>0</v>
@@ -15017,11 +15017,11 @@
         <v>0</v>
       </c>
       <c r="H176" t="n">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="J176" t="inlineStr">
         <is>
-          <t>Reforma e ampliação do Fórum da Comarca de Ipanema/MG</t>
+          <t>Contrato a retomada da construção do novo Fórum da Comarca de Ibirité/MG</t>
         </is>
       </c>
       <c r="K176" t="inlineStr">
@@ -15044,19 +15044,19 @@
       </c>
       <c r="O176" t="inlineStr">
         <is>
-          <t>Região Intermediária de Juíz de Fora</t>
+          <t>Região Intermediária de Belo Horizonte</t>
         </is>
       </c>
       <c r="P176" t="inlineStr">
         <is>
-          <t>IPANEMA</t>
+          <t>IBIRITÉ</t>
         </is>
       </c>
       <c r="Q176" t="n">
         <v>0</v>
       </c>
       <c r="R176" t="n">
-        <v>2893112</v>
+        <v>12445680</v>
       </c>
       <c r="S176" t="n">
         <v>0</v>
@@ -15100,11 +15100,11 @@
         <v>0</v>
       </c>
       <c r="H177" t="n">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="J177" t="inlineStr">
         <is>
-          <t>Contrato a execução da obra de reforma e ampliação do Fórum da Comarca de Ipatinga/MG</t>
+          <t>Contrato a execução de obras de reforma e ampliação do Fórum da Comarca de Igarapé/MG</t>
         </is>
       </c>
       <c r="K177" t="inlineStr">
@@ -15114,11 +15114,11 @@
       </c>
       <c r="L177" t="inlineStr">
         <is>
-          <t>PORCENTAGEM DE OBRA REALIZADA</t>
+          <t>UNIDADE</t>
         </is>
       </c>
       <c r="M177" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="N177" t="inlineStr">
         <is>
@@ -15127,19 +15127,19 @@
       </c>
       <c r="O177" t="inlineStr">
         <is>
-          <t>Região Intermediária de Ipatinga</t>
+          <t>Região Intermediária de Belo Horizonte</t>
         </is>
       </c>
       <c r="P177" t="inlineStr">
         <is>
-          <t>IPATINGA</t>
+          <t>IGARAPÉ</t>
         </is>
       </c>
       <c r="Q177" t="n">
         <v>0</v>
       </c>
       <c r="R177" t="n">
-        <v>23154808</v>
+        <v>8883525</v>
       </c>
       <c r="S177" t="n">
         <v>0</v>
@@ -15183,11 +15183,11 @@
         <v>0</v>
       </c>
       <c r="H178" t="n">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="J178" t="inlineStr">
         <is>
-          <t>Obra de construção do novo prédio do Fórum da Comarca de Juiz de Fora.</t>
+          <t>Reforma e ampliação do Fórum da Comarca de Ipanema/MG</t>
         </is>
       </c>
       <c r="K178" t="inlineStr">
@@ -15197,11 +15197,11 @@
       </c>
       <c r="L178" t="inlineStr">
         <is>
-          <t>PORCENTAGEM DE OBRA REALIZADA</t>
+          <t>UNIDADE</t>
         </is>
       </c>
       <c r="M178" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="N178" t="inlineStr">
         <is>
@@ -15215,20 +15215,20 @@
       </c>
       <c r="P178" t="inlineStr">
         <is>
-          <t>JUIZ DE FORA</t>
+          <t>IPANEMA</t>
         </is>
       </c>
       <c r="Q178" t="n">
         <v>0</v>
       </c>
       <c r="R178" t="n">
-        <v>13277349</v>
+        <v>2893112</v>
       </c>
       <c r="S178" t="n">
         <v>0</v>
       </c>
       <c r="T178" t="n">
-        <v>10000000</v>
+        <v>0</v>
       </c>
       <c r="U178" t="n">
         <v>0</v>
@@ -15266,11 +15266,11 @@
         <v>0</v>
       </c>
       <c r="H179" t="n">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="J179" t="inlineStr">
         <is>
-          <t>Retomada da construção do novo Fórum da Comarca de Mateus Leme/</t>
+          <t>Contrato a execução da obra de reforma e ampliação do Fórum da Comarca de Ipatinga/MG</t>
         </is>
       </c>
       <c r="K179" t="inlineStr">
@@ -15280,11 +15280,11 @@
       </c>
       <c r="L179" t="inlineStr">
         <is>
-          <t>UNIDADE</t>
+          <t>PORCENTAGEM DE OBRA REALIZADA</t>
         </is>
       </c>
       <c r="M179" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="N179" t="inlineStr">
         <is>
@@ -15293,19 +15293,19 @@
       </c>
       <c r="O179" t="inlineStr">
         <is>
-          <t>Região Intermediária de Belo Horizonte</t>
+          <t>Região Intermediária de Ipatinga</t>
         </is>
       </c>
       <c r="P179" t="inlineStr">
         <is>
-          <t>MATEUS LEME</t>
+          <t>IPATINGA</t>
         </is>
       </c>
       <c r="Q179" t="n">
         <v>0</v>
       </c>
       <c r="R179" t="n">
-        <v>2635417</v>
+        <v>23154808</v>
       </c>
       <c r="S179" t="n">
         <v>0</v>
@@ -15349,11 +15349,11 @@
         <v>0</v>
       </c>
       <c r="H180" t="n">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="J180" t="inlineStr">
         <is>
-          <t>Contrato a retomada da construção do novo prédio do Fórum da Comarca de Minas Novas/MG</t>
+          <t>Obra de construção do novo prédio do Fórum da Comarca de Juiz de Fora.</t>
         </is>
       </c>
       <c r="K180" t="inlineStr">
@@ -15363,11 +15363,11 @@
       </c>
       <c r="L180" t="inlineStr">
         <is>
-          <t>UNIDADE</t>
+          <t>PORCENTAGEM DE OBRA REALIZADA</t>
         </is>
       </c>
       <c r="M180" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="N180" t="inlineStr">
         <is>
@@ -15376,25 +15376,25 @@
       </c>
       <c r="O180" t="inlineStr">
         <is>
-          <t>Região Intermediária de Teófilo Otoni</t>
+          <t>Região Intermediária de Juíz de Fora</t>
         </is>
       </c>
       <c r="P180" t="inlineStr">
         <is>
-          <t>MINAS NOVAS</t>
+          <t>JUIZ DE FORA</t>
         </is>
       </c>
       <c r="Q180" t="n">
         <v>0</v>
       </c>
       <c r="R180" t="n">
-        <v>2460571</v>
+        <v>13277349</v>
       </c>
       <c r="S180" t="n">
         <v>0</v>
       </c>
       <c r="T180" t="n">
-        <v>0</v>
+        <v>10000000</v>
       </c>
       <c r="U180" t="n">
         <v>0</v>
@@ -15432,11 +15432,11 @@
         <v>0</v>
       </c>
       <c r="H181" t="n">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="J181" t="inlineStr">
         <is>
-          <t>Obra de construção do novo Fórum da Comarca de Montalvânia/MG.</t>
+          <t>Retomada da construção do novo Fórum da Comarca de Mateus Leme/</t>
         </is>
       </c>
       <c r="K181" t="inlineStr">
@@ -15459,19 +15459,19 @@
       </c>
       <c r="O181" t="inlineStr">
         <is>
-          <t>Região Intermediária de Montes Claros</t>
+          <t>Região Intermediária de Belo Horizonte</t>
         </is>
       </c>
       <c r="P181" t="inlineStr">
         <is>
-          <t>MONTALVÂNIA</t>
+          <t>MATEUS LEME</t>
         </is>
       </c>
       <c r="Q181" t="n">
         <v>0</v>
       </c>
       <c r="R181" t="n">
-        <v>4384188</v>
+        <v>2635417</v>
       </c>
       <c r="S181" t="n">
         <v>0</v>
@@ -15515,11 +15515,11 @@
         <v>0</v>
       </c>
       <c r="H182" t="n">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="J182" t="inlineStr">
         <is>
-          <t>Reforma e Ampliação do Fórum da Comarca de Monte Belo/MG</t>
+          <t>Contrato a retomada da construção do novo prédio do Fórum da Comarca de Minas Novas/MG</t>
         </is>
       </c>
       <c r="K182" t="inlineStr">
@@ -15529,11 +15529,11 @@
       </c>
       <c r="L182" t="inlineStr">
         <is>
-          <t>PORCENTAGEM DE OBRA REALIZADA</t>
+          <t>UNIDADE</t>
         </is>
       </c>
       <c r="M182" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="N182" t="inlineStr">
         <is>
@@ -15542,25 +15542,25 @@
       </c>
       <c r="O182" t="inlineStr">
         <is>
-          <t>Região Intermediária de Varginha</t>
+          <t>Região Intermediária de Teófilo Otoni</t>
         </is>
       </c>
       <c r="P182" t="inlineStr">
         <is>
-          <t>MONTE BELO</t>
+          <t>MINAS NOVAS</t>
         </is>
       </c>
       <c r="Q182" t="n">
         <v>0</v>
       </c>
       <c r="R182" t="n">
-        <v>3521927</v>
+        <v>2460571</v>
       </c>
       <c r="S182" t="n">
         <v>0</v>
       </c>
       <c r="T182" t="n">
-        <v>3380482</v>
+        <v>0</v>
       </c>
       <c r="U182" t="n">
         <v>0</v>
@@ -15598,11 +15598,11 @@
         <v>0</v>
       </c>
       <c r="H183" t="n">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="J183" t="inlineStr">
         <is>
-          <t>Contrato a construção do novo prédio do Fórum da Comarca de Palma/MG</t>
+          <t>Obra de construção do novo Fórum da Comarca de Montalvânia/MG.</t>
         </is>
       </c>
       <c r="K183" t="inlineStr">
@@ -15625,19 +15625,19 @@
       </c>
       <c r="O183" t="inlineStr">
         <is>
-          <t>Região Intermediária de Juíz de Fora</t>
+          <t>Região Intermediária de Montes Claros</t>
         </is>
       </c>
       <c r="P183" t="inlineStr">
         <is>
-          <t>PALMA</t>
+          <t>MONTALVÂNIA</t>
         </is>
       </c>
       <c r="Q183" t="n">
         <v>0</v>
       </c>
       <c r="R183" t="n">
-        <v>926947</v>
+        <v>4384188</v>
       </c>
       <c r="S183" t="n">
         <v>0</v>
@@ -15681,11 +15681,11 @@
         <v>0</v>
       </c>
       <c r="H184" t="n">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="J184" t="inlineStr">
         <is>
-          <t>Construção do novo prédio do Fórum da Comarca de Pitangui/MG</t>
+          <t>Reforma e Ampliação do Fórum da Comarca de Monte Belo/MG</t>
         </is>
       </c>
       <c r="K184" t="inlineStr">
@@ -15695,11 +15695,11 @@
       </c>
       <c r="L184" t="inlineStr">
         <is>
-          <t>UNIDADE</t>
+          <t>PORCENTAGEM DE OBRA REALIZADA</t>
         </is>
       </c>
       <c r="M184" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="N184" t="inlineStr">
         <is>
@@ -15708,25 +15708,25 @@
       </c>
       <c r="O184" t="inlineStr">
         <is>
-          <t>Região Intermediária de Divinópolis</t>
+          <t>Região Intermediária de Varginha</t>
         </is>
       </c>
       <c r="P184" t="inlineStr">
         <is>
-          <t>PITANGUI</t>
+          <t>MONTE BELO</t>
         </is>
       </c>
       <c r="Q184" t="n">
         <v>0</v>
       </c>
       <c r="R184" t="n">
-        <v>6438640</v>
+        <v>3521927</v>
       </c>
       <c r="S184" t="n">
         <v>0</v>
       </c>
       <c r="T184" t="n">
-        <v>0</v>
+        <v>3380482</v>
       </c>
       <c r="U184" t="n">
         <v>0</v>
@@ -15764,11 +15764,11 @@
         <v>0</v>
       </c>
       <c r="H185" t="n">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="J185" t="inlineStr">
         <is>
-          <t>Contrato a obra de reforma e ampliação do Fórum da Comarca de Teófilo Otoni/MG</t>
+          <t>Contrato a construção do novo prédio do Fórum da Comarca de Palma/MG</t>
         </is>
       </c>
       <c r="K185" t="inlineStr">
@@ -15791,19 +15791,19 @@
       </c>
       <c r="O185" t="inlineStr">
         <is>
-          <t>Região Intermediária de Teófilo Otoni</t>
+          <t>Região Intermediária de Juíz de Fora</t>
         </is>
       </c>
       <c r="P185" t="inlineStr">
         <is>
-          <t>TEÓFILO OTONI</t>
+          <t>PALMA</t>
         </is>
       </c>
       <c r="Q185" t="n">
         <v>0</v>
       </c>
       <c r="R185" t="n">
-        <v>1785448</v>
+        <v>926947</v>
       </c>
       <c r="S185" t="n">
         <v>0</v>
@@ -15847,11 +15847,11 @@
         <v>0</v>
       </c>
       <c r="H186" t="n">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="J186" t="inlineStr">
         <is>
-          <t>Contrato a execução de obras de construção do novo prédio do Fórum da Comarca de Vespasiano/MG</t>
+          <t>Construção do novo prédio do Fórum da Comarca de Pitangui/MG</t>
         </is>
       </c>
       <c r="K186" t="inlineStr">
@@ -15874,19 +15874,19 @@
       </c>
       <c r="O186" t="inlineStr">
         <is>
-          <t>Região Intermediária de Belo Horizonte</t>
+          <t>Região Intermediária de Divinópolis</t>
         </is>
       </c>
       <c r="P186" t="inlineStr">
         <is>
-          <t>VESPASIANO</t>
+          <t>PITANGUI</t>
         </is>
       </c>
       <c r="Q186" t="n">
         <v>0</v>
       </c>
       <c r="R186" t="n">
-        <v>11774850</v>
+        <v>6438640</v>
       </c>
       <c r="S186" t="n">
         <v>0</v>
@@ -15930,11 +15930,11 @@
         <v>0</v>
       </c>
       <c r="H187" t="n">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="J187" t="inlineStr">
         <is>
-          <t>Modernização de quatro elevadores (ANEXO I)</t>
+          <t>Contrato a obra de reforma e ampliação do Fórum da Comarca de Teófilo Otoni/MG</t>
         </is>
       </c>
       <c r="K187" t="inlineStr">
@@ -15944,11 +15944,11 @@
       </c>
       <c r="L187" t="inlineStr">
         <is>
-          <t>PORCENTAGEM DE OBRA REALIZADA</t>
+          <t>UNIDADE</t>
         </is>
       </c>
       <c r="M187" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="N187" t="inlineStr">
         <is>
@@ -15957,19 +15957,19 @@
       </c>
       <c r="O187" t="inlineStr">
         <is>
-          <t>Região Intermediária de Belo Horizonte</t>
+          <t>Região Intermediária de Teófilo Otoni</t>
         </is>
       </c>
       <c r="P187" t="inlineStr">
         <is>
-          <t>BELO HORIZONTE</t>
+          <t>TEÓFILO OTONI</t>
         </is>
       </c>
       <c r="Q187" t="n">
         <v>0</v>
       </c>
       <c r="R187" t="n">
-        <v>516930</v>
+        <v>1785448</v>
       </c>
       <c r="S187" t="n">
         <v>0</v>
@@ -16013,11 +16013,11 @@
         <v>0</v>
       </c>
       <c r="H188" t="n">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="J188" t="inlineStr">
         <is>
-          <t>Modernização de três elevadores JESP CONSUMO – R. PADRE ROLIM, Nº 424 / BELO HZTE</t>
+          <t>Contrato a execução de obras de construção do novo prédio do Fórum da Comarca de Vespasiano/MG</t>
         </is>
       </c>
       <c r="K188" t="inlineStr">
@@ -16027,11 +16027,11 @@
       </c>
       <c r="L188" t="inlineStr">
         <is>
-          <t>PORCENTAGEM DE OBRA REALIZADA</t>
+          <t>UNIDADE</t>
         </is>
       </c>
       <c r="M188" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="N188" t="inlineStr">
         <is>
@@ -16045,14 +16045,14 @@
       </c>
       <c r="P188" t="inlineStr">
         <is>
-          <t>BELO HORIZONTE</t>
+          <t>VESPASIANO</t>
         </is>
       </c>
       <c r="Q188" t="n">
         <v>0</v>
       </c>
       <c r="R188" t="n">
-        <v>330410</v>
+        <v>11774850</v>
       </c>
       <c r="S188" t="n">
         <v>0</v>
@@ -16096,11 +16096,11 @@
         <v>0</v>
       </c>
       <c r="H189" t="n">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="J189" t="inlineStr">
         <is>
-          <t>Sistema de Modernização Audiovisual dos Plenários do Edifício Sede e Edifício Francisco Sales do Tribunal de Justiça de Minas Gerais.</t>
+          <t>Modernização de quatro elevadores (ANEXO I)</t>
         </is>
       </c>
       <c r="K189" t="inlineStr">
@@ -16135,7 +16135,7 @@
         <v>0</v>
       </c>
       <c r="R189" t="n">
-        <v>173128</v>
+        <v>516930</v>
       </c>
       <c r="S189" t="n">
         <v>0</v>
@@ -16179,11 +16179,11 @@
         <v>0</v>
       </c>
       <c r="H190" t="n">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="J190" t="inlineStr">
         <is>
-          <t>Prestação de serviço técnico especializado de avaliação de conformidade do projeto estrutural de reforma e ampliação do Edifício Sede do TRIBUNAL, localizado em Belo Horizonte/MG</t>
+          <t>Modernização de três elevadores JESP CONSUMO – R. PADRE ROLIM, Nº 424 / BELO HZTE</t>
         </is>
       </c>
       <c r="K190" t="inlineStr">
@@ -16218,7 +16218,7 @@
         <v>0</v>
       </c>
       <c r="R190" t="n">
-        <v>65000</v>
+        <v>330410</v>
       </c>
       <c r="S190" t="n">
         <v>0</v>
@@ -16262,11 +16262,11 @@
         <v>0</v>
       </c>
       <c r="H191" t="n">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="J191" t="inlineStr">
         <is>
-          <t>Serviço técnico profissional especializado de elaboração de projetos para construções, ampliações e/ou reformas de edificações do TRIBUNAL em diversas comarcas.</t>
+          <t>Sistema de Modernização Audiovisual dos Plenários do Edifício Sede e Edifício Francisco Sales do Tribunal de Justiça de Minas Gerais.</t>
         </is>
       </c>
       <c r="K191" t="inlineStr">
@@ -16289,31 +16289,31 @@
       </c>
       <c r="O191" t="inlineStr">
         <is>
-          <t>Estadual</t>
+          <t>Região Intermediária de Belo Horizonte</t>
         </is>
       </c>
       <c r="P191" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
+          <t>BELO HORIZONTE</t>
         </is>
       </c>
       <c r="Q191" t="n">
         <v>0</v>
       </c>
       <c r="R191" t="n">
-        <v>2224014</v>
+        <v>173128</v>
       </c>
       <c r="S191" t="n">
         <v>0</v>
       </c>
       <c r="T191" t="n">
-        <v>2224014</v>
+        <v>0</v>
       </c>
       <c r="U191" t="n">
         <v>0</v>
       </c>
       <c r="V191" t="n">
-        <v>1297341</v>
+        <v>0</v>
       </c>
       <c r="W191" t="n">
         <v>0</v>
@@ -16345,11 +16345,11 @@
         <v>0</v>
       </c>
       <c r="H192" t="n">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="J192" t="inlineStr">
         <is>
-          <t>Prestação de serviço técnico de engenharia de memória de cálculo dos ajustes e coordenograma do relé de proteção secundário para subestações.</t>
+          <t>Prestação de serviço técnico especializado de avaliação de conformidade do projeto estrutural de reforma e ampliação do Edifício Sede do TRIBUNAL, localizado em Belo Horizonte/MG</t>
         </is>
       </c>
       <c r="K192" t="inlineStr">
@@ -16372,19 +16372,19 @@
       </c>
       <c r="O192" t="inlineStr">
         <is>
-          <t>Estadual</t>
+          <t>Região Intermediária de Belo Horizonte</t>
         </is>
       </c>
       <c r="P192" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
+          <t>BELO HORIZONTE</t>
         </is>
       </c>
       <c r="Q192" t="n">
         <v>0</v>
       </c>
       <c r="R192" t="n">
-        <v>80526</v>
+        <v>65000</v>
       </c>
       <c r="S192" t="n">
         <v>0</v>
@@ -16428,11 +16428,11 @@
         <v>0</v>
       </c>
       <c r="H193" t="n">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="J193" t="inlineStr">
         <is>
-          <t>prestação de serviço por empresa de engenharia especializada para a elaboração de estudo, projeto executivo, fornecimento, instalação, comissionamento, monitoramento, assistência técnica em garantia e manutenção de sistemas de geração de energia fotovoltaica em diversas edificações ocupadas pelo TJ.</t>
+          <t>Serviço técnico profissional especializado de elaboração de projetos para construções, ampliações e/ou reformas de edificações do TRIBUNAL em diversas comarcas.</t>
         </is>
       </c>
       <c r="K193" t="inlineStr">
@@ -16467,19 +16467,19 @@
         <v>0</v>
       </c>
       <c r="R193" t="n">
-        <v>1502849</v>
+        <v>2224014</v>
       </c>
       <c r="S193" t="n">
         <v>0</v>
       </c>
       <c r="T193" t="n">
-        <v>0</v>
+        <v>2224014</v>
       </c>
       <c r="U193" t="n">
         <v>0</v>
       </c>
       <c r="V193" t="n">
-        <v>0</v>
+        <v>1297341</v>
       </c>
       <c r="W193" t="n">
         <v>0</v>
@@ -16511,11 +16511,11 @@
         <v>0</v>
       </c>
       <c r="H194" t="n">
-        <v>373</v>
+        <v>369</v>
       </c>
       <c r="J194" t="inlineStr">
         <is>
-          <t>Execução da retomada da obra de reforma e ampliação da edificação do Fórum da Comarca de Cachoeira de Minas/MG.</t>
+          <t>Prestação de serviço técnico de engenharia de memória de cálculo dos ajustes e coordenograma do relé de proteção secundário para subestações.</t>
         </is>
       </c>
       <c r="K194" t="inlineStr">
@@ -16525,11 +16525,11 @@
       </c>
       <c r="L194" t="inlineStr">
         <is>
-          <t>UNIDADE</t>
+          <t>PORCENTAGEM DE OBRA REALIZADA</t>
         </is>
       </c>
       <c r="M194" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="N194" t="inlineStr">
         <is>
@@ -16538,19 +16538,19 @@
       </c>
       <c r="O194" t="inlineStr">
         <is>
-          <t>Região Intermediária de Pouso Alegre</t>
+          <t>Estadual</t>
         </is>
       </c>
       <c r="P194" t="inlineStr">
         <is>
-          <t>CACHOEIRA DE MINAS</t>
+          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
         </is>
       </c>
       <c r="Q194" t="n">
         <v>0</v>
       </c>
       <c r="R194" t="n">
-        <v>1983976</v>
+        <v>80526</v>
       </c>
       <c r="S194" t="n">
         <v>0</v>
@@ -16594,25 +16594,25 @@
         <v>0</v>
       </c>
       <c r="H195" t="n">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="J195" t="inlineStr">
         <is>
-          <t>Obra de construção do novo Fórum da Comarca de Salinas/MG</t>
+          <t>prestação de serviço por empresa de engenharia especializada para a elaboração de estudo, projeto executivo, fornecimento, instalação, comissionamento, monitoramento, assistência técnica em garantia e manutenção de sistemas de geração de energia fotovoltaica em diversas edificações ocupadas pelo TJ.</t>
         </is>
       </c>
       <c r="K195" t="inlineStr">
         <is>
-          <t>INICIANDO</t>
+          <t>EXECUÇÃO</t>
         </is>
       </c>
       <c r="L195" t="inlineStr">
         <is>
-          <t>UNIDADE</t>
+          <t>PORCENTAGEM DE OBRA REALIZADA</t>
         </is>
       </c>
       <c r="M195" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="N195" t="inlineStr">
         <is>
@@ -16621,19 +16621,19 @@
       </c>
       <c r="O195" t="inlineStr">
         <is>
-          <t>Região Intermediária de Montes Claros</t>
+          <t>Estadual</t>
         </is>
       </c>
       <c r="P195" t="inlineStr">
         <is>
-          <t>SALINAS</t>
+          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
         </is>
       </c>
       <c r="Q195" t="n">
         <v>0</v>
       </c>
       <c r="R195" t="n">
-        <v>11685801</v>
+        <v>1502849</v>
       </c>
       <c r="S195" t="n">
         <v>0</v>
@@ -16677,16 +16677,16 @@
         <v>0</v>
       </c>
       <c r="H196" t="n">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="J196" t="inlineStr">
         <is>
-          <t>Construção do novo prédio do Fórum da Comarca de Campina Verde/MG</t>
+          <t>Execução da retomada da obra de reforma e ampliação da edificação do Fórum da Comarca de Cachoeira de Minas/MG.</t>
         </is>
       </c>
       <c r="K196" t="inlineStr">
         <is>
-          <t>INICIANDO</t>
+          <t>EXECUÇÃO</t>
         </is>
       </c>
       <c r="L196" t="inlineStr">
@@ -16704,19 +16704,19 @@
       </c>
       <c r="O196" t="inlineStr">
         <is>
-          <t>Região Intermediária de Uberlândia</t>
+          <t>Região Intermediária de Pouso Alegre</t>
         </is>
       </c>
       <c r="P196" t="inlineStr">
         <is>
-          <t>CAMPINA VERDE</t>
+          <t>CACHOEIRA DE MINAS</t>
         </is>
       </c>
       <c r="Q196" t="n">
         <v>0</v>
       </c>
       <c r="R196" t="n">
-        <v>7474450</v>
+        <v>1983976</v>
       </c>
       <c r="S196" t="n">
         <v>0</v>
@@ -16760,11 +16760,11 @@
         <v>0</v>
       </c>
       <c r="H197" t="n">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="J197" t="inlineStr">
         <is>
-          <t>Construção do novo prédio do Fórum da Comarca de Caldas/MG</t>
+          <t>Obra de construção do novo Fórum da Comarca de Salinas/MG</t>
         </is>
       </c>
       <c r="K197" t="inlineStr">
@@ -16787,19 +16787,19 @@
       </c>
       <c r="O197" t="inlineStr">
         <is>
-          <t>Região Intermediária de Pouso Alegre</t>
+          <t>Região Intermediária de Montes Claros</t>
         </is>
       </c>
       <c r="P197" t="inlineStr">
         <is>
-          <t>CALDAS</t>
+          <t>SALINAS</t>
         </is>
       </c>
       <c r="Q197" t="n">
         <v>0</v>
       </c>
       <c r="R197" t="n">
-        <v>7474540</v>
+        <v>11685801</v>
       </c>
       <c r="S197" t="n">
         <v>0</v>
@@ -16843,11 +16843,11 @@
         <v>0</v>
       </c>
       <c r="H198" t="n">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="J198" t="inlineStr">
         <is>
-          <t>Reforma parcial do Fórum da Comarca de Itamonte/MG.</t>
+          <t>Construção do novo prédio do Fórum da Comarca de Campina Verde/MG</t>
         </is>
       </c>
       <c r="K198" t="inlineStr">
@@ -16870,19 +16870,19 @@
       </c>
       <c r="O198" t="inlineStr">
         <is>
-          <t>Região Intermediária de Pouso Alegre</t>
+          <t>Região Intermediária de Uberlândia</t>
         </is>
       </c>
       <c r="P198" t="inlineStr">
         <is>
-          <t>ITAMONTE</t>
+          <t>CAMPINA VERDE</t>
         </is>
       </c>
       <c r="Q198" t="n">
         <v>0</v>
       </c>
       <c r="R198" t="n">
-        <v>980282</v>
+        <v>7474450</v>
       </c>
       <c r="S198" t="n">
         <v>0</v>
@@ -16926,11 +16926,11 @@
         <v>0</v>
       </c>
       <c r="H199" t="n">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="J199" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada para verificação de conformidade e emissão de parecer relativo ao projeto de esquadrias na obra de Reforma do Fórum Lafayette</t>
+          <t>Construção do novo prédio do Fórum da Comarca de Caldas/MG</t>
         </is>
       </c>
       <c r="K199" t="inlineStr">
@@ -16940,11 +16940,11 @@
       </c>
       <c r="L199" t="inlineStr">
         <is>
-          <t>PORCENTAGEM DE OBRA REALIZADA</t>
+          <t>UNIDADE</t>
         </is>
       </c>
       <c r="M199" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="N199" t="inlineStr">
         <is>
@@ -16953,19 +16953,19 @@
       </c>
       <c r="O199" t="inlineStr">
         <is>
-          <t>Região Intermediária de Belo Horizonte</t>
+          <t>Região Intermediária de Pouso Alegre</t>
         </is>
       </c>
       <c r="P199" t="inlineStr">
         <is>
-          <t>BELO HORIZONTE</t>
+          <t>CALDAS</t>
         </is>
       </c>
       <c r="Q199" t="n">
         <v>0</v>
       </c>
       <c r="R199" t="n">
-        <v>2781</v>
+        <v>7474540</v>
       </c>
       <c r="S199" t="n">
         <v>0</v>
@@ -17009,16 +17009,16 @@
         <v>0</v>
       </c>
       <c r="H200" t="n">
-        <v>391</v>
+        <v>378</v>
       </c>
       <c r="J200" t="inlineStr">
         <is>
-          <t>Prestação de serviço técnico-profissional especializado de elaboração de projetos executivos, especificação técnica, orçamento e planejamento para ampliação do edifício sede do TRIBUNAL</t>
+          <t>Reforma parcial do Fórum da Comarca de Itamonte/MG.</t>
         </is>
       </c>
       <c r="K200" t="inlineStr">
         <is>
-          <t>EXECUÇÃO</t>
+          <t>INICIANDO</t>
         </is>
       </c>
       <c r="L200" t="inlineStr">
@@ -17027,7 +17027,7 @@
         </is>
       </c>
       <c r="M200" t="n">
-        <v>28</v>
+        <v>1</v>
       </c>
       <c r="N200" t="inlineStr">
         <is>
@@ -17036,19 +17036,19 @@
       </c>
       <c r="O200" t="inlineStr">
         <is>
-          <t>Região Intermediária de Belo Horizonte</t>
+          <t>Região Intermediária de Pouso Alegre</t>
         </is>
       </c>
       <c r="P200" t="inlineStr">
         <is>
-          <t>BELO HORIZONTE</t>
+          <t>ITAMONTE</t>
         </is>
       </c>
       <c r="Q200" t="n">
         <v>0</v>
       </c>
       <c r="R200" t="n">
-        <v>261742</v>
+        <v>980282</v>
       </c>
       <c r="S200" t="n">
         <v>0</v>
@@ -17092,16 +17092,16 @@
         <v>0</v>
       </c>
       <c r="H201" t="n">
-        <v>392</v>
+        <v>379</v>
       </c>
       <c r="J201" t="inlineStr">
         <is>
-          <t>Elaboração de projetos para construções, ampliações e / ou reformas de edificações do Tribunal em diversas comarcas</t>
+          <t>Contratação de empresa especializada para verificação de conformidade e emissão de parecer relativo ao projeto de esquadrias na obra de Reforma do Fórum Lafayette</t>
         </is>
       </c>
       <c r="K201" t="inlineStr">
         <is>
-          <t>EXECUÇÃO</t>
+          <t>INICIANDO</t>
         </is>
       </c>
       <c r="L201" t="inlineStr">
@@ -17119,19 +17119,19 @@
       </c>
       <c r="O201" t="inlineStr">
         <is>
-          <t>Estadual</t>
+          <t>Região Intermediária de Belo Horizonte</t>
         </is>
       </c>
       <c r="P201" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
+          <t>BELO HORIZONTE</t>
         </is>
       </c>
       <c r="Q201" t="n">
         <v>0</v>
       </c>
       <c r="R201" t="n">
-        <v>574526</v>
+        <v>2781</v>
       </c>
       <c r="S201" t="n">
         <v>0</v>
@@ -17175,7 +17175,7 @@
         <v>0</v>
       </c>
       <c r="H202" t="n">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="J202" t="inlineStr">
         <is>
@@ -17189,11 +17189,11 @@
       </c>
       <c r="L202" t="inlineStr">
         <is>
-          <t>PORCENTAGEM DE OBRA REALIZADA</t>
+          <t>UNIDADE</t>
         </is>
       </c>
       <c r="M202" t="n">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="N202" t="inlineStr">
         <is>
@@ -17214,7 +17214,7 @@
         <v>0</v>
       </c>
       <c r="R202" t="n">
-        <v>290056</v>
+        <v>261742</v>
       </c>
       <c r="S202" t="n">
         <v>0</v>
@@ -17258,11 +17258,11 @@
         <v>0</v>
       </c>
       <c r="H203" t="n">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="J203" t="inlineStr">
         <is>
-          <t>elaboração de projetos estruturais desuperestrutura, fundação (mesoestrutura e infraestrutura)e demais elementos estruturais necessários à implantação de uma edificação.</t>
+          <t>Elaboração de projetos para construções, ampliações e / ou reformas de edificações do Tribunal em diversas comarcas</t>
         </is>
       </c>
       <c r="K203" t="inlineStr">
@@ -17297,7 +17297,7 @@
         <v>0</v>
       </c>
       <c r="R203" t="n">
-        <v>23383</v>
+        <v>574526</v>
       </c>
       <c r="S203" t="n">
         <v>0</v>
@@ -17341,16 +17341,16 @@
         <v>0</v>
       </c>
       <c r="H204" t="n">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="J204" t="inlineStr">
         <is>
-          <t>BH EJEF - REFORMA GERAL</t>
+          <t>Prestação de serviço técnico-profissional especializado de elaboração de projetos executivos, especificação técnica, orçamento e planejamento para ampliação do edifício sede do TRIBUNAL</t>
         </is>
       </c>
       <c r="K204" t="inlineStr">
         <is>
-          <t>INICIANDO</t>
+          <t>EXECUÇÃO</t>
         </is>
       </c>
       <c r="L204" t="inlineStr">
@@ -17380,7 +17380,7 @@
         <v>0</v>
       </c>
       <c r="R204" t="n">
-        <v>24949508</v>
+        <v>290056</v>
       </c>
       <c r="S204" t="n">
         <v>0</v>
@@ -17424,16 +17424,16 @@
         <v>0</v>
       </c>
       <c r="H205" t="n">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="J205" t="inlineStr">
         <is>
-          <t>BH CEOP MURO</t>
+          <t>elaboração de projetos estruturais desuperestrutura, fundação (mesoestrutura e infraestrutura)e demais elementos estruturais necessários à implantação de uma edificação.</t>
         </is>
       </c>
       <c r="K205" t="inlineStr">
         <is>
-          <t>INICIANDO</t>
+          <t>EXECUÇÃO</t>
         </is>
       </c>
       <c r="L205" t="inlineStr">
@@ -17451,19 +17451,19 @@
       </c>
       <c r="O205" t="inlineStr">
         <is>
-          <t>Região Intermediária de Belo Horizonte</t>
+          <t>Estadual</t>
         </is>
       </c>
       <c r="P205" t="inlineStr">
         <is>
-          <t>BELO HORIZONTE</t>
+          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
         </is>
       </c>
       <c r="Q205" t="n">
         <v>0</v>
       </c>
       <c r="R205" t="n">
-        <v>225405</v>
+        <v>23383</v>
       </c>
       <c r="S205" t="n">
         <v>0</v>
@@ -17507,16 +17507,16 @@
         <v>0</v>
       </c>
       <c r="H206" t="n">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="J206" t="inlineStr">
         <is>
-          <t>ITAJUBÁ - CONSTRUÇÃO NOVO FÓRUM</t>
+          <t>BH EJEF - REFORMA GERAL</t>
         </is>
       </c>
       <c r="K206" t="inlineStr">
         <is>
-          <t>EXECUÇÃO</t>
+          <t>INICIANDO</t>
         </is>
       </c>
       <c r="L206" t="inlineStr">
@@ -17534,19 +17534,19 @@
       </c>
       <c r="O206" t="inlineStr">
         <is>
-          <t>Região Intermediária de Pouso Alegre</t>
+          <t>Região Intermediária de Belo Horizonte</t>
         </is>
       </c>
       <c r="P206" t="inlineStr">
         <is>
-          <t>ITAJUBÁ</t>
+          <t>BELO HORIZONTE</t>
         </is>
       </c>
       <c r="Q206" t="n">
         <v>0</v>
       </c>
       <c r="R206" t="n">
-        <v>4564282</v>
+        <v>24949508</v>
       </c>
       <c r="S206" t="n">
         <v>0</v>
@@ -17590,16 +17590,16 @@
         <v>0</v>
       </c>
       <c r="H207" t="n">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="J207" t="inlineStr">
         <is>
-          <t>ITAÚNA - CONSTRUÇÃO NOVO FÓRUM PAD. P9 - RETOMADA DA OBRA</t>
+          <t>BH CEOP MURO</t>
         </is>
       </c>
       <c r="K207" t="inlineStr">
         <is>
-          <t>EXECUÇÃO</t>
+          <t>INICIANDO</t>
         </is>
       </c>
       <c r="L207" t="inlineStr">
@@ -17617,19 +17617,19 @@
       </c>
       <c r="O207" t="inlineStr">
         <is>
-          <t>Região Intermediária de Divinópolis</t>
+          <t>Região Intermediária de Belo Horizonte</t>
         </is>
       </c>
       <c r="P207" t="inlineStr">
         <is>
-          <t>ITAÚNA</t>
+          <t>BELO HORIZONTE</t>
         </is>
       </c>
       <c r="Q207" t="n">
         <v>0</v>
       </c>
       <c r="R207" t="n">
-        <v>14223089</v>
+        <v>225405</v>
       </c>
       <c r="S207" t="n">
         <v>0</v>
@@ -17673,11 +17673,11 @@
         <v>0</v>
       </c>
       <c r="H208" t="n">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="J208" t="inlineStr">
         <is>
-          <t>MONTES CLAROS - CONSTRUÇÃO NOVO FÓRUM PAD. - P24</t>
+          <t>ITAJUBÁ - CONSTRUÇÃO NOVO FÓRUM</t>
         </is>
       </c>
       <c r="K208" t="inlineStr">
@@ -17687,11 +17687,11 @@
       </c>
       <c r="L208" t="inlineStr">
         <is>
-          <t>UNIDADE</t>
+          <t>PORCENTAGEM DE OBRA REALIZADA</t>
         </is>
       </c>
       <c r="M208" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="N208" t="inlineStr">
         <is>
@@ -17700,19 +17700,19 @@
       </c>
       <c r="O208" t="inlineStr">
         <is>
-          <t>Região Intermediária de Montes Claros</t>
+          <t>Região Intermediária de Pouso Alegre</t>
         </is>
       </c>
       <c r="P208" t="inlineStr">
         <is>
-          <t>MONTES CLAROS</t>
+          <t>ITAJUBÁ</t>
         </is>
       </c>
       <c r="Q208" t="n">
         <v>0</v>
       </c>
       <c r="R208" t="n">
-        <v>12451930</v>
+        <v>4564282</v>
       </c>
       <c r="S208" t="n">
         <v>0</v>
@@ -17756,11 +17756,11 @@
         <v>0</v>
       </c>
       <c r="H209" t="n">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="J209" t="inlineStr">
         <is>
-          <t>PARÁ DE MINAS - CONSTRUÇÃO DO NOVO FÓRUM - PAD. P9 - RETOMADA DA OBRA</t>
+          <t>ITAÚNA - CONSTRUÇÃO NOVO FÓRUM PAD. P9 - RETOMADA DA OBRA</t>
         </is>
       </c>
       <c r="K209" t="inlineStr">
@@ -17770,11 +17770,11 @@
       </c>
       <c r="L209" t="inlineStr">
         <is>
-          <t>UNIDADE</t>
+          <t>PORCENTAGEM DE OBRA REALIZADA</t>
         </is>
       </c>
       <c r="M209" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="N209" t="inlineStr">
         <is>
@@ -17788,14 +17788,14 @@
       </c>
       <c r="P209" t="inlineStr">
         <is>
-          <t>PARÁ DE MINAS</t>
+          <t>ITAÚNA</t>
         </is>
       </c>
       <c r="Q209" t="n">
         <v>0</v>
       </c>
       <c r="R209" t="n">
-        <v>19677622</v>
+        <v>14223089</v>
       </c>
       <c r="S209" t="n">
         <v>0</v>
@@ -17839,11 +17839,11 @@
         <v>0</v>
       </c>
       <c r="H210" t="n">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="J210" t="inlineStr">
         <is>
-          <t>POÇOS DE CALDAS - CONSTRUÇÃO NOVO FÓRUM PAF. NLN6 - RETOMADA DA OBRA</t>
+          <t>MONTES CLAROS - CONSTRUÇÃO NOVO FÓRUM PAD. - P24</t>
         </is>
       </c>
       <c r="K210" t="inlineStr">
@@ -17853,11 +17853,11 @@
       </c>
       <c r="L210" t="inlineStr">
         <is>
-          <t>PORCENTAGEM DE OBRA REALIZADA</t>
+          <t>UNIDADE</t>
         </is>
       </c>
       <c r="M210" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="N210" t="inlineStr">
         <is>
@@ -17866,19 +17866,19 @@
       </c>
       <c r="O210" t="inlineStr">
         <is>
-          <t>Região Intermediária de Pouso Alegre</t>
+          <t>Região Intermediária de Montes Claros</t>
         </is>
       </c>
       <c r="P210" t="inlineStr">
         <is>
-          <t>POÇOS DE CALDAS</t>
+          <t>MONTES CLAROS</t>
         </is>
       </c>
       <c r="Q210" t="n">
         <v>0</v>
       </c>
       <c r="R210" t="n">
-        <v>10731360</v>
+        <v>12451930</v>
       </c>
       <c r="S210" t="n">
         <v>0</v>
@@ -17922,11 +17922,11 @@
         <v>0</v>
       </c>
       <c r="H211" t="n">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="J211" t="inlineStr">
         <is>
-          <t>DIVERSAS COMARCAS - PRESTAÇÃO DE SERVIÇOS TÉCNICOS ESPECIALIZADOS.</t>
+          <t>PARÁ DE MINAS - CONSTRUÇÃO DO NOVO FÓRUM - PAD. P9 - RETOMADA DA OBRA</t>
         </is>
       </c>
       <c r="K211" t="inlineStr">
@@ -17936,11 +17936,11 @@
       </c>
       <c r="L211" t="inlineStr">
         <is>
-          <t>PORCENTAGEM DE OBRA REALIZADA</t>
+          <t>UNIDADE</t>
         </is>
       </c>
       <c r="M211" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="N211" t="inlineStr">
         <is>
@@ -17949,19 +17949,19 @@
       </c>
       <c r="O211" t="inlineStr">
         <is>
-          <t>Estadual</t>
+          <t>Região Intermediária de Divinópolis</t>
         </is>
       </c>
       <c r="P211" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
+          <t>PARÁ DE MINAS</t>
         </is>
       </c>
       <c r="Q211" t="n">
         <v>0</v>
       </c>
       <c r="R211" t="n">
-        <v>48899</v>
+        <v>19677622</v>
       </c>
       <c r="S211" t="n">
         <v>0</v>
@@ -18005,16 +18005,16 @@
         <v>0</v>
       </c>
       <c r="H212" t="n">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="J212" t="inlineStr">
         <is>
-          <t>BH - ED, SEDE - 3ª PARCELA (2º SUBSOLO E DATA CENTER</t>
+          <t>POÇOS DE CALDAS - CONSTRUÇÃO NOVO FÓRUM PAF. NLN6 - RETOMADA DA OBRA</t>
         </is>
       </c>
       <c r="K212" t="inlineStr">
         <is>
-          <t>INICIANDO</t>
+          <t>EXECUÇÃO</t>
         </is>
       </c>
       <c r="L212" t="inlineStr">
@@ -18032,19 +18032,19 @@
       </c>
       <c r="O212" t="inlineStr">
         <is>
-          <t>Região Intermediária de Belo Horizonte</t>
+          <t>Região Intermediária de Pouso Alegre</t>
         </is>
       </c>
       <c r="P212" t="inlineStr">
         <is>
-          <t>BELO HORIZONTE</t>
+          <t>POÇOS DE CALDAS</t>
         </is>
       </c>
       <c r="Q212" t="n">
         <v>0</v>
       </c>
       <c r="R212" t="n">
-        <v>7305961</v>
+        <v>10731360</v>
       </c>
       <c r="S212" t="n">
         <v>0</v>
@@ -18088,16 +18088,16 @@
         <v>0</v>
       </c>
       <c r="H213" t="n">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="J213" t="inlineStr">
         <is>
-          <t>BH - RUA MANAUS - IMPERMEABILIZAÇÃO</t>
+          <t>DIVERSAS COMARCAS - PRESTAÇÃO DE SERVIÇOS TÉCNICOS ESPECIALIZADOS.</t>
         </is>
       </c>
       <c r="K213" t="inlineStr">
         <is>
-          <t>INICIANDO</t>
+          <t>EXECUÇÃO</t>
         </is>
       </c>
       <c r="L213" t="inlineStr">
@@ -18115,19 +18115,19 @@
       </c>
       <c r="O213" t="inlineStr">
         <is>
-          <t>Região Intermediária de Belo Horizonte</t>
+          <t>Estadual</t>
         </is>
       </c>
       <c r="P213" t="inlineStr">
         <is>
-          <t>BELO HORIZONTE</t>
+          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
         </is>
       </c>
       <c r="Q213" t="n">
         <v>0</v>
       </c>
       <c r="R213" t="n">
-        <v>277825</v>
+        <v>48899</v>
       </c>
       <c r="S213" t="n">
         <v>0</v>
@@ -18171,11 +18171,11 @@
         <v>0</v>
       </c>
       <c r="H214" t="n">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="J214" t="inlineStr">
         <is>
-          <t>DIVERSAS COMARCAS - EXECUÇÃO DE SONDAGEM DE SOLO E DE SERVIÇOS</t>
+          <t>BH - ED, SEDE - 3ª PARCELA (2º SUBSOLO E DATA CENTER</t>
         </is>
       </c>
       <c r="K214" t="inlineStr">
@@ -18198,31 +18198,31 @@
       </c>
       <c r="O214" t="inlineStr">
         <is>
-          <t>Estadual</t>
+          <t>Região Intermediária de Belo Horizonte</t>
         </is>
       </c>
       <c r="P214" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
+          <t>BELO HORIZONTE</t>
         </is>
       </c>
       <c r="Q214" t="n">
         <v>0</v>
       </c>
       <c r="R214" t="n">
-        <v>1425919</v>
+        <v>7305961</v>
       </c>
       <c r="S214" t="n">
         <v>0</v>
       </c>
       <c r="T214" t="n">
-        <v>1425919</v>
+        <v>0</v>
       </c>
       <c r="U214" t="n">
         <v>0</v>
       </c>
       <c r="V214" t="n">
-        <v>332715</v>
+        <v>0</v>
       </c>
       <c r="W214" t="n">
         <v>0</v>
@@ -18254,11 +18254,11 @@
         <v>0</v>
       </c>
       <c r="H215" t="n">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="J215" t="inlineStr">
         <is>
-          <t>DIVERSAS COMARCAS - ACESSIBILIDADE</t>
+          <t>BH - RUA MANAUS - IMPERMEABILIZAÇÃO</t>
         </is>
       </c>
       <c r="K215" t="inlineStr">
@@ -18281,19 +18281,19 @@
       </c>
       <c r="O215" t="inlineStr">
         <is>
-          <t>Estadual</t>
+          <t>Região Intermediária de Belo Horizonte</t>
         </is>
       </c>
       <c r="P215" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
+          <t>BELO HORIZONTE</t>
         </is>
       </c>
       <c r="Q215" t="n">
         <v>0</v>
       </c>
       <c r="R215" t="n">
-        <v>455190</v>
+        <v>277825</v>
       </c>
       <c r="S215" t="n">
         <v>0</v>
@@ -18337,11 +18337,11 @@
         <v>0</v>
       </c>
       <c r="H216" t="n">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="J216" t="inlineStr">
         <is>
-          <t>ERVÁLIA - REFORMA DO ESTACIONAMENTO</t>
+          <t>DIVERSAS COMARCAS - EXECUÇÃO DE SONDAGEM DE SOLO E DE SERVIÇOS</t>
         </is>
       </c>
       <c r="K216" t="inlineStr">
@@ -18364,31 +18364,31 @@
       </c>
       <c r="O216" t="inlineStr">
         <is>
-          <t>Região Intermediária de Juíz de Fora</t>
+          <t>Estadual</t>
         </is>
       </c>
       <c r="P216" t="inlineStr">
         <is>
-          <t>ERVÁLIA</t>
+          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
         </is>
       </c>
       <c r="Q216" t="n">
         <v>0</v>
       </c>
       <c r="R216" t="n">
-        <v>865920</v>
+        <v>1425919</v>
       </c>
       <c r="S216" t="n">
         <v>0</v>
       </c>
       <c r="T216" t="n">
-        <v>0</v>
+        <v>1425919</v>
       </c>
       <c r="U216" t="n">
         <v>0</v>
       </c>
       <c r="V216" t="n">
-        <v>0</v>
+        <v>332715</v>
       </c>
       <c r="W216" t="n">
         <v>0</v>
@@ -18420,11 +18420,11 @@
         <v>0</v>
       </c>
       <c r="H217" t="n">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="J217" t="inlineStr">
         <is>
-          <t>CAPELINHA - IMPERMEABILIZAÇÃO</t>
+          <t>DIVERSAS COMARCAS - ACESSIBILIDADE</t>
         </is>
       </c>
       <c r="K217" t="inlineStr">
@@ -18447,25 +18447,25 @@
       </c>
       <c r="O217" t="inlineStr">
         <is>
-          <t>Região Intermediária de Teófilo Otoni</t>
+          <t>Estadual</t>
         </is>
       </c>
       <c r="P217" t="inlineStr">
         <is>
-          <t>CAPELINHA</t>
+          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
         </is>
       </c>
       <c r="Q217" t="n">
         <v>0</v>
       </c>
       <c r="R217" t="n">
-        <v>52000</v>
+        <v>455190</v>
       </c>
       <c r="S217" t="n">
         <v>0</v>
       </c>
       <c r="T217" t="n">
-        <v>156000</v>
+        <v>0</v>
       </c>
       <c r="U217" t="n">
         <v>0</v>
@@ -18503,11 +18503,11 @@
         <v>0</v>
       </c>
       <c r="H218" t="n">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="J218" t="inlineStr">
         <is>
-          <t>PASSOS - NOVO ELEVADOR</t>
+          <t>ERVÁLIA - REFORMA DO ESTACIONAMENTO</t>
         </is>
       </c>
       <c r="K218" t="inlineStr">
@@ -18530,25 +18530,25 @@
       </c>
       <c r="O218" t="inlineStr">
         <is>
-          <t>Região Intermediária de Varginha</t>
+          <t>Região Intermediária de Juíz de Fora</t>
         </is>
       </c>
       <c r="P218" t="inlineStr">
         <is>
-          <t>PASSOS</t>
+          <t>ERVÁLIA</t>
         </is>
       </c>
       <c r="Q218" t="n">
         <v>0</v>
       </c>
       <c r="R218" t="n">
-        <v>160000</v>
+        <v>865920</v>
       </c>
       <c r="S218" t="n">
         <v>0</v>
       </c>
       <c r="T218" t="n">
-        <v>80000</v>
+        <v>0</v>
       </c>
       <c r="U218" t="n">
         <v>0</v>
@@ -18586,11 +18586,11 @@
         <v>0</v>
       </c>
       <c r="H219" t="n">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="J219" t="inlineStr">
         <is>
-          <t>RIBEIRÃO DAS NEVES - AR CONDICIONADO</t>
+          <t>CAPELINHA - IMPERMEABILIZAÇÃO</t>
         </is>
       </c>
       <c r="K219" t="inlineStr">
@@ -18613,25 +18613,25 @@
       </c>
       <c r="O219" t="inlineStr">
         <is>
-          <t>Região Intermediária de Belo Horizonte</t>
+          <t>Região Intermediária de Teófilo Otoni</t>
         </is>
       </c>
       <c r="P219" t="inlineStr">
         <is>
-          <t>RIBEIRÃO DAS NEVES</t>
+          <t>CAPELINHA</t>
         </is>
       </c>
       <c r="Q219" t="n">
         <v>0</v>
       </c>
       <c r="R219" t="n">
-        <v>1351111</v>
+        <v>52000</v>
       </c>
       <c r="S219" t="n">
         <v>0</v>
       </c>
       <c r="T219" t="n">
-        <v>1688889</v>
+        <v>156000</v>
       </c>
       <c r="U219" t="n">
         <v>0</v>
@@ -18669,11 +18669,11 @@
         <v>0</v>
       </c>
       <c r="H220" t="n">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="J220" t="inlineStr">
         <is>
-          <t>UNAÍ - AR CONDICIONADO</t>
+          <t>PASSOS - NOVO ELEVADOR</t>
         </is>
       </c>
       <c r="K220" t="inlineStr">
@@ -18696,25 +18696,25 @@
       </c>
       <c r="O220" t="inlineStr">
         <is>
-          <t>Região Intermediária de Patos de Minas</t>
+          <t>Região Intermediária de Varginha</t>
         </is>
       </c>
       <c r="P220" t="inlineStr">
         <is>
-          <t>UNAÍ</t>
+          <t>PASSOS</t>
         </is>
       </c>
       <c r="Q220" t="n">
         <v>0</v>
       </c>
       <c r="R220" t="n">
-        <v>1013333</v>
+        <v>160000</v>
       </c>
       <c r="S220" t="n">
         <v>0</v>
       </c>
       <c r="T220" t="n">
-        <v>506667</v>
+        <v>80000</v>
       </c>
       <c r="U220" t="n">
         <v>0</v>
@@ -18752,11 +18752,11 @@
         <v>0</v>
       </c>
       <c r="H221" t="n">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="J221" t="inlineStr">
         <is>
-          <t>MEDINA - CONSTRUÇÃO NOVO FÓRUM</t>
+          <t>RIBEIRÃO DAS NEVES - AR CONDICIONADO</t>
         </is>
       </c>
       <c r="K221" t="inlineStr">
@@ -18779,25 +18779,25 @@
       </c>
       <c r="O221" t="inlineStr">
         <is>
-          <t>Região Intermediária de Teófilo Otoni</t>
+          <t>Região Intermediária de Belo Horizonte</t>
         </is>
       </c>
       <c r="P221" t="inlineStr">
         <is>
-          <t>MEDINA</t>
+          <t>RIBEIRÃO DAS NEVES</t>
         </is>
       </c>
       <c r="Q221" t="n">
         <v>0</v>
       </c>
       <c r="R221" t="n">
-        <v>7619738</v>
+        <v>1351111</v>
       </c>
       <c r="S221" t="n">
         <v>0</v>
       </c>
       <c r="T221" t="n">
-        <v>5684051</v>
+        <v>1688889</v>
       </c>
       <c r="U221" t="n">
         <v>0</v>
@@ -18835,11 +18835,11 @@
         <v>0</v>
       </c>
       <c r="H222" t="n">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="J222" t="inlineStr">
         <is>
-          <t>ITABIRITO</t>
+          <t>UNAÍ - AR CONDICIONADO</t>
         </is>
       </c>
       <c r="K222" t="inlineStr">
@@ -18862,25 +18862,25 @@
       </c>
       <c r="O222" t="inlineStr">
         <is>
-          <t>Região Intermediária de Belo Horizonte</t>
+          <t>Região Intermediária de Patos de Minas</t>
         </is>
       </c>
       <c r="P222" t="inlineStr">
         <is>
-          <t>ITABIRITO</t>
+          <t>UNAÍ</t>
         </is>
       </c>
       <c r="Q222" t="n">
         <v>0</v>
       </c>
       <c r="R222" t="n">
-        <v>7619738</v>
+        <v>1013333</v>
       </c>
       <c r="S222" t="n">
         <v>0</v>
       </c>
       <c r="T222" t="n">
-        <v>5684051</v>
+        <v>506667</v>
       </c>
       <c r="U222" t="n">
         <v>0</v>
@@ -18918,11 +18918,11 @@
         <v>0</v>
       </c>
       <c r="H223" t="n">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="J223" t="inlineStr">
         <is>
-          <t>CONQUISTA - CONSTRUÇÃO NOVO FÓRUM</t>
+          <t>MEDINA - CONSTRUÇÃO NOVO FÓRUM</t>
         </is>
       </c>
       <c r="K223" t="inlineStr">
@@ -18932,11 +18932,11 @@
       </c>
       <c r="L223" t="inlineStr">
         <is>
-          <t>UNIDADE</t>
+          <t>PORCENTAGEM DE OBRA REALIZADA</t>
         </is>
       </c>
       <c r="M223" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="N223" t="inlineStr">
         <is>
@@ -18945,25 +18945,25 @@
       </c>
       <c r="O223" t="inlineStr">
         <is>
-          <t>Região Intermediária de Uberaba</t>
+          <t>Região Intermediária de Teófilo Otoni</t>
         </is>
       </c>
       <c r="P223" t="inlineStr">
         <is>
-          <t>CONQUISTA</t>
+          <t>MEDINA</t>
         </is>
       </c>
       <c r="Q223" t="n">
         <v>0</v>
       </c>
       <c r="R223" t="n">
-        <v>4572211</v>
+        <v>7619738</v>
       </c>
       <c r="S223" t="n">
         <v>0</v>
       </c>
       <c r="T223" t="n">
-        <v>1187789</v>
+        <v>5684051</v>
       </c>
       <c r="U223" t="n">
         <v>0</v>
@@ -19001,11 +19001,11 @@
         <v>0</v>
       </c>
       <c r="H224" t="n">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="J224" t="inlineStr">
         <is>
-          <t>SETE LAGOAS - REFORMA E AMPLIAÇÃO DO FÓRUM</t>
+          <t>ITABIRITO</t>
         </is>
       </c>
       <c r="K224" t="inlineStr">
@@ -19033,26 +19033,26 @@
       </c>
       <c r="P224" t="inlineStr">
         <is>
-          <t>SETE LAGOAS</t>
+          <t>ITABIRITO</t>
         </is>
       </c>
       <c r="Q224" t="n">
         <v>0</v>
       </c>
       <c r="R224" t="n">
-        <v>8333333</v>
+        <v>7619738</v>
       </c>
       <c r="S224" t="n">
         <v>0</v>
       </c>
       <c r="T224" t="n">
-        <v>25000000</v>
+        <v>5684051</v>
       </c>
       <c r="U224" t="n">
         <v>0</v>
       </c>
       <c r="V224" t="n">
-        <v>16666667</v>
+        <v>0</v>
       </c>
       <c r="W224" t="n">
         <v>0</v>
@@ -19084,11 +19084,11 @@
         <v>0</v>
       </c>
       <c r="H225" t="n">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="J225" t="inlineStr">
         <is>
-          <t>RAUL SOARES - CONSTRUÇÃO NOVO FÓRUM PAD. M2</t>
+          <t>CONQUISTA - CONSTRUÇÃO NOVO FÓRUM</t>
         </is>
       </c>
       <c r="K225" t="inlineStr">
@@ -19098,11 +19098,11 @@
       </c>
       <c r="L225" t="inlineStr">
         <is>
-          <t>PORCENTAGEM DE OBRA REALIZADA</t>
+          <t>UNIDADE</t>
         </is>
       </c>
       <c r="M225" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="N225" t="inlineStr">
         <is>
@@ -19111,25 +19111,25 @@
       </c>
       <c r="O225" t="inlineStr">
         <is>
-          <t>Região Intermediária de Ipatinga</t>
+          <t>Região Intermediária de Uberaba</t>
         </is>
       </c>
       <c r="P225" t="inlineStr">
         <is>
-          <t>RAUL SOARES</t>
+          <t>CONQUISTA</t>
         </is>
       </c>
       <c r="Q225" t="n">
         <v>0</v>
       </c>
       <c r="R225" t="n">
-        <v>3618663</v>
+        <v>4572211</v>
       </c>
       <c r="S225" t="n">
         <v>0</v>
       </c>
       <c r="T225" t="n">
-        <v>5181337</v>
+        <v>1187789</v>
       </c>
       <c r="U225" t="n">
         <v>0</v>
@@ -19167,11 +19167,11 @@
         <v>0</v>
       </c>
       <c r="H226" t="n">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="J226" t="inlineStr">
         <is>
-          <t>RIO CASCA - CONSTRUÇÃO NOVO FÓRUM</t>
+          <t>SETE LAGOAS - REFORMA E AMPLIAÇÃO DO FÓRUM</t>
         </is>
       </c>
       <c r="K226" t="inlineStr">
@@ -19194,31 +19194,31 @@
       </c>
       <c r="O226" t="inlineStr">
         <is>
-          <t>Região Intermediária de Juíz de Fora</t>
+          <t>Região Intermediária de Belo Horizonte</t>
         </is>
       </c>
       <c r="P226" t="inlineStr">
         <is>
-          <t>RIO CASCA</t>
+          <t>SETE LAGOAS</t>
         </is>
       </c>
       <c r="Q226" t="n">
         <v>0</v>
       </c>
       <c r="R226" t="n">
-        <v>3618663</v>
+        <v>8333333</v>
       </c>
       <c r="S226" t="n">
         <v>0</v>
       </c>
       <c r="T226" t="n">
-        <v>5181337</v>
+        <v>25000000</v>
       </c>
       <c r="U226" t="n">
         <v>0</v>
       </c>
       <c r="V226" t="n">
-        <v>0</v>
+        <v>16666667</v>
       </c>
       <c r="W226" t="n">
         <v>0</v>
@@ -19250,11 +19250,11 @@
         <v>0</v>
       </c>
       <c r="H227" t="n">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="J227" t="inlineStr">
         <is>
-          <t>PASSA TEMPO - CONSTRUÇÃO NOVO FÓRUM</t>
+          <t>RAUL SOARES - CONSTRUÇÃO NOVO FÓRUM PAD. M2</t>
         </is>
       </c>
       <c r="K227" t="inlineStr">
@@ -19277,25 +19277,25 @@
       </c>
       <c r="O227" t="inlineStr">
         <is>
-          <t>Região Intermediária de Divinópolis</t>
+          <t>Região Intermediária de Ipatinga</t>
         </is>
       </c>
       <c r="P227" t="inlineStr">
         <is>
-          <t>PASSA TEMPO</t>
+          <t>RAUL SOARES</t>
         </is>
       </c>
       <c r="Q227" t="n">
         <v>0</v>
       </c>
       <c r="R227" t="n">
-        <v>4054125</v>
+        <v>3618663</v>
       </c>
       <c r="S227" t="n">
         <v>0</v>
       </c>
       <c r="T227" t="n">
-        <v>1705875</v>
+        <v>5181337</v>
       </c>
       <c r="U227" t="n">
         <v>0</v>
@@ -19333,11 +19333,11 @@
         <v>0</v>
       </c>
       <c r="H228" t="n">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="J228" t="inlineStr">
         <is>
-          <t>TRÊS PONTAS - CONSTRUÇÃO DO NOVO FÓRUM</t>
+          <t>RIO CASCA - CONSTRUÇÃO NOVO FÓRUM</t>
         </is>
       </c>
       <c r="K228" t="inlineStr">
@@ -19360,25 +19360,25 @@
       </c>
       <c r="O228" t="inlineStr">
         <is>
-          <t>Região Intermediária de Varginha</t>
+          <t>Região Intermediária de Juíz de Fora</t>
         </is>
       </c>
       <c r="P228" t="inlineStr">
         <is>
-          <t>TRÊS PONTAS</t>
+          <t>RIO CASCA</t>
         </is>
       </c>
       <c r="Q228" t="n">
         <v>0</v>
       </c>
       <c r="R228" t="n">
-        <v>4319141</v>
+        <v>3618663</v>
       </c>
       <c r="S228" t="n">
         <v>0</v>
       </c>
       <c r="T228" t="n">
-        <v>12480859</v>
+        <v>5181337</v>
       </c>
       <c r="U228" t="n">
         <v>0</v>
@@ -19416,11 +19416,11 @@
         <v>0</v>
       </c>
       <c r="H229" t="n">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="J229" t="inlineStr">
         <is>
-          <t>CARANGOLA - CONSTRUÇÃO DO NOVO FÓRUM</t>
+          <t>PASSA TEMPO - CONSTRUÇÃO NOVO FÓRUM</t>
         </is>
       </c>
       <c r="K229" t="inlineStr">
@@ -19443,25 +19443,25 @@
       </c>
       <c r="O229" t="inlineStr">
         <is>
-          <t>Região Intermediária de Juíz de Fora</t>
+          <t>Região Intermediária de Divinópolis</t>
         </is>
       </c>
       <c r="P229" t="inlineStr">
         <is>
-          <t>CARANGOLA</t>
+          <t>PASSA TEMPO</t>
         </is>
       </c>
       <c r="Q229" t="n">
         <v>0</v>
       </c>
       <c r="R229" t="n">
-        <v>4319141</v>
+        <v>4054125</v>
       </c>
       <c r="S229" t="n">
         <v>0</v>
       </c>
       <c r="T229" t="n">
-        <v>12480859</v>
+        <v>1705875</v>
       </c>
       <c r="U229" t="n">
         <v>0</v>
@@ -19499,11 +19499,11 @@
         <v>0</v>
       </c>
       <c r="H230" t="n">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="J230" t="inlineStr">
         <is>
-          <t>SENADOR FIRMINO - REFORMA E AMPLIAÇÃO DO FÓRUM</t>
+          <t>TRÊS PONTAS - CONSTRUÇÃO DO NOVO FÓRUM</t>
         </is>
       </c>
       <c r="K230" t="inlineStr">
@@ -19526,31 +19526,31 @@
       </c>
       <c r="O230" t="inlineStr">
         <is>
-          <t>Região Intermediária de Juíz de Fora</t>
+          <t>Região Intermediária de Varginha</t>
         </is>
       </c>
       <c r="P230" t="inlineStr">
         <is>
-          <t>SENADOR FIRMINO</t>
+          <t>TRÊS PONTAS</t>
         </is>
       </c>
       <c r="Q230" t="n">
         <v>0</v>
       </c>
       <c r="R230" t="n">
-        <v>2387133</v>
+        <v>4319141</v>
       </c>
       <c r="S230" t="n">
         <v>0</v>
       </c>
       <c r="T230" t="n">
-        <v>5729120</v>
+        <v>12480859</v>
       </c>
       <c r="U230" t="n">
         <v>0</v>
       </c>
       <c r="V230" t="n">
-        <v>477427</v>
+        <v>0</v>
       </c>
       <c r="W230" t="n">
         <v>0</v>
@@ -19582,11 +19582,11 @@
         <v>0</v>
       </c>
       <c r="H231" t="n">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="J231" t="inlineStr">
         <is>
-          <t>SABINÓPOLIS - CONSTRUÇÃO NOVO FÓRUM</t>
+          <t>CARANGOLA - CONSTRUÇÃO DO NOVO FÓRUM</t>
         </is>
       </c>
       <c r="K231" t="inlineStr">
@@ -19609,25 +19609,25 @@
       </c>
       <c r="O231" t="inlineStr">
         <is>
-          <t>Região Intermediária de Governador Valadares</t>
+          <t>Região Intermediária de Juíz de Fora</t>
         </is>
       </c>
       <c r="P231" t="inlineStr">
         <is>
-          <t>SABINÓPOLIS</t>
+          <t>CARANGOLA</t>
         </is>
       </c>
       <c r="Q231" t="n">
         <v>0</v>
       </c>
       <c r="R231" t="n">
-        <v>1868091</v>
+        <v>4319141</v>
       </c>
       <c r="S231" t="n">
         <v>0</v>
       </c>
       <c r="T231" t="n">
-        <v>5331909</v>
+        <v>12480859</v>
       </c>
       <c r="U231" t="n">
         <v>0</v>
@@ -19665,11 +19665,11 @@
         <v>0</v>
       </c>
       <c r="H232" t="n">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="J232" t="inlineStr">
         <is>
-          <t>SÃO GONÇALO DO SAPUCAÍ - CONSTRUÇÃO DO NOVO FÓRUM</t>
+          <t>SENADOR FIRMINO - REFORMA E AMPLIAÇÃO DO FÓRUM</t>
         </is>
       </c>
       <c r="K232" t="inlineStr">
@@ -19692,31 +19692,31 @@
       </c>
       <c r="O232" t="inlineStr">
         <is>
-          <t>Região Intermediária de Varginha</t>
+          <t>Região Intermediária de Juíz de Fora</t>
         </is>
       </c>
       <c r="P232" t="inlineStr">
         <is>
-          <t>SÃO GONÇALO DO SAPUCAÍ</t>
+          <t>SENADOR FIRMINO</t>
         </is>
       </c>
       <c r="Q232" t="n">
         <v>0</v>
       </c>
       <c r="R232" t="n">
-        <v>1225627</v>
+        <v>2387133</v>
       </c>
       <c r="S232" t="n">
         <v>0</v>
       </c>
       <c r="T232" t="n">
-        <v>12534373</v>
+        <v>5729120</v>
       </c>
       <c r="U232" t="n">
         <v>0</v>
       </c>
       <c r="V232" t="n">
-        <v>0</v>
+        <v>477427</v>
       </c>
       <c r="W232" t="n">
         <v>0</v>
@@ -19748,11 +19748,11 @@
         <v>0</v>
       </c>
       <c r="H233" t="n">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="J233" t="inlineStr">
         <is>
-          <t>ALMENARA - CONSTRUÇÃO DO NOVO FÓRUM</t>
+          <t>SABINÓPOLIS - CONSTRUÇÃO NOVO FÓRUM</t>
         </is>
       </c>
       <c r="K233" t="inlineStr">
@@ -19775,31 +19775,31 @@
       </c>
       <c r="O233" t="inlineStr">
         <is>
-          <t>Região Intermediária de Teófilo Otoni</t>
+          <t>Região Intermediária de Governador Valadares</t>
         </is>
       </c>
       <c r="P233" t="inlineStr">
         <is>
-          <t>ALMENARA</t>
+          <t>SABINÓPOLIS</t>
         </is>
       </c>
       <c r="Q233" t="n">
         <v>0</v>
       </c>
       <c r="R233" t="n">
-        <v>1743993</v>
+        <v>1868091</v>
       </c>
       <c r="S233" t="n">
         <v>0</v>
       </c>
       <c r="T233" t="n">
-        <v>13154677</v>
+        <v>5331909</v>
       </c>
       <c r="U233" t="n">
         <v>0</v>
       </c>
       <c r="V233" t="n">
-        <v>1901331</v>
+        <v>0</v>
       </c>
       <c r="W233" t="n">
         <v>0</v>
@@ -19831,11 +19831,11 @@
         <v>0</v>
       </c>
       <c r="H234" t="n">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="J234" t="inlineStr">
         <is>
-          <t>PIRAPORA - CONSTRUÇÃO NOVO FÓRUM</t>
+          <t>SÃO GONÇALO DO SAPUCAÍ - CONSTRUÇÃO DO NOVO FÓRUM</t>
         </is>
       </c>
       <c r="K234" t="inlineStr">
@@ -19858,31 +19858,31 @@
       </c>
       <c r="O234" t="inlineStr">
         <is>
-          <t>Região Intermediária de Montes Claros</t>
+          <t>Região Intermediária de Varginha</t>
         </is>
       </c>
       <c r="P234" t="inlineStr">
         <is>
-          <t>PIRAPORA</t>
+          <t>SÃO GONÇALO DO SAPUCAÍ</t>
         </is>
       </c>
       <c r="Q234" t="n">
         <v>0</v>
       </c>
       <c r="R234" t="n">
-        <v>575000</v>
+        <v>1225627</v>
       </c>
       <c r="S234" t="n">
         <v>0</v>
       </c>
       <c r="T234" t="n">
-        <v>14080000</v>
+        <v>12534373</v>
       </c>
       <c r="U234" t="n">
         <v>0</v>
       </c>
       <c r="V234" t="n">
-        <v>5345000</v>
+        <v>0</v>
       </c>
       <c r="W234" t="n">
         <v>0</v>
@@ -19914,11 +19914,11 @@
         <v>0</v>
       </c>
       <c r="H235" t="n">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="J235" t="inlineStr">
         <is>
-          <t>BH - ED. SEDE 4ª PARCELA (REFORMA PARCIAL, 1º SUBS</t>
+          <t>ALMENARA - CONSTRUÇÃO DO NOVO FÓRUM</t>
         </is>
       </c>
       <c r="K235" t="inlineStr">
@@ -19941,31 +19941,31 @@
       </c>
       <c r="O235" t="inlineStr">
         <is>
-          <t>Região Intermediária de Belo Horizonte</t>
+          <t>Região Intermediária de Teófilo Otoni</t>
         </is>
       </c>
       <c r="P235" t="inlineStr">
         <is>
-          <t>BELO HORIZONTE</t>
+          <t>ALMENARA</t>
         </is>
       </c>
       <c r="Q235" t="n">
         <v>0</v>
       </c>
       <c r="R235" t="n">
-        <v>2520000</v>
+        <v>1743993</v>
       </c>
       <c r="S235" t="n">
         <v>0</v>
       </c>
       <c r="T235" t="n">
-        <v>1260000</v>
+        <v>13154677</v>
       </c>
       <c r="U235" t="n">
         <v>0</v>
       </c>
       <c r="V235" t="n">
-        <v>0</v>
+        <v>1901331</v>
       </c>
       <c r="W235" t="n">
         <v>0</v>
@@ -19997,11 +19997,11 @@
         <v>0</v>
       </c>
       <c r="H236" t="n">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="J236" t="inlineStr">
         <is>
-          <t>BH - ED. SEDE AMPLIAÇÃO CONSTRUÇÃO DA TORRE SUL E</t>
+          <t>PIRAPORA - CONSTRUÇÃO NOVO FÓRUM</t>
         </is>
       </c>
       <c r="K236" t="inlineStr">
@@ -20024,37 +20024,37 @@
       </c>
       <c r="O236" t="inlineStr">
         <is>
-          <t>Região Intermediária de Belo Horizonte</t>
+          <t>Região Intermediária de Montes Claros</t>
         </is>
       </c>
       <c r="P236" t="inlineStr">
         <is>
-          <t>BELO HORIZONTE</t>
+          <t>PIRAPORA</t>
         </is>
       </c>
       <c r="Q236" t="n">
         <v>0</v>
       </c>
       <c r="R236" t="n">
-        <v>13000000</v>
+        <v>575000</v>
       </c>
       <c r="S236" t="n">
         <v>0</v>
       </c>
       <c r="T236" t="n">
-        <v>99320000</v>
+        <v>14080000</v>
       </c>
       <c r="U236" t="n">
         <v>0</v>
       </c>
       <c r="V236" t="n">
-        <v>243360000</v>
+        <v>5345000</v>
       </c>
       <c r="W236" t="n">
         <v>0</v>
       </c>
       <c r="X236" t="n">
-        <v>243360000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="237">
@@ -20080,11 +20080,11 @@
         <v>0</v>
       </c>
       <c r="H237" t="n">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="J237" t="inlineStr">
         <is>
-          <t>BH - ED. MANAUS - 2ª PARCELA (COBERTURA)</t>
+          <t>BH - ED. SEDE 4ª PARCELA (REFORMA PARCIAL, 1º SUBS</t>
         </is>
       </c>
       <c r="K237" t="inlineStr">
@@ -20119,13 +20119,13 @@
         <v>0</v>
       </c>
       <c r="R237" t="n">
-        <v>800000</v>
+        <v>2520000</v>
       </c>
       <c r="S237" t="n">
         <v>0</v>
       </c>
       <c r="T237" t="n">
-        <v>800000</v>
+        <v>1260000</v>
       </c>
       <c r="U237" t="n">
         <v>0</v>
@@ -20163,11 +20163,11 @@
         <v>0</v>
       </c>
       <c r="H238" t="n">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="J238" t="inlineStr">
         <is>
-          <t>BH - UNIDADE FRANCISCO SALES - REFORMA PARCIAL</t>
+          <t>BH - ED. SEDE AMPLIAÇÃO CONSTRUÇÃO DA TORRE SUL E</t>
         </is>
       </c>
       <c r="K238" t="inlineStr">
@@ -20177,7 +20177,7 @@
       </c>
       <c r="L238" t="inlineStr">
         <is>
-          <t>UNIDADE</t>
+          <t>PORCENTAGEM DE OBRA REALIZADA</t>
         </is>
       </c>
       <c r="M238" t="n">
@@ -20202,25 +20202,25 @@
         <v>0</v>
       </c>
       <c r="R238" t="n">
-        <v>1493333</v>
+        <v>13000000</v>
       </c>
       <c r="S238" t="n">
         <v>0</v>
       </c>
       <c r="T238" t="n">
-        <v>1306667</v>
+        <v>99320000</v>
       </c>
       <c r="U238" t="n">
         <v>0</v>
       </c>
       <c r="V238" t="n">
-        <v>0</v>
+        <v>243360000</v>
       </c>
       <c r="W238" t="n">
         <v>0</v>
       </c>
       <c r="X238" t="n">
-        <v>0</v>
+        <v>243360000</v>
       </c>
     </row>
     <row r="239">
@@ -20246,11 +20246,11 @@
         <v>0</v>
       </c>
       <c r="H239" t="n">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="J239" t="inlineStr">
         <is>
-          <t>BH - CINCÃO - ESTANTERIA</t>
+          <t>BH - ED. MANAUS - 2ª PARCELA (COBERTURA)</t>
         </is>
       </c>
       <c r="K239" t="inlineStr">
@@ -20285,13 +20285,13 @@
         <v>0</v>
       </c>
       <c r="R239" t="n">
-        <v>3066667</v>
+        <v>800000</v>
       </c>
       <c r="S239" t="n">
         <v>0</v>
       </c>
       <c r="T239" t="n">
-        <v>6133333</v>
+        <v>800000</v>
       </c>
       <c r="U239" t="n">
         <v>0</v>
@@ -20329,11 +20329,11 @@
         <v>0</v>
       </c>
       <c r="H240" t="n">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="J240" t="inlineStr">
         <is>
-          <t>DIVERSAS COMARCAS - PLANO AVCB</t>
+          <t>BH - UNIDADE FRANCISCO SALES - REFORMA PARCIAL</t>
         </is>
       </c>
       <c r="K240" t="inlineStr">
@@ -20343,11 +20343,11 @@
       </c>
       <c r="L240" t="inlineStr">
         <is>
-          <t>PORCENTAGEM DE OBRA REALIZADA</t>
+          <t>UNIDADE</t>
         </is>
       </c>
       <c r="M240" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="N240" t="inlineStr">
         <is>
@@ -20356,25 +20356,25 @@
       </c>
       <c r="O240" t="inlineStr">
         <is>
-          <t>Estadual</t>
+          <t>Região Intermediária de Belo Horizonte</t>
         </is>
       </c>
       <c r="P240" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
+          <t>BELO HORIZONTE</t>
         </is>
       </c>
       <c r="Q240" t="n">
         <v>0</v>
       </c>
       <c r="R240" t="n">
-        <v>400000</v>
+        <v>1493333</v>
       </c>
       <c r="S240" t="n">
         <v>0</v>
       </c>
       <c r="T240" t="n">
-        <v>2000000</v>
+        <v>1306667</v>
       </c>
       <c r="U240" t="n">
         <v>0</v>
@@ -20412,11 +20412,11 @@
         <v>0</v>
       </c>
       <c r="H241" t="n">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="J241" t="inlineStr">
         <is>
-          <t>DIVERSAS COMARCAS - SERVIÇO TÉCNICO PROFISSIONAL E</t>
+          <t>BH - CINCÃO - ESTANTERIA</t>
         </is>
       </c>
       <c r="K241" t="inlineStr">
@@ -20439,31 +20439,31 @@
       </c>
       <c r="O241" t="inlineStr">
         <is>
-          <t>Estadual</t>
+          <t>Região Intermediária de Belo Horizonte</t>
         </is>
       </c>
       <c r="P241" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
+          <t>BELO HORIZONTE</t>
         </is>
       </c>
       <c r="Q241" t="n">
         <v>0</v>
       </c>
       <c r="R241" t="n">
-        <v>375000</v>
+        <v>3066667</v>
       </c>
       <c r="S241" t="n">
         <v>0</v>
       </c>
       <c r="T241" t="n">
-        <v>375000</v>
+        <v>6133333</v>
       </c>
       <c r="U241" t="n">
         <v>0</v>
       </c>
       <c r="V241" t="n">
-        <v>218750</v>
+        <v>0</v>
       </c>
       <c r="W241" t="n">
         <v>0</v>
@@ -20495,11 +20495,11 @@
         <v>0</v>
       </c>
       <c r="H242" t="n">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="J242" t="inlineStr">
         <is>
-          <t>DIVERSAS COMARCAS - PRESTAÇÃO DE SERVIÇOS TÉCNICOS ESPECIALIZADOS</t>
+          <t>DIVERSAS COMARCAS - PLANO AVCB</t>
         </is>
       </c>
       <c r="K242" t="inlineStr">
@@ -20513,7 +20513,7 @@
         </is>
       </c>
       <c r="M242" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="N242" t="inlineStr">
         <is>
@@ -20534,19 +20534,19 @@
         <v>0</v>
       </c>
       <c r="R242" t="n">
-        <v>300000</v>
+        <v>400000</v>
       </c>
       <c r="S242" t="n">
         <v>0</v>
       </c>
       <c r="T242" t="n">
-        <v>300000</v>
+        <v>2000000</v>
       </c>
       <c r="U242" t="n">
         <v>0</v>
       </c>
       <c r="V242" t="n">
-        <v>275000</v>
+        <v>0</v>
       </c>
       <c r="W242" t="n">
         <v>0</v>
@@ -20578,11 +20578,11 @@
         <v>0</v>
       </c>
       <c r="H243" t="n">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="J243" t="inlineStr">
         <is>
-          <t>DIVERSAS COMARCAS - ESLABORAÇÃO DE PROJETOS ESTRUTURAIS</t>
+          <t>DIVERSAS COMARCAS - SERVIÇO TÉCNICO PROFISSIONAL E</t>
         </is>
       </c>
       <c r="K243" t="inlineStr">
@@ -20617,19 +20617,19 @@
         <v>0</v>
       </c>
       <c r="R243" t="n">
-        <v>169444</v>
+        <v>375000</v>
       </c>
       <c r="S243" t="n">
         <v>0</v>
       </c>
       <c r="T243" t="n">
-        <v>166667</v>
+        <v>375000</v>
       </c>
       <c r="U243" t="n">
         <v>0</v>
       </c>
       <c r="V243" t="n">
-        <v>166667</v>
+        <v>218750</v>
       </c>
       <c r="W243" t="n">
         <v>0</v>
@@ -20661,11 +20661,11 @@
         <v>0</v>
       </c>
       <c r="H244" t="n">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="J244" t="inlineStr">
         <is>
-          <t>DIVERSAS COMARCAS - ACESSIBILIDADE - RETOMADA</t>
+          <t>DIVERSAS COMARCAS - PRESTAÇÃO DE SERVIÇOS TÉCNICOS ESPECIALIZADOS</t>
         </is>
       </c>
       <c r="K244" t="inlineStr">
@@ -20688,31 +20688,31 @@
       </c>
       <c r="O244" t="inlineStr">
         <is>
-          <t>Região Intermediária de Belo Horizonte</t>
+          <t>Estadual</t>
         </is>
       </c>
       <c r="P244" t="inlineStr">
         <is>
-          <t>BELO HORIZONTE</t>
+          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
         </is>
       </c>
       <c r="Q244" t="n">
         <v>0</v>
       </c>
       <c r="R244" t="n">
-        <v>225000</v>
+        <v>300000</v>
       </c>
       <c r="S244" t="n">
         <v>0</v>
       </c>
       <c r="T244" t="n">
-        <v>375000</v>
+        <v>300000</v>
       </c>
       <c r="U244" t="n">
         <v>0</v>
       </c>
       <c r="V244" t="n">
-        <v>0</v>
+        <v>275000</v>
       </c>
       <c r="W244" t="n">
         <v>0</v>
@@ -20744,11 +20744,11 @@
         <v>0</v>
       </c>
       <c r="H245" t="n">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="J245" t="inlineStr">
         <is>
-          <t>DIVERSAS COMARCAS - ACESSIBILIDADE</t>
+          <t>DIVERSAS COMARCAS - ESLABORAÇÃO DE PROJETOS ESTRUTURAIS</t>
         </is>
       </c>
       <c r="K245" t="inlineStr">
@@ -20783,19 +20783,19 @@
         <v>0</v>
       </c>
       <c r="R245" t="n">
-        <v>150000</v>
+        <v>169444</v>
       </c>
       <c r="S245" t="n">
         <v>0</v>
       </c>
       <c r="T245" t="n">
-        <v>450000</v>
+        <v>166667</v>
       </c>
       <c r="U245" t="n">
         <v>0</v>
       </c>
       <c r="V245" t="n">
-        <v>0</v>
+        <v>166667</v>
       </c>
       <c r="W245" t="n">
         <v>0</v>
@@ -20827,11 +20827,11 @@
         <v>0</v>
       </c>
       <c r="H246" t="n">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="J246" t="inlineStr">
         <is>
-          <t>ITAOBIM - FÓRUNS DIGITAIS</t>
+          <t>DIVERSAS COMARCAS - ACESSIBILIDADE - RETOMADA</t>
         </is>
       </c>
       <c r="K246" t="inlineStr">
@@ -20854,25 +20854,25 @@
       </c>
       <c r="O246" t="inlineStr">
         <is>
-          <t>Região Intermediária de Teófilo Otoni</t>
+          <t>Região Intermediária de Belo Horizonte</t>
         </is>
       </c>
       <c r="P246" t="inlineStr">
         <is>
-          <t>ITAOBIM</t>
+          <t>BELO HORIZONTE</t>
         </is>
       </c>
       <c r="Q246" t="n">
         <v>0</v>
       </c>
       <c r="R246" t="n">
-        <v>1235948</v>
+        <v>225000</v>
       </c>
       <c r="S246" t="n">
         <v>0</v>
       </c>
       <c r="T246" t="n">
-        <v>244052</v>
+        <v>375000</v>
       </c>
       <c r="U246" t="n">
         <v>0</v>
@@ -20910,11 +20910,11 @@
         <v>0</v>
       </c>
       <c r="H247" t="n">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="J247" t="inlineStr">
         <is>
-          <t>PONTO CHIQUE - FÓRUNS DIGITAIS</t>
+          <t>DIVERSAS COMARCAS - ACESSIBILIDADE</t>
         </is>
       </c>
       <c r="K247" t="inlineStr">
@@ -20937,25 +20937,25 @@
       </c>
       <c r="O247" t="inlineStr">
         <is>
-          <t>Região Intermediária de Montes Claros</t>
+          <t>Estadual</t>
         </is>
       </c>
       <c r="P247" t="inlineStr">
         <is>
-          <t>PONTO CHIQUE</t>
+          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
         </is>
       </c>
       <c r="Q247" t="n">
         <v>0</v>
       </c>
       <c r="R247" t="n">
-        <v>1235948</v>
+        <v>150000</v>
       </c>
       <c r="S247" t="n">
         <v>0</v>
       </c>
       <c r="T247" t="n">
-        <v>244052</v>
+        <v>450000</v>
       </c>
       <c r="U247" t="n">
         <v>0</v>
@@ -20993,11 +20993,11 @@
         <v>0</v>
       </c>
       <c r="H248" t="n">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="J248" t="inlineStr">
         <is>
-          <t>FORMOSO - FÓRUNS DIGITAIS</t>
+          <t>ITAOBIM - FÓRUNS DIGITAIS</t>
         </is>
       </c>
       <c r="K248" t="inlineStr">
@@ -21020,12 +21020,12 @@
       </c>
       <c r="O248" t="inlineStr">
         <is>
-          <t>Região Intermediária de Patos de Minas</t>
+          <t>Região Intermediária de Teófilo Otoni</t>
         </is>
       </c>
       <c r="P248" t="inlineStr">
         <is>
-          <t>FORMOSO</t>
+          <t>ITAOBIM</t>
         </is>
       </c>
       <c r="Q248" t="n">
@@ -21076,11 +21076,11 @@
         <v>0</v>
       </c>
       <c r="H249" t="n">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="J249" t="inlineStr">
         <is>
-          <t>CARMO DA CACHOEIRA - FÓRUNS DIGITAIS</t>
+          <t>PONTO CHIQUE - FÓRUNS DIGITAIS</t>
         </is>
       </c>
       <c r="K249" t="inlineStr">
@@ -21103,25 +21103,25 @@
       </c>
       <c r="O249" t="inlineStr">
         <is>
-          <t>Região Intermediária de Varginha</t>
+          <t>Região Intermediária de Montes Claros</t>
         </is>
       </c>
       <c r="P249" t="inlineStr">
         <is>
-          <t>CARMO DA CACHOEIRA</t>
+          <t>PONTO CHIQUE</t>
         </is>
       </c>
       <c r="Q249" t="n">
         <v>0</v>
       </c>
       <c r="R249" t="n">
-        <v>1014836</v>
+        <v>1235948</v>
       </c>
       <c r="S249" t="n">
         <v>0</v>
       </c>
       <c r="T249" t="n">
-        <v>465164</v>
+        <v>244052</v>
       </c>
       <c r="U249" t="n">
         <v>0</v>
@@ -21159,11 +21159,11 @@
         <v>0</v>
       </c>
       <c r="H250" t="n">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="J250" t="inlineStr">
         <is>
-          <t>FD 05</t>
+          <t>FORMOSO - FÓRUNS DIGITAIS</t>
         </is>
       </c>
       <c r="K250" t="inlineStr">
@@ -21186,25 +21186,25 @@
       </c>
       <c r="O250" t="inlineStr">
         <is>
-          <t>Estadual</t>
+          <t>Região Intermediária de Patos de Minas</t>
         </is>
       </c>
       <c r="P250" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
+          <t>FORMOSO</t>
         </is>
       </c>
       <c r="Q250" t="n">
         <v>0</v>
       </c>
       <c r="R250" t="n">
-        <v>1014836</v>
+        <v>1235948</v>
       </c>
       <c r="S250" t="n">
         <v>0</v>
       </c>
       <c r="T250" t="n">
-        <v>465164</v>
+        <v>244052</v>
       </c>
       <c r="U250" t="n">
         <v>0</v>
@@ -21242,11 +21242,11 @@
         <v>0</v>
       </c>
       <c r="H251" t="n">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="J251" t="inlineStr">
         <is>
-          <t>FD 06</t>
+          <t>CARMO DA CACHOEIRA - FÓRUNS DIGITAIS</t>
         </is>
       </c>
       <c r="K251" t="inlineStr">
@@ -21269,12 +21269,12 @@
       </c>
       <c r="O251" t="inlineStr">
         <is>
-          <t>Estadual</t>
+          <t>Região Intermediária de Varginha</t>
         </is>
       </c>
       <c r="P251" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
+          <t>CARMO DA CACHOEIRA</t>
         </is>
       </c>
       <c r="Q251" t="n">
@@ -21325,11 +21325,11 @@
         <v>0</v>
       </c>
       <c r="H252" t="n">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="J252" t="inlineStr">
         <is>
-          <t>FD 07</t>
+          <t>FD 05</t>
         </is>
       </c>
       <c r="K252" t="inlineStr">
@@ -21364,13 +21364,13 @@
         <v>0</v>
       </c>
       <c r="R252" t="n">
-        <v>832056</v>
+        <v>1014836</v>
       </c>
       <c r="S252" t="n">
         <v>0</v>
       </c>
       <c r="T252" t="n">
-        <v>647944</v>
+        <v>465164</v>
       </c>
       <c r="U252" t="n">
         <v>0</v>
@@ -21408,11 +21408,11 @@
         <v>0</v>
       </c>
       <c r="H253" t="n">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="J253" t="inlineStr">
         <is>
-          <t>FD 08</t>
+          <t>FD 06</t>
         </is>
       </c>
       <c r="K253" t="inlineStr">
@@ -21447,13 +21447,13 @@
         <v>0</v>
       </c>
       <c r="R253" t="n">
-        <v>832056</v>
+        <v>1014836</v>
       </c>
       <c r="S253" t="n">
         <v>0</v>
       </c>
       <c r="T253" t="n">
-        <v>647944</v>
+        <v>465164</v>
       </c>
       <c r="U253" t="n">
         <v>0</v>
@@ -21491,11 +21491,11 @@
         <v>0</v>
       </c>
       <c r="H254" t="n">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="J254" t="inlineStr">
         <is>
-          <t>FD 09</t>
+          <t>FD 07</t>
         </is>
       </c>
       <c r="K254" t="inlineStr">
@@ -21574,11 +21574,11 @@
         <v>0</v>
       </c>
       <c r="H255" t="n">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="J255" t="inlineStr">
         <is>
-          <t>FD 10</t>
+          <t>FD 08</t>
         </is>
       </c>
       <c r="K255" t="inlineStr">
@@ -21657,11 +21657,11 @@
         <v>0</v>
       </c>
       <c r="H256" t="n">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="J256" t="inlineStr">
         <is>
-          <t>FD 11</t>
+          <t>FD 09</t>
         </is>
       </c>
       <c r="K256" t="inlineStr">
@@ -21696,13 +21696,13 @@
         <v>0</v>
       </c>
       <c r="R256" t="n">
-        <v>457024</v>
+        <v>832056</v>
       </c>
       <c r="S256" t="n">
         <v>0</v>
       </c>
       <c r="T256" t="n">
-        <v>1022976</v>
+        <v>647944</v>
       </c>
       <c r="U256" t="n">
         <v>0</v>
@@ -21740,11 +21740,11 @@
         <v>0</v>
       </c>
       <c r="H257" t="n">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="J257" t="inlineStr">
         <is>
-          <t>FD 12</t>
+          <t>FD 10</t>
         </is>
       </c>
       <c r="K257" t="inlineStr">
@@ -21754,11 +21754,11 @@
       </c>
       <c r="L257" t="inlineStr">
         <is>
-          <t>UNIDADE</t>
+          <t>PORCENTAGEM DE OBRA REALIZADA</t>
         </is>
       </c>
       <c r="M257" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="N257" t="inlineStr">
         <is>
@@ -21779,13 +21779,13 @@
         <v>0</v>
       </c>
       <c r="R257" t="n">
-        <v>457024</v>
+        <v>832056</v>
       </c>
       <c r="S257" t="n">
         <v>0</v>
       </c>
       <c r="T257" t="n">
-        <v>1022976</v>
+        <v>647944</v>
       </c>
       <c r="U257" t="n">
         <v>0</v>
@@ -21823,11 +21823,11 @@
         <v>0</v>
       </c>
       <c r="H258" t="n">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="J258" t="inlineStr">
         <is>
-          <t>FD 13</t>
+          <t>FD 11</t>
         </is>
       </c>
       <c r="K258" t="inlineStr">
@@ -21906,11 +21906,11 @@
         <v>0</v>
       </c>
       <c r="H259" t="n">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="J259" t="inlineStr">
         <is>
-          <t>FD 15</t>
+          <t>FD 12</t>
         </is>
       </c>
       <c r="K259" t="inlineStr">
@@ -21920,11 +21920,11 @@
       </c>
       <c r="L259" t="inlineStr">
         <is>
-          <t>PORCENTAGEM DE OBRA REALIZADA</t>
+          <t>UNIDADE</t>
         </is>
       </c>
       <c r="M259" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="N259" t="inlineStr">
         <is>
@@ -21989,11 +21989,11 @@
         <v>0</v>
       </c>
       <c r="H260" t="n">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="J260" t="inlineStr">
         <is>
-          <t>FD 14</t>
+          <t>FD 13</t>
         </is>
       </c>
       <c r="K260" t="inlineStr">
@@ -22072,11 +22072,11 @@
         <v>0</v>
       </c>
       <c r="H261" t="n">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="J261" t="inlineStr">
         <is>
-          <t>FD 16</t>
+          <t>FD 15</t>
         </is>
       </c>
       <c r="K261" t="inlineStr">
@@ -22111,13 +22111,13 @@
         <v>0</v>
       </c>
       <c r="R261" t="n">
-        <v>142080</v>
+        <v>457024</v>
       </c>
       <c r="S261" t="n">
         <v>0</v>
       </c>
       <c r="T261" t="n">
-        <v>1337920</v>
+        <v>1022976</v>
       </c>
       <c r="U261" t="n">
         <v>0</v>
@@ -22155,11 +22155,11 @@
         <v>0</v>
       </c>
       <c r="H262" t="n">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="J262" t="inlineStr">
         <is>
-          <t>FD 17</t>
+          <t>FD 14</t>
         </is>
       </c>
       <c r="K262" t="inlineStr">
@@ -22194,13 +22194,13 @@
         <v>0</v>
       </c>
       <c r="R262" t="n">
-        <v>142080</v>
+        <v>457024</v>
       </c>
       <c r="S262" t="n">
         <v>0</v>
       </c>
       <c r="T262" t="n">
-        <v>1337920</v>
+        <v>1022976</v>
       </c>
       <c r="U262" t="n">
         <v>0</v>
@@ -22238,11 +22238,11 @@
         <v>0</v>
       </c>
       <c r="H263" t="n">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="J263" t="inlineStr">
         <is>
-          <t>FD 18</t>
+          <t>FD 16</t>
         </is>
       </c>
       <c r="K263" t="inlineStr">
@@ -22321,11 +22321,11 @@
         <v>0</v>
       </c>
       <c r="H264" t="n">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="J264" t="inlineStr">
         <is>
-          <t>FD 19</t>
+          <t>FD 17</t>
         </is>
       </c>
       <c r="K264" t="inlineStr">
@@ -22360,13 +22360,13 @@
         <v>0</v>
       </c>
       <c r="R264" t="n">
-        <v>50000</v>
+        <v>142080</v>
       </c>
       <c r="S264" t="n">
         <v>0</v>
       </c>
       <c r="T264" t="n">
-        <v>1430000</v>
+        <v>1337920</v>
       </c>
       <c r="U264" t="n">
         <v>0</v>
@@ -22404,11 +22404,11 @@
         <v>0</v>
       </c>
       <c r="H265" t="n">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="J265" t="inlineStr">
         <is>
-          <t>FD 20</t>
+          <t>FD 18</t>
         </is>
       </c>
       <c r="K265" t="inlineStr">
@@ -22443,13 +22443,13 @@
         <v>0</v>
       </c>
       <c r="R265" t="n">
-        <v>50000</v>
+        <v>142080</v>
       </c>
       <c r="S265" t="n">
         <v>0</v>
       </c>
       <c r="T265" t="n">
-        <v>1430000</v>
+        <v>1337920</v>
       </c>
       <c r="U265" t="n">
         <v>0</v>
@@ -22487,11 +22487,11 @@
         <v>0</v>
       </c>
       <c r="H266" t="n">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="J266" t="inlineStr">
         <is>
-          <t>BH - DIVERSOS PRÉDIOS - OBRAS E SERVIÇOS EMERGENCIAIS</t>
+          <t>FD 19</t>
         </is>
       </c>
       <c r="K266" t="inlineStr">
@@ -22514,37 +22514,37 @@
       </c>
       <c r="O266" t="inlineStr">
         <is>
-          <t>Região Intermediária de Belo Horizonte</t>
+          <t>Estadual</t>
         </is>
       </c>
       <c r="P266" t="inlineStr">
         <is>
-          <t>BELO HORIZONTE</t>
+          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
         </is>
       </c>
       <c r="Q266" t="n">
         <v>0</v>
       </c>
       <c r="R266" t="n">
-        <v>150000</v>
+        <v>50000</v>
       </c>
       <c r="S266" t="n">
         <v>0</v>
       </c>
       <c r="T266" t="n">
-        <v>150000</v>
+        <v>1430000</v>
       </c>
       <c r="U266" t="n">
         <v>0</v>
       </c>
       <c r="V266" t="n">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="W266" t="n">
         <v>0</v>
       </c>
       <c r="X266" t="n">
-        <v>150000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="267">
@@ -22570,11 +22570,11 @@
         <v>0</v>
       </c>
       <c r="H267" t="n">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="J267" t="inlineStr">
         <is>
-          <t>DIVERSAS COMARCAS - OBRAS E SERVIÇOS EMERGENCIAIS</t>
+          <t>FD 20</t>
         </is>
       </c>
       <c r="K267" t="inlineStr">
@@ -22609,25 +22609,25 @@
         <v>0</v>
       </c>
       <c r="R267" t="n">
-        <v>150000</v>
+        <v>50000</v>
       </c>
       <c r="S267" t="n">
         <v>0</v>
       </c>
       <c r="T267" t="n">
-        <v>150000</v>
+        <v>1430000</v>
       </c>
       <c r="U267" t="n">
         <v>0</v>
       </c>
       <c r="V267" t="n">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="W267" t="n">
         <v>0</v>
       </c>
       <c r="X267" t="n">
-        <v>150000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="268">
@@ -22653,11 +22653,11 @@
         <v>0</v>
       </c>
       <c r="H268" t="n">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="J268" t="inlineStr">
         <is>
-          <t>DIVERSAS COMARCAS - PROJETOS DIVERSOS</t>
+          <t>BH - DIVERSOS PRÉDIOS - OBRAS E SERVIÇOS EMERGENCIAIS</t>
         </is>
       </c>
       <c r="K268" t="inlineStr">
@@ -22680,12 +22680,12 @@
       </c>
       <c r="O268" t="inlineStr">
         <is>
-          <t>Estadual</t>
+          <t>Região Intermediária de Belo Horizonte</t>
         </is>
       </c>
       <c r="P268" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
+          <t>BELO HORIZONTE</t>
         </is>
       </c>
       <c r="Q268" t="n">
@@ -22736,11 +22736,11 @@
         <v>0</v>
       </c>
       <c r="H269" t="n">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="J269" t="inlineStr">
         <is>
-          <t>BH ED. SEDE REFORMA HELIPONTO</t>
+          <t>DIVERSAS COMARCAS - OBRAS E SERVIÇOS EMERGENCIAIS</t>
         </is>
       </c>
       <c r="K269" t="inlineStr">
@@ -22763,85 +22763,82 @@
       </c>
       <c r="O269" t="inlineStr">
         <is>
-          <t>Região Intermediária de Belo Horizonte</t>
+          <t>Estadual</t>
         </is>
       </c>
       <c r="P269" t="inlineStr">
         <is>
-          <t>BELO HORIZONTE</t>
+          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
         </is>
       </c>
       <c r="Q269" t="n">
         <v>0</v>
       </c>
       <c r="R269" t="n">
-        <v>1577516</v>
+        <v>150000</v>
       </c>
       <c r="S269" t="n">
         <v>0</v>
       </c>
       <c r="T269" t="n">
-        <v>0</v>
+        <v>150000</v>
       </c>
       <c r="U269" t="n">
         <v>0</v>
       </c>
       <c r="V269" t="n">
-        <v>0</v>
+        <v>150000</v>
       </c>
       <c r="W269" t="n">
         <v>0</v>
       </c>
       <c r="X269" t="n">
-        <v>0</v>
+        <v>150000</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="n">
-        <v>4291</v>
+        <v>4031</v>
       </c>
       <c r="B270" t="n">
+        <v>2</v>
+      </c>
+      <c r="C270" t="n">
+        <v>61</v>
+      </c>
+      <c r="D270" t="n">
+        <v>706</v>
+      </c>
+      <c r="E270" t="n">
+        <v>2091</v>
+      </c>
+      <c r="F270" t="n">
+        <v>1</v>
+      </c>
+      <c r="G270" t="n">
+        <v>0</v>
+      </c>
+      <c r="H270" t="n">
+        <v>461</v>
+      </c>
+      <c r="J270" t="inlineStr">
+        <is>
+          <t>DIVERSAS COMARCAS - PROJETOS DIVERSOS</t>
+        </is>
+      </c>
+      <c r="K270" t="inlineStr">
+        <is>
+          <t>INICIANDO</t>
+        </is>
+      </c>
+      <c r="L270" t="inlineStr">
+        <is>
+          <t>PORCENTAGEM DE OBRA REALIZADA</t>
+        </is>
+      </c>
+      <c r="M270" t="n">
         <v>10</v>
       </c>
-      <c r="C270" t="n">
-        <v>122</v>
-      </c>
-      <c r="D270" t="n">
-        <v>59</v>
-      </c>
-      <c r="E270" t="n">
-        <v>2024</v>
-      </c>
-      <c r="F270" t="n">
-        <v>1</v>
-      </c>
-      <c r="G270" t="n">
-        <v>0</v>
-      </c>
-      <c r="H270" t="n">
-        <v>120</v>
-      </c>
-      <c r="I270" t="n">
-        <v>11288</v>
-      </c>
-      <c r="J270" t="inlineStr">
-        <is>
-          <t>Reforma da estrutura física da sede administrativa da Unidade de Saúde de Teófilo Otoni.</t>
-        </is>
-      </c>
-      <c r="K270" t="inlineStr">
-        <is>
-          <t>INICIANDO</t>
-        </is>
-      </c>
-      <c r="L270" t="inlineStr">
-        <is>
-          <t>UNIDADE</t>
-        </is>
-      </c>
-      <c r="M270" t="n">
-        <v>1</v>
-      </c>
       <c r="N270" t="inlineStr">
         <is>
           <t>Sim</t>
@@ -22849,85 +22846,82 @@
       </c>
       <c r="O270" t="inlineStr">
         <is>
-          <t>Região Intermediária de Teófilo Otoni</t>
+          <t>Estadual</t>
         </is>
       </c>
       <c r="P270" t="inlineStr">
         <is>
-          <t>TEÓFILO OTONI</t>
+          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
         </is>
       </c>
       <c r="Q270" t="n">
-        <v>540000</v>
+        <v>0</v>
       </c>
       <c r="R270" t="n">
-        <v>0</v>
+        <v>150000</v>
       </c>
       <c r="S270" t="n">
         <v>0</v>
       </c>
       <c r="T270" t="n">
-        <v>0</v>
+        <v>150000</v>
       </c>
       <c r="U270" t="n">
         <v>0</v>
       </c>
       <c r="V270" t="n">
-        <v>0</v>
+        <v>150000</v>
       </c>
       <c r="W270" t="n">
         <v>0</v>
       </c>
       <c r="X270" t="n">
-        <v>0</v>
+        <v>150000</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="n">
-        <v>4291</v>
+        <v>4031</v>
       </c>
       <c r="B271" t="n">
+        <v>2</v>
+      </c>
+      <c r="C271" t="n">
+        <v>61</v>
+      </c>
+      <c r="D271" t="n">
+        <v>706</v>
+      </c>
+      <c r="E271" t="n">
+        <v>2091</v>
+      </c>
+      <c r="F271" t="n">
+        <v>1</v>
+      </c>
+      <c r="G271" t="n">
+        <v>0</v>
+      </c>
+      <c r="H271" t="n">
+        <v>462</v>
+      </c>
+      <c r="J271" t="inlineStr">
+        <is>
+          <t>BH ED. SEDE REFORMA HELIPONTO</t>
+        </is>
+      </c>
+      <c r="K271" t="inlineStr">
+        <is>
+          <t>INICIANDO</t>
+        </is>
+      </c>
+      <c r="L271" t="inlineStr">
+        <is>
+          <t>PORCENTAGEM DE OBRA REALIZADA</t>
+        </is>
+      </c>
+      <c r="M271" t="n">
         <v>10</v>
       </c>
-      <c r="C271" t="n">
-        <v>122</v>
-      </c>
-      <c r="D271" t="n">
-        <v>59</v>
-      </c>
-      <c r="E271" t="n">
-        <v>2024</v>
-      </c>
-      <c r="F271" t="n">
-        <v>1</v>
-      </c>
-      <c r="G271" t="n">
-        <v>0</v>
-      </c>
-      <c r="H271" t="n">
-        <v>122</v>
-      </c>
-      <c r="I271" t="n">
-        <v>11285</v>
-      </c>
-      <c r="J271" t="inlineStr">
-        <is>
-          <t>Reforma da estrutura física da sede administrativa da Unidade Regional de Saúde de Uberlândia.</t>
-        </is>
-      </c>
-      <c r="K271" t="inlineStr">
-        <is>
-          <t>INICIANDO</t>
-        </is>
-      </c>
-      <c r="L271" t="inlineStr">
-        <is>
-          <t>UNIDADE</t>
-        </is>
-      </c>
-      <c r="M271" t="n">
-        <v>1</v>
-      </c>
       <c r="N271" t="inlineStr">
         <is>
           <t>Sim</t>
@@ -22935,19 +22929,19 @@
       </c>
       <c r="O271" t="inlineStr">
         <is>
-          <t>Região Intermediária de Uberlândia</t>
+          <t>Região Intermediária de Belo Horizonte</t>
         </is>
       </c>
       <c r="P271" t="inlineStr">
         <is>
-          <t>UBERLÂNDIA</t>
+          <t>BELO HORIZONTE</t>
         </is>
       </c>
       <c r="Q271" t="n">
-        <v>120000</v>
+        <v>0</v>
       </c>
       <c r="R271" t="n">
-        <v>0</v>
+        <v>1577516</v>
       </c>
       <c r="S271" t="n">
         <v>0</v>
@@ -22991,14 +22985,14 @@
         <v>0</v>
       </c>
       <c r="H272" t="n">
-        <v>129</v>
+        <v>120</v>
       </c>
       <c r="I272" t="n">
-        <v>11289</v>
+        <v>11288</v>
       </c>
       <c r="J272" t="inlineStr">
         <is>
-          <t>Reforma da estrutura física da sede administrativa da Unidade de Saúde de Barbacena.</t>
+          <t>Reforma da estrutura física da sede administrativa da Unidade de Saúde de Teófilo Otoni.</t>
         </is>
       </c>
       <c r="K272" t="inlineStr">
@@ -23021,16 +23015,16 @@
       </c>
       <c r="O272" t="inlineStr">
         <is>
-          <t>Região Intermediária de Barbacena</t>
+          <t>Região Intermediária de Teófilo Otoni</t>
         </is>
       </c>
       <c r="P272" t="inlineStr">
         <is>
-          <t>BARBACENA</t>
+          <t>TEÓFILO OTONI</t>
         </is>
       </c>
       <c r="Q272" t="n">
-        <v>50000</v>
+        <v>540000</v>
       </c>
       <c r="R272" t="n">
         <v>0</v>
@@ -23077,14 +23071,14 @@
         <v>0</v>
       </c>
       <c r="H273" t="n">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="I273" t="n">
-        <v>11286</v>
+        <v>11285</v>
       </c>
       <c r="J273" t="inlineStr">
         <is>
-          <t>Reforma da estrutura física da sede administrativa da Unidade Regional de Saúde de Uberaba.</t>
+          <t>Reforma da estrutura física da sede administrativa da Unidade Regional de Saúde de Uberlândia.</t>
         </is>
       </c>
       <c r="K273" t="inlineStr">
@@ -23107,12 +23101,12 @@
       </c>
       <c r="O273" t="inlineStr">
         <is>
-          <t>Região Intermediária de Uberaba</t>
+          <t>Região Intermediária de Uberlândia</t>
         </is>
       </c>
       <c r="P273" t="inlineStr">
         <is>
-          <t>UBERABA</t>
+          <t>UBERLÂNDIA</t>
         </is>
       </c>
       <c r="Q273" t="n">
@@ -23163,14 +23157,14 @@
         <v>0</v>
       </c>
       <c r="H274" t="n">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="I274" t="n">
-        <v>11292</v>
+        <v>11289</v>
       </c>
       <c r="J274" t="inlineStr">
         <is>
-          <t>Reforma da estrutura física da sede administrativa da Unidade de Saúde de Ubá.</t>
+          <t>Reforma da estrutura física da sede administrativa da Unidade de Saúde de Barbacena.</t>
         </is>
       </c>
       <c r="K274" t="inlineStr">
@@ -23193,16 +23187,16 @@
       </c>
       <c r="O274" t="inlineStr">
         <is>
-          <t>Região Intermediária de Juíz de Fora</t>
+          <t>Região Intermediária de Barbacena</t>
         </is>
       </c>
       <c r="P274" t="inlineStr">
         <is>
-          <t>UBÁ</t>
+          <t>BARBACENA</t>
         </is>
       </c>
       <c r="Q274" t="n">
-        <v>120000</v>
+        <v>50000</v>
       </c>
       <c r="R274" t="n">
         <v>0</v>
@@ -23249,14 +23243,14 @@
         <v>0</v>
       </c>
       <c r="H275" t="n">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="I275" t="n">
-        <v>11291</v>
+        <v>11286</v>
       </c>
       <c r="J275" t="inlineStr">
         <is>
-          <t>Reforma da estrutura física da sede administrativa da Unidade de Saúde de São João Del Rei.</t>
+          <t>Reforma da estrutura física da sede administrativa da Unidade Regional de Saúde de Uberaba.</t>
         </is>
       </c>
       <c r="K275" t="inlineStr">
@@ -23279,12 +23273,12 @@
       </c>
       <c r="O275" t="inlineStr">
         <is>
-          <t>Região Intermediária de Barbacena</t>
+          <t>Região Intermediária de Uberaba</t>
         </is>
       </c>
       <c r="P275" t="inlineStr">
         <is>
-          <t>SÃO JOÃO DEL REI</t>
+          <t>UBERABA</t>
         </is>
       </c>
       <c r="Q275" t="n">
@@ -23314,19 +23308,19 @@
     </row>
     <row r="276">
       <c r="A276" t="n">
-        <v>4381</v>
+        <v>4291</v>
       </c>
       <c r="B276" t="n">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="C276" t="n">
-        <v>782</v>
+        <v>122</v>
       </c>
       <c r="D276" t="n">
-        <v>82</v>
+        <v>59</v>
       </c>
       <c r="E276" t="n">
-        <v>4382</v>
+        <v>2024</v>
       </c>
       <c r="F276" t="n">
         <v>1</v>
@@ -23335,11 +23329,14 @@
         <v>0</v>
       </c>
       <c r="H276" t="n">
-        <v>328</v>
+        <v>131</v>
+      </c>
+      <c r="I276" t="n">
+        <v>11292</v>
       </c>
       <c r="J276" t="inlineStr">
         <is>
-          <t>SEGURANÇA VIÁRIA DE DIVERSOS TRECHOS</t>
+          <t>Reforma da estrutura física da sede administrativa da Unidade de Saúde de Ubá.</t>
         </is>
       </c>
       <c r="K276" t="inlineStr">
@@ -23353,28 +23350,28 @@
         </is>
       </c>
       <c r="M276" t="n">
-        <v>200</v>
+        <v>1</v>
       </c>
       <c r="N276" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="O276" t="inlineStr">
         <is>
-          <t>Estadual</t>
+          <t>Região Intermediária de Juíz de Fora</t>
         </is>
       </c>
       <c r="P276" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
+          <t>UBÁ</t>
         </is>
       </c>
       <c r="Q276" t="n">
-        <v>0</v>
+        <v>120000</v>
       </c>
       <c r="R276" t="n">
-        <v>20000000</v>
+        <v>0</v>
       </c>
       <c r="S276" t="n">
         <v>0</v>
@@ -23397,32 +23394,35 @@
     </row>
     <row r="277">
       <c r="A277" t="n">
-        <v>5031</v>
+        <v>4291</v>
       </c>
       <c r="B277" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="C277" t="n">
-        <v>572</v>
+        <v>122</v>
       </c>
       <c r="D277" t="n">
-        <v>133</v>
+        <v>59</v>
       </c>
       <c r="E277" t="n">
-        <v>3015</v>
+        <v>2024</v>
       </c>
       <c r="F277" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G277" t="n">
         <v>0</v>
       </c>
       <c r="H277" t="n">
-        <v>4</v>
+        <v>132</v>
+      </c>
+      <c r="I277" t="n">
+        <v>11291</v>
       </c>
       <c r="J277" t="inlineStr">
         <is>
-          <t>ARAXÁ</t>
+          <t>Reforma da estrutura física da sede administrativa da Unidade de Saúde de São João Del Rei.</t>
         </is>
       </c>
       <c r="K277" t="inlineStr">
@@ -23440,24 +23440,24 @@
       </c>
       <c r="N277" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="O277" t="inlineStr">
         <is>
-          <t>Região Intermediária de Uberaba</t>
+          <t>Região Intermediária de Barbacena</t>
         </is>
       </c>
       <c r="P277" t="inlineStr">
         <is>
-          <t>ARAXÁ</t>
+          <t>SÃO JOÃO DEL REI</t>
         </is>
       </c>
       <c r="Q277" t="n">
-        <v>0</v>
+        <v>120000</v>
       </c>
       <c r="R277" t="n">
-        <v>6380000</v>
+        <v>0</v>
       </c>
       <c r="S277" t="n">
         <v>0</v>
@@ -23480,32 +23480,32 @@
     </row>
     <row r="278">
       <c r="A278" t="n">
-        <v>5081</v>
+        <v>4381</v>
       </c>
       <c r="B278" t="n">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="C278" t="n">
-        <v>512</v>
+        <v>782</v>
       </c>
       <c r="D278" t="n">
-        <v>21</v>
+        <v>82</v>
       </c>
       <c r="E278" t="n">
-        <v>8008</v>
+        <v>4382</v>
       </c>
       <c r="F278" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G278" t="n">
         <v>0</v>
       </c>
       <c r="H278" t="n">
-        <v>146</v>
+        <v>328</v>
       </c>
       <c r="J278" t="inlineStr">
         <is>
-          <t>IMPLANTAÇÃO OU AMPLIAÇÃO REALIZADA EM SISTEMAS DE ABASTECIMENTO DE ÁGUA QUE PODEM CONTEMPLAR SISTEMA PRODUTOR QUE PODE SER ATRAVÉS DE POÇO PROFUNDO OU CAPTAÇÃO SUPERFICIAL, ESTAÇÃO DE TRATAMENTO DE ÁGUA, ADUTORAS, ESTAÇÕES ELEVATÓRIAS, RESERVATÓRIOS E REDES DE DISTRIBUIÇÃO DE ÁGUA PARA OPERAÇÃO DAS UNIDADES DE TRATAMENTO E DISTRIBUIÇÃO DE ÁGUA TRATADA EM LOCALIDADES QUE A COPASA TENHA OU VENHA A TER A CONCESSÃO PARA O SERVIÇO DE ABASTECIMENTO DE ÁGUA. IMPLANTAÇÃO OU AMPLIAÇÃO REALIZADA EM SISTEMAS DE ESGOTAMENTO SANITÁRIO QUE PODEM CONTEMPLAR ESTAÇÃO DE TRATAMENTO DE ESGOTO, ESTAÇÕES ELEVATÓRIAS, INTERCEPTORES E REDES COLETORAS PARA OPERAÇÃO DAS UNIDADES DE COLETA E TRATAMENTO DE ESGOTO EM LOCALIDADES QUE A COPASA TENHA OU VENHA A TER A CONCESSÃO PARA O SERVIÇO DE ESGOTAMENTO SANITÁRIO.</t>
+          <t>SEGURANÇA VIÁRIA DE DIVERSOS TRECHOS</t>
         </is>
       </c>
       <c r="K278" t="inlineStr">
@@ -23515,11 +23515,11 @@
       </c>
       <c r="L278" t="inlineStr">
         <is>
-          <t>ECONOMIA RESIDENCIAL</t>
+          <t>UNIDADE</t>
         </is>
       </c>
       <c r="M278" t="n">
-        <v>95000</v>
+        <v>200</v>
       </c>
       <c r="N278" t="inlineStr">
         <is>
@@ -23540,42 +23540,42 @@
         <v>0</v>
       </c>
       <c r="R278" t="n">
-        <v>1388000000</v>
+        <v>20000000</v>
       </c>
       <c r="S278" t="n">
         <v>0</v>
       </c>
       <c r="T278" t="n">
-        <v>1388000000</v>
+        <v>0</v>
       </c>
       <c r="U278" t="n">
         <v>0</v>
       </c>
       <c r="V278" t="n">
-        <v>1388000000</v>
+        <v>0</v>
       </c>
       <c r="W278" t="n">
         <v>0</v>
       </c>
       <c r="X278" t="n">
-        <v>1388000000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="n">
-        <v>5081</v>
+        <v>5031</v>
       </c>
       <c r="B279" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C279" t="n">
-        <v>512</v>
+        <v>572</v>
       </c>
       <c r="D279" t="n">
-        <v>21</v>
+        <v>133</v>
       </c>
       <c r="E279" t="n">
-        <v>8009</v>
+        <v>3015</v>
       </c>
       <c r="F279" t="n">
         <v>0</v>
@@ -23584,11 +23584,11 @@
         <v>0</v>
       </c>
       <c r="H279" t="n">
-        <v>147</v>
+        <v>4</v>
       </c>
       <c r="J279" t="inlineStr">
         <is>
-          <t>AMPLIAÇÃO REALIZADA, OPERAÇÃO, MANUTENÇÃO E CONSERVAÇÃO DAS UNIDADES DE ADUÇÃO DO SISTEMA PRODUTOR RIO MANSO; REVERSÃO DOS ATIVOS À COMPANHIA DE SANEAMENTO DE MINAS GERAIS.</t>
+          <t>ARAXÁ</t>
         </is>
       </c>
       <c r="K279" t="inlineStr">
@@ -23598,7 +23598,7 @@
       </c>
       <c r="L279" t="inlineStr">
         <is>
-          <t>METRO CÚBICO P/ SEGUNDO</t>
+          <t>UNIDADE</t>
         </is>
       </c>
       <c r="M279" t="n">
@@ -23611,54 +23611,54 @@
       </c>
       <c r="O279" t="inlineStr">
         <is>
-          <t>Região Intermediária de Belo Horizonte</t>
+          <t>Região Intermediária de Uberaba</t>
         </is>
       </c>
       <c r="P279" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE BELO HORIZONTE</t>
+          <t>ARAXÁ</t>
         </is>
       </c>
       <c r="Q279" t="n">
         <v>0</v>
       </c>
       <c r="R279" t="n">
-        <v>48428689</v>
+        <v>6380000</v>
       </c>
       <c r="S279" t="n">
         <v>0</v>
       </c>
       <c r="T279" t="n">
-        <v>43803484</v>
+        <v>0</v>
       </c>
       <c r="U279" t="n">
         <v>0</v>
       </c>
       <c r="V279" t="n">
-        <v>42450254</v>
+        <v>0</v>
       </c>
       <c r="W279" t="n">
         <v>0</v>
       </c>
       <c r="X279" t="n">
-        <v>40450254</v>
+        <v>0</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="n">
-        <v>5141</v>
+        <v>5081</v>
       </c>
       <c r="B280" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="C280" t="n">
-        <v>126</v>
+        <v>512</v>
       </c>
       <c r="D280" t="n">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="E280" t="n">
-        <v>6006</v>
+        <v>8008</v>
       </c>
       <c r="F280" t="n">
         <v>0</v>
@@ -23667,11 +23667,11 @@
         <v>0</v>
       </c>
       <c r="H280" t="n">
-        <v>51</v>
+        <v>146</v>
       </c>
       <c r="J280" t="inlineStr">
         <is>
-          <t>ELABORAÇÃO E EXECUÇÃO DE PROJETOS RELACIONADOS À REFORMA, MODERNIZAÇÃO E ADEQUAÇÃO DAS INSTALAÇÕES PREDIAIS DA COMPANHIA.</t>
+          <t>IMPLANTAÇÃO OU AMPLIAÇÃO REALIZADA EM SISTEMAS DE ABASTECIMENTO DE ÁGUA QUE PODEM CONTEMPLAR SISTEMA PRODUTOR QUE PODE SER ATRAVÉS DE POÇO PROFUNDO OU CAPTAÇÃO SUPERFICIAL, ESTAÇÃO DE TRATAMENTO DE ÁGUA, ADUTORAS, ESTAÇÕES ELEVATÓRIAS, RESERVATÓRIOS E REDES DE DISTRIBUIÇÃO DE ÁGUA PARA OPERAÇÃO DAS UNIDADES DE TRATAMENTO E DISTRIBUIÇÃO DE ÁGUA TRATADA EM LOCALIDADES QUE A COPASA TENHA OU VENHA A TER A CONCESSÃO PARA O SERVIÇO DE ABASTECIMENTO DE ÁGUA. IMPLANTAÇÃO OU AMPLIAÇÃO REALIZADA EM SISTEMAS DE ESGOTAMENTO SANITÁRIO QUE PODEM CONTEMPLAR ESTAÇÃO DE TRATAMENTO DE ESGOTO, ESTAÇÕES ELEVATÓRIAS, INTERCEPTORES E REDES COLETORAS PARA OPERAÇÃO DAS UNIDADES DE COLETA E TRATAMENTO DE ESGOTO EM LOCALIDADES QUE A COPASA TENHA OU VENHA A TER A CONCESSÃO PARA O SERVIÇO DE ESGOTAMENTO SANITÁRIO.</t>
         </is>
       </c>
       <c r="K280" t="inlineStr">
@@ -23681,11 +23681,11 @@
       </c>
       <c r="L280" t="inlineStr">
         <is>
-          <t>PERCENTUAL</t>
+          <t>ECONOMIA RESIDENCIAL</t>
         </is>
       </c>
       <c r="M280" t="n">
-        <v>100</v>
+        <v>95000</v>
       </c>
       <c r="N280" t="inlineStr">
         <is>
@@ -23706,42 +23706,42 @@
         <v>0</v>
       </c>
       <c r="R280" t="n">
-        <v>13233200</v>
+        <v>1388000000</v>
       </c>
       <c r="S280" t="n">
         <v>0</v>
       </c>
       <c r="T280" t="n">
-        <v>6250000</v>
+        <v>1388000000</v>
       </c>
       <c r="U280" t="n">
         <v>0</v>
       </c>
       <c r="V280" t="n">
-        <v>3250000</v>
+        <v>1388000000</v>
       </c>
       <c r="W280" t="n">
         <v>0</v>
       </c>
       <c r="X280" t="n">
-        <v>3250000</v>
+        <v>1388000000</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="n">
-        <v>5251</v>
+        <v>5081</v>
       </c>
       <c r="B281" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="C281" t="n">
-        <v>121</v>
+        <v>512</v>
       </c>
       <c r="D281" t="n">
-        <v>133</v>
+        <v>21</v>
       </c>
       <c r="E281" t="n">
-        <v>3018</v>
+        <v>8009</v>
       </c>
       <c r="F281" t="n">
         <v>0</v>
@@ -23750,11 +23750,11 @@
         <v>0</v>
       </c>
       <c r="H281" t="n">
-        <v>3</v>
+        <v>147</v>
       </c>
       <c r="J281" t="inlineStr">
         <is>
-          <t>EXPANSÃO DA INFRAESTRUTURA DE DISTRIBUIÇÃO DE GÁS NATURAL, EM GASODUTOS VIRTUAIS E PRIMÁRIOS, EM MINAS GERAIS.</t>
+          <t>AMPLIAÇÃO REALIZADA, OPERAÇÃO, MANUTENÇÃO E CONSERVAÇÃO DAS UNIDADES DE ADUÇÃO DO SISTEMA PRODUTOR RIO MANSO; REVERSÃO DOS ATIVOS À COMPANHIA DE SANEAMENTO DE MINAS GERAIS.</t>
         </is>
       </c>
       <c r="K281" t="inlineStr">
@@ -23764,11 +23764,11 @@
       </c>
       <c r="L281" t="inlineStr">
         <is>
-          <t>AÇÃO</t>
+          <t>METRO CÚBICO P/ SEGUNDO</t>
         </is>
       </c>
       <c r="M281" t="n">
-        <v>163</v>
+        <v>1</v>
       </c>
       <c r="N281" t="inlineStr">
         <is>
@@ -23782,49 +23782,49 @@
       </c>
       <c r="P281" t="inlineStr">
         <is>
-          <t>BELO HORIZONTE</t>
+          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE BELO HORIZONTE</t>
         </is>
       </c>
       <c r="Q281" t="n">
         <v>0</v>
       </c>
       <c r="R281" t="n">
-        <v>285487805</v>
+        <v>48428689</v>
       </c>
       <c r="S281" t="n">
         <v>0</v>
       </c>
       <c r="T281" t="n">
-        <v>192101111</v>
+        <v>43803484</v>
       </c>
       <c r="U281" t="n">
         <v>0</v>
       </c>
       <c r="V281" t="n">
-        <v>279542051</v>
+        <v>42450254</v>
       </c>
       <c r="W281" t="n">
         <v>0</v>
       </c>
       <c r="X281" t="n">
-        <v>393567557</v>
+        <v>40450254</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="n">
-        <v>5391</v>
+        <v>5141</v>
       </c>
       <c r="B282" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="C282" t="n">
-        <v>752</v>
+        <v>126</v>
       </c>
       <c r="D282" t="n">
-        <v>92</v>
+        <v>30</v>
       </c>
       <c r="E282" t="n">
-        <v>3004</v>
+        <v>6006</v>
       </c>
       <c r="F282" t="n">
         <v>0</v>
@@ -23833,11 +23833,11 @@
         <v>0</v>
       </c>
       <c r="H282" t="n">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="J282" t="inlineStr">
         <is>
-          <t>EXPANSÃO E AQUISIÇÃO DO SISTEMA DE TRANSMISSÃO</t>
+          <t>ELABORAÇÃO E EXECUÇÃO DE PROJETOS RELACIONADOS À REFORMA, MODERNIZAÇÃO E ADEQUAÇÃO DAS INSTALAÇÕES PREDIAIS DA COMPANHIA.</t>
         </is>
       </c>
       <c r="K282" t="inlineStr">
@@ -23847,11 +23847,11 @@
       </c>
       <c r="L282" t="inlineStr">
         <is>
-          <t>UNIDADE</t>
+          <t>PERCENTUAL</t>
         </is>
       </c>
       <c r="M282" t="n">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="N282" t="inlineStr">
         <is>
@@ -23860,54 +23860,54 @@
       </c>
       <c r="O282" t="inlineStr">
         <is>
-          <t>Região Intermediária de Barbacena</t>
+          <t>Estadual</t>
         </is>
       </c>
       <c r="P282" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE BARBACENA</t>
+          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
         </is>
       </c>
       <c r="Q282" t="n">
         <v>0</v>
       </c>
       <c r="R282" t="n">
-        <v>2755</v>
+        <v>13233200</v>
       </c>
       <c r="S282" t="n">
         <v>0</v>
       </c>
       <c r="T282" t="n">
-        <v>0</v>
+        <v>6250000</v>
       </c>
       <c r="U282" t="n">
         <v>0</v>
       </c>
       <c r="V282" t="n">
-        <v>0</v>
+        <v>3250000</v>
       </c>
       <c r="W282" t="n">
         <v>0</v>
       </c>
       <c r="X282" t="n">
-        <v>0</v>
+        <v>3250000</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="n">
-        <v>5391</v>
+        <v>5251</v>
       </c>
       <c r="B283" t="n">
         <v>25</v>
       </c>
       <c r="C283" t="n">
-        <v>752</v>
+        <v>121</v>
       </c>
       <c r="D283" t="n">
-        <v>92</v>
+        <v>133</v>
       </c>
       <c r="E283" t="n">
-        <v>3004</v>
+        <v>3018</v>
       </c>
       <c r="F283" t="n">
         <v>0</v>
@@ -23916,11 +23916,11 @@
         <v>0</v>
       </c>
       <c r="H283" t="n">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="J283" t="inlineStr">
         <is>
-          <t>EXPANSÃO E AQUISIÇÃO DO SISTEMA DE TRANSMISSÃO</t>
+          <t>EXPANSÃO DA INFRAESTRUTURA DE DISTRIBUIÇÃO DE GÁS NATURAL, EM GASODUTOS VIRTUAIS E PRIMÁRIOS, EM MINAS GERAIS.</t>
         </is>
       </c>
       <c r="K283" t="inlineStr">
@@ -23930,11 +23930,11 @@
       </c>
       <c r="L283" t="inlineStr">
         <is>
-          <t>UNIDADE</t>
+          <t>AÇÃO</t>
         </is>
       </c>
       <c r="M283" t="n">
-        <v>5</v>
+        <v>163</v>
       </c>
       <c r="N283" t="inlineStr">
         <is>
@@ -23948,32 +23948,32 @@
       </c>
       <c r="P283" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE BELO HORIZONTE</t>
+          <t>BELO HORIZONTE</t>
         </is>
       </c>
       <c r="Q283" t="n">
         <v>0</v>
       </c>
       <c r="R283" t="n">
-        <v>16917549</v>
+        <v>285487805</v>
       </c>
       <c r="S283" t="n">
         <v>0</v>
       </c>
       <c r="T283" t="n">
-        <v>371590</v>
+        <v>192101111</v>
       </c>
       <c r="U283" t="n">
         <v>0</v>
       </c>
       <c r="V283" t="n">
-        <v>0</v>
+        <v>279542051</v>
       </c>
       <c r="W283" t="n">
         <v>0</v>
       </c>
       <c r="X283" t="n">
-        <v>0</v>
+        <v>393567557</v>
       </c>
     </row>
     <row r="284">
@@ -23999,7 +23999,7 @@
         <v>0</v>
       </c>
       <c r="H284" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="J284" t="inlineStr">
         <is>
@@ -24017,7 +24017,7 @@
         </is>
       </c>
       <c r="M284" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N284" t="inlineStr">
         <is>
@@ -24026,37 +24026,37 @@
       </c>
       <c r="O284" t="inlineStr">
         <is>
-          <t>Região Intermediária de Divinópolis</t>
+          <t>Região Intermediária de Barbacena</t>
         </is>
       </c>
       <c r="P284" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE DIVINÓPOLIS</t>
+          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE BARBACENA</t>
         </is>
       </c>
       <c r="Q284" t="n">
         <v>0</v>
       </c>
       <c r="R284" t="n">
-        <v>62676806</v>
+        <v>2755</v>
       </c>
       <c r="S284" t="n">
         <v>0</v>
       </c>
       <c r="T284" t="n">
-        <v>115118832</v>
+        <v>0</v>
       </c>
       <c r="U284" t="n">
         <v>0</v>
       </c>
       <c r="V284" t="n">
-        <v>79688927</v>
+        <v>0</v>
       </c>
       <c r="W284" t="n">
         <v>0</v>
       </c>
       <c r="X284" t="n">
-        <v>283680</v>
+        <v>0</v>
       </c>
     </row>
     <row r="285">
@@ -24082,7 +24082,7 @@
         <v>0</v>
       </c>
       <c r="H285" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J285" t="inlineStr">
         <is>
@@ -24100,7 +24100,7 @@
         </is>
       </c>
       <c r="M285" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="N285" t="inlineStr">
         <is>
@@ -24109,25 +24109,25 @@
       </c>
       <c r="O285" t="inlineStr">
         <is>
-          <t>Região Intermediária de Governador Valadares</t>
+          <t>Região Intermediária de Belo Horizonte</t>
         </is>
       </c>
       <c r="P285" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE GOVERNADOR VALADARES</t>
+          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE BELO HORIZONTE</t>
         </is>
       </c>
       <c r="Q285" t="n">
         <v>0</v>
       </c>
       <c r="R285" t="n">
-        <v>20902948</v>
+        <v>16917549</v>
       </c>
       <c r="S285" t="n">
         <v>0</v>
       </c>
       <c r="T285" t="n">
-        <v>69651136</v>
+        <v>371590</v>
       </c>
       <c r="U285" t="n">
         <v>0</v>
@@ -24165,7 +24165,7 @@
         <v>0</v>
       </c>
       <c r="H286" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="J286" t="inlineStr">
         <is>
@@ -24183,7 +24183,7 @@
         </is>
       </c>
       <c r="M286" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N286" t="inlineStr">
         <is>
@@ -24192,37 +24192,37 @@
       </c>
       <c r="O286" t="inlineStr">
         <is>
-          <t>Região Intermediária de Ipatinga</t>
+          <t>Região Intermediária de Divinópolis</t>
         </is>
       </c>
       <c r="P286" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE IPATINGA</t>
+          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE DIVINÓPOLIS</t>
         </is>
       </c>
       <c r="Q286" t="n">
         <v>0</v>
       </c>
       <c r="R286" t="n">
-        <v>7399783</v>
+        <v>62676806</v>
       </c>
       <c r="S286" t="n">
         <v>0</v>
       </c>
       <c r="T286" t="n">
-        <v>8267000</v>
+        <v>115118832</v>
       </c>
       <c r="U286" t="n">
         <v>0</v>
       </c>
       <c r="V286" t="n">
-        <v>0</v>
+        <v>79688927</v>
       </c>
       <c r="W286" t="n">
         <v>0</v>
       </c>
       <c r="X286" t="n">
-        <v>0</v>
+        <v>283680</v>
       </c>
     </row>
     <row r="287">
@@ -24248,7 +24248,7 @@
         <v>0</v>
       </c>
       <c r="H287" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="J287" t="inlineStr">
         <is>
@@ -24275,37 +24275,37 @@
       </c>
       <c r="O287" t="inlineStr">
         <is>
-          <t>Região Intermediária de Juíz de Fora</t>
+          <t>Região Intermediária de Governador Valadares</t>
         </is>
       </c>
       <c r="P287" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE JUÍZ DE FORA</t>
+          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE GOVERNADOR VALADARES</t>
         </is>
       </c>
       <c r="Q287" t="n">
         <v>0</v>
       </c>
       <c r="R287" t="n">
-        <v>9324503</v>
+        <v>20902948</v>
       </c>
       <c r="S287" t="n">
         <v>0</v>
       </c>
       <c r="T287" t="n">
-        <v>2680463</v>
+        <v>69651136</v>
       </c>
       <c r="U287" t="n">
         <v>0</v>
       </c>
       <c r="V287" t="n">
-        <v>664998</v>
+        <v>0</v>
       </c>
       <c r="W287" t="n">
         <v>0</v>
       </c>
       <c r="X287" t="n">
-        <v>504320</v>
+        <v>0</v>
       </c>
     </row>
     <row r="288">
@@ -24331,7 +24331,7 @@
         <v>0</v>
       </c>
       <c r="H288" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="J288" t="inlineStr">
         <is>
@@ -24349,7 +24349,7 @@
         </is>
       </c>
       <c r="M288" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N288" t="inlineStr">
         <is>
@@ -24358,25 +24358,25 @@
       </c>
       <c r="O288" t="inlineStr">
         <is>
-          <t>Região Intermediária de Montes Claros</t>
+          <t>Região Intermediária de Ipatinga</t>
         </is>
       </c>
       <c r="P288" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE MONTES CLAROS</t>
+          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE IPATINGA</t>
         </is>
       </c>
       <c r="Q288" t="n">
         <v>0</v>
       </c>
       <c r="R288" t="n">
-        <v>56185150</v>
+        <v>7399783</v>
       </c>
       <c r="S288" t="n">
         <v>0</v>
       </c>
       <c r="T288" t="n">
-        <v>0</v>
+        <v>8267000</v>
       </c>
       <c r="U288" t="n">
         <v>0</v>
@@ -24414,7 +24414,7 @@
         <v>0</v>
       </c>
       <c r="H289" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="J289" t="inlineStr">
         <is>
@@ -24441,37 +24441,37 @@
       </c>
       <c r="O289" t="inlineStr">
         <is>
-          <t>Região Intermediária de Pouso Alegre</t>
+          <t>Região Intermediária de Juíz de Fora</t>
         </is>
       </c>
       <c r="P289" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE POUSO ALEGRE</t>
+          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE JUÍZ DE FORA</t>
         </is>
       </c>
       <c r="Q289" t="n">
         <v>0</v>
       </c>
       <c r="R289" t="n">
-        <v>1975648</v>
+        <v>9324503</v>
       </c>
       <c r="S289" t="n">
         <v>0</v>
       </c>
       <c r="T289" t="n">
-        <v>0</v>
+        <v>2680463</v>
       </c>
       <c r="U289" t="n">
         <v>0</v>
       </c>
       <c r="V289" t="n">
-        <v>0</v>
+        <v>664998</v>
       </c>
       <c r="W289" t="n">
         <v>0</v>
       </c>
       <c r="X289" t="n">
-        <v>0</v>
+        <v>504320</v>
       </c>
     </row>
     <row r="290">
@@ -24497,7 +24497,7 @@
         <v>0</v>
       </c>
       <c r="H290" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="J290" t="inlineStr">
         <is>
@@ -24524,19 +24524,19 @@
       </c>
       <c r="O290" t="inlineStr">
         <is>
-          <t>Região Intermediária de Uberaba</t>
+          <t>Região Intermediária de Montes Claros</t>
         </is>
       </c>
       <c r="P290" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE UBERABA</t>
+          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE MONTES CLAROS</t>
         </is>
       </c>
       <c r="Q290" t="n">
         <v>0</v>
       </c>
       <c r="R290" t="n">
-        <v>45823571</v>
+        <v>56185150</v>
       </c>
       <c r="S290" t="n">
         <v>0</v>
@@ -24580,7 +24580,7 @@
         <v>0</v>
       </c>
       <c r="H291" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="J291" t="inlineStr">
         <is>
@@ -24607,25 +24607,25 @@
       </c>
       <c r="O291" t="inlineStr">
         <is>
-          <t>Região Intermediária de Uberlândia</t>
+          <t>Região Intermediária de Pouso Alegre</t>
         </is>
       </c>
       <c r="P291" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE UBERLÂNDIA</t>
+          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE POUSO ALEGRE</t>
         </is>
       </c>
       <c r="Q291" t="n">
         <v>0</v>
       </c>
       <c r="R291" t="n">
-        <v>10027160</v>
+        <v>1975648</v>
       </c>
       <c r="S291" t="n">
         <v>0</v>
       </c>
       <c r="T291" t="n">
-        <v>23136628</v>
+        <v>0</v>
       </c>
       <c r="U291" t="n">
         <v>0</v>
@@ -24663,7 +24663,7 @@
         <v>0</v>
       </c>
       <c r="H292" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="J292" t="inlineStr">
         <is>
@@ -24690,31 +24690,31 @@
       </c>
       <c r="O292" t="inlineStr">
         <is>
-          <t>Região Intermediária de Varginha</t>
+          <t>Região Intermediária de Uberaba</t>
         </is>
       </c>
       <c r="P292" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE VARGINHA</t>
+          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE UBERABA</t>
         </is>
       </c>
       <c r="Q292" t="n">
         <v>0</v>
       </c>
       <c r="R292" t="n">
-        <v>100000</v>
+        <v>45823571</v>
       </c>
       <c r="S292" t="n">
         <v>0</v>
       </c>
       <c r="T292" t="n">
-        <v>141077</v>
+        <v>0</v>
       </c>
       <c r="U292" t="n">
         <v>0</v>
       </c>
       <c r="V292" t="n">
-        <v>30479075</v>
+        <v>0</v>
       </c>
       <c r="W292" t="n">
         <v>0</v>
@@ -24746,7 +24746,7 @@
         <v>0</v>
       </c>
       <c r="H293" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="J293" t="inlineStr">
         <is>
@@ -24773,37 +24773,37 @@
       </c>
       <c r="O293" t="inlineStr">
         <is>
-          <t>Estadual</t>
+          <t>Região Intermediária de Uberlândia</t>
         </is>
       </c>
       <c r="P293" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
+          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE UBERLÂNDIA</t>
         </is>
       </c>
       <c r="Q293" t="n">
         <v>0</v>
       </c>
       <c r="R293" t="n">
-        <v>204104</v>
+        <v>10027160</v>
       </c>
       <c r="S293" t="n">
         <v>0</v>
       </c>
       <c r="T293" t="n">
-        <v>147245000</v>
+        <v>23136628</v>
       </c>
       <c r="U293" t="n">
         <v>0</v>
       </c>
       <c r="V293" t="n">
-        <v>123727000</v>
+        <v>0</v>
       </c>
       <c r="W293" t="n">
         <v>0</v>
       </c>
       <c r="X293" t="n">
-        <v>82310000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="294">
@@ -24820,7 +24820,7 @@
         <v>92</v>
       </c>
       <c r="E294" t="n">
-        <v>3005</v>
+        <v>3004</v>
       </c>
       <c r="F294" t="n">
         <v>0</v>
@@ -24829,11 +24829,11 @@
         <v>0</v>
       </c>
       <c r="H294" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="J294" t="inlineStr">
         <is>
-          <t>REFORMAS DE SUBESTAÇÕES E LINHAS DE TRANSMISSÃO</t>
+          <t>EXPANSÃO E AQUISIÇÃO DO SISTEMA DE TRANSMISSÃO</t>
         </is>
       </c>
       <c r="K294" t="inlineStr">
@@ -24856,31 +24856,31 @@
       </c>
       <c r="O294" t="inlineStr">
         <is>
-          <t>Região Intermediária de Barbacena</t>
+          <t>Região Intermediária de Varginha</t>
         </is>
       </c>
       <c r="P294" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE BARBACENA</t>
+          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE VARGINHA</t>
         </is>
       </c>
       <c r="Q294" t="n">
         <v>0</v>
       </c>
       <c r="R294" t="n">
-        <v>2560929</v>
+        <v>100000</v>
       </c>
       <c r="S294" t="n">
         <v>0</v>
       </c>
       <c r="T294" t="n">
-        <v>0</v>
+        <v>141077</v>
       </c>
       <c r="U294" t="n">
         <v>0</v>
       </c>
       <c r="V294" t="n">
-        <v>0</v>
+        <v>30479075</v>
       </c>
       <c r="W294" t="n">
         <v>0</v>
@@ -24903,7 +24903,7 @@
         <v>92</v>
       </c>
       <c r="E295" t="n">
-        <v>3005</v>
+        <v>3004</v>
       </c>
       <c r="F295" t="n">
         <v>0</v>
@@ -24912,11 +24912,11 @@
         <v>0</v>
       </c>
       <c r="H295" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="J295" t="inlineStr">
         <is>
-          <t>REFORMAS DE SUBESTAÇÕES E LINHAS DE TRANSMISSÃO</t>
+          <t>EXPANSÃO E AQUISIÇÃO DO SISTEMA DE TRANSMISSÃO</t>
         </is>
       </c>
       <c r="K295" t="inlineStr">
@@ -24930,7 +24930,7 @@
         </is>
       </c>
       <c r="M295" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="N295" t="inlineStr">
         <is>
@@ -24939,37 +24939,37 @@
       </c>
       <c r="O295" t="inlineStr">
         <is>
-          <t>Região Intermediária de Belo Horizonte</t>
+          <t>Estadual</t>
         </is>
       </c>
       <c r="P295" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE BELO HORIZONTE</t>
+          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
         </is>
       </c>
       <c r="Q295" t="n">
         <v>0</v>
       </c>
       <c r="R295" t="n">
-        <v>43838882</v>
+        <v>204104</v>
       </c>
       <c r="S295" t="n">
         <v>0</v>
       </c>
       <c r="T295" t="n">
-        <v>2914709</v>
+        <v>147245000</v>
       </c>
       <c r="U295" t="n">
         <v>0</v>
       </c>
       <c r="V295" t="n">
-        <v>0</v>
+        <v>123727000</v>
       </c>
       <c r="W295" t="n">
         <v>0</v>
       </c>
       <c r="X295" t="n">
-        <v>0</v>
+        <v>82310000</v>
       </c>
     </row>
     <row r="296">
@@ -24995,7 +24995,7 @@
         <v>0</v>
       </c>
       <c r="H296" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="J296" t="inlineStr">
         <is>
@@ -25013,7 +25013,7 @@
         </is>
       </c>
       <c r="M296" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N296" t="inlineStr">
         <is>
@@ -25022,37 +25022,37 @@
       </c>
       <c r="O296" t="inlineStr">
         <is>
-          <t>Região Intermediária de Divinópolis</t>
+          <t>Região Intermediária de Barbacena</t>
         </is>
       </c>
       <c r="P296" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE DIVINÓPOLIS</t>
+          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE BARBACENA</t>
         </is>
       </c>
       <c r="Q296" t="n">
         <v>0</v>
       </c>
       <c r="R296" t="n">
-        <v>38083472</v>
+        <v>2560929</v>
       </c>
       <c r="S296" t="n">
         <v>0</v>
       </c>
       <c r="T296" t="n">
-        <v>57130830</v>
+        <v>0</v>
       </c>
       <c r="U296" t="n">
         <v>0</v>
       </c>
       <c r="V296" t="n">
-        <v>25124121</v>
+        <v>0</v>
       </c>
       <c r="W296" t="n">
         <v>0</v>
       </c>
       <c r="X296" t="n">
-        <v>8632550</v>
+        <v>0</v>
       </c>
     </row>
     <row r="297">
@@ -25078,7 +25078,7 @@
         <v>0</v>
       </c>
       <c r="H297" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="J297" t="inlineStr">
         <is>
@@ -25096,7 +25096,7 @@
         </is>
       </c>
       <c r="M297" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="N297" t="inlineStr">
         <is>
@@ -25105,25 +25105,25 @@
       </c>
       <c r="O297" t="inlineStr">
         <is>
-          <t>Região Intermediária de Governador Valadares</t>
+          <t>Região Intermediária de Belo Horizonte</t>
         </is>
       </c>
       <c r="P297" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE GOVERNADOR VALADARES</t>
+          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE BELO HORIZONTE</t>
         </is>
       </c>
       <c r="Q297" t="n">
         <v>0</v>
       </c>
       <c r="R297" t="n">
-        <v>7630637</v>
+        <v>43838882</v>
       </c>
       <c r="S297" t="n">
         <v>0</v>
       </c>
       <c r="T297" t="n">
-        <v>0</v>
+        <v>2914709</v>
       </c>
       <c r="U297" t="n">
         <v>0</v>
@@ -25161,7 +25161,7 @@
         <v>0</v>
       </c>
       <c r="H298" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="J298" t="inlineStr">
         <is>
@@ -25179,7 +25179,7 @@
         </is>
       </c>
       <c r="M298" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N298" t="inlineStr">
         <is>
@@ -25188,37 +25188,37 @@
       </c>
       <c r="O298" t="inlineStr">
         <is>
-          <t>Região Intermediária de Ipatinga</t>
+          <t>Região Intermediária de Divinópolis</t>
         </is>
       </c>
       <c r="P298" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE IPATINGA</t>
+          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE DIVINÓPOLIS</t>
         </is>
       </c>
       <c r="Q298" t="n">
         <v>0</v>
       </c>
       <c r="R298" t="n">
-        <v>8681251</v>
+        <v>38083472</v>
       </c>
       <c r="S298" t="n">
         <v>0</v>
       </c>
       <c r="T298" t="n">
-        <v>0</v>
+        <v>57130830</v>
       </c>
       <c r="U298" t="n">
         <v>0</v>
       </c>
       <c r="V298" t="n">
-        <v>0</v>
+        <v>25124121</v>
       </c>
       <c r="W298" t="n">
         <v>0</v>
       </c>
       <c r="X298" t="n">
-        <v>0</v>
+        <v>8632550</v>
       </c>
     </row>
     <row r="299">
@@ -25244,7 +25244,7 @@
         <v>0</v>
       </c>
       <c r="H299" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="J299" t="inlineStr">
         <is>
@@ -25262,7 +25262,7 @@
         </is>
       </c>
       <c r="M299" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N299" t="inlineStr">
         <is>
@@ -25271,25 +25271,25 @@
       </c>
       <c r="O299" t="inlineStr">
         <is>
-          <t>Região Intermediária de Juíz de Fora</t>
+          <t>Região Intermediária de Governador Valadares</t>
         </is>
       </c>
       <c r="P299" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE JUÍZ DE FORA</t>
+          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE GOVERNADOR VALADARES</t>
         </is>
       </c>
       <c r="Q299" t="n">
         <v>0</v>
       </c>
       <c r="R299" t="n">
-        <v>8252326</v>
+        <v>7630637</v>
       </c>
       <c r="S299" t="n">
         <v>0</v>
       </c>
       <c r="T299" t="n">
-        <v>6265962</v>
+        <v>0</v>
       </c>
       <c r="U299" t="n">
         <v>0</v>
@@ -25327,7 +25327,7 @@
         <v>0</v>
       </c>
       <c r="H300" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="J300" t="inlineStr">
         <is>
@@ -25345,7 +25345,7 @@
         </is>
       </c>
       <c r="M300" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N300" t="inlineStr">
         <is>
@@ -25354,19 +25354,19 @@
       </c>
       <c r="O300" t="inlineStr">
         <is>
-          <t>Região Intermediária de Montes Claros</t>
+          <t>Região Intermediária de Ipatinga</t>
         </is>
       </c>
       <c r="P300" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE MONTES CLAROS</t>
+          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE IPATINGA</t>
         </is>
       </c>
       <c r="Q300" t="n">
         <v>0</v>
       </c>
       <c r="R300" t="n">
-        <v>9495682</v>
+        <v>8681251</v>
       </c>
       <c r="S300" t="n">
         <v>0</v>
@@ -25410,7 +25410,7 @@
         <v>0</v>
       </c>
       <c r="H301" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="J301" t="inlineStr">
         <is>
@@ -25428,7 +25428,7 @@
         </is>
       </c>
       <c r="M301" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N301" t="inlineStr">
         <is>
@@ -25437,25 +25437,25 @@
       </c>
       <c r="O301" t="inlineStr">
         <is>
-          <t>Região Intermediária de Uberaba</t>
+          <t>Região Intermediária de Juíz de Fora</t>
         </is>
       </c>
       <c r="P301" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE UBERABA</t>
+          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE JUÍZ DE FORA</t>
         </is>
       </c>
       <c r="Q301" t="n">
         <v>0</v>
       </c>
       <c r="R301" t="n">
-        <v>35366196</v>
+        <v>8252326</v>
       </c>
       <c r="S301" t="n">
         <v>0</v>
       </c>
       <c r="T301" t="n">
-        <v>6763231</v>
+        <v>6265962</v>
       </c>
       <c r="U301" t="n">
         <v>0</v>
@@ -25493,7 +25493,7 @@
         <v>0</v>
       </c>
       <c r="H302" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="J302" t="inlineStr">
         <is>
@@ -25520,37 +25520,37 @@
       </c>
       <c r="O302" t="inlineStr">
         <is>
-          <t>Região Intermediária de Uberlândia</t>
+          <t>Região Intermediária de Montes Claros</t>
         </is>
       </c>
       <c r="P302" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE UBERLÂNDIA</t>
+          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE MONTES CLAROS</t>
         </is>
       </c>
       <c r="Q302" t="n">
         <v>0</v>
       </c>
       <c r="R302" t="n">
-        <v>25085657</v>
+        <v>9495682</v>
       </c>
       <c r="S302" t="n">
         <v>0</v>
       </c>
       <c r="T302" t="n">
-        <v>34647084</v>
+        <v>0</v>
       </c>
       <c r="U302" t="n">
         <v>0</v>
       </c>
       <c r="V302" t="n">
-        <v>31299410</v>
+        <v>0</v>
       </c>
       <c r="W302" t="n">
         <v>0</v>
       </c>
       <c r="X302" t="n">
-        <v>16001800</v>
+        <v>0</v>
       </c>
     </row>
     <row r="303">
@@ -25576,7 +25576,7 @@
         <v>0</v>
       </c>
       <c r="H303" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="J303" t="inlineStr">
         <is>
@@ -25594,7 +25594,7 @@
         </is>
       </c>
       <c r="M303" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N303" t="inlineStr">
         <is>
@@ -25603,37 +25603,37 @@
       </c>
       <c r="O303" t="inlineStr">
         <is>
-          <t>Região Intermediária de Varginha</t>
+          <t>Região Intermediária de Uberaba</t>
         </is>
       </c>
       <c r="P303" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE VARGINHA</t>
+          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE UBERABA</t>
         </is>
       </c>
       <c r="Q303" t="n">
         <v>0</v>
       </c>
       <c r="R303" t="n">
-        <v>10474907</v>
+        <v>35366196</v>
       </c>
       <c r="S303" t="n">
         <v>0</v>
       </c>
       <c r="T303" t="n">
-        <v>24818124</v>
+        <v>6763231</v>
       </c>
       <c r="U303" t="n">
         <v>0</v>
       </c>
       <c r="V303" t="n">
-        <v>28169469</v>
+        <v>0</v>
       </c>
       <c r="W303" t="n">
         <v>0</v>
       </c>
       <c r="X303" t="n">
-        <v>17475650</v>
+        <v>0</v>
       </c>
     </row>
     <row r="304">
@@ -25659,7 +25659,7 @@
         <v>0</v>
       </c>
       <c r="H304" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="J304" t="inlineStr">
         <is>
@@ -25677,7 +25677,7 @@
         </is>
       </c>
       <c r="M304" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N304" t="inlineStr">
         <is>
@@ -25686,37 +25686,37 @@
       </c>
       <c r="O304" t="inlineStr">
         <is>
-          <t>Estadual</t>
+          <t>Região Intermediária de Uberlândia</t>
         </is>
       </c>
       <c r="P304" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
+          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE UBERLÂNDIA</t>
         </is>
       </c>
       <c r="Q304" t="n">
         <v>0</v>
       </c>
       <c r="R304" t="n">
-        <v>27143828</v>
+        <v>25085657</v>
       </c>
       <c r="S304" t="n">
         <v>0</v>
       </c>
       <c r="T304" t="n">
-        <v>730599807</v>
+        <v>34647084</v>
       </c>
       <c r="U304" t="n">
         <v>0</v>
       </c>
       <c r="V304" t="n">
-        <v>584970561</v>
+        <v>31299410</v>
       </c>
       <c r="W304" t="n">
         <v>0</v>
       </c>
       <c r="X304" t="n">
-        <v>439221764</v>
+        <v>16001800</v>
       </c>
     </row>
     <row r="305">
@@ -25730,10 +25730,10 @@
         <v>752</v>
       </c>
       <c r="D305" t="n">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E305" t="n">
-        <v>3001</v>
+        <v>3005</v>
       </c>
       <c r="F305" t="n">
         <v>0</v>
@@ -25742,11 +25742,11 @@
         <v>0</v>
       </c>
       <c r="H305" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="J305" t="inlineStr">
         <is>
-          <t>EXPANSÃO DO SISTEMA DE GERAÇÃO</t>
+          <t>REFORMAS DE SUBESTAÇÕES E LINHAS DE TRANSMISSÃO</t>
         </is>
       </c>
       <c r="K305" t="inlineStr">
@@ -25769,42 +25769,42 @@
       </c>
       <c r="O305" t="inlineStr">
         <is>
-          <t>Região Intermediária de Belo Horizonte</t>
+          <t>Região Intermediária de Varginha</t>
         </is>
       </c>
       <c r="P305" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE BELO HORIZONTE</t>
+          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE VARGINHA</t>
         </is>
       </c>
       <c r="Q305" t="n">
         <v>0</v>
       </c>
       <c r="R305" t="n">
-        <v>100000</v>
+        <v>10474907</v>
       </c>
       <c r="S305" t="n">
         <v>0</v>
       </c>
       <c r="T305" t="n">
-        <v>338387000</v>
+        <v>24818124</v>
       </c>
       <c r="U305" t="n">
         <v>0</v>
       </c>
       <c r="V305" t="n">
-        <v>416585000</v>
+        <v>28169469</v>
       </c>
       <c r="W305" t="n">
         <v>0</v>
       </c>
       <c r="X305" t="n">
-        <v>149872000</v>
+        <v>17475650</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="n">
-        <v>5401</v>
+        <v>5391</v>
       </c>
       <c r="B306" t="n">
         <v>25</v>
@@ -25813,10 +25813,10 @@
         <v>752</v>
       </c>
       <c r="D306" t="n">
-        <v>72</v>
+        <v>92</v>
       </c>
       <c r="E306" t="n">
-        <v>3002</v>
+        <v>3005</v>
       </c>
       <c r="F306" t="n">
         <v>0</v>
@@ -25825,11 +25825,11 @@
         <v>0</v>
       </c>
       <c r="H306" t="n">
-        <v>5</v>
+        <v>42</v>
       </c>
       <c r="J306" t="inlineStr">
         <is>
-          <t>EXECUÇÃO DO PLANO DE DESENVOLVIMENTO DA DISTRIBUIDORA (PDD)</t>
+          <t>REFORMAS DE SUBESTAÇÕES E LINHAS DE TRANSMISSÃO</t>
         </is>
       </c>
       <c r="K306" t="inlineStr">
@@ -25843,7 +25843,7 @@
         </is>
       </c>
       <c r="M306" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="N306" t="inlineStr">
         <is>
@@ -25852,42 +25852,42 @@
       </c>
       <c r="O306" t="inlineStr">
         <is>
-          <t>Região Intermediária de Barbacena</t>
+          <t>Estadual</t>
         </is>
       </c>
       <c r="P306" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE BARBACENA</t>
+          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
         </is>
       </c>
       <c r="Q306" t="n">
         <v>0</v>
       </c>
       <c r="R306" t="n">
-        <v>173325517</v>
+        <v>27143828</v>
       </c>
       <c r="S306" t="n">
         <v>0</v>
       </c>
       <c r="T306" t="n">
-        <v>175158242</v>
+        <v>730599807</v>
       </c>
       <c r="U306" t="n">
         <v>0</v>
       </c>
       <c r="V306" t="n">
-        <v>156313303</v>
+        <v>584970561</v>
       </c>
       <c r="W306" t="n">
         <v>0</v>
       </c>
       <c r="X306" t="n">
-        <v>237240548</v>
+        <v>439221764</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="n">
-        <v>5401</v>
+        <v>5391</v>
       </c>
       <c r="B307" t="n">
         <v>25</v>
@@ -25896,10 +25896,10 @@
         <v>752</v>
       </c>
       <c r="D307" t="n">
-        <v>72</v>
+        <v>94</v>
       </c>
       <c r="E307" t="n">
-        <v>3002</v>
+        <v>3001</v>
       </c>
       <c r="F307" t="n">
         <v>0</v>
@@ -25908,11 +25908,11 @@
         <v>0</v>
       </c>
       <c r="H307" t="n">
-        <v>6</v>
+        <v>43</v>
       </c>
       <c r="J307" t="inlineStr">
         <is>
-          <t>EXECUÇÃO DO PLANO DE DESENVOLVIMENTO DA DISTRIBUIDORA (PDD)</t>
+          <t>EXPANSÃO DO SISTEMA DE GERAÇÃO</t>
         </is>
       </c>
       <c r="K307" t="inlineStr">
@@ -25926,7 +25926,7 @@
         </is>
       </c>
       <c r="M307" t="n">
-        <v>40</v>
+        <v>1</v>
       </c>
       <c r="N307" t="inlineStr">
         <is>
@@ -25947,25 +25947,25 @@
         <v>0</v>
       </c>
       <c r="R307" t="n">
-        <v>1120942874</v>
+        <v>100000</v>
       </c>
       <c r="S307" t="n">
         <v>0</v>
       </c>
       <c r="T307" t="n">
-        <v>1139053548</v>
+        <v>338387000</v>
       </c>
       <c r="U307" t="n">
         <v>0</v>
       </c>
       <c r="V307" t="n">
-        <v>1044251133</v>
+        <v>416585000</v>
       </c>
       <c r="W307" t="n">
         <v>0</v>
       </c>
       <c r="X307" t="n">
-        <v>929396291</v>
+        <v>149872000</v>
       </c>
     </row>
     <row r="308">
@@ -25991,7 +25991,7 @@
         <v>0</v>
       </c>
       <c r="H308" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J308" t="inlineStr">
         <is>
@@ -26009,7 +26009,7 @@
         </is>
       </c>
       <c r="M308" t="n">
-        <v>186</v>
+        <v>30</v>
       </c>
       <c r="N308" t="inlineStr">
         <is>
@@ -26018,37 +26018,37 @@
       </c>
       <c r="O308" t="inlineStr">
         <is>
-          <t>Região Intermediária de Divinópolis</t>
+          <t>Região Intermediária de Barbacena</t>
         </is>
       </c>
       <c r="P308" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE DIVINÓPOLIS</t>
+          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE BARBACENA</t>
         </is>
       </c>
       <c r="Q308" t="n">
         <v>0</v>
       </c>
       <c r="R308" t="n">
-        <v>490941164</v>
+        <v>173325517</v>
       </c>
       <c r="S308" t="n">
         <v>0</v>
       </c>
       <c r="T308" t="n">
-        <v>490336380</v>
+        <v>175158242</v>
       </c>
       <c r="U308" t="n">
         <v>0</v>
       </c>
       <c r="V308" t="n">
-        <v>768797092</v>
+        <v>156313303</v>
       </c>
       <c r="W308" t="n">
         <v>0</v>
       </c>
       <c r="X308" t="n">
-        <v>598706756</v>
+        <v>237240548</v>
       </c>
     </row>
     <row r="309">
@@ -26074,7 +26074,7 @@
         <v>0</v>
       </c>
       <c r="H309" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J309" t="inlineStr">
         <is>
@@ -26092,7 +26092,7 @@
         </is>
       </c>
       <c r="M309" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="N309" t="inlineStr">
         <is>
@@ -26101,37 +26101,37 @@
       </c>
       <c r="O309" t="inlineStr">
         <is>
-          <t>Região Intermediária de Governador Valadares</t>
+          <t>Região Intermediária de Belo Horizonte</t>
         </is>
       </c>
       <c r="P309" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE GOVERNADOR VALADARES</t>
+          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE BELO HORIZONTE</t>
         </is>
       </c>
       <c r="Q309" t="n">
         <v>0</v>
       </c>
       <c r="R309" t="n">
-        <v>186072723</v>
+        <v>1120942874</v>
       </c>
       <c r="S309" t="n">
         <v>0</v>
       </c>
       <c r="T309" t="n">
-        <v>344516295</v>
+        <v>1139053548</v>
       </c>
       <c r="U309" t="n">
         <v>0</v>
       </c>
       <c r="V309" t="n">
-        <v>161000776</v>
+        <v>1044251133</v>
       </c>
       <c r="W309" t="n">
         <v>0</v>
       </c>
       <c r="X309" t="n">
-        <v>187736103</v>
+        <v>929396291</v>
       </c>
     </row>
     <row r="310">
@@ -26157,7 +26157,7 @@
         <v>0</v>
       </c>
       <c r="H310" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="J310" t="inlineStr">
         <is>
@@ -26175,7 +26175,7 @@
         </is>
       </c>
       <c r="M310" t="n">
-        <v>1</v>
+        <v>186</v>
       </c>
       <c r="N310" t="inlineStr">
         <is>
@@ -26184,37 +26184,37 @@
       </c>
       <c r="O310" t="inlineStr">
         <is>
-          <t>Região Intermediária de Ipatinga</t>
+          <t>Região Intermediária de Divinópolis</t>
         </is>
       </c>
       <c r="P310" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE IPATINGA</t>
+          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE DIVINÓPOLIS</t>
         </is>
       </c>
       <c r="Q310" t="n">
         <v>0</v>
       </c>
       <c r="R310" t="n">
-        <v>163742706</v>
+        <v>490941164</v>
       </c>
       <c r="S310" t="n">
         <v>0</v>
       </c>
       <c r="T310" t="n">
-        <v>235942789</v>
+        <v>490336380</v>
       </c>
       <c r="U310" t="n">
         <v>0</v>
       </c>
       <c r="V310" t="n">
-        <v>277257526</v>
+        <v>768797092</v>
       </c>
       <c r="W310" t="n">
         <v>0</v>
       </c>
       <c r="X310" t="n">
-        <v>184594645</v>
+        <v>598706756</v>
       </c>
     </row>
     <row r="311">
@@ -26240,7 +26240,7 @@
         <v>0</v>
       </c>
       <c r="H311" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J311" t="inlineStr">
         <is>
@@ -26258,7 +26258,7 @@
         </is>
       </c>
       <c r="M311" t="n">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="N311" t="inlineStr">
         <is>
@@ -26267,37 +26267,37 @@
       </c>
       <c r="O311" t="inlineStr">
         <is>
-          <t>Região Intermediária de Juíz de Fora</t>
+          <t>Região Intermediária de Governador Valadares</t>
         </is>
       </c>
       <c r="P311" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE JUÍZ DE FORA</t>
+          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE GOVERNADOR VALADARES</t>
         </is>
       </c>
       <c r="Q311" t="n">
         <v>0</v>
       </c>
       <c r="R311" t="n">
-        <v>174469498</v>
+        <v>186072723</v>
       </c>
       <c r="S311" t="n">
         <v>0</v>
       </c>
       <c r="T311" t="n">
-        <v>179457178</v>
+        <v>344516295</v>
       </c>
       <c r="U311" t="n">
         <v>0</v>
       </c>
       <c r="V311" t="n">
-        <v>172873473</v>
+        <v>161000776</v>
       </c>
       <c r="W311" t="n">
         <v>0</v>
       </c>
       <c r="X311" t="n">
-        <v>185947905</v>
+        <v>187736103</v>
       </c>
     </row>
     <row r="312">
@@ -26323,7 +26323,7 @@
         <v>0</v>
       </c>
       <c r="H312" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="J312" t="inlineStr">
         <is>
@@ -26341,7 +26341,7 @@
         </is>
       </c>
       <c r="M312" t="n">
-        <v>73</v>
+        <v>1</v>
       </c>
       <c r="N312" t="inlineStr">
         <is>
@@ -26350,37 +26350,37 @@
       </c>
       <c r="O312" t="inlineStr">
         <is>
-          <t>Região Intermediária de Montes Claros</t>
+          <t>Região Intermediária de Ipatinga</t>
         </is>
       </c>
       <c r="P312" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE MONTES CLAROS</t>
+          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE IPATINGA</t>
         </is>
       </c>
       <c r="Q312" t="n">
         <v>0</v>
       </c>
       <c r="R312" t="n">
-        <v>465051090</v>
+        <v>163742706</v>
       </c>
       <c r="S312" t="n">
         <v>0</v>
       </c>
       <c r="T312" t="n">
-        <v>426001328</v>
+        <v>235942789</v>
       </c>
       <c r="U312" t="n">
         <v>0</v>
       </c>
       <c r="V312" t="n">
-        <v>406601466</v>
+        <v>277257526</v>
       </c>
       <c r="W312" t="n">
         <v>0</v>
       </c>
       <c r="X312" t="n">
-        <v>522438700</v>
+        <v>184594645</v>
       </c>
     </row>
     <row r="313">
@@ -26406,7 +26406,7 @@
         <v>0</v>
       </c>
       <c r="H313" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="J313" t="inlineStr">
         <is>
@@ -26424,7 +26424,7 @@
         </is>
       </c>
       <c r="M313" t="n">
-        <v>190</v>
+        <v>26</v>
       </c>
       <c r="N313" t="inlineStr">
         <is>
@@ -26433,37 +26433,37 @@
       </c>
       <c r="O313" t="inlineStr">
         <is>
-          <t>Região Intermediária de Patos de Minas</t>
+          <t>Região Intermediária de Juíz de Fora</t>
         </is>
       </c>
       <c r="P313" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE PATOS DE MINAS</t>
+          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE JUÍZ DE FORA</t>
         </is>
       </c>
       <c r="Q313" t="n">
         <v>0</v>
       </c>
       <c r="R313" t="n">
-        <v>307578393</v>
+        <v>174469498</v>
       </c>
       <c r="S313" t="n">
         <v>0</v>
       </c>
       <c r="T313" t="n">
-        <v>396019699</v>
+        <v>179457178</v>
       </c>
       <c r="U313" t="n">
         <v>0</v>
       </c>
       <c r="V313" t="n">
-        <v>186433355</v>
+        <v>172873473</v>
       </c>
       <c r="W313" t="n">
         <v>0</v>
       </c>
       <c r="X313" t="n">
-        <v>280209020</v>
+        <v>185947905</v>
       </c>
     </row>
     <row r="314">
@@ -26489,7 +26489,7 @@
         <v>0</v>
       </c>
       <c r="H314" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="J314" t="inlineStr">
         <is>
@@ -26507,7 +26507,7 @@
         </is>
       </c>
       <c r="M314" t="n">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="N314" t="inlineStr">
         <is>
@@ -26516,37 +26516,37 @@
       </c>
       <c r="O314" t="inlineStr">
         <is>
-          <t>Região Intermediária de Pouso Alegre</t>
+          <t>Região Intermediária de Montes Claros</t>
         </is>
       </c>
       <c r="P314" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE POUSO ALEGRE</t>
+          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE MONTES CLAROS</t>
         </is>
       </c>
       <c r="Q314" t="n">
         <v>0</v>
       </c>
       <c r="R314" t="n">
-        <v>163826695</v>
+        <v>465051090</v>
       </c>
       <c r="S314" t="n">
         <v>0</v>
       </c>
       <c r="T314" t="n">
-        <v>138339062</v>
+        <v>426001328</v>
       </c>
       <c r="U314" t="n">
         <v>0</v>
       </c>
       <c r="V314" t="n">
-        <v>145444243</v>
+        <v>406601466</v>
       </c>
       <c r="W314" t="n">
         <v>0</v>
       </c>
       <c r="X314" t="n">
-        <v>177988747</v>
+        <v>522438700</v>
       </c>
     </row>
     <row r="315">
@@ -26572,7 +26572,7 @@
         <v>0</v>
       </c>
       <c r="H315" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J315" t="inlineStr">
         <is>
@@ -26590,7 +26590,7 @@
         </is>
       </c>
       <c r="M315" t="n">
-        <v>28</v>
+        <v>190</v>
       </c>
       <c r="N315" t="inlineStr">
         <is>
@@ -26599,37 +26599,37 @@
       </c>
       <c r="O315" t="inlineStr">
         <is>
-          <t>Região Intermediária de Teófilo Otoni</t>
+          <t>Região Intermediária de Patos de Minas</t>
         </is>
       </c>
       <c r="P315" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE TEÓFILO OTONI</t>
+          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE PATOS DE MINAS</t>
         </is>
       </c>
       <c r="Q315" t="n">
         <v>0</v>
       </c>
       <c r="R315" t="n">
-        <v>313867376</v>
+        <v>307578393</v>
       </c>
       <c r="S315" t="n">
         <v>0</v>
       </c>
       <c r="T315" t="n">
-        <v>460495100</v>
+        <v>396019699</v>
       </c>
       <c r="U315" t="n">
         <v>0</v>
       </c>
       <c r="V315" t="n">
-        <v>395179068</v>
+        <v>186433355</v>
       </c>
       <c r="W315" t="n">
         <v>0</v>
       </c>
       <c r="X315" t="n">
-        <v>316117306</v>
+        <v>280209020</v>
       </c>
     </row>
     <row r="316">
@@ -26655,7 +26655,7 @@
         <v>0</v>
       </c>
       <c r="H316" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="J316" t="inlineStr">
         <is>
@@ -26673,7 +26673,7 @@
         </is>
       </c>
       <c r="M316" t="n">
-        <v>76</v>
+        <v>65</v>
       </c>
       <c r="N316" t="inlineStr">
         <is>
@@ -26682,37 +26682,37 @@
       </c>
       <c r="O316" t="inlineStr">
         <is>
-          <t>Região Intermediária de Uberaba</t>
+          <t>Região Intermediária de Pouso Alegre</t>
         </is>
       </c>
       <c r="P316" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE UBERABA</t>
+          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE POUSO ALEGRE</t>
         </is>
       </c>
       <c r="Q316" t="n">
         <v>0</v>
       </c>
       <c r="R316" t="n">
-        <v>248524996</v>
+        <v>163826695</v>
       </c>
       <c r="S316" t="n">
         <v>0</v>
       </c>
       <c r="T316" t="n">
-        <v>127122707</v>
+        <v>138339062</v>
       </c>
       <c r="U316" t="n">
         <v>0</v>
       </c>
       <c r="V316" t="n">
-        <v>130234154</v>
+        <v>145444243</v>
       </c>
       <c r="W316" t="n">
         <v>0</v>
       </c>
       <c r="X316" t="n">
-        <v>170876115</v>
+        <v>177988747</v>
       </c>
     </row>
     <row r="317">
@@ -26738,7 +26738,7 @@
         <v>0</v>
       </c>
       <c r="H317" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="J317" t="inlineStr">
         <is>
@@ -26756,7 +26756,7 @@
         </is>
       </c>
       <c r="M317" t="n">
-        <v>74</v>
+        <v>28</v>
       </c>
       <c r="N317" t="inlineStr">
         <is>
@@ -26765,37 +26765,37 @@
       </c>
       <c r="O317" t="inlineStr">
         <is>
-          <t>Região Intermediária de Uberlândia</t>
+          <t>Região Intermediária de Teófilo Otoni</t>
         </is>
       </c>
       <c r="P317" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE UBERLÂNDIA</t>
+          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE TEÓFILO OTONI</t>
         </is>
       </c>
       <c r="Q317" t="n">
         <v>0</v>
       </c>
       <c r="R317" t="n">
-        <v>225931007</v>
+        <v>313867376</v>
       </c>
       <c r="S317" t="n">
         <v>0</v>
       </c>
       <c r="T317" t="n">
-        <v>166159583</v>
+        <v>460495100</v>
       </c>
       <c r="U317" t="n">
         <v>0</v>
       </c>
       <c r="V317" t="n">
-        <v>152518141</v>
+        <v>395179068</v>
       </c>
       <c r="W317" t="n">
         <v>0</v>
       </c>
       <c r="X317" t="n">
-        <v>236932823</v>
+        <v>316117306</v>
       </c>
     </row>
     <row r="318">
@@ -26821,7 +26821,7 @@
         <v>0</v>
       </c>
       <c r="H318" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="J318" t="inlineStr">
         <is>
@@ -26839,7 +26839,7 @@
         </is>
       </c>
       <c r="M318" t="n">
-        <v>15</v>
+        <v>76</v>
       </c>
       <c r="N318" t="inlineStr">
         <is>
@@ -26848,37 +26848,37 @@
       </c>
       <c r="O318" t="inlineStr">
         <is>
-          <t>Região Intermediária de Varginha</t>
+          <t>Região Intermediária de Uberaba</t>
         </is>
       </c>
       <c r="P318" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE VARGINHA</t>
+          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE UBERABA</t>
         </is>
       </c>
       <c r="Q318" t="n">
         <v>0</v>
       </c>
       <c r="R318" t="n">
-        <v>354935944</v>
+        <v>248524996</v>
       </c>
       <c r="S318" t="n">
         <v>0</v>
       </c>
       <c r="T318" t="n">
-        <v>451276526</v>
+        <v>127122707</v>
       </c>
       <c r="U318" t="n">
         <v>0</v>
       </c>
       <c r="V318" t="n">
-        <v>277910526</v>
+        <v>130234154</v>
       </c>
       <c r="W318" t="n">
         <v>0</v>
       </c>
       <c r="X318" t="n">
-        <v>343154711</v>
+        <v>170876115</v>
       </c>
     </row>
     <row r="319">
@@ -26904,7 +26904,7 @@
         <v>0</v>
       </c>
       <c r="H319" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J319" t="inlineStr">
         <is>
@@ -26922,7 +26922,7 @@
         </is>
       </c>
       <c r="M319" t="n">
-        <v>1</v>
+        <v>74</v>
       </c>
       <c r="N319" t="inlineStr">
         <is>
@@ -26931,119 +26931,285 @@
       </c>
       <c r="O319" t="inlineStr">
         <is>
-          <t>Estadual</t>
+          <t>Região Intermediária de Uberlândia</t>
         </is>
       </c>
       <c r="P319" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
+          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE UBERLÂNDIA</t>
         </is>
       </c>
       <c r="Q319" t="n">
         <v>0</v>
       </c>
       <c r="R319" t="n">
-        <v>332667205</v>
+        <v>225931007</v>
       </c>
       <c r="S319" t="n">
         <v>0</v>
       </c>
       <c r="T319" t="n">
-        <v>342708994</v>
+        <v>166159583</v>
       </c>
       <c r="U319" t="n">
         <v>0</v>
       </c>
       <c r="V319" t="n">
-        <v>506294167</v>
+        <v>152518141</v>
       </c>
       <c r="W319" t="n">
         <v>0</v>
       </c>
       <c r="X319" t="n">
-        <v>234441655</v>
+        <v>236932823</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="n">
+        <v>5401</v>
+      </c>
+      <c r="B320" t="n">
+        <v>25</v>
+      </c>
+      <c r="C320" t="n">
+        <v>752</v>
+      </c>
+      <c r="D320" t="n">
+        <v>72</v>
+      </c>
+      <c r="E320" t="n">
+        <v>3002</v>
+      </c>
+      <c r="F320" t="n">
+        <v>0</v>
+      </c>
+      <c r="G320" t="n">
+        <v>0</v>
+      </c>
+      <c r="H320" t="n">
+        <v>17</v>
+      </c>
+      <c r="J320" t="inlineStr">
+        <is>
+          <t>EXECUÇÃO DO PLANO DE DESENVOLVIMENTO DA DISTRIBUIDORA (PDD)</t>
+        </is>
+      </c>
+      <c r="K320" t="inlineStr">
+        <is>
+          <t>INICIANDO</t>
+        </is>
+      </c>
+      <c r="L320" t="inlineStr">
+        <is>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="M320" t="n">
+        <v>15</v>
+      </c>
+      <c r="N320" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="O320" t="inlineStr">
+        <is>
+          <t>Região Intermediária de Varginha</t>
+        </is>
+      </c>
+      <c r="P320" t="inlineStr">
+        <is>
+          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE VARGINHA</t>
+        </is>
+      </c>
+      <c r="Q320" t="n">
+        <v>0</v>
+      </c>
+      <c r="R320" t="n">
+        <v>354935944</v>
+      </c>
+      <c r="S320" t="n">
+        <v>0</v>
+      </c>
+      <c r="T320" t="n">
+        <v>451276526</v>
+      </c>
+      <c r="U320" t="n">
+        <v>0</v>
+      </c>
+      <c r="V320" t="n">
+        <v>277910526</v>
+      </c>
+      <c r="W320" t="n">
+        <v>0</v>
+      </c>
+      <c r="X320" t="n">
+        <v>343154711</v>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="n">
+        <v>5401</v>
+      </c>
+      <c r="B321" t="n">
+        <v>25</v>
+      </c>
+      <c r="C321" t="n">
+        <v>752</v>
+      </c>
+      <c r="D321" t="n">
+        <v>72</v>
+      </c>
+      <c r="E321" t="n">
+        <v>3002</v>
+      </c>
+      <c r="F321" t="n">
+        <v>0</v>
+      </c>
+      <c r="G321" t="n">
+        <v>0</v>
+      </c>
+      <c r="H321" t="n">
+        <v>18</v>
+      </c>
+      <c r="J321" t="inlineStr">
+        <is>
+          <t>EXECUÇÃO DO PLANO DE DESENVOLVIMENTO DA DISTRIBUIDORA (PDD)</t>
+        </is>
+      </c>
+      <c r="K321" t="inlineStr">
+        <is>
+          <t>INICIANDO</t>
+        </is>
+      </c>
+      <c r="L321" t="inlineStr">
+        <is>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="M321" t="n">
+        <v>1</v>
+      </c>
+      <c r="N321" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="O321" t="inlineStr">
+        <is>
+          <t>Estadual</t>
+        </is>
+      </c>
+      <c r="P321" t="inlineStr">
+        <is>
+          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
+        </is>
+      </c>
+      <c r="Q321" t="n">
+        <v>0</v>
+      </c>
+      <c r="R321" t="n">
+        <v>332667205</v>
+      </c>
+      <c r="S321" t="n">
+        <v>0</v>
+      </c>
+      <c r="T321" t="n">
+        <v>342708994</v>
+      </c>
+      <c r="U321" t="n">
+        <v>0</v>
+      </c>
+      <c r="V321" t="n">
+        <v>506294167</v>
+      </c>
+      <c r="W321" t="n">
+        <v>0</v>
+      </c>
+      <c r="X321" t="n">
+        <v>234441655</v>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="n">
         <v>5511</v>
       </c>
-      <c r="B320" t="n">
+      <c r="B322" t="n">
         <v>17</v>
       </c>
-      <c r="C320" t="n">
+      <c r="C322" t="n">
         <v>512</v>
       </c>
-      <c r="D320" t="n">
+      <c r="D322" t="n">
         <v>21</v>
       </c>
-      <c r="E320" t="n">
+      <c r="E322" t="n">
         <v>8012</v>
       </c>
-      <c r="F320" t="n">
-        <v>0</v>
-      </c>
-      <c r="G320" t="n">
-        <v>0</v>
-      </c>
-      <c r="H320" t="n">
+      <c r="F322" t="n">
+        <v>0</v>
+      </c>
+      <c r="G322" t="n">
+        <v>0</v>
+      </c>
+      <c r="H322" t="n">
         <v>148</v>
       </c>
-      <c r="J320" t="inlineStr">
+      <c r="J322" t="inlineStr">
         <is>
           <t>IMPLANTAÇÃO OU AMPLIAÇÃO REALIZADA EM SISTEMAS DE ABASTECIMENTO DE ÁGUA QUE PODEM CONTEMPLAR SISTEMA PRODUTOR QUE PODE SER ATRAVÉS DE POÇO PROFUNDO OU CAPTAÇÃO SUPERFICIAL, ESTAÇÃO DE TRATAMENTO DE ÁGUA, ADUTORAS, ESTAÇÕES ELEVATÓRIAS, RESERVATÓRIOS E REDES DE DISTRIBUIÇÃO DE ÁGUA PARA OPERAÇÃO DAS UNIDADES DE TRATAMENTO E DISTRIBUIÇÃO DE ÁGUA TRATADA EM LOCALIDADES QUE A COPANOR TENHA OU VENHA A TER A CONCESSÃO PARA O SERVIÇO DE ABASTECIMENTO DE ÁGUA. IMPLANTAÇÃO OU AMPLIAÇÃO REALIZADA EM SISTEMAS DE ESGOTAMENTO SANITÁRIO QUE PODEM CONTEMPLAR ESTAÇÃO DE TRATAMENTO DE ESGOTO, ESTAÇÕES ELEVATÓRIAS, INTERCEPTORES E REDES COLETORAS PARA OPERAÇÃO DAS UNIDADES DE COLETA E TRATAMENTO DE ESGOTO EM LOCALIDADES QUE A COPANOR TENHA OU VENHA A TER A CONCESSÃO PARA O SERVIÇO DE ESGOTAMENTO SANITÁRIO.</t>
         </is>
       </c>
-      <c r="K320" t="inlineStr">
+      <c r="K322" t="inlineStr">
         <is>
           <t>INICIANDO</t>
         </is>
       </c>
-      <c r="L320" t="inlineStr">
+      <c r="L322" t="inlineStr">
         <is>
           <t>ECONOMIA RESIDENCIAL</t>
         </is>
       </c>
-      <c r="M320" t="n">
+      <c r="M322" t="n">
         <v>4000</v>
       </c>
-      <c r="N320" t="inlineStr">
+      <c r="N322" t="inlineStr">
         <is>
           <t>Não</t>
         </is>
       </c>
-      <c r="O320" t="inlineStr">
+      <c r="O322" t="inlineStr">
         <is>
           <t>Região Intermediária de Teófilo Otoni</t>
         </is>
       </c>
-      <c r="P320" t="inlineStr">
+      <c r="P322" t="inlineStr">
         <is>
           <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE TEÓFILO OTONI</t>
         </is>
       </c>
-      <c r="Q320" t="n">
-        <v>0</v>
-      </c>
-      <c r="R320" t="n">
+      <c r="Q322" t="n">
+        <v>0</v>
+      </c>
+      <c r="R322" t="n">
         <v>45000000</v>
       </c>
-      <c r="S320" t="n">
-        <v>0</v>
-      </c>
-      <c r="T320" t="n">
+      <c r="S322" t="n">
+        <v>0</v>
+      </c>
+      <c r="T322" t="n">
         <v>45000000</v>
       </c>
-      <c r="U320" t="n">
-        <v>0</v>
-      </c>
-      <c r="V320" t="n">
+      <c r="U322" t="n">
+        <v>0</v>
+      </c>
+      <c r="V322" t="n">
         <v>45000000</v>
       </c>
-      <c r="W320" t="n">
-        <v>0</v>
-      </c>
-      <c r="X320" t="n">
+      <c r="W322" t="n">
+        <v>0</v>
+      </c>
+      <c r="X322" t="n">
         <v>45000000</v>
       </c>
     </row>

--- a/bancos/SISOR/BASE_DETALHAMENTO_OBRAS.xlsx
+++ b/bancos/SISOR/BASE_DETALHAMENTO_OBRAS.xlsx
@@ -4221,7 +4221,7 @@
         <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>101</v>
+        <v>465</v>
       </c>
       <c r="I46" t="n">
         <v>12495</v>
@@ -4639,7 +4639,7 @@
         <v>0</v>
       </c>
       <c r="H51" t="n">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="J51" t="inlineStr">
         <is>
@@ -10535,7 +10535,7 @@
         <v>0</v>
       </c>
       <c r="H122" t="n">
-        <v>84</v>
+        <v>467</v>
       </c>
       <c r="J122" t="inlineStr">
         <is>

--- a/bancos/SISOR/BASE_DETALHAMENTO_OBRAS.xlsx
+++ b/bancos/SISOR/BASE_DETALHAMENTO_OBRAS.xlsx
@@ -7633,7 +7633,7 @@
         <v>150000</v>
       </c>
       <c r="R120" t="n">
-        <v>20000000</v>
+        <v>19850000</v>
       </c>
     </row>
     <row r="121">

--- a/bancos/SISOR/BASE_DETALHAMENTO_OBRAS.xlsx
+++ b/bancos/SISOR/BASE_DETALHAMENTO_OBRAS.xlsx
@@ -7142,7 +7142,7 @@
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>REDIMENSIONAMENTO DE REDE ELÉTRICA (NRPMSO'S) - Garantir a segurança elétrica para implementação de novos equipamentos</t>
+          <t>REDIMENSIONAMENTO DE REDE ELÉTRICA (NRPMSO`S) - Garantir a segurança elétrica para implementação de novos equipamentos</t>
         </is>
       </c>
       <c r="K112" t="inlineStr">
@@ -13964,7 +13964,7 @@
       </c>
       <c r="J231" t="inlineStr">
         <is>
-          <t>CONSERVAÇÃO DA MALHA VIÁRIA DAS 40ª URG'S</t>
+          <t>CONSERVAÇÃO DA MALHA VIÁRIA DAS 40ª URG`S</t>
         </is>
       </c>
       <c r="K231" t="inlineStr">

--- a/bancos/SISOR/BASE_DETALHAMENTO_OBRAS.xlsx
+++ b/bancos/SISOR/BASE_DETALHAMENTO_OBRAS.xlsx
@@ -767,19 +767,19 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>1251</v>
+        <v>1091</v>
       </c>
       <c r="B6" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="C6" t="n">
-        <v>302</v>
+        <v>62</v>
       </c>
       <c r="D6" t="n">
-        <v>135</v>
+        <v>714</v>
       </c>
       <c r="E6" t="n">
-        <v>2060</v>
+        <v>1064</v>
       </c>
       <c r="F6" t="n">
         <v>1</v>
@@ -790,12 +790,9 @@
       <c r="H6" t="n">
         <v>5</v>
       </c>
-      <c r="I6" t="n">
-        <v>12876</v>
-      </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Adequação da estrutura física do NAIS/9ª RPM, visando ao atendimento dos requisitos necessários à regularização junto aos órgãos de controle, especialmente à Vigilância Sanitária e à Secretaria de Saúde</t>
+          <t>Sedes Próprias Diversas</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -803,31 +800,23 @@
           <t>INICIANDO</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>UNIDADE</t>
-        </is>
-      </c>
-      <c r="M6" t="n">
-        <v>1</v>
-      </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Região Intermediária de Uberlândia</t>
+          <t>Estadual</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>UBERLÂNDIA</t>
+          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>60000</v>
+        <v>19960975</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -859,11 +848,11 @@
         <v>6</v>
       </c>
       <c r="I7" t="n">
-        <v>12882</v>
+        <v>12876</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Projeto elétrico, hidráulico, esgoto, rede, serralheria (prateleiras) e arquitetônico para reforma do CAO/CODONT; Valor estimado: R$ 197.856,73.</t>
+          <t>Adequação da estrutura física do NAIS/9ª RPM, visando ao atendimento dos requisitos necessários à regularização junto aos órgãos de controle, especialmente à Vigilância Sanitária e à Secretaria de Saúde</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -886,16 +875,16 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Região Intermediária de Belo Horizonte</t>
+          <t>Região Intermediária de Uberlândia</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>BELO HORIZONTE</t>
+          <t>UBERLÂNDIA</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>197857</v>
+        <v>60000</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
@@ -927,11 +916,11 @@
         <v>7</v>
       </c>
       <c r="I8" t="n">
-        <v>12880</v>
+        <v>12882</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Projeto de reestruturação dos consultórios de roseta para linha;</t>
+          <t xml:space="preserve"> Projeto elétrico, hidráulico, esgoto, rede, serralheria (prateleiras) e arquitetônico para reforma do CAO/CODONT; Valor estimado: R$ 197.856,73.</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -963,7 +952,7 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>1929103</v>
+        <v>197857</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -995,11 +984,11 @@
         <v>8</v>
       </c>
       <c r="I9" t="n">
-        <v>12881</v>
+        <v>12880</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Execução das obras de reestruturação dos consultórios de roseta para linha;</t>
+          <t xml:space="preserve"> Projeto de reestruturação dos consultórios de roseta para linha;</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1063,11 +1052,11 @@
         <v>9</v>
       </c>
       <c r="I10" t="n">
-        <v>12878</v>
+        <v>12881</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Contratação de elaboração de estudo e projeto para adaptação do NAIS/5GRS, em atendimento às normas de vigilância sanitária para coleta de resíduos sólidos médico-hospitalares e construção de vestiários.</t>
+          <t>Execução das obras de reestruturação dos consultórios de roseta para linha;</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1090,16 +1079,16 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Região Intermediária de Governador Valadares</t>
+          <t>Região Intermediária de Belo Horizonte</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>GOVERNADOR VALADARES</t>
+          <t>BELO HORIZONTE</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>41022</v>
+        <v>1929103</v>
       </c>
       <c r="R10" t="n">
         <v>0</v>
@@ -1131,11 +1120,11 @@
         <v>10</v>
       </c>
       <c r="I11" t="n">
-        <v>12875</v>
+        <v>12878</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Construlção de local adequado para o armazenamento e descarte de resíduos de serviços de saúde, sendo necessária a adequação da estrutura física para atendimento às exigências dos órgãos de controle e consequente obtenção do alvará sanitário.</t>
+          <t>Contratação de elaboração de estudo e projeto para adaptação do NAIS/5GRS, em atendimento às normas de vigilância sanitária para coleta de resíduos sólidos médico-hospitalares e construção de vestiários.</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1158,16 +1147,16 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Região Intermediária de Teófilo Otoni</t>
+          <t>Região Intermediária de Governador Valadares</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>DIAMANTINA</t>
+          <t>GOVERNADOR VALADARES</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>100000</v>
+        <v>41022</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -1175,32 +1164,35 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>1261</v>
+        <v>1251</v>
       </c>
       <c r="B12" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>368</v>
+        <v>302</v>
       </c>
       <c r="D12" t="n">
-        <v>168</v>
+        <v>135</v>
       </c>
       <c r="E12" t="n">
-        <v>4519</v>
+        <v>2060</v>
       </c>
       <c r="F12" t="n">
         <v>1</v>
       </c>
       <c r="G12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
         <v>11</v>
       </c>
+      <c r="I12" t="n">
+        <v>12875</v>
+      </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>OBRA PARA REFORÇO ESTRUTURAL, REFORMA E AMPLIAÇÃO - EE ABRE CAMPO</t>
+          <t>Construlção de local adequado para o armazenamento e descarte de resíduos de serviços de saúde, sendo necessária a adequação da estrutura física para atendimento às exigências dos órgãos de controle e consequente obtenção do alvará sanitário.</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1208,6 +1200,11 @@
           <t>INICIANDO</t>
         </is>
       </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>UNIDADE</t>
+        </is>
+      </c>
       <c r="M12" t="n">
         <v>1</v>
       </c>
@@ -1218,16 +1215,16 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Região Intermediária de Juíz de Fora</t>
+          <t>Região Intermediária de Teófilo Otoni</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>ABRE CAMPO</t>
+          <t>DIAMANTINA</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>380000</v>
+        <v>100000</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -1260,7 +1257,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>OBRA DE COMBATE A INCÊNDIO DE TODO O COMPLEXO E ACESSIBILIDADE NO CAMPUS GAMELEIRA - PRÉDIOS A,B,C,D (INCLUNDO MUSEU ESCOLA ANA MARIA CASASANTA PEIXOTO E MUSEU LEOPOLDO CATHOUD) E EE LEON RENAULT</t>
+          <t>OBRA PARA REFORÇO ESTRUTURAL, REFORMA E AMPLIAÇÃO - EE ABRE CAMPO</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1278,16 +1275,16 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Região Intermediária de Belo Horizonte</t>
+          <t>Região Intermediária de Juíz de Fora</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>BELO HORIZONTE</t>
+          <t>ABRE CAMPO</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>653600</v>
+        <v>380000</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -1320,7 +1317,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>REFORMA GERAL, RESTAURAÇÃO E RECUPERAÇÃO ESTRUTURAL EE GETÚLIO VARGAS</t>
+          <t>OBRA DE COMBATE A INCÊNDIO DE TODO O COMPLEXO E ACESSIBILIDADE NO CAMPUS GAMELEIRA - PRÉDIOS A,B,C,D (INCLUNDO MUSEU ESCOLA ANA MARIA CASASANTA PEIXOTO E MUSEU LEOPOLDO CATHOUD) E EE LEON RENAULT</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1347,7 +1344,7 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>332120</v>
+        <v>653600</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -1380,7 +1377,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>OBRA PARA RESTAURAÇÃO DO PRÉDIO EE JOSÉ BONIFÁCIO</t>
+          <t>REFORMA GERAL, RESTAURAÇÃO E RECUPERAÇÃO ESTRUTURAL EE GETÚLIO VARGAS</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1407,7 +1404,7 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>1033600</v>
+        <v>332120</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
@@ -1440,7 +1437,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>PROJETOS EXECUTIVOS PARA REFORMA E RESTAURAÇÃO EE OLEGÁRIO MACIEL</t>
+          <t>OBRA PARA RESTAURAÇÃO DO PRÉDIO EE JOSÉ BONIFÁCIO</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1467,7 +1464,7 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>59660</v>
+        <v>1033600</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
@@ -1500,7 +1497,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>OBRA PARA REFORMA E RESTAURAÇÃO EE OLEGÁRIO MACIEL</t>
+          <t>PROJETOS EXECUTIVOS PARA REFORMA E RESTAURAÇÃO EE OLEGÁRIO MACIEL</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1527,7 +1524,7 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>83600</v>
+        <v>59660</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -1560,7 +1557,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>OBRAS DE REFORMA GERAL EE PROF CAETANO AZEREDO</t>
+          <t>OBRA PARA REFORMA E RESTAURAÇÃO EE OLEGÁRIO MACIEL</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1587,7 +1584,7 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>805600</v>
+        <v>83600</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -1620,7 +1617,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>OBRA PARA REGULARIZAÇÃO DO PROCESSO DE SEGURANÇA CONTRA INCÊNDIO E PÂNICO (PSCIP), ADEQUAÇÃO À ACESSIBILIDADE EE PEDRO II</t>
+          <t>OBRAS DE REFORMA GERAL EE PROF CAETANO AZEREDO</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -1647,7 +1644,7 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>387600</v>
+        <v>805600</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
@@ -1680,7 +1677,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>OBRA PARA REFORMA E RESTAURAÇÃO (SOLUÇÃO DE PROBLEMAS ESTRUTURAIS) EE SANDOVAL AZEVEDO</t>
+          <t>OBRA PARA REGULARIZAÇÃO DO PROCESSO DE SEGURANÇA CONTRA INCÊNDIO E PÂNICO (PSCIP), ADEQUAÇÃO À ACESSIBILIDADE EE PEDRO II</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -1707,7 +1704,7 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>251560</v>
+        <v>387600</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
@@ -1740,7 +1737,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>OBRA DE REFORMA GERAL/RESTAURAÇÃO (MENOS TELHADO DA CASA MODELO, MURO DE ARRIMO) EE SÃO RAFAEL</t>
+          <t>OBRA PARA REFORMA E RESTAURAÇÃO (SOLUÇÃO DE PROBLEMAS ESTRUTURAIS) EE SANDOVAL AZEVEDO</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -1767,7 +1764,7 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>2121920</v>
+        <v>251560</v>
       </c>
       <c r="R21" t="n">
         <v>0</v>
@@ -1800,7 +1797,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>OBRA DE REFORMA - ESTRUTURA ESCOLA GUIGNARD UEMG</t>
+          <t>OBRA DE REFORMA GERAL/RESTAURAÇÃO (MENOS TELHADO DA CASA MODELO, MURO DE ARRIMO) EE SÃO RAFAEL</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -1827,7 +1824,7 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>1929640</v>
+        <v>2121920</v>
       </c>
       <c r="R22" t="n">
         <v>0</v>
@@ -1860,12 +1857,12 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>OBRAS DE REFORMA E RESTAURAÇÃO DOS PRÉDIOS INSTITUTO DE EDUCAÇÃO DE MINAS GERAIS - IEMG</t>
+          <t>OBRA DE REFORMA - ESTRUTURA ESCOLA GUIGNARD UEMG</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>EXECUÇÃO</t>
+          <t>INICIANDO</t>
         </is>
       </c>
       <c r="M23" t="n">
@@ -1887,7 +1884,7 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>3040000</v>
+        <v>1929640</v>
       </c>
       <c r="R23" t="n">
         <v>0</v>
@@ -1920,12 +1917,12 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>OBRA PARA REFORMA, DO PRÉDIO DO ANTIGO AUDITÓRIO DO CAMPUS DA SEE-  GAMELEIRA, PARA ABRIGAR A NOVA SEDE DA SRE MET B - SEDE DA SRE MET B - AUDITÓRIO GAMELEIRA</t>
+          <t>OBRAS DE REFORMA E RESTAURAÇÃO DOS PRÉDIOS INSTITUTO DE EDUCAÇÃO DE MINAS GERAIS - IEMG</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>INICIANDO</t>
+          <t>EXECUÇÃO</t>
         </is>
       </c>
       <c r="M24" t="n">
@@ -1947,7 +1944,7 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>3025160</v>
+        <v>3040000</v>
       </c>
       <c r="R24" t="n">
         <v>0</v>
@@ -1980,7 +1977,7 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>OBRA  PARA REFORMA/RESTAURAÇÃO EE SÃO JOAQUIM</t>
+          <t>OBRA PARA REFORMA, DO PRÉDIO DO ANTIGO AUDITÓRIO DO CAMPUS DA SEE-  GAMELEIRA, PARA ABRIGAR A NOVA SEDE DA SRE MET B - SEDE DA SRE MET B - AUDITÓRIO GAMELEIRA</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -2003,11 +2000,11 @@
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>CONCEIÇÃO DO MATO DENTRO</t>
+          <t>BELO HORIZONTE</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>2105200</v>
+        <v>3025160</v>
       </c>
       <c r="R25" t="n">
         <v>0</v>
@@ -2040,12 +2037,12 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>OBRA DE ESTRUTURA E OUTRAS, EM PRÉDIO TOMBADO</t>
+          <t>OBRA  PARA REFORMA/RESTAURAÇÃO EE SÃO JOAQUIM</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>EXECUÇÃO</t>
+          <t>INICIANDO</t>
         </is>
       </c>
       <c r="M26" t="n">
@@ -2063,11 +2060,11 @@
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>CORDISBURGO</t>
+          <t>CONCEIÇÃO DO MATO DENTRO</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>260300</v>
+        <v>2105200</v>
       </c>
       <c r="R26" t="n">
         <v>0</v>
@@ -2100,12 +2097,12 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>OBRA PARA REFORMA E SOLUÇÃO DE PROBLEMAS ESTRUTURAIS EE ODILON BEHRENS</t>
+          <t>OBRA DE ESTRUTURA E OUTRAS, EM PRÉDIO TOMBADO</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>INICIANDO</t>
+          <t>EXECUÇÃO</t>
         </is>
       </c>
       <c r="M27" t="n">
@@ -2118,16 +2115,16 @@
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>Região Intermediária de Governador Valadares</t>
+          <t>Região Intermediária de Belo Horizonte</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>GUANHÃES</t>
+          <t>CORDISBURGO</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>1705060</v>
+        <v>260300</v>
       </c>
       <c r="R27" t="n">
         <v>0</v>
@@ -2160,7 +2157,7 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t xml:space="preserve"> OBRA PARA SOLUÇÃO DE DESLIZAMENTO DE TERRA DE PARTE DO TALUDE E A RUPTURA DE PARTE DO MURO DIVISÓRIO INTERNO EE SELIM JOSÉ DE SALES</t>
+          <t>OBRA PARA REFORMA E SOLUÇÃO DE PROBLEMAS ESTRUTURAIS EE ODILON BEHRENS</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -2178,16 +2175,16 @@
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>Região Intermediária de Ipatinga</t>
+          <t>Região Intermediária de Governador Valadares</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>IPATINGA</t>
+          <t>GUANHÃES</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>190000</v>
+        <v>1705060</v>
       </c>
       <c r="R28" t="n">
         <v>0</v>
@@ -2220,7 +2217,7 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>OBRAS PARA RESTAURAÇÃO DO PRÉDIO EE WENCESLAU BRAZ</t>
+          <t xml:space="preserve"> OBRA PARA SOLUÇÃO DE DESLIZAMENTO DE TERRA DE PARTE DO TALUDE E A RUPTURA DE PARTE DO MURO DIVISÓRIO INTERNO EE SELIM JOSÉ DE SALES</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -2238,16 +2235,16 @@
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>Região Intermediária de Pouso Alegre</t>
+          <t>Região Intermediária de Ipatinga</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>ITAJUBÁ</t>
+          <t>IPATINGA</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>2420600</v>
+        <v>190000</v>
       </c>
       <c r="R29" t="n">
         <v>0</v>
@@ -2280,7 +2277,7 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>OBRA PARA REFORMA E CONTENÇÃO E ESTABILIDADE DE TALUDE E DO PRÉDIO EE SÃO JOSÉ</t>
+          <t>OBRAS PARA RESTAURAÇÃO DO PRÉDIO EE WENCESLAU BRAZ</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -2298,16 +2295,16 @@
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>Região Intermediária de Juíz de Fora</t>
+          <t>Região Intermediária de Pouso Alegre</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>ALÉM PARAÍBA</t>
+          <t>ITAJUBÁ</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>691600</v>
+        <v>2420600</v>
       </c>
       <c r="R30" t="n">
         <v>0</v>
@@ -2340,7 +2337,7 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>OBRA PARA RESTAURAÇÃO DO PRÉDIO EE RAUL SOARES</t>
+          <t>OBRA PARA REFORMA E CONTENÇÃO E ESTABILIDADE DE TALUDE E DO PRÉDIO EE SÃO JOSÉ</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -2358,16 +2355,16 @@
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>Região Intermediária de Uberlândia</t>
+          <t>Região Intermediária de Juíz de Fora</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>ARAGUARI</t>
+          <t>ALÉM PARAÍBA</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>380000</v>
+        <v>691600</v>
       </c>
       <c r="R31" t="n">
         <v>0</v>
@@ -2400,12 +2397,12 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>OBRA PARA REFORMA GERAL E RESTAURAÇÃO EE AFONSO PENA</t>
+          <t>OBRA PARA RESTAURAÇÃO DO PRÉDIO EE RAUL SOARES</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>EXECUÇÃO</t>
+          <t>INICIANDO</t>
         </is>
       </c>
       <c r="M32" t="n">
@@ -2418,16 +2415,16 @@
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>Região Intermediária de Belo Horizonte</t>
+          <t>Região Intermediária de Uberlândia</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>BELO HORIZONTE</t>
+          <t>ARAGUARI</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>1194340</v>
+        <v>380000</v>
       </c>
       <c r="R32" t="n">
         <v>0</v>
@@ -2460,12 +2457,12 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>REFORMA GERAL, RESTAURAÇÃO E RECUPERAÇÃO ESTRUTURAL EE FRANCISCO SALES</t>
+          <t>OBRA PARA REFORMA GERAL E RESTAURAÇÃO EE AFONSO PENA</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>INICIANDO</t>
+          <t>EXECUÇÃO</t>
         </is>
       </c>
       <c r="M33" t="n">
@@ -2487,7 +2484,7 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>407740</v>
+        <v>1194340</v>
       </c>
       <c r="R33" t="n">
         <v>0</v>
@@ -2520,7 +2517,7 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>OBRA PARA REFORMA E RESTAURAÇÃO COMPLEMENTARES - UNIDADE I EE GOV MILTON CAMPOS</t>
+          <t>REFORMA GERAL, RESTAURAÇÃO E RECUPERAÇÃO ESTRUTURAL EE FRANCISCO SALES</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -2547,7 +2544,7 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>1102000</v>
+        <v>407740</v>
       </c>
       <c r="R34" t="n">
         <v>0</v>
@@ -2580,7 +2577,7 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>OBRA PARA TALUDE E MURO EE PROFA MARIA AMÉLIA GUIMARÃES</t>
+          <t>OBRA PARA REFORMA E RESTAURAÇÃO COMPLEMENTARES - UNIDADE I EE GOV MILTON CAMPOS</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -2607,7 +2604,7 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>190000</v>
+        <v>1102000</v>
       </c>
       <c r="R35" t="n">
         <v>0</v>
@@ -2640,7 +2637,7 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>RESTAURAÇÃO, CONSERVAÇÃO E PRESERVAÇÃO ANTIGA ESCOLA DE APRENDIZES MARINHEIROS E CASA DO COMANDANTE - FUCAM (EE PROFESSORA MARIETA AMORIM VIEIRA)</t>
+          <t>OBRA PARA TALUDE E MURO EE PROFA MARIA AMÉLIA GUIMARÃES</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -2658,16 +2655,16 @@
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>Região Intermediária de Montes Claros</t>
+          <t>Região Intermediária de Belo Horizonte</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>BURITIZEIRO</t>
+          <t>BELO HORIZONTE</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>235600</v>
+        <v>190000</v>
       </c>
       <c r="R36" t="n">
         <v>0</v>
@@ -2700,7 +2697,7 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>ATENDIMENTOS ESCOLAS ESTADUAIS - CAIXAS ESCOLARES E CONVÊNIOS</t>
+          <t>RESTAURAÇÃO, CONSERVAÇÃO E PRESERVAÇÃO ANTIGA ESCOLA DE APRENDIZES MARINHEIROS E CASA DO COMANDANTE - FUCAM (EE PROFESSORA MARIETA AMORIM VIEIRA)</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -2715,6 +2712,22 @@
         <is>
           <t>Sim</t>
         </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>Região Intermediária de Montes Claros</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>BURITIZEIRO</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>235600</v>
+      </c>
+      <c r="R37" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -2744,7 +2757,7 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>OBRA - PROBLEMAS ESTRUTURAIS, ALÉM DE REFORMA E AMPLIAÇÃO DO PRÉDIO EE DR LAURO CORREA DO AMARAL</t>
+          <t>ATENDIMENTOS ESCOLAS ESTADUAIS - CAIXAS ESCOLARES E CONVÊNIOS</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -2759,22 +2772,6 @@
         <is>
           <t>Sim</t>
         </is>
-      </c>
-      <c r="O38" t="inlineStr">
-        <is>
-          <t>Região Intermediária de Varginha</t>
-        </is>
-      </c>
-      <c r="P38" t="inlineStr">
-        <is>
-          <t>GUAPÉ</t>
-        </is>
-      </c>
-      <c r="Q38" t="n">
-        <v>387600</v>
-      </c>
-      <c r="R38" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -2804,7 +2801,7 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>CONCLUSÃO DA OBRA DE CONTENÇÃO DE TALUDE E RECUPERAÇÕES NA CONSTRUÇÃO EE ANTÔNIO MARINHO CAMPOS</t>
+          <t>OBRA - PROBLEMAS ESTRUTURAIS, ALÉM DE REFORMA E AMPLIAÇÃO DO PRÉDIO EE DR LAURO CORREA DO AMARAL</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -2822,16 +2819,16 @@
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>Região Intermediária de Belo Horizonte</t>
+          <t>Região Intermediária de Varginha</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>IBIRITÉ</t>
+          <t>GUAPÉ</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>361760</v>
+        <v>387600</v>
       </c>
       <c r="R39" t="n">
         <v>0</v>
@@ -2864,7 +2861,7 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>OBRA DE CONTENÇÃO, REFORMA E REFORÇO ESTRUTURAL DO PRÉDIO EE ANTÔNIO PAPINI</t>
+          <t>CONCLUSÃO DA OBRA DE CONTENÇÃO DE TALUDE E RECUPERAÇÕES NA CONSTRUÇÃO EE ANTÔNIO MARINHO CAMPOS</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -2882,16 +2879,16 @@
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>Região Intermediária de Ipatinga</t>
+          <t>Região Intermediária de Belo Horizonte</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>JOÃO MONLEVADE</t>
+          <t>IBIRITÉ</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>218500</v>
+        <v>361760</v>
       </c>
       <c r="R40" t="n">
         <v>0</v>
@@ -2924,7 +2921,7 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>OBRA PARA REFORMA/RESTAURAÇÃO E  REPAROS ESTRUTURAIS EE DUQUE DE CAXIAS</t>
+          <t>OBRA DE CONTENÇÃO, REFORMA E REFORÇO ESTRUTURAL DO PRÉDIO EE ANTÔNIO PAPINI</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -2942,16 +2939,16 @@
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>Região Intermediária de Juíz de Fora</t>
+          <t>Região Intermediária de Ipatinga</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>JUIZ DE FORA</t>
+          <t>JOÃO MONLEVADE</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>1976000</v>
+        <v>218500</v>
       </c>
       <c r="R41" t="n">
         <v>0</v>
@@ -2984,7 +2981,7 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>OBRA DE CONSTRUÇÃO DA SEDESEDE DA SRE DE MONTES CLAROS</t>
+          <t>OBRA PARA REFORMA/RESTAURAÇÃO E  REPAROS ESTRUTURAIS EE DUQUE DE CAXIAS</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -3002,16 +2999,16 @@
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>Região Intermediária de Montes Claros</t>
+          <t>Região Intermediária de Juíz de Fora</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>MONTES CLAROS</t>
+          <t>JUIZ DE FORA</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>805600</v>
+        <v>1976000</v>
       </c>
       <c r="R42" t="n">
         <v>0</v>
@@ -3044,7 +3041,7 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>OBRAS DE CONTENÇÃO EE AUGUSTO DE LIMA</t>
+          <t>OBRA DE CONSTRUÇÃO DA SEDESEDE DA SRE DE MONTES CLAROS</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -3062,16 +3059,16 @@
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>Região Intermediária de Belo Horizonte</t>
+          <t>Região Intermediária de Montes Claros</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>NOVA LIMA</t>
+          <t>MONTES CLAROS</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>760000</v>
+        <v>805600</v>
       </c>
       <c r="R43" t="n">
         <v>0</v>
@@ -3104,7 +3101,7 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>OBRA PARA SOLUÇÃO DE PROBLEMAS  ESTRUTURAIS NO EDIFÍCIO, INCLUINDO INFILTRAÇÃO NAS PAREDES, DETERIORAÇÃO DO GUARDA-CORPO NA FACHADA, ABATIMENTO NO PISO, ASSOALHO DANIFICADO E INCLINAÇÃO DA FACHADA.EE PROFESSOR PINHEIRO CAMPOS</t>
+          <t>OBRAS DE CONTENÇÃO EE AUGUSTO DE LIMA</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -3122,16 +3119,16 @@
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>Região Intermediária de Divinópolis</t>
+          <t>Região Intermediária de Belo Horizonte</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>OLIVEIRA</t>
+          <t>NOVA LIMA</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>653600</v>
+        <v>760000</v>
       </c>
       <c r="R44" t="n">
         <v>0</v>
@@ -3164,12 +3161,12 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>REFORMA GERAL E RESTAURAÇÃO EE DOM PEDRO II</t>
+          <t>OBRA PARA SOLUÇÃO DE PROBLEMAS  ESTRUTURAIS NO EDIFÍCIO, INCLUINDO INFILTRAÇÃO NAS PAREDES, DETERIORAÇÃO DO GUARDA-CORPO NA FACHADA, ABATIMENTO NO PISO, ASSOALHO DANIFICADO E INCLINAÇÃO DA FACHADA.EE PROFESSOR PINHEIRO CAMPOS</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>EXECUÇÃO</t>
+          <t>INICIANDO</t>
         </is>
       </c>
       <c r="M45" t="n">
@@ -3182,16 +3179,16 @@
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>Região Intermediária de Belo Horizonte</t>
+          <t>Região Intermediária de Divinópolis</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>OURO PRETO</t>
+          <t>OLIVEIRA</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>1204600</v>
+        <v>653600</v>
       </c>
       <c r="R45" t="n">
         <v>0</v>
@@ -3224,12 +3221,12 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>OBRA PARA RESTAURAÇÃO EE PROFESSOR ANTÔNIO DIAS MACIEL</t>
+          <t>REFORMA GERAL E RESTAURAÇÃO EE DOM PEDRO II</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>INICIANDO</t>
+          <t>EXECUÇÃO</t>
         </is>
       </c>
       <c r="M46" t="n">
@@ -3242,16 +3239,16 @@
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>Região Intermediária de Patos de Minas</t>
+          <t>Região Intermediária de Belo Horizonte</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>PATOS DE MINAS</t>
+          <t>OURO PRETO</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>1927740</v>
+        <v>1204600</v>
       </c>
       <c r="R46" t="n">
         <v>0</v>
@@ -3284,7 +3281,7 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>OBRA RESTAURAÇÃO INSTITUTO DE EDUCAÇÃO DE JUIZ DE FORA</t>
+          <t>OBRA PARA RESTAURAÇÃO EE PROFESSOR ANTÔNIO DIAS MACIEL</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -3302,16 +3299,16 @@
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>Região Intermediária de Juíz de Fora</t>
+          <t>Região Intermediária de Patos de Minas</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>JUIZ DE FORA</t>
+          <t>PATOS DE MINAS</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>653600</v>
+        <v>1927740</v>
       </c>
       <c r="R47" t="n">
         <v>0</v>
@@ -3344,7 +3341,7 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>OBRA - PROBLEMAS REFERENTES À CONTENÇÃO DE TALUDE E DRENAGEM PLUVIALEE HENRIQUE BURNIER</t>
+          <t>OBRA RESTAURAÇÃO INSTITUTO DE EDUCAÇÃO DE JUIZ DE FORA</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -3371,7 +3368,7 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>19000</v>
+        <v>653600</v>
       </c>
       <c r="R48" t="n">
         <v>0</v>
@@ -3404,7 +3401,7 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>OBRA - PROBLEMAS REFERENTES À CONTENÇÃO DE TALUDE E DRENAGEM PLUVIALEE BATISTA DE OLIVEIRA</t>
+          <t>OBRA - PROBLEMAS REFERENTES À CONTENÇÃO DE TALUDE E DRENAGEM PLUVIALEE HENRIQUE BURNIER</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -3464,7 +3461,7 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>OBRA REFORMA, RESTAURAÇÃO E AMPLIAÇÃOEE ANA ROCHA (PREDIO EE FREI LEOPOLDO)</t>
+          <t>OBRA - PROBLEMAS REFERENTES À CONTENÇÃO DE TALUDE E DRENAGEM PLUVIALEE BATISTA DE OLIVEIRA</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -3482,16 +3479,16 @@
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>Região Intermediária de Patos de Minas</t>
+          <t>Região Intermediária de Juíz de Fora</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>MATUTINA</t>
+          <t>JUIZ DE FORA</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>1318600</v>
+        <v>19000</v>
       </c>
       <c r="R50" t="n">
         <v>0</v>
@@ -3524,12 +3521,12 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>OBRA PARA REFORMA DA EDIFICAÇÃO E EXECUÇÃO DAS OBRAS DE ESTABILIZAÇÃO DE TALUDE, REFORÇO DA CONTENÇÃO E CONSTRUÇÃO DE NOVO MURO DE DIVISA EE JULIETA DE OLIVEIRA MACEDO</t>
+          <t>OBRA REFORMA, RESTAURAÇÃO E AMPLIAÇÃOEE ANA ROCHA (PREDIO EE FREI LEOPOLDO)</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>EXECUÇÃO</t>
+          <t>INICIANDO</t>
         </is>
       </c>
       <c r="M51" t="n">
@@ -3542,16 +3539,16 @@
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>Região Intermediária de Juíz de Fora</t>
+          <t>Região Intermediária de Patos de Minas</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>MURIAÉ</t>
+          <t>MATUTINA</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>653600</v>
+        <v>1318600</v>
       </c>
       <c r="R51" t="n">
         <v>0</v>
@@ -3584,12 +3581,12 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>CONSTRUÇÃO DE PRÉDIO DA SEDE DA SRE DE MURIAÉ</t>
+          <t>OBRA PARA REFORMA DA EDIFICAÇÃO E EXECUÇÃO DAS OBRAS DE ESTABILIZAÇÃO DE TALUDE, REFORÇO DA CONTENÇÃO E CONSTRUÇÃO DE NOVO MURO DE DIVISA EE JULIETA DE OLIVEIRA MACEDO</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>INICIANDO</t>
+          <t>EXECUÇÃO</t>
         </is>
       </c>
       <c r="M52" t="n">
@@ -3611,7 +3608,7 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>19000</v>
+        <v>653600</v>
       </c>
       <c r="R52" t="n">
         <v>0</v>
@@ -3644,7 +3641,7 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>OBRA DE REFORMA SEDE DA SRE DE NOVA ERA</t>
+          <t>CONSTRUÇÃO DE PRÉDIO DA SEDE DA SRE DE MURIAÉ</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
@@ -3662,12 +3659,12 @@
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>Região Intermediária de Ipatinga</t>
+          <t>Região Intermediária de Juíz de Fora</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>NOVA ERA</t>
+          <t>MURIAÉ</t>
         </is>
       </c>
       <c r="Q53" t="n">
@@ -3704,7 +3701,7 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>OBRAS PARA PROBLEMAS ESTRUTURAIS NO AUDITÓRIO (ESTRUTURA PISO E TELHADO) - REFORMA GERAL E RESTAURAÇÃO - PRÉDIO TOMBADOEE FRANCISCO FERNANDES</t>
+          <t>OBRA DE REFORMA SEDE DA SRE DE NOVA ERA</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
@@ -3722,16 +3719,16 @@
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>Região Intermediária de Divinópolis</t>
+          <t>Região Intermediária de Ipatinga</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>OLIVEIRA</t>
+          <t>NOVA ERA</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>760000</v>
+        <v>19000</v>
       </c>
       <c r="R54" t="n">
         <v>0</v>
@@ -3764,7 +3761,7 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBRA PARA REFORMA GERAL / RESTAURAÇÃO EE CONSELHEIRO AFONSO PENA </t>
+          <t>OBRAS PARA PROBLEMAS ESTRUTURAIS NO AUDITÓRIO (ESTRUTURA PISO E TELHADO) - REFORMA GERAL E RESTAURAÇÃO - PRÉDIO TOMBADOEE FRANCISCO FERNANDES</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -3782,16 +3779,16 @@
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>Região Intermediária de Belo Horizonte</t>
+          <t>Região Intermediária de Divinópolis</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>PARAOPEBA</t>
+          <t>OLIVEIRA</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>19000</v>
+        <v>760000</v>
       </c>
       <c r="R55" t="n">
         <v>0</v>
@@ -3824,7 +3821,7 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>OBRA PARA RESTAURAÇÃOEE DOM LUSTOSA</t>
+          <t xml:space="preserve">OBRA PARA REFORMA GERAL / RESTAURAÇÃO EE CONSELHEIRO AFONSO PENA </t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
@@ -3842,12 +3839,12 @@
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>Região Intermediária de Patos de Minas</t>
+          <t>Região Intermediária de Belo Horizonte</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>PATROCÍNIO</t>
+          <t>PARAOPEBA</t>
         </is>
       </c>
       <c r="Q56" t="n">
@@ -3884,7 +3881,7 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>OBRA DE RESTAURAÇÃOSEDE DA SRE DE PATROCÍNIO</t>
+          <t>OBRA PARA RESTAURAÇÃOEE DOM LUSTOSA</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
@@ -3944,7 +3941,7 @@
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>OBRA PARA REFORMA E RESTAURAÇÃO DO PRÉDIOEE FRANCISCA BOTELHO</t>
+          <t>OBRA DE RESTAURAÇÃOSEDE DA SRE DE PATROCÍNIO</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
@@ -3962,16 +3959,16 @@
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>Região Intermediária de Divinópolis</t>
+          <t>Região Intermediária de Patos de Minas</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>PITANGUI</t>
+          <t>PATROCÍNIO</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>434720</v>
+        <v>19000</v>
       </c>
       <c r="R58" t="n">
         <v>0</v>
@@ -4004,7 +4001,7 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>OBRA  DE REFORMA E RESTAURAÇÃOCESEC TANCREDO NEVES (PRÉDIO OCUPADO ANTERIORMENTE PELA EE FARNESE MACIEL )</t>
+          <t>OBRA PARA REFORMA E RESTAURAÇÃO DO PRÉDIOEE FRANCISCA BOTELHO</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -4022,16 +4019,16 @@
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>Região Intermediária de Patos de Minas</t>
+          <t>Região Intermediária de Divinópolis</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>PRESIDENTE OLEGÁRIO</t>
+          <t>PITANGUI</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>221160</v>
+        <v>434720</v>
       </c>
       <c r="R59" t="n">
         <v>0</v>
@@ -4064,7 +4061,7 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>CONCLUSÃO DA OBRA DE REFORMA E RESTAURAÇÃO EE JOAO DOS SANTOS</t>
+          <t>OBRA  DE REFORMA E RESTAURAÇÃOCESEC TANCREDO NEVES (PRÉDIO OCUPADO ANTERIORMENTE PELA EE FARNESE MACIEL )</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
@@ -4082,16 +4079,16 @@
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>Região Intermediária de Barbacena</t>
+          <t>Região Intermediária de Patos de Minas</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>SÃO JOÃO DEL REI</t>
+          <t>PRESIDENTE OLEGÁRIO</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>1748000</v>
+        <v>221160</v>
       </c>
       <c r="R60" t="n">
         <v>0</v>
@@ -4124,7 +4121,7 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>OBRA PARA SOLUÇÃO DE PROBLEMAS ESTRUTURAISSEDE DA SRE DE SETE LAGOAS</t>
+          <t>CONCLUSÃO DA OBRA DE REFORMA E RESTAURAÇÃO EE JOAO DOS SANTOS</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
@@ -4142,16 +4139,16 @@
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>Região Intermediária de Belo Horizonte</t>
+          <t>Região Intermediária de Barbacena</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>SETE LAGOAS</t>
+          <t>SÃO JOÃO DEL REI</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>479560</v>
+        <v>1748000</v>
       </c>
       <c r="R61" t="n">
         <v>0</v>
@@ -4184,7 +4181,7 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>OBRA PARA REPAROS ESTRUTURAIS (EXECUÇÃO DO REFORÇO DE FUNDAÇÃO E SERVIÇOS CORRELATOS) - 1A ETAPAEE DEPUTADO CARLOS PEIXOTO FILHO</t>
+          <t>OBRA PARA SOLUÇÃO DE PROBLEMAS ESTRUTURAISSEDE DA SRE DE SETE LAGOAS</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
@@ -4202,16 +4199,16 @@
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>Região Intermediária de Juíz de Fora</t>
+          <t>Região Intermediária de Belo Horizonte</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>UBÁ</t>
+          <t>SETE LAGOAS</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>228000</v>
+        <v>479560</v>
       </c>
       <c r="R62" t="n">
         <v>0</v>
@@ -4244,12 +4241,12 @@
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>CONSTRUÇÃO DE ESCOLA - 16 SALAS DE AULA (NO BAIRRO JARDIM CÉLIA)EE 13 DE MAIO</t>
+          <t>OBRA PARA REPAROS ESTRUTURAIS (EXECUÇÃO DO REFORÇO DE FUNDAÇÃO E SERVIÇOS CORRELATOS) - 1A ETAPAEE DEPUTADO CARLOS PEIXOTO FILHO</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>EXECUÇÃO</t>
+          <t>INICIANDO</t>
         </is>
       </c>
       <c r="M63" t="n">
@@ -4262,16 +4259,16 @@
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>Região Intermediária de Uberlândia</t>
+          <t>Região Intermediária de Juíz de Fora</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>UBERLÂNDIA</t>
+          <t>UBÁ</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>2552080</v>
+        <v>228000</v>
       </c>
       <c r="R63" t="n">
         <v>0</v>
@@ -4304,12 +4301,12 @@
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>REFORMA / REFORÇO ESTRUTURALEE CORAÇÃO DE JESUS</t>
+          <t>CONSTRUÇÃO DE ESCOLA - 16 SALAS DE AULA (NO BAIRRO JARDIM CÉLIA)EE 13 DE MAIO</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>INICIANDO</t>
+          <t>EXECUÇÃO</t>
         </is>
       </c>
       <c r="M64" t="n">
@@ -4322,16 +4319,16 @@
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>Região Intermediária de Varginha</t>
+          <t>Região Intermediária de Uberlândia</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>VARGINHA</t>
+          <t>UBERLÂNDIA</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>1386240</v>
+        <v>2552080</v>
       </c>
       <c r="R64" t="n">
         <v>0</v>
@@ -4364,7 +4361,7 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>OBRA PARA REFORMA/RESTAURAÇÃO EE BRASIL</t>
+          <t>REFORMA / REFORÇO ESTRUTURALEE CORAÇÃO DE JESUS</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
@@ -4391,7 +4388,7 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>1900000</v>
+        <v>1386240</v>
       </c>
       <c r="R65" t="n">
         <v>0</v>
@@ -4424,7 +4421,7 @@
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>OBRA DE REFORMA E RESTAURAÇÃOEE DR. JOÃO PINHEIRO</t>
+          <t>OBRA PARA REFORMA/RESTAURAÇÃO EE BRASIL</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
@@ -4447,11 +4444,11 @@
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>SÃO GONÇALO DO SAPUCAÍ</t>
+          <t>VARGINHA</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>1008140</v>
+        <v>1900000</v>
       </c>
       <c r="R66" t="n">
         <v>0</v>
@@ -4484,7 +4481,7 @@
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>OBRAS PARA MURO DE ARRIMO E DRENAGEM, ALÉM DE REFORMA/RESTAURAÇÃO EE MINISTRO EDMUNDO LINS</t>
+          <t>OBRA DE REFORMA E RESTAURAÇÃOEE DR. JOÃO PINHEIRO</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
@@ -4502,16 +4499,16 @@
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>Região Intermediária de Teófilo Otoni</t>
+          <t>Região Intermediária de Varginha</t>
         </is>
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>SERRO</t>
+          <t>SÃO GONÇALO DO SAPUCAÍ</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>380000</v>
+        <v>1008140</v>
       </c>
       <c r="R67" t="n">
         <v>0</v>
@@ -4544,7 +4541,7 @@
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>OBRA PARA REFORMA E RESTAURAÇÃOEE DR. ARTHUR BERNARDES</t>
+          <t>OBRAS PARA MURO DE ARRIMO E DRENAGEM, ALÉM DE REFORMA/RESTAURAÇÃO EE MINISTRO EDMUNDO LINS</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
@@ -4562,16 +4559,16 @@
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>Região Intermediária de Belo Horizonte</t>
+          <t>Região Intermediária de Teófilo Otoni</t>
         </is>
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>SETE LAGOAS</t>
+          <t>SERRO</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>228000</v>
+        <v>380000</v>
       </c>
       <c r="R68" t="n">
         <v>0</v>
@@ -4604,7 +4601,7 @@
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>OBRA PARA SOLUÇÃO DE PROBLEMAS ESTRUTURAISEE HAYDÉE DE SOUZA ABREU</t>
+          <t>OBRA PARA REFORMA E RESTAURAÇÃOEE DR. ARTHUR BERNARDES</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
@@ -4622,16 +4619,16 @@
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>Região Intermediária de Ipatinga</t>
+          <t>Região Intermediária de Belo Horizonte</t>
         </is>
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>TIMÓTEO</t>
+          <t>SETE LAGOAS</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>539600</v>
+        <v>228000</v>
       </c>
       <c r="R69" t="n">
         <v>0</v>
@@ -4664,7 +4661,7 @@
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>OBRA - MANUTENÇÃO E REVISÃO COMPLETA DAS COBERTURAS; PINTURA EXTERNA E INTERNA; RESTAURO DE ESQUADRIAS;  REVISÃO DE TODA A REDE ELÉTRICA; RESTAURO DA PINTURA ARTÍSTICA DO RODATETO E PROSPECÇÃO EXPLORATÓRIA NO HALL DE ENTRADA, VISANDO AVALIAR A EXISTÊ</t>
+          <t>OBRA PARA SOLUÇÃO DE PROBLEMAS ESTRUTURAISEE HAYDÉE DE SOUZA ABREU</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
@@ -4682,16 +4679,16 @@
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>Região Intermediária de Uberlândia</t>
+          <t>Região Intermediária de Ipatinga</t>
         </is>
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>UBERLÂNDIA</t>
+          <t>TIMÓTEO</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>19000</v>
+        <v>539600</v>
       </c>
       <c r="R70" t="n">
         <v>0</v>
@@ -4724,12 +4721,12 @@
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>OBRA PARA RESTAURAÇÃO EE AFONSO PENA</t>
+          <t>OBRA - MANUTENÇÃO E REVISÃO COMPLETA DAS COBERTURAS; PINTURA EXTERNA E INTERNA; RESTAURO DE ESQUADRIAS;  REVISÃO DE TODA A REDE ELÉTRICA; RESTAURO DA PINTURA ARTÍSTICA DO RODATETO E PROSPECÇÃO EXPLORATÓRIA NO HALL DE ENTRADA, VISANDO AVALIAR A EXISTÊ</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>EXECUÇÃO</t>
+          <t>INICIANDO</t>
         </is>
       </c>
       <c r="M71" t="n">
@@ -4742,16 +4739,16 @@
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>Região Intermediária de Varginha</t>
+          <t>Região Intermediária de Uberlândia</t>
         </is>
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>VARGINHA</t>
+          <t>UBERLÂNDIA</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>2074800</v>
+        <v>19000</v>
       </c>
       <c r="R71" t="n">
         <v>0</v>
@@ -4759,35 +4756,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>1301</v>
+        <v>1261</v>
       </c>
       <c r="B72" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C72" t="n">
-        <v>451</v>
+        <v>368</v>
       </c>
       <c r="D72" t="n">
-        <v>81</v>
+        <v>168</v>
       </c>
       <c r="E72" t="n">
-        <v>1037</v>
+        <v>4519</v>
       </c>
       <c r="F72" t="n">
         <v>1</v>
       </c>
       <c r="G72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H72" t="n">
         <v>71</v>
       </c>
-      <c r="I72" t="n">
-        <v>12404</v>
-      </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>DC-018/2023-Execução das serviço de Aumento de capacidade e Recuperação de Rodovia (aumento de capacidade) no trecho Três Pontas - Varginhas (Estaca 80 a 610), com 10,60 km de extensão, na Rodovia MG-167</t>
+          <t>OBRA PARA RESTAURAÇÃO EE AFONSO PENA</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
@@ -4795,9 +4789,12 @@
           <t>EXECUÇÃO</t>
         </is>
       </c>
+      <c r="M72" t="n">
+        <v>1</v>
+      </c>
       <c r="N72" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="O72" t="inlineStr">
@@ -4807,14 +4804,14 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>TRÊS PONTAS</t>
+          <t>VARGINHA</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>280106</v>
+        <v>2074800</v>
       </c>
       <c r="R72" t="n">
-        <v>519640</v>
+        <v>0</v>
       </c>
     </row>
     <row r="73">
@@ -4843,11 +4840,11 @@
         <v>72</v>
       </c>
       <c r="I73" t="n">
-        <v>12780</v>
+        <v>12404</v>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>Execução das obras de Implantação de Passarela na Rodovia MG-010, Km 15+850, trecho Belo Horizonte - Lagoa Santa (Cidade Administrativa), extensão de 312,00 m</t>
+          <t>DC-018/2023-Execução das serviço de Aumento de capacidade e Recuperação de Rodovia (aumento de capacidade) no trecho Três Pontas - Varginhas (Estaca 80 a 610), com 10,60 km de extensão, na Rodovia MG-167</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
@@ -4862,19 +4859,19 @@
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t>Região Intermediária de Belo Horizonte</t>
+          <t>Região Intermediária de Varginha</t>
         </is>
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>BELO HORIZONTE</t>
+          <t>TRÊS PONTAS</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>894720</v>
+        <v>280106</v>
       </c>
       <c r="R73" t="n">
-        <v>4087644</v>
+        <v>519640</v>
       </c>
     </row>
     <row r="74">
@@ -4903,11 +4900,11 @@
         <v>73</v>
       </c>
       <c r="I74" t="n">
-        <v>10397</v>
+        <v>12780</v>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>PRC-22.021/18 -Melhoramento e pavimentação no trecho Ibertioga  Piedade do Rio Grande, na Rodovia MG/338, extensão de 13,25km</t>
+          <t>Execução das obras de Implantação de Passarela na Rodovia MG-010, Km 15+850, trecho Belo Horizonte - Lagoa Santa (Cidade Administrativa), extensão de 312,00 m</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
@@ -4922,19 +4919,19 @@
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t>Região Intermediária de Barbacena</t>
+          <t>Região Intermediária de Belo Horizonte</t>
         </is>
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>IBERTIOGA</t>
+          <t>BELO HORIZONTE</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>8264640</v>
+        <v>894720</v>
       </c>
       <c r="R74" t="n">
-        <v>19153735</v>
+        <v>4087644</v>
       </c>
     </row>
     <row r="75">
@@ -4963,11 +4960,11 @@
         <v>74</v>
       </c>
       <c r="I75" t="n">
-        <v>12850</v>
+        <v>10397</v>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>Melhoramento e pavimentação do trecho de Jaboticatubas - Lagoa Santa, em rodovia Municipal.</t>
+          <t>PRC-22.021/18 -Melhoramento e pavimentação no trecho Ibertioga  Piedade do Rio Grande, na Rodovia MG/338, extensão de 13,25km</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
@@ -4982,19 +4979,19 @@
       </c>
       <c r="O75" t="inlineStr">
         <is>
-          <t>Região Intermediária de Belo Horizonte</t>
+          <t>Região Intermediária de Barbacena</t>
         </is>
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>JABOTICATUBAS</t>
+          <t>IBERTIOGA</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>3155040</v>
+        <v>8264640</v>
       </c>
       <c r="R75" t="n">
-        <v>23943007</v>
+        <v>19153735</v>
       </c>
     </row>
     <row r="76">
@@ -5023,11 +5020,11 @@
         <v>75</v>
       </c>
       <c r="I76" t="n">
-        <v>12634</v>
+        <v>12850</v>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>Melhoramento e pavimentação do Trecho Itapagipe - Entrº 364 (Campina Verde) MGC 154 - LOTE 01</t>
+          <t>Melhoramento e pavimentação do trecho de Jaboticatubas - Lagoa Santa, em rodovia Municipal.</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
@@ -5042,19 +5039,19 @@
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t>Região Intermediária de Uberaba</t>
+          <t>Região Intermediária de Belo Horizonte</t>
         </is>
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>ITAPAGIPE</t>
+          <t>JABOTICATUBAS</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>4840800</v>
+        <v>3155040</v>
       </c>
       <c r="R76" t="n">
-        <v>26593690</v>
+        <v>23943007</v>
       </c>
     </row>
     <row r="77">
@@ -5083,11 +5080,11 @@
         <v>76</v>
       </c>
       <c r="I77" t="n">
-        <v>12785</v>
+        <v>12634</v>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>Execução da Obra de Engenharia de Melhoramento e pavimentação da Interseção de acesso ao Presídio de Iturama, na via Municipal, com extensão de 2,000 km.</t>
+          <t>Melhoramento e pavimentação do Trecho Itapagipe - Entrº 364 (Campina Verde) MGC 154 - LOTE 01</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
@@ -5107,14 +5104,14 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>ITURAMA</t>
+          <t>ITAPAGIPE</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>613500</v>
+        <v>4840800</v>
       </c>
       <c r="R77" t="n">
-        <v>2870210</v>
+        <v>26593690</v>
       </c>
     </row>
     <row r="78">
@@ -5143,11 +5140,11 @@
         <v>77</v>
       </c>
       <c r="I78" t="n">
-        <v>12824</v>
+        <v>12785</v>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>Melhoramento e Pavimentação em Rodovia de Ligação no trecho Entrº LMG-690 (Paracatu) - Entrº Entre Ribeiros - Lote 1 - Segmento 1 (0 a 835), extensão: 16,700 km e Segmento 2 (835 a 1250), extensão 8,300 km.</t>
+          <t>Execução da Obra de Engenharia de Melhoramento e pavimentação da Interseção de acesso ao Presídio de Iturama, na via Municipal, com extensão de 2,000 km.</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
@@ -5162,19 +5159,19 @@
       </c>
       <c r="O78" t="inlineStr">
         <is>
-          <t>Região Intermediária de Patos de Minas</t>
+          <t>Região Intermediária de Uberaba</t>
         </is>
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>PARACATU</t>
+          <t>ITURAMA</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>5963400</v>
+        <v>613500</v>
       </c>
       <c r="R78" t="n">
-        <v>23280000</v>
+        <v>2870210</v>
       </c>
     </row>
     <row r="79">
@@ -5203,11 +5200,11 @@
         <v>78</v>
       </c>
       <c r="I79" t="n">
-        <v>4716</v>
+        <v>12824</v>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>Entr. BR/365-Entr. LMG/782 (p/ Iraí de Minas), Monte Carmelo-Chapada de Minas e Pindaibas-Ent.BR/365</t>
+          <t>Melhoramento e Pavimentação em Rodovia de Ligação no trecho Entrº LMG-690 (Paracatu) - Entrº Entre Ribeiros - Lote 1 - Segmento 1 (0 a 835), extensão: 16,700 km e Segmento 2 (835 a 1250), extensão 8,300 km.</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
@@ -5222,19 +5219,19 @@
       </c>
       <c r="O79" t="inlineStr">
         <is>
-          <t>Região Intermediária de Uberlândia</t>
+          <t>Região Intermediária de Patos de Minas</t>
         </is>
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>MONTE CARMELO</t>
+          <t>PARACATU</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>3620820</v>
+        <v>5963400</v>
       </c>
       <c r="R79" t="n">
-        <v>19100000</v>
+        <v>23280000</v>
       </c>
     </row>
     <row r="80">
@@ -5262,14 +5259,17 @@
       <c r="H80" t="n">
         <v>79</v>
       </c>
+      <c r="I80" t="n">
+        <v>4716</v>
+      </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>Recapeamento de vias / pavimentação de trecho rodoviário / pavimentação e obra de arte especial no trecho viário; para melhoria da infraestrutura viária do Estado de Minas Gerais (8 propostas de novos convênios)</t>
+          <t>Entr. BR/365-Entr. LMG/782 (p/ Iraí de Minas), Monte Carmelo-Chapada de Minas e Pindaibas-Ent.BR/365</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>INICIANDO</t>
+          <t>EXECUÇÃO</t>
         </is>
       </c>
       <c r="N80" t="inlineStr">
@@ -5279,19 +5279,19 @@
       </c>
       <c r="O80" t="inlineStr">
         <is>
-          <t>Estadual</t>
+          <t>Região Intermediária de Uberlândia</t>
         </is>
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
+          <t>MONTE CARMELO</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>0</v>
+        <v>3620820</v>
       </c>
       <c r="R80" t="n">
-        <v>11755000</v>
+        <v>19100000</v>
       </c>
     </row>
     <row r="81">
@@ -5305,10 +5305,10 @@
         <v>451</v>
       </c>
       <c r="D81" t="n">
-        <v>99</v>
+        <v>81</v>
       </c>
       <c r="E81" t="n">
-        <v>1038</v>
+        <v>1037</v>
       </c>
       <c r="F81" t="n">
         <v>1</v>
@@ -5319,17 +5319,14 @@
       <c r="H81" t="n">
         <v>80</v>
       </c>
-      <c r="I81" t="n">
-        <v>11140</v>
-      </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t xml:space="preserve">CONSTRUÇÃO DE 64 UNIDADES HABITACIONAIS PAC FNHIS </t>
+          <t>Recapeamento de vias / pavimentação de trecho rodoviário / pavimentação e obra de arte especial no trecho viário; para melhoria da infraestrutura viária do Estado de Minas Gerais (8 propostas de novos convênios)</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>EXECUÇÃO</t>
+          <t>INICIANDO</t>
         </is>
       </c>
       <c r="N81" t="inlineStr">
@@ -5339,19 +5336,19 @@
       </c>
       <c r="O81" t="inlineStr">
         <is>
-          <t>Região Intermediária de Belo Horizonte</t>
+          <t>Estadual</t>
         </is>
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>CONTAGEM</t>
+          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>1839798</v>
+        <v>0</v>
       </c>
       <c r="R81" t="n">
-        <v>3269655</v>
+        <v>11755000</v>
       </c>
     </row>
     <row r="82">
@@ -5380,11 +5377,11 @@
         <v>81</v>
       </c>
       <c r="I82" t="n">
-        <v>11531</v>
+        <v>11140</v>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>REQUALIFICAÇÃO URBANA E AMBIENTAL DO RIBEIRÃO ARRUDAS - FNHIS/2009 - Continuidade da execução do PTTS (Programa de Trabalho Técnico-Social)</t>
+          <t xml:space="preserve">CONSTRUÇÃO DE 64 UNIDADES HABITACIONAIS PAC FNHIS </t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
@@ -5408,10 +5405,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>222899</v>
+        <v>1839798</v>
       </c>
       <c r="R82" t="n">
-        <v>0</v>
+        <v>3269655</v>
       </c>
     </row>
     <row r="83">
@@ -5428,7 +5425,7 @@
         <v>99</v>
       </c>
       <c r="E83" t="n">
-        <v>4262</v>
+        <v>1038</v>
       </c>
       <c r="F83" t="n">
         <v>1</v>
@@ -5439,9 +5436,12 @@
       <c r="H83" t="n">
         <v>82</v>
       </c>
+      <c r="I83" t="n">
+        <v>11531</v>
+      </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>Aquisição de materiais para obras - mata-burros, vigas metálicas e bueiros metálicos</t>
+          <t>REQUALIFICAÇÃO URBANA E AMBIENTAL DO RIBEIRÃO ARRUDAS - FNHIS/2009 - Continuidade da execução do PTTS (Programa de Trabalho Técnico-Social)</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
@@ -5456,16 +5456,16 @@
       </c>
       <c r="O83" t="inlineStr">
         <is>
-          <t>Estadual</t>
+          <t>Região Intermediária de Belo Horizonte</t>
         </is>
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
+          <t>CONTAGEM</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>10932874</v>
+        <v>222899</v>
       </c>
       <c r="R83" t="n">
         <v>0</v>
@@ -5476,16 +5476,16 @@
         <v>1301</v>
       </c>
       <c r="B84" t="n">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="C84" t="n">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="D84" t="n">
-        <v>117</v>
+        <v>99</v>
       </c>
       <c r="E84" t="n">
-        <v>4290</v>
+        <v>4262</v>
       </c>
       <c r="F84" t="n">
         <v>1</v>
@@ -5496,12 +5496,9 @@
       <c r="H84" t="n">
         <v>83</v>
       </c>
-      <c r="I84" t="n">
-        <v>12510</v>
-      </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t xml:space="preserve"> tratamento viário para implantação de sistema BRS em dois corredores de importância metropolitana na Região Metropolitana de Belo Horizonte (RMBH)</t>
+          <t>Aquisição de materiais para obras - mata-burros, vigas metálicas e bueiros metálicos</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
@@ -5516,19 +5513,19 @@
       </c>
       <c r="O84" t="inlineStr">
         <is>
-          <t>Região Intermediária de Belo Horizonte</t>
+          <t>Estadual</t>
         </is>
       </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>BELO HORIZONTE</t>
+          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>0</v>
+        <v>10932874</v>
       </c>
       <c r="R84" t="n">
-        <v>40000000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="85">
@@ -5556,14 +5553,17 @@
       <c r="H85" t="n">
         <v>84</v>
       </c>
+      <c r="I85" t="n">
+        <v>12510</v>
+      </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>Pagamento reajuste previsão INCC - Contrato de repasse 970648 (PAC MOBILIDADE - Obra Av Brasília)</t>
+          <t xml:space="preserve"> tratamento viário para implantação de sistema BRS em dois corredores de importância metropolitana na Região Metropolitana de Belo Horizonte (RMBH)</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>INICIANDO</t>
+          <t>EXECUÇÃO</t>
         </is>
       </c>
       <c r="N85" t="inlineStr">
@@ -5582,10 +5582,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>478579</v>
+        <v>0</v>
       </c>
       <c r="R85" t="n">
-        <v>0</v>
+        <v>40000000</v>
       </c>
     </row>
     <row r="86">
@@ -5615,7 +5615,7 @@
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>Pagamento reajuste previsão INCC - Contrato de repasse 970648 (PAC MOBILIDADE - Obra Av Civilização/Vilarinho)</t>
+          <t>Pagamento reajuste previsão INCC - Contrato de repasse 970648 (PAC MOBILIDADE - Obra Av Brasília)</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
@@ -5639,7 +5639,7 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>2246479</v>
+        <v>478579</v>
       </c>
       <c r="R86" t="n">
         <v>0</v>
@@ -5672,7 +5672,7 @@
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>Pagamento reajuste previsão INCC - Contrato de repasse 970648 (PAC MOBILIDADE -  Obras Estações  BRT MG10)</t>
+          <t>Pagamento reajuste previsão INCC - Contrato de repasse 970648 (PAC MOBILIDADE - Obra Av Civilização/Vilarinho)</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
@@ -5696,7 +5696,7 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>156926</v>
+        <v>2246479</v>
       </c>
       <c r="R87" t="n">
         <v>0</v>
@@ -5707,16 +5707,16 @@
         <v>1301</v>
       </c>
       <c r="B88" t="n">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="C88" t="n">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="D88" t="n">
-        <v>139</v>
+        <v>117</v>
       </c>
       <c r="E88" t="n">
-        <v>1036</v>
+        <v>4290</v>
       </c>
       <c r="F88" t="n">
         <v>1</v>
@@ -5727,17 +5727,14 @@
       <c r="H88" t="n">
         <v>87</v>
       </c>
-      <c r="I88" t="n">
-        <v>12453</v>
-      </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>LOTE 1 EXECUCAO DAS OBRAS DE ESTABILIZACAO E CONTENCAO DE ENCOSTAS EM AREAS URBANAS EM ALEM PARAIBA</t>
+          <t>Pagamento reajuste previsão INCC - Contrato de repasse 970648 (PAC MOBILIDADE -  Obras Estações  BRT MG10)</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>EXECUÇÃO</t>
+          <t>INICIANDO</t>
         </is>
       </c>
       <c r="N88" t="inlineStr">
@@ -5747,19 +5744,19 @@
       </c>
       <c r="O88" t="inlineStr">
         <is>
-          <t>Região Intermediária de Juíz de Fora</t>
+          <t>Região Intermediária de Belo Horizonte</t>
         </is>
       </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>ALÉM PARAÍBA</t>
+          <t>BELO HORIZONTE</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>0</v>
+        <v>156926</v>
       </c>
       <c r="R88" t="n">
-        <v>539924</v>
+        <v>0</v>
       </c>
     </row>
     <row r="89">
@@ -5788,11 +5785,11 @@
         <v>88</v>
       </c>
       <c r="I89" t="n">
-        <v>12454</v>
+        <v>12453</v>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>LOTE  2 -  EXECUCAO DAS OBRAS DE ESTABILIZACAO E CONTENCAO DE ENCOSTAS EM AREAS URBANAS EM MURIAE</t>
+          <t>LOTE 1 EXECUCAO DAS OBRAS DE ESTABILIZACAO E CONTENCAO DE ENCOSTAS EM AREAS URBANAS EM ALEM PARAIBA</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
@@ -5812,14 +5809,14 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>MURIAÉ</t>
+          <t>ALÉM PARAÍBA</t>
         </is>
       </c>
       <c r="Q89" t="n">
         <v>0</v>
       </c>
       <c r="R89" t="n">
-        <v>15337533</v>
+        <v>539924</v>
       </c>
     </row>
     <row r="90">
@@ -5848,11 +5845,11 @@
         <v>89</v>
       </c>
       <c r="I90" t="n">
-        <v>11521</v>
+        <v>12454</v>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>Obras de contenção de encostas em Sabará - Intervenção em setores de risco alto e muito alto, no âmbito do Programa PAC Gestão de Riscos e Resposta a Desastres.</t>
+          <t>LOTE  2 -  EXECUCAO DAS OBRAS DE ESTABILIZACAO E CONTENCAO DE ENCOSTAS EM AREAS URBANAS EM MURIAE</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
@@ -5867,19 +5864,19 @@
       </c>
       <c r="O90" t="inlineStr">
         <is>
-          <t>Região Intermediária de Belo Horizonte</t>
+          <t>Região Intermediária de Juíz de Fora</t>
         </is>
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>SABARÁ</t>
+          <t>MURIAÉ</t>
         </is>
       </c>
       <c r="Q90" t="n">
         <v>0</v>
       </c>
       <c r="R90" t="n">
-        <v>1440021</v>
+        <v>15337533</v>
       </c>
     </row>
     <row r="91">
@@ -5908,11 +5905,11 @@
         <v>90</v>
       </c>
       <c r="I91" t="n">
-        <v>11519</v>
+        <v>11521</v>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>Obras de contenção de encostas em João Monlevade - Intervenção em setores de risco alto e muito alto, no âmbito do Programa PAC Gestão de Riscos e Resposta a Desastres.</t>
+          <t>Obras de contenção de encostas em Sabará - Intervenção em setores de risco alto e muito alto, no âmbito do Programa PAC Gestão de Riscos e Resposta a Desastres.</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
@@ -5927,19 +5924,19 @@
       </c>
       <c r="O91" t="inlineStr">
         <is>
-          <t>Região Intermediária de Ipatinga</t>
+          <t>Região Intermediária de Belo Horizonte</t>
         </is>
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>JOÃO MONLEVADE</t>
+          <t>SABARÁ</t>
         </is>
       </c>
       <c r="Q91" t="n">
         <v>0</v>
       </c>
       <c r="R91" t="n">
-        <v>6942767</v>
+        <v>1440021</v>
       </c>
     </row>
     <row r="92">
@@ -5968,16 +5965,16 @@
         <v>91</v>
       </c>
       <c r="I92" t="n">
-        <v>11512</v>
+        <v>11519</v>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>bras de contenção de encostas em Timóteo - Intervenção em setores de risco alto e muito alto, no âmbito do Programa PAC Gestão de Riscos e Respostas a Desastres.</t>
+          <t>Obras de contenção de encostas em João Monlevade - Intervenção em setores de risco alto e muito alto, no âmbito do Programa PAC Gestão de Riscos e Resposta a Desastres.</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>INICIANDO</t>
+          <t>EXECUÇÃO</t>
         </is>
       </c>
       <c r="N92" t="inlineStr">
@@ -5992,14 +5989,14 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>TIMÓTEO</t>
+          <t>JOÃO MONLEVADE</t>
         </is>
       </c>
       <c r="Q92" t="n">
         <v>0</v>
       </c>
       <c r="R92" t="n">
-        <v>14686005</v>
+        <v>6942767</v>
       </c>
     </row>
     <row r="93">
@@ -6028,16 +6025,16 @@
         <v>92</v>
       </c>
       <c r="I93" t="n">
-        <v>11514</v>
+        <v>11512</v>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>Obras de Contenção de encostas em Ouro Preto - Intervenção em setores de risco alto e muito alto, no ambito do programa PAC gestão de riscos e resposta a desastres.</t>
+          <t>bras de contenção de encostas em Timóteo - Intervenção em setores de risco alto e muito alto, no âmbito do Programa PAC Gestão de Riscos e Respostas a Desastres.</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>EXECUÇÃO</t>
+          <t>INICIANDO</t>
         </is>
       </c>
       <c r="N93" t="inlineStr">
@@ -6047,19 +6044,19 @@
       </c>
       <c r="O93" t="inlineStr">
         <is>
-          <t>Região Intermediária de Belo Horizonte</t>
+          <t>Região Intermediária de Ipatinga</t>
         </is>
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>OURO PRETO</t>
+          <t>TIMÓTEO</t>
         </is>
       </c>
       <c r="Q93" t="n">
         <v>0</v>
       </c>
       <c r="R93" t="n">
-        <v>52160376</v>
+        <v>14686005</v>
       </c>
     </row>
     <row r="94">
@@ -6088,11 +6085,11 @@
         <v>93</v>
       </c>
       <c r="I94" t="n">
-        <v>11511</v>
+        <v>11514</v>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>Obras de Contenção de encostas em Manhumirim, Lajinha, Ervália,Sabinópolis e Diogo de Vasconcelos - Intervenção em setores de risco alto e muito alto. No ambito do Programa PAC gestão de riscos e proposta a desastres.</t>
+          <t>Obras de Contenção de encostas em Ouro Preto - Intervenção em setores de risco alto e muito alto, no ambito do programa PAC gestão de riscos e resposta a desastres.</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
@@ -6107,19 +6104,19 @@
       </c>
       <c r="O94" t="inlineStr">
         <is>
-          <t>Estadual</t>
+          <t>Região Intermediária de Belo Horizonte</t>
         </is>
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
+          <t>OURO PRETO</t>
         </is>
       </c>
       <c r="Q94" t="n">
         <v>0</v>
       </c>
       <c r="R94" t="n">
-        <v>20521500</v>
+        <v>52160376</v>
       </c>
     </row>
     <row r="95">
@@ -6148,11 +6145,11 @@
         <v>94</v>
       </c>
       <c r="I95" t="n">
-        <v>11520</v>
+        <v>11511</v>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>Obras de contenção de encostas em Santa Luzia - Intervenção em setores de risco alto e muito alto, no âmbito do Programa PAC Gestão de Riscos e Resposta a Desastres.</t>
+          <t>Obras de Contenção de encostas em Manhumirim, Lajinha, Ervália,Sabinópolis e Diogo de Vasconcelos - Intervenção em setores de risco alto e muito alto. No ambito do Programa PAC gestão de riscos e proposta a desastres.</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
@@ -6167,19 +6164,19 @@
       </c>
       <c r="O95" t="inlineStr">
         <is>
-          <t>Região Intermediária de Belo Horizonte</t>
+          <t>Estadual</t>
         </is>
       </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t>SANTA LUZIA</t>
+          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
         </is>
       </c>
       <c r="Q95" t="n">
         <v>0</v>
       </c>
       <c r="R95" t="n">
-        <v>6952445</v>
+        <v>20521500</v>
       </c>
     </row>
     <row r="96">
@@ -6208,11 +6205,11 @@
         <v>95</v>
       </c>
       <c r="I96" t="n">
-        <v>11513</v>
+        <v>11520</v>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>Obras de Contenção de encostas em Ewbank da Câmara, Matias Barbosa e Visconde do Rio Branco - Intervenção em setores de risco alto e muito alto, no ambito do programa PAC gestão de riscos e proposta a desastre.</t>
+          <t>Obras de contenção de encostas em Santa Luzia - Intervenção em setores de risco alto e muito alto, no âmbito do Programa PAC Gestão de Riscos e Resposta a Desastres.</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
@@ -6227,19 +6224,19 @@
       </c>
       <c r="O96" t="inlineStr">
         <is>
-          <t>Estadual</t>
+          <t>Região Intermediária de Belo Horizonte</t>
         </is>
       </c>
       <c r="P96" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
+          <t>SANTA LUZIA</t>
         </is>
       </c>
       <c r="Q96" t="n">
         <v>0</v>
       </c>
       <c r="R96" t="n">
-        <v>12959175</v>
+        <v>6952445</v>
       </c>
     </row>
     <row r="97">
@@ -6268,11 +6265,11 @@
         <v>96</v>
       </c>
       <c r="I97" t="n">
-        <v>11977</v>
+        <v>11513</v>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>Execução de Obras de Contenção de Encostas em Cataguases/MG - Intervenção em setores de risco alto e muito alto, no âmbito do programa PAC Gestão de Riscos e Resposta a Desastres.</t>
+          <t>Obras de Contenção de encostas em Ewbank da Câmara, Matias Barbosa e Visconde do Rio Branco - Intervenção em setores de risco alto e muito alto, no ambito do programa PAC gestão de riscos e proposta a desastre.</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
@@ -6287,19 +6284,19 @@
       </c>
       <c r="O97" t="inlineStr">
         <is>
-          <t>Região Intermediária de Juíz de Fora</t>
+          <t>Estadual</t>
         </is>
       </c>
       <c r="P97" t="inlineStr">
         <is>
-          <t>CATAGUASES</t>
+          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
         </is>
       </c>
       <c r="Q97" t="n">
         <v>0</v>
       </c>
       <c r="R97" t="n">
-        <v>38244490</v>
+        <v>12959175</v>
       </c>
     </row>
     <row r="98">
@@ -6328,11 +6325,11 @@
         <v>97</v>
       </c>
       <c r="I98" t="n">
-        <v>11162</v>
+        <v>11977</v>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>OBRAS DE ESTABILIZAÇÃO E CONTENÇÃO DE ENCOSTAS E DESLIZAMENTOS EM ÁREAS URBANAS</t>
+          <t>Execução de Obras de Contenção de Encostas em Cataguases/MG - Intervenção em setores de risco alto e muito alto, no âmbito do programa PAC Gestão de Riscos e Resposta a Desastres.</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
@@ -6347,19 +6344,19 @@
       </c>
       <c r="O98" t="inlineStr">
         <is>
-          <t>Estadual</t>
+          <t>Região Intermediária de Juíz de Fora</t>
         </is>
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
+          <t>CATAGUASES</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>9858067</v>
+        <v>0</v>
       </c>
       <c r="R98" t="n">
-        <v>0</v>
+        <v>38244490</v>
       </c>
     </row>
     <row r="99">
@@ -6376,7 +6373,7 @@
         <v>139</v>
       </c>
       <c r="E99" t="n">
-        <v>1039</v>
+        <v>1036</v>
       </c>
       <c r="F99" t="n">
         <v>1</v>
@@ -6388,11 +6385,11 @@
         <v>98</v>
       </c>
       <c r="I99" t="n">
-        <v>12699</v>
+        <v>11162</v>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>SERVIÇOS TÉCNICOS ESPECIALIZADOS PARA A CONCLUSÃO DA IMPLEMENTAÇÃO DO PTTS  PROJETO DE TRABALHO TÉCNICO SOCIAL- PROGRAMA DE REQUALIFICAÇÃO URBANA E AMBIENTAL E CONTROLE DE CHEIAS DO CÓRREGO FERRUGEM</t>
+          <t>OBRAS DE ESTABILIZAÇÃO E CONTENÇÃO DE ENCOSTAS E DESLIZAMENTOS EM ÁREAS URBANAS</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
@@ -6407,16 +6404,16 @@
       </c>
       <c r="O99" t="inlineStr">
         <is>
-          <t>Região Intermediária de Belo Horizonte</t>
+          <t>Estadual</t>
         </is>
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>CONTAGEM</t>
+          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>299895</v>
+        <v>9858067</v>
       </c>
       <c r="R99" t="n">
         <v>0</v>
@@ -6448,11 +6445,11 @@
         <v>99</v>
       </c>
       <c r="I100" t="n">
-        <v>11536</v>
+        <v>12699</v>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>Construção de 192 unidades habitacionais referente a 2ª etapa da Requalificação urbana e ambiental do Córrego Ferrugem</t>
+          <t>SERVIÇOS TÉCNICOS ESPECIALIZADOS PARA A CONCLUSÃO DA IMPLEMENTAÇÃO DO PTTS  PROJETO DE TRABALHO TÉCNICO SOCIAL- PROGRAMA DE REQUALIFICAÇÃO URBANA E AMBIENTAL E CONTROLE DE CHEIAS DO CÓRREGO FERRUGEM</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
@@ -6476,7 +6473,7 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>4565604</v>
+        <v>299895</v>
       </c>
       <c r="R100" t="n">
         <v>0</v>
@@ -6496,7 +6493,7 @@
         <v>139</v>
       </c>
       <c r="E101" t="n">
-        <v>1041</v>
+        <v>1039</v>
       </c>
       <c r="F101" t="n">
         <v>1</v>
@@ -6508,11 +6505,11 @@
         <v>100</v>
       </c>
       <c r="I101" t="n">
-        <v>11855</v>
+        <v>11536</v>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>REMANESCENTE DAS OBRAS DE INFRAESTRUTURA PARA A CONCLUSAO DAS BACIAS DO CONTROLE DE CHEIAS DO CORREGO RIACHO DAS PEDRAS.</t>
+          <t>Construção de 192 unidades habitacionais referente a 2ª etapa da Requalificação urbana e ambiental do Córrego Ferrugem</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
@@ -6536,10 +6533,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>6286532</v>
+        <v>4565604</v>
       </c>
       <c r="R101" t="n">
-        <v>2728583</v>
+        <v>0</v>
       </c>
     </row>
     <row r="102">
@@ -6568,11 +6565,11 @@
         <v>101</v>
       </c>
       <c r="I102" t="n">
-        <v>11973</v>
+        <v>11855</v>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>execução do Plano de Trabalho Técnico-Social - PTTS, que é uma exigência do contrato de financiamento PAC RIACHO</t>
+          <t>REMANESCENTE DAS OBRAS DE INFRAESTRUTURA PARA A CONCLUSAO DAS BACIAS DO CONTROLE DE CHEIAS DO CORREGO RIACHO DAS PEDRAS.</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
@@ -6596,27 +6593,27 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>193263</v>
+        <v>6286532</v>
       </c>
       <c r="R102" t="n">
-        <v>0</v>
+        <v>2728583</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>1371</v>
+        <v>1301</v>
       </c>
       <c r="B103" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C103" t="n">
-        <v>511</v>
+        <v>451</v>
       </c>
       <c r="D103" t="n">
-        <v>101</v>
+        <v>139</v>
       </c>
       <c r="E103" t="n">
-        <v>4118</v>
+        <v>1041</v>
       </c>
       <c r="F103" t="n">
         <v>1</v>
@@ -6627,14 +6624,17 @@
       <c r="H103" t="n">
         <v>102</v>
       </c>
+      <c r="I103" t="n">
+        <v>11973</v>
+      </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>Programa Água Doce - RIMC</t>
+          <t>execução do Plano de Trabalho Técnico-Social - PTTS, que é uma exigência do contrato de financiamento PAC RIACHO</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>INICIANDO</t>
+          <t>EXECUÇÃO</t>
         </is>
       </c>
       <c r="N103" t="inlineStr">
@@ -6644,19 +6644,19 @@
       </c>
       <c r="O103" t="inlineStr">
         <is>
-          <t>Região Intermediária de Montes Claros</t>
+          <t>Região Intermediária de Belo Horizonte</t>
         </is>
       </c>
       <c r="P103" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE MONTES CLAROS</t>
+          <t>CONTAGEM</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>0</v>
+        <v>193263</v>
       </c>
       <c r="R103" t="n">
-        <v>4547000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="104">
@@ -6686,7 +6686,7 @@
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>Programa Água Doce - RITO</t>
+          <t>Programa Água Doce - RIMC</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
@@ -6701,12 +6701,12 @@
       </c>
       <c r="O104" t="inlineStr">
         <is>
-          <t>Região Intermediária de Teófilo Otoni</t>
+          <t>Região Intermediária de Montes Claros</t>
         </is>
       </c>
       <c r="P104" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE TEÓFILO OTONI</t>
+          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE MONTES CLAROS</t>
         </is>
       </c>
       <c r="Q104" t="n">
@@ -6718,37 +6718,37 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>1451</v>
+        <v>1371</v>
       </c>
       <c r="B105" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="C105" t="n">
-        <v>421</v>
+        <v>511</v>
       </c>
       <c r="D105" t="n">
-        <v>130</v>
+        <v>101</v>
       </c>
       <c r="E105" t="n">
-        <v>1048</v>
+        <v>4118</v>
       </c>
       <c r="F105" t="n">
         <v>1</v>
       </c>
       <c r="G105" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H105" t="n">
         <v>104</v>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>Construção de uma unidade prisional de segurança média com aproximadamente 800 (oitocentas) vagas.</t>
+          <t>Programa Água Doce - RITO</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>PARALISADO</t>
+          <t>INICIANDO</t>
         </is>
       </c>
       <c r="N105" t="inlineStr">
@@ -6758,19 +6758,19 @@
       </c>
       <c r="O105" t="inlineStr">
         <is>
-          <t>Estadual</t>
+          <t>Região Intermediária de Teófilo Otoni</t>
         </is>
       </c>
       <c r="P105" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
+          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE TEÓFILO OTONI</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>904245</v>
+        <v>0</v>
       </c>
       <c r="R105" t="n">
-        <v>44308050</v>
+        <v>4547000</v>
       </c>
     </row>
     <row r="106">
@@ -6781,13 +6781,13 @@
         <v>6</v>
       </c>
       <c r="C106" t="n">
-        <v>243</v>
+        <v>421</v>
       </c>
       <c r="D106" t="n">
-        <v>146</v>
+        <v>130</v>
       </c>
       <c r="E106" t="n">
-        <v>4441</v>
+        <v>1048</v>
       </c>
       <c r="F106" t="n">
         <v>1</v>
@@ -6800,7 +6800,7 @@
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>Construção e implementação de modelos alternativos de prestação da Medida Socioeducativa de Privação de Liberdade no Estado de Minas Gerais.</t>
+          <t>Construção de uma unidade prisional de segurança média com aproximadamente 800 (oitocentas) vagas.</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
@@ -6815,19 +6815,19 @@
       </c>
       <c r="O106" t="inlineStr">
         <is>
-          <t>Região Intermediária de Belo Horizonte</t>
+          <t>Estadual</t>
         </is>
       </c>
       <c r="P106" t="inlineStr">
         <is>
-          <t>BELO HORIZONTE</t>
+          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>6999284</v>
+        <v>904245</v>
       </c>
       <c r="R106" t="n">
-        <v>0</v>
+        <v>44308050</v>
       </c>
     </row>
     <row r="107">
@@ -6877,11 +6877,11 @@
       </c>
       <c r="P107" t="inlineStr">
         <is>
-          <t>BETIM</t>
+          <t>BELO HORIZONTE</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>651694</v>
+        <v>6999284</v>
       </c>
       <c r="R107" t="n">
         <v>0</v>
@@ -6929,12 +6929,12 @@
       </c>
       <c r="O108" t="inlineStr">
         <is>
-          <t>Região Intermediária de Varginha</t>
+          <t>Região Intermediária de Belo Horizonte</t>
         </is>
       </c>
       <c r="P108" t="inlineStr">
         <is>
-          <t>ALFENAS</t>
+          <t>BETIM</t>
         </is>
       </c>
       <c r="Q108" t="n">
@@ -6986,16 +6986,16 @@
       </c>
       <c r="O109" t="inlineStr">
         <is>
-          <t>Região Intermediária de Belo Horizonte</t>
+          <t>Região Intermediária de Varginha</t>
         </is>
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>CONTAGEM</t>
+          <t>ALFENAS</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>1472757</v>
+        <v>651694</v>
       </c>
       <c r="R109" t="n">
         <v>0</v>
@@ -7043,16 +7043,16 @@
       </c>
       <c r="O110" t="inlineStr">
         <is>
-          <t>Região Intermediária de Uberaba</t>
+          <t>Região Intermediária de Belo Horizonte</t>
         </is>
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>ARAXÁ</t>
+          <t>CONTAGEM</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>651694</v>
+        <v>1472757</v>
       </c>
       <c r="R110" t="n">
         <v>0</v>
@@ -7100,16 +7100,16 @@
       </c>
       <c r="O111" t="inlineStr">
         <is>
-          <t>Estadual</t>
+          <t>Região Intermediária de Uberaba</t>
         </is>
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
+          <t>ARAXÁ</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>18572878</v>
+        <v>651694</v>
       </c>
       <c r="R111" t="n">
         <v>0</v>
@@ -7117,37 +7117,37 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>1501</v>
+        <v>1451</v>
       </c>
       <c r="B112" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C112" t="n">
-        <v>122</v>
+        <v>243</v>
       </c>
       <c r="D112" t="n">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E112" t="n">
-        <v>4476</v>
+        <v>4441</v>
       </c>
       <c r="F112" t="n">
         <v>1</v>
       </c>
       <c r="G112" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H112" t="n">
         <v>111</v>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>REDIMENSIONAMENTO DE REDE ELÉTRICA (NRPMSO`S) - Garantir a segurança elétrica para implementação de novos equipamentos</t>
+          <t>Construção e implementação de modelos alternativos de prestação da Medida Socioeducativa de Privação de Liberdade no Estado de Minas Gerais.</t>
         </is>
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>INICIANDO</t>
+          <t>PARALISADO</t>
         </is>
       </c>
       <c r="N112" t="inlineStr">
@@ -7157,16 +7157,16 @@
       </c>
       <c r="O112" t="inlineStr">
         <is>
-          <t>Região Intermediária de Belo Horizonte</t>
+          <t>Estadual</t>
         </is>
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>BELO HORIZONTE</t>
+          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>270000</v>
+        <v>18572878</v>
       </c>
       <c r="R112" t="n">
         <v>0</v>
@@ -7183,10 +7183,10 @@
         <v>122</v>
       </c>
       <c r="D113" t="n">
-        <v>156</v>
+        <v>147</v>
       </c>
       <c r="E113" t="n">
-        <v>4465</v>
+        <v>4476</v>
       </c>
       <c r="F113" t="n">
         <v>1</v>
@@ -7199,7 +7199,7 @@
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>Construção de um abrigo de Resíduos Sólidos e guaritas de segurança externa na CAMG</t>
+          <t>REDIMENSIONAMENTO DE REDE ELÉTRICA (NRPMSO`S) - Garantir a segurança elétrica para implementação de novos equipamentos</t>
         </is>
       </c>
       <c r="K113" t="inlineStr">
@@ -7223,7 +7223,7 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>1100000</v>
+        <v>270000</v>
       </c>
       <c r="R113" t="n">
         <v>0</v>
@@ -7256,7 +7256,7 @@
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t xml:space="preserve">Execução do projeto de reutilização da água da purga </t>
+          <t>Construção de um abrigo de Resíduos Sólidos e guaritas de segurança externa na CAMG</t>
         </is>
       </c>
       <c r="K114" t="inlineStr">
@@ -7280,7 +7280,7 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>624000</v>
+        <v>1100000</v>
       </c>
       <c r="R114" t="n">
         <v>0</v>
@@ -7313,7 +7313,7 @@
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>Projeto de modernização da alimentação elétrica emergencial dos elevadores</t>
+          <t xml:space="preserve">Execução do projeto de reutilização da água da purga </t>
         </is>
       </c>
       <c r="K115" t="inlineStr">
@@ -7337,7 +7337,7 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>210000</v>
+        <v>624000</v>
       </c>
       <c r="R115" t="n">
         <v>0</v>
@@ -7370,7 +7370,7 @@
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>Programa de monitoramento e responsabilidade técnica das barragens da Cidade Administrativa</t>
+          <t>Projeto de modernização da alimentação elétrica emergencial dos elevadores</t>
         </is>
       </c>
       <c r="K116" t="inlineStr">
@@ -7394,7 +7394,7 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>150000</v>
+        <v>210000</v>
       </c>
       <c r="R116" t="n">
         <v>0</v>
@@ -7427,7 +7427,7 @@
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>Impermeabilização das coberturas do prédio Alterosa e reforço estrutural do estacionamento do Alterosas</t>
+          <t>Programa de monitoramento e responsabilidade técnica das barragens da Cidade Administrativa</t>
         </is>
       </c>
       <c r="K117" t="inlineStr">
@@ -7451,7 +7451,7 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>3918408</v>
+        <v>150000</v>
       </c>
       <c r="R117" t="n">
         <v>0</v>
@@ -7468,10 +7468,10 @@
         <v>122</v>
       </c>
       <c r="D118" t="n">
-        <v>705</v>
+        <v>156</v>
       </c>
       <c r="E118" t="n">
-        <v>2500</v>
+        <v>4465</v>
       </c>
       <c r="F118" t="n">
         <v>1</v>
@@ -7484,7 +7484,7 @@
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>Projeto AVCB para o antigo prédio do IOF na av. Augusto de Lima</t>
+          <t>Impermeabilização das coberturas do prédio Alterosa e reforço estrutural do estacionamento do Alterosas</t>
         </is>
       </c>
       <c r="K118" t="inlineStr">
@@ -7492,17 +7492,9 @@
           <t>INICIANDO</t>
         </is>
       </c>
-      <c r="L118" t="inlineStr">
-        <is>
-          <t>UNIDADE</t>
-        </is>
-      </c>
-      <c r="M118" t="n">
-        <v>1</v>
-      </c>
       <c r="N118" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="O118" t="inlineStr">
@@ -7516,7 +7508,7 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>282000</v>
+        <v>3918408</v>
       </c>
       <c r="R118" t="n">
         <v>0</v>
@@ -7524,19 +7516,19 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>1511</v>
+        <v>1501</v>
       </c>
       <c r="B119" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C119" t="n">
-        <v>181</v>
+        <v>122</v>
       </c>
       <c r="D119" t="n">
-        <v>32</v>
+        <v>705</v>
       </c>
       <c r="E119" t="n">
-        <v>1006</v>
+        <v>2500</v>
       </c>
       <c r="F119" t="n">
         <v>1</v>
@@ -7549,7 +7541,7 @@
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t xml:space="preserve">1ª Fase da Execução da Obra de Reformas e Adaptações da Antiga Cadeia Pública de Teofilo Otoni onde será instalada a Nova Delegacia Especializada no Atendimento a Mulher da DRPC de Teofilo Otoni. </t>
+          <t>Projeto AVCB para o antigo prédio do IOF na av. Augusto de Lima</t>
         </is>
       </c>
       <c r="K119" t="inlineStr">
@@ -7557,26 +7549,34 @@
           <t>INICIANDO</t>
         </is>
       </c>
+      <c r="L119" t="inlineStr">
+        <is>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="M119" t="n">
+        <v>1</v>
+      </c>
       <c r="N119" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="O119" t="inlineStr">
         <is>
-          <t>Estadual</t>
+          <t>Região Intermediária de Belo Horizonte</t>
         </is>
       </c>
       <c r="P119" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
+          <t>BELO HORIZONTE</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>0</v>
+        <v>282000</v>
       </c>
       <c r="R119" t="n">
-        <v>1000000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="120">
@@ -7593,7 +7593,7 @@
         <v>32</v>
       </c>
       <c r="E120" t="n">
-        <v>4063</v>
+        <v>1006</v>
       </c>
       <c r="F120" t="n">
         <v>1</v>
@@ -7606,7 +7606,7 @@
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>Construção do Complexo que irá abrigar o Núcleo Integrado de Perícias</t>
+          <t xml:space="preserve">1ª Fase da Execução da Obra de Reformas e Adaptações da Antiga Cadeia Pública de Teofilo Otoni onde será instalada a Nova Delegacia Especializada no Atendimento a Mulher da DRPC de Teofilo Otoni. </t>
         </is>
       </c>
       <c r="K120" t="inlineStr">
@@ -7621,36 +7621,36 @@
       </c>
       <c r="O120" t="inlineStr">
         <is>
-          <t>Região Intermediária de Belo Horizonte</t>
+          <t>Estadual</t>
         </is>
       </c>
       <c r="P120" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE BELO HORIZONTE</t>
+          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="R120" t="n">
-        <v>19850000</v>
+        <v>1000000</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>1541</v>
+        <v>1511</v>
       </c>
       <c r="B121" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C121" t="n">
-        <v>122</v>
+        <v>181</v>
       </c>
       <c r="D121" t="n">
-        <v>705</v>
+        <v>32</v>
       </c>
       <c r="E121" t="n">
-        <v>2500</v>
+        <v>4063</v>
       </c>
       <c r="F121" t="n">
         <v>1</v>
@@ -7663,12 +7663,12 @@
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>REFORMA DA ESCOLA DE SAÚDE PÚBLICA DO MUNICÍPIO DE BELO HORIZONTE</t>
+          <t>Construção do Complexo que irá abrigar o Núcleo Integrado de Perícias</t>
         </is>
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>EXECUÇÃO</t>
+          <t>INICIANDO</t>
         </is>
       </c>
       <c r="N121" t="inlineStr">
@@ -7683,31 +7683,31 @@
       </c>
       <c r="P121" t="inlineStr">
         <is>
-          <t>BELO HORIZONTE</t>
+          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE BELO HORIZONTE</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>2896100</v>
+        <v>150000</v>
       </c>
       <c r="R121" t="n">
-        <v>0</v>
+        <v>19850000</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>2011</v>
+        <v>1541</v>
       </c>
       <c r="B122" t="n">
         <v>10</v>
       </c>
       <c r="C122" t="n">
-        <v>302</v>
+        <v>122</v>
       </c>
       <c r="D122" t="n">
-        <v>88</v>
+        <v>705</v>
       </c>
       <c r="E122" t="n">
-        <v>4231</v>
+        <v>2500</v>
       </c>
       <c r="F122" t="n">
         <v>1</v>
@@ -7718,17 +7718,14 @@
       <c r="H122" t="n">
         <v>121</v>
       </c>
-      <c r="I122" t="n">
-        <v>12871</v>
-      </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t xml:space="preserve">EXECUCAO DE OBRAS POR CONTRATO DE BENS PATRIMONIAVEIS adequação do HGIP para obtenção do AVCB                       </t>
+          <t>REFORMA DA ESCOLA DE SAÚDE PÚBLICA DO MUNICÍPIO DE BELO HORIZONTE</t>
         </is>
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t>INICIANDO</t>
+          <t>EXECUÇÃO</t>
         </is>
       </c>
       <c r="N122" t="inlineStr">
@@ -7747,10 +7744,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>0</v>
+        <v>2896100</v>
       </c>
       <c r="R122" t="n">
-        <v>2000000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="123">
@@ -7779,11 +7776,11 @@
         <v>122</v>
       </c>
       <c r="I123" t="n">
-        <v>9999</v>
+        <v>12871</v>
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t xml:space="preserve">Reforma da Endoscopia - HGIP </t>
+          <t xml:space="preserve">EXECUCAO DE OBRAS POR CONTRATO DE BENS PATRIMONIAVEIS adequação do HGIP para obtenção do AVCB                       </t>
         </is>
       </c>
       <c r="K123" t="inlineStr">
@@ -7810,7 +7807,7 @@
         <v>0</v>
       </c>
       <c r="R123" t="n">
-        <v>1600000</v>
+        <v>2000000</v>
       </c>
     </row>
     <row r="124">
@@ -7821,13 +7818,13 @@
         <v>10</v>
       </c>
       <c r="C124" t="n">
-        <v>122</v>
+        <v>302</v>
       </c>
       <c r="D124" t="n">
-        <v>705</v>
+        <v>88</v>
       </c>
       <c r="E124" t="n">
-        <v>2500</v>
+        <v>4231</v>
       </c>
       <c r="F124" t="n">
         <v>1</v>
@@ -7839,11 +7836,11 @@
         <v>123</v>
       </c>
       <c r="I124" t="n">
-        <v>12690</v>
+        <v>9999</v>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>Apoio à GELENG, no atendimento às demandas de serviços de reforma e manutenção nas unidades.</t>
+          <t xml:space="preserve">Reforma da Endoscopia - HGIP </t>
         </is>
       </c>
       <c r="K124" t="inlineStr">
@@ -7870,24 +7867,24 @@
         <v>0</v>
       </c>
       <c r="R124" t="n">
-        <v>2200000</v>
+        <v>1600000</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>2101</v>
+        <v>2011</v>
       </c>
       <c r="B125" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="C125" t="n">
-        <v>541</v>
+        <v>122</v>
       </c>
       <c r="D125" t="n">
-        <v>31</v>
+        <v>705</v>
       </c>
       <c r="E125" t="n">
-        <v>4058</v>
+        <v>2500</v>
       </c>
       <c r="F125" t="n">
         <v>1</v>
@@ -7898,9 +7895,12 @@
       <c r="H125" t="n">
         <v>124</v>
       </c>
+      <c r="I125" t="n">
+        <v>12690</v>
+      </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>Construção do Cetras de Governador Valadares</t>
+          <t>Apoio à GELENG, no atendimento às demandas de serviços de reforma e manutenção nas unidades.</t>
         </is>
       </c>
       <c r="K125" t="inlineStr">
@@ -7908,34 +7908,26 @@
           <t>INICIANDO</t>
         </is>
       </c>
-      <c r="L125" t="inlineStr">
-        <is>
-          <t>UNIDADE</t>
-        </is>
-      </c>
-      <c r="M125" t="n">
-        <v>1</v>
-      </c>
       <c r="N125" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="O125" t="inlineStr">
         <is>
-          <t>Estadual</t>
+          <t>Região Intermediária de Belo Horizonte</t>
         </is>
       </c>
       <c r="P125" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
+          <t>BELO HORIZONTE</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>350000</v>
+        <v>0</v>
       </c>
       <c r="R125" t="n">
-        <v>0</v>
+        <v>2200000</v>
       </c>
     </row>
     <row r="126">
@@ -7952,7 +7944,7 @@
         <v>31</v>
       </c>
       <c r="E126" t="n">
-        <v>4059</v>
+        <v>4058</v>
       </c>
       <c r="F126" t="n">
         <v>1</v>
@@ -7965,7 +7957,7 @@
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>APA Parque Cataguás</t>
+          <t>Construção do Cetras de Governador Valadares</t>
         </is>
       </c>
       <c r="K126" t="inlineStr">
@@ -7997,7 +7989,7 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>1000000</v>
+        <v>350000</v>
       </c>
       <c r="R126" t="n">
         <v>0</v>
@@ -8005,19 +7997,19 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>2151</v>
+        <v>2101</v>
       </c>
       <c r="B127" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="C127" t="n">
-        <v>572</v>
+        <v>541</v>
       </c>
       <c r="D127" t="n">
-        <v>75</v>
+        <v>31</v>
       </c>
       <c r="E127" t="n">
-        <v>1023</v>
+        <v>4059</v>
       </c>
       <c r="F127" t="n">
         <v>1</v>
@@ -8030,7 +8022,7 @@
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA PARA ELABORAÇÃO DE ESTUDOS TÉCNICOS, LEVANTAMENTOS TOPOGRÁFICOS, SONDAGENS, ESTUDOS AMBIENTAIS, PROJETOS DE ARQUITETURA E ENGENHARIA, ORÇAMENTOS, MEMORIAIS DESCRITIVOS E AFINS</t>
+          <t>APA Parque Cataguás</t>
         </is>
       </c>
       <c r="K127" t="inlineStr">
@@ -8038,23 +8030,31 @@
           <t>INICIANDO</t>
         </is>
       </c>
+      <c r="L127" t="inlineStr">
+        <is>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="M127" t="n">
+        <v>1</v>
+      </c>
       <c r="N127" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="O127" t="inlineStr">
         <is>
-          <t>Região Intermediária de Belo Horizonte</t>
+          <t>Estadual</t>
         </is>
       </c>
       <c r="P127" t="inlineStr">
         <is>
-          <t>IBIRITÉ</t>
+          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>200000</v>
+        <v>1000000</v>
       </c>
       <c r="R127" t="n">
         <v>0</v>
@@ -8068,13 +8068,13 @@
         <v>12</v>
       </c>
       <c r="C128" t="n">
-        <v>122</v>
+        <v>572</v>
       </c>
       <c r="D128" t="n">
-        <v>705</v>
+        <v>75</v>
       </c>
       <c r="E128" t="n">
-        <v>2500</v>
+        <v>1023</v>
       </c>
       <c r="F128" t="n">
         <v>1</v>
@@ -8087,7 +8087,7 @@
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DO CONSÓRCIO PGM / SINAURB CIDERSU (PGM CONSTRUÇÕES E EMPREENDIMENTOS LTDA E SINAURB SERVIÇOS E EMPREENDIMENTOS LTDA) PRESTAÇÃO DE SERVIÇOS COMUNS E CONTÍNUOS DE ENGENHARIA, SOB DEMANDA, DESTINADOS À MANUTENÇÃO PREDIAL, CONSERVAÇÃO E EXEC</t>
+          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA PARA ELABORAÇÃO DE ESTUDOS TÉCNICOS, LEVANTAMENTOS TOPOGRÁFICOS, SONDAGENS, ESTUDOS AMBIENTAIS, PROJETOS DE ARQUITETURA E ENGENHARIA, ORÇAMENTOS, MEMORIAIS DESCRITIVOS E AFINS</t>
         </is>
       </c>
       <c r="K128" t="inlineStr">
@@ -8111,7 +8111,7 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>1500000</v>
+        <v>200000</v>
       </c>
       <c r="R128" t="n">
         <v>0</v>
@@ -8119,19 +8119,19 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>2161</v>
+        <v>2151</v>
       </c>
       <c r="B129" t="n">
         <v>12</v>
       </c>
       <c r="C129" t="n">
-        <v>242</v>
+        <v>122</v>
       </c>
       <c r="D129" t="n">
-        <v>5</v>
+        <v>705</v>
       </c>
       <c r="E129" t="n">
-        <v>1030</v>
+        <v>2500</v>
       </c>
       <c r="F129" t="n">
         <v>1</v>
@@ -8144,12 +8144,12 @@
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>Projeto para melhoria de acessibilidade nas unidades da FUCAM</t>
+          <t>CONTRATAÇÃO DO CONSÓRCIO PGM / SINAURB CIDERSU (PGM CONSTRUÇÕES E EMPREENDIMENTOS LTDA E SINAURB SERVIÇOS E EMPREENDIMENTOS LTDA) PRESTAÇÃO DE SERVIÇOS COMUNS E CONTÍNUOS DE ENGENHARIA, SOB DEMANDA, DESTINADOS À MANUTENÇÃO PREDIAL, CONSERVAÇÃO E EXEC</t>
         </is>
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t>PARALISADO</t>
+          <t>INICIANDO</t>
         </is>
       </c>
       <c r="N129" t="inlineStr">
@@ -8159,16 +8159,16 @@
       </c>
       <c r="O129" t="inlineStr">
         <is>
-          <t>Região Intermediária de Montes Claros</t>
+          <t>Região Intermediária de Belo Horizonte</t>
         </is>
       </c>
       <c r="P129" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE MONTES CLAROS</t>
+          <t>IBIRITÉ</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>14000</v>
+        <v>1500000</v>
       </c>
       <c r="R129" t="n">
         <v>0</v>
@@ -8216,16 +8216,16 @@
       </c>
       <c r="O130" t="inlineStr">
         <is>
-          <t>Região Intermediária de Patos de Minas</t>
+          <t>Região Intermediária de Montes Claros</t>
         </is>
       </c>
       <c r="P130" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE PATOS DE MINAS</t>
+          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE MONTES CLAROS</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>3000</v>
+        <v>14000</v>
       </c>
       <c r="R130" t="n">
         <v>0</v>
@@ -8273,12 +8273,12 @@
       </c>
       <c r="O131" t="inlineStr">
         <is>
-          <t>Região Intermediária de Belo Horizonte</t>
+          <t>Região Intermediária de Patos de Minas</t>
         </is>
       </c>
       <c r="P131" t="inlineStr">
         <is>
-          <t>ESMERALDAS</t>
+          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE PATOS DE MINAS</t>
         </is>
       </c>
       <c r="Q131" t="n">
@@ -8290,19 +8290,19 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>2261</v>
+        <v>2161</v>
       </c>
       <c r="B132" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C132" t="n">
-        <v>303</v>
+        <v>242</v>
       </c>
       <c r="D132" t="n">
-        <v>154</v>
+        <v>5</v>
       </c>
       <c r="E132" t="n">
-        <v>4460</v>
+        <v>1030</v>
       </c>
       <c r="F132" t="n">
         <v>1</v>
@@ -8313,17 +8313,14 @@
       <c r="H132" t="n">
         <v>131</v>
       </c>
-      <c r="I132" t="n">
-        <v>12502</v>
-      </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>Execução de Obras da nova sede da Divisão de Controle de Qualidade.</t>
+          <t>Projeto para melhoria de acessibilidade nas unidades da FUCAM</t>
         </is>
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t>INICIANDO</t>
+          <t>PARALISADO</t>
         </is>
       </c>
       <c r="N132" t="inlineStr">
@@ -8338,11 +8335,11 @@
       </c>
       <c r="P132" t="inlineStr">
         <is>
-          <t>BELO HORIZONTE</t>
+          <t>ESMERALDAS</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>500000</v>
+        <v>3000</v>
       </c>
       <c r="R132" t="n">
         <v>0</v>
@@ -8356,13 +8353,13 @@
         <v>10</v>
       </c>
       <c r="C133" t="n">
-        <v>122</v>
+        <v>303</v>
       </c>
       <c r="D133" t="n">
-        <v>705</v>
+        <v>154</v>
       </c>
       <c r="E133" t="n">
-        <v>2500</v>
+        <v>4460</v>
       </c>
       <c r="F133" t="n">
         <v>1</v>
@@ -8374,11 +8371,11 @@
         <v>132</v>
       </c>
       <c r="I133" t="n">
-        <v>12500</v>
+        <v>12502</v>
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t>Novo Prédio Administrativo da FUNED em Steel Frame (Unidade IV)</t>
+          <t>Execução de Obras da nova sede da Divisão de Controle de Qualidade.</t>
         </is>
       </c>
       <c r="K133" t="inlineStr">
@@ -8402,7 +8399,7 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>10535000</v>
+        <v>500000</v>
       </c>
       <c r="R133" t="n">
         <v>0</v>
@@ -8433,9 +8430,12 @@
       <c r="H134" t="n">
         <v>133</v>
       </c>
+      <c r="I134" t="n">
+        <v>12500</v>
+      </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t>Obras de adequação estrutural do refeitório para atendimento às exigências da Vigilância Sanitária Municipal.</t>
+          <t>Novo Prédio Administrativo da FUNED em Steel Frame (Unidade IV)</t>
         </is>
       </c>
       <c r="K134" t="inlineStr">
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>500000</v>
+        <v>10535000</v>
       </c>
       <c r="R134" t="n">
         <v>0</v>
@@ -8467,19 +8467,19 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>2301</v>
+        <v>2261</v>
       </c>
       <c r="B135" t="n">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="C135" t="n">
-        <v>782</v>
+        <v>122</v>
       </c>
       <c r="D135" t="n">
-        <v>81</v>
+        <v>705</v>
       </c>
       <c r="E135" t="n">
-        <v>4268</v>
+        <v>2500</v>
       </c>
       <c r="F135" t="n">
         <v>1</v>
@@ -8492,7 +8492,7 @@
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t>REABILITAÇÃO DA MG-010 (CONCEIÇÃO DO MATO DENTRO A SERRO)</t>
+          <t>Obras de adequação estrutural do refeitório para atendimento às exigências da Vigilância Sanitária Municipal.</t>
         </is>
       </c>
       <c r="K135" t="inlineStr">
@@ -8507,19 +8507,19 @@
       </c>
       <c r="O135" t="inlineStr">
         <is>
-          <t>Estadual</t>
+          <t>Região Intermediária de Belo Horizonte</t>
         </is>
       </c>
       <c r="P135" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
+          <t>BELO HORIZONTE</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>0</v>
+        <v>500000</v>
       </c>
       <c r="R135" t="n">
-        <v>5000000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="136">
@@ -8549,7 +8549,7 @@
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t>REABILITAÇÃO DA MG-129 (OURO PRETO A OURO BRANCO)</t>
+          <t>REABILITAÇÃO DA MG-010 (CONCEIÇÃO DO MATO DENTRO A SERRO)</t>
         </is>
       </c>
       <c r="K136" t="inlineStr">
@@ -8606,7 +8606,7 @@
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>RESTAURAÇÃO RODOVIA MG-010, TRECHO CONCEIÇÃO DO MATO DENTRO - SERRO (DISTRITO DE MATO GROSSO) E RECOMPOSIÇÃO DE TALUDE ERODIDO</t>
+          <t>REABILITAÇÃO DA MG-129 (OURO PRETO A OURO BRANCO)</t>
         </is>
       </c>
       <c r="K137" t="inlineStr">
@@ -8633,7 +8633,7 @@
         <v>0</v>
       </c>
       <c r="R137" t="n">
-        <v>10000000</v>
+        <v>5000000</v>
       </c>
     </row>
     <row r="138">
@@ -8663,7 +8663,7 @@
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t>ARCOS - CORUMBÁ - RODOVIA: MG-170 (ENTR BR-354 - AGRIMIG)</t>
+          <t>RESTAURAÇÃO RODOVIA MG-010, TRECHO CONCEIÇÃO DO MATO DENTRO - SERRO (DISTRITO DE MATO GROSSO) E RECOMPOSIÇÃO DE TALUDE ERODIDO</t>
         </is>
       </c>
       <c r="K138" t="inlineStr">
@@ -8687,10 +8687,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>9792000</v>
+        <v>0</v>
       </c>
       <c r="R138" t="n">
-        <v>0</v>
+        <v>10000000</v>
       </c>
     </row>
     <row r="139">
@@ -8720,7 +8720,7 @@
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t>MG-129 - OURO PRETO A OURO BRANCO</t>
+          <t>ARCOS - CORUMBÁ - RODOVIA: MG-170 (ENTR BR-354 - AGRIMIG)</t>
         </is>
       </c>
       <c r="K139" t="inlineStr">
@@ -8744,7 +8744,7 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>1000000</v>
+        <v>9792000</v>
       </c>
       <c r="R139" t="n">
         <v>0</v>
@@ -8777,7 +8777,7 @@
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t>RECUPERAÇÃO DE EROSÃO EM TALUDE DE CORTE NA RODOVIA MGC-354, KM 167,8, TRECHO: RIBEIRÃO DA MATA - AV MARABÁ (PATOS DE MINAS)</t>
+          <t>MG-129 - OURO PRETO A OURO BRANCO</t>
         </is>
       </c>
       <c r="K140" t="inlineStr">
@@ -8801,7 +8801,7 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>143000</v>
+        <v>1000000</v>
       </c>
       <c r="R140" t="n">
         <v>0</v>
@@ -8834,7 +8834,7 @@
       </c>
       <c r="J141" t="inlineStr">
         <is>
-          <t>RESTAURAÇÃO DA INTERSEÇÃO NA RODOVIA MGC-354, KM 150,9, TRECHO: TRAVESSIA URBANA DE PRESIDENTE OLEGÁRIO</t>
+          <t>RECUPERAÇÃO DE EROSÃO EM TALUDE DE CORTE NA RODOVIA MGC-354, KM 167,8, TRECHO: RIBEIRÃO DA MATA - AV MARABÁ (PATOS DE MINAS)</t>
         </is>
       </c>
       <c r="K141" t="inlineStr">
@@ -8858,7 +8858,7 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>5876140</v>
+        <v>143000</v>
       </c>
       <c r="R141" t="n">
         <v>0</v>
@@ -8891,7 +8891,7 @@
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>RESTAURAÇÃO DA INTERSEÇÃO NA RODOVIA MGC-354, KM 176,2, TRECHO: AV MARABÁ (PATOS DE MINAS) - ENTR BR 365</t>
+          <t>RESTAURAÇÃO DA INTERSEÇÃO NA RODOVIA MGC-354, KM 150,9, TRECHO: TRAVESSIA URBANA DE PRESIDENTE OLEGÁRIO</t>
         </is>
       </c>
       <c r="K142" t="inlineStr">
@@ -8915,7 +8915,7 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>1132500</v>
+        <v>5876140</v>
       </c>
       <c r="R142" t="n">
         <v>0</v>
@@ -8948,7 +8948,7 @@
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t>RESTAURAÇÃO E 3ª FAIXA, TRECHO ENTR. BR-354 (CAXAMBÚ) - ENTR. BR-381 (PALMELA DISTRITO DE CAMPANHA), NA MGC-267</t>
+          <t>RESTAURAÇÃO DA INTERSEÇÃO NA RODOVIA MGC-354, KM 176,2, TRECHO: AV MARABÁ (PATOS DE MINAS) - ENTR BR 365</t>
         </is>
       </c>
       <c r="K143" t="inlineStr">
@@ -8972,7 +8972,7 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>1000000</v>
+        <v>1132500</v>
       </c>
       <c r="R143" t="n">
         <v>0</v>
@@ -9005,7 +9005,7 @@
       </c>
       <c r="J144" t="inlineStr">
         <is>
-          <t>RESTAURAÇÃO E AUMENTO DE CAPACIDADE (3ª FAIXA) DO TRECHO SERRA DO SALITRE - SALITRE DE MINAS, NA MG-230</t>
+          <t>RESTAURAÇÃO E 3ª FAIXA, TRECHO ENTR. BR-354 (CAXAMBÚ) - ENTR. BR-381 (PALMELA DISTRITO DE CAMPANHA), NA MGC-267</t>
         </is>
       </c>
       <c r="K144" t="inlineStr">
@@ -9029,7 +9029,7 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>34710000</v>
+        <v>1000000</v>
       </c>
       <c r="R144" t="n">
         <v>0</v>
@@ -9062,7 +9062,7 @@
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t>RESTAURAÇÃO E AUMENTO DE CAPACIDADE DO TRECHO MG-344 (ENTR. P/ CÁSSIA) - DIVISA MG/SP, NA MG-444, EXT. 23,9 KM</t>
+          <t>RESTAURAÇÃO E AUMENTO DE CAPACIDADE (3ª FAIXA) DO TRECHO SERRA DO SALITRE - SALITRE DE MINAS, NA MG-230</t>
         </is>
       </c>
       <c r="K145" t="inlineStr">
@@ -9086,7 +9086,7 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>59000000</v>
+        <v>34710000</v>
       </c>
       <c r="R145" t="n">
         <v>0</v>
@@ -9119,7 +9119,7 @@
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t>RESTAURAÇÃO E AUMENTO DE CAPACIDADE DO TRECHO PARÁ DE MINAS - PAPAGAIOS (3ª FAIXA) - LOTE 1</t>
+          <t>RESTAURAÇÃO E AUMENTO DE CAPACIDADE DO TRECHO MG-344 (ENTR. P/ CÁSSIA) - DIVISA MG/SP, NA MG-444, EXT. 23,9 KM</t>
         </is>
       </c>
       <c r="K146" t="inlineStr">
@@ -9143,7 +9143,7 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>1000000</v>
+        <v>59000000</v>
       </c>
       <c r="R146" t="n">
         <v>0</v>
@@ -9176,7 +9176,7 @@
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t>RESTAURAÇÃO E AUMENTO DE CAPACIDADE DO TRECHO: UNAÍ A GARAPUAVA</t>
+          <t>RESTAURAÇÃO E AUMENTO DE CAPACIDADE DO TRECHO PARÁ DE MINAS - PAPAGAIOS (3ª FAIXA) - LOTE 1</t>
         </is>
       </c>
       <c r="K147" t="inlineStr">
@@ -9233,7 +9233,7 @@
       </c>
       <c r="J148" t="inlineStr">
         <is>
-          <t>RESTAURAÇÃO TIMÓTEO - ENTR. LMG-760 (CAVA GRANDE), NA MG-425</t>
+          <t>RESTAURAÇÃO E AUMENTO DE CAPACIDADE DO TRECHO: UNAÍ A GARAPUAVA</t>
         </is>
       </c>
       <c r="K148" t="inlineStr">
@@ -9257,7 +9257,7 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>200000</v>
+        <v>1000000</v>
       </c>
       <c r="R148" t="n">
         <v>0</v>
@@ -9290,7 +9290,7 @@
       </c>
       <c r="J149" t="inlineStr">
         <is>
-          <t>RESTAURAÇÃO TRECHO ENTR. LMG764 (P/ MATUTINA) - SÃO GOTARDO, NA MG- 235 - 3ª FAIXA</t>
+          <t>RESTAURAÇÃO TIMÓTEO - ENTR. LMG-760 (CAVA GRANDE), NA MG-425</t>
         </is>
       </c>
       <c r="K149" t="inlineStr">
@@ -9314,7 +9314,7 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>1000000</v>
+        <v>200000</v>
       </c>
       <c r="R149" t="n">
         <v>0</v>
@@ -9347,7 +9347,7 @@
       </c>
       <c r="J150" t="inlineStr">
         <is>
-          <t>RESTAURAÇÃO TRECHO ENTR. MGC-120 (B) (DONA EUZÉBIA) - ENTR. MGC-265, NA MG-285</t>
+          <t>RESTAURAÇÃO TRECHO ENTR. LMG764 (P/ MATUTINA) - SÃO GOTARDO, NA MG- 235 - 3ª FAIXA</t>
         </is>
       </c>
       <c r="K150" t="inlineStr">
@@ -9371,7 +9371,7 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>30980000</v>
+        <v>1000000</v>
       </c>
       <c r="R150" t="n">
         <v>0</v>
@@ -9404,7 +9404,7 @@
       </c>
       <c r="J151" t="inlineStr">
         <is>
-          <t>RESTAURAÇÃO TRECHO ENTR. MGC-265/MG-452 (P/ PAIVA) - ENTR. BR-040, NA MG-448</t>
+          <t>RESTAURAÇÃO TRECHO ENTR. MGC-120 (B) (DONA EUZÉBIA) - ENTR. MGC-265, NA MG-285</t>
         </is>
       </c>
       <c r="K151" t="inlineStr">
@@ -9428,7 +9428,7 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>25655000</v>
+        <v>30980000</v>
       </c>
       <c r="R151" t="n">
         <v>0</v>
@@ -9461,7 +9461,7 @@
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t>RESTAURAÇÃO TRECHO PIRAÚBA (ENTR. MG-285) - PAIVA (ENTR. MG-488/MG-455), NA MG-265 E 3ª FAIXA</t>
+          <t>RESTAURAÇÃO TRECHO ENTR. MGC-265/MG-452 (P/ PAIVA) - ENTR. BR-040, NA MG-448</t>
         </is>
       </c>
       <c r="K152" t="inlineStr">
@@ -9485,7 +9485,7 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>66560000</v>
+        <v>25655000</v>
       </c>
       <c r="R152" t="n">
         <v>0</v>
@@ -9518,7 +9518,7 @@
       </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t>RESTAURAÇÃO TRECHO SÃO GOTARDO - ENTR. BR-354 (P/ PATOS DE MINAS), NA MG-235</t>
+          <t>RESTAURAÇÃO TRECHO PIRAÚBA (ENTR. MG-285) - PAIVA (ENTR. MG-488/MG-455), NA MG-265 E 3ª FAIXA</t>
         </is>
       </c>
       <c r="K153" t="inlineStr">
@@ -9542,7 +9542,7 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>1000000</v>
+        <v>66560000</v>
       </c>
       <c r="R153" t="n">
         <v>0</v>
@@ -9575,7 +9575,7 @@
       </c>
       <c r="J154" t="inlineStr">
         <is>
-          <t>RESTAURAÇÃO TRÊS PONTAS - VARGINHA, NA MG-167</t>
+          <t>RESTAURAÇÃO TRECHO SÃO GOTARDO - ENTR. BR-354 (P/ PATOS DE MINAS), NA MG-235</t>
         </is>
       </c>
       <c r="K154" t="inlineStr">
@@ -9599,7 +9599,7 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>25464500</v>
+        <v>1000000</v>
       </c>
       <c r="R154" t="n">
         <v>0</v>
@@ -9619,7 +9619,7 @@
         <v>81</v>
       </c>
       <c r="E155" t="n">
-        <v>4272</v>
+        <v>4268</v>
       </c>
       <c r="F155" t="n">
         <v>1</v>
@@ -9632,7 +9632,7 @@
       </c>
       <c r="J155" t="inlineStr">
         <is>
-          <t>BDCC 3X3 CÓRREGO CAVALO, TRECHO ENTR. BR-040 - PORTO DIAMANTE</t>
+          <t>RESTAURAÇÃO TRÊS PONTAS - VARGINHA, NA MG-167</t>
         </is>
       </c>
       <c r="K155" t="inlineStr">
@@ -9656,7 +9656,7 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>100000</v>
+        <v>25464500</v>
       </c>
       <c r="R155" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
       </c>
       <c r="J156" t="inlineStr">
         <is>
-          <t>COMPLEMENTAÇÃO DA CONSTRUÇÃO DA PONTE SOBRE O RIO SÃO FRANCISCO, PINTÓPOLIS</t>
+          <t>BDCC 3X3 CÓRREGO CAVALO, TRECHO ENTR. BR-040 - PORTO DIAMANTE</t>
         </is>
       </c>
       <c r="K156" t="inlineStr">
@@ -9713,7 +9713,7 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>24000000</v>
+        <v>100000</v>
       </c>
       <c r="R156" t="n">
         <v>0</v>
@@ -9746,7 +9746,7 @@
       </c>
       <c r="J157" t="inlineStr">
         <is>
-          <t>ENCABEÇAMENTO E PONTE CÓRREGO SÃO BARTOLOMEU E ENCABEÇAMENTO CÓRREGO BARBADINHO, TRECHO CANABRAVA (JOÃO PINHEIRO) - ENTR. MG-181, NA LMG-698</t>
+          <t>COMPLEMENTAÇÃO DA CONSTRUÇÃO DA PONTE SOBRE O RIO SÃO FRANCISCO, PINTÓPOLIS</t>
         </is>
       </c>
       <c r="K157" t="inlineStr">
@@ -9770,7 +9770,7 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>252000</v>
+        <v>24000000</v>
       </c>
       <c r="R157" t="n">
         <v>0</v>
@@ -9803,7 +9803,7 @@
       </c>
       <c r="J158" t="inlineStr">
         <is>
-          <t>ENCABEÇAMENTO E PONTE SOBRE CÓRREGO AMENDOIM, NO TRECHO RIACHINHO - GUARAPUAVA (UNAÍ), NA LMG-638</t>
+          <t>ENCABEÇAMENTO E PONTE CÓRREGO SÃO BARTOLOMEU E ENCABEÇAMENTO CÓRREGO BARBADINHO, TRECHO CANABRAVA (JOÃO PINHEIRO) - ENTR. MG-181, NA LMG-698</t>
         </is>
       </c>
       <c r="K158" t="inlineStr">
@@ -9827,7 +9827,7 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>319200</v>
+        <v>252000</v>
       </c>
       <c r="R158" t="n">
         <v>0</v>
@@ -9860,7 +9860,7 @@
       </c>
       <c r="J159" t="inlineStr">
         <is>
-          <t>ENCABEÇAMENTO E PONTE SOBRE CÓRREGO BOI PRETO, NO TRECHO RIACHINHO - GUARAPUAVA (UNAÍ), NA LMG-638</t>
+          <t>ENCABEÇAMENTO E PONTE SOBRE CÓRREGO AMENDOIM, NO TRECHO RIACHINHO - GUARAPUAVA (UNAÍ), NA LMG-638</t>
         </is>
       </c>
       <c r="K159" t="inlineStr">
@@ -9884,7 +9884,7 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>495600</v>
+        <v>319200</v>
       </c>
       <c r="R159" t="n">
         <v>0</v>
@@ -9917,7 +9917,7 @@
       </c>
       <c r="J160" t="inlineStr">
         <is>
-          <t>ENCABEÇAMENTO E PONTE SOBRE O CÓRREGO DAS LAJES, TRECHO ENTR. MGC-479 (SERRA DAS ARARAS) - ENTR. MG-402, NA LMG-622</t>
+          <t>ENCABEÇAMENTO E PONTE SOBRE CÓRREGO BOI PRETO, NO TRECHO RIACHINHO - GUARAPUAVA (UNAÍ), NA LMG-638</t>
         </is>
       </c>
       <c r="K160" t="inlineStr">
@@ -9941,7 +9941,7 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>679000</v>
+        <v>495600</v>
       </c>
       <c r="R160" t="n">
         <v>0</v>
@@ -9974,7 +9974,7 @@
       </c>
       <c r="J161" t="inlineStr">
         <is>
-          <t>ENCABEÇAMENTO E PONTE SOBRE O RIO SANTO INÁCIO, TRECHO ENTR. MG-188 (COROMANDEL) - DISTRITO DE VEREDA, NA LMG-747</t>
+          <t>ENCABEÇAMENTO E PONTE SOBRE O CÓRREGO DAS LAJES, TRECHO ENTR. MGC-479 (SERRA DAS ARARAS) - ENTR. MG-402, NA LMG-622</t>
         </is>
       </c>
       <c r="K161" t="inlineStr">
@@ -9998,7 +9998,7 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>440000</v>
+        <v>679000</v>
       </c>
       <c r="R161" t="n">
         <v>0</v>
@@ -10031,7 +10031,7 @@
       </c>
       <c r="J162" t="inlineStr">
         <is>
-          <t>ENCABEÇAMENTO E PONTE SOBRE O RIO SÃO JOÃO, TRECHO IGARATINGA - ENTR. MG-252, NA MG-430 (SEMI-INTEGRADA)</t>
+          <t>ENCABEÇAMENTO E PONTE SOBRE O RIO SANTO INÁCIO, TRECHO ENTR. MG-188 (COROMANDEL) - DISTRITO DE VEREDA, NA LMG-747</t>
         </is>
       </c>
       <c r="K162" t="inlineStr">
@@ -10055,7 +10055,7 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>14920000</v>
+        <v>440000</v>
       </c>
       <c r="R162" t="n">
         <v>0</v>
@@ -10088,7 +10088,7 @@
       </c>
       <c r="J163" t="inlineStr">
         <is>
-          <t>ENCABEÇAMENTO E PONTE SOBRE O RIO SERRA BRANCA, TRECHO PAI PEDRO - CATUTI, NA MGC-122</t>
+          <t>ENCABEÇAMENTO E PONTE SOBRE O RIO SÃO JOÃO, TRECHO IGARATINGA - ENTR. MG-252, NA MG-430 (SEMI-INTEGRADA)</t>
         </is>
       </c>
       <c r="K163" t="inlineStr">
@@ -10112,7 +10112,7 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>8798400</v>
+        <v>14920000</v>
       </c>
       <c r="R163" t="n">
         <v>0</v>
@@ -10145,7 +10145,7 @@
       </c>
       <c r="J164" t="inlineStr">
         <is>
-          <t>ENCABEÇAMENTOS E PONTES SOBRE CÓRREGO VEREDINHA E RIBEIRÃO MARQUES, NO TRECHO RIACHINHO - GUARAPUAVA (UNAÍ), NA LMG-638</t>
+          <t>ENCABEÇAMENTO E PONTE SOBRE O RIO SERRA BRANCA, TRECHO PAI PEDRO - CATUTI, NA MGC-122</t>
         </is>
       </c>
       <c r="K164" t="inlineStr">
@@ -10169,7 +10169,7 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>369600</v>
+        <v>8798400</v>
       </c>
       <c r="R164" t="n">
         <v>0</v>
@@ -10202,7 +10202,7 @@
       </c>
       <c r="J165" t="inlineStr">
         <is>
-          <t>LMG-722 (ROCHINHA A LAGAMAR, PONTE SOBRE O RIO PARANAÍBA)</t>
+          <t>ENCABEÇAMENTOS E PONTES SOBRE CÓRREGO VEREDINHA E RIBEIRÃO MARQUES, NO TRECHO RIACHINHO - GUARAPUAVA (UNAÍ), NA LMG-638</t>
         </is>
       </c>
       <c r="K165" t="inlineStr">
@@ -10226,7 +10226,7 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>1000000</v>
+        <v>369600</v>
       </c>
       <c r="R165" t="n">
         <v>0</v>
@@ -10259,7 +10259,7 @@
       </c>
       <c r="J166" t="inlineStr">
         <is>
-          <t>MGC-267 (CORDISLÂNDIA A CARVALHÓPOLIS, PONTE SOBRE O RIO SAPUCAÍ -  LOTE 01)</t>
+          <t>LMG-722 (ROCHINHA A LAGAMAR, PONTE SOBRE O RIO PARANAÍBA)</t>
         </is>
       </c>
       <c r="K166" t="inlineStr">
@@ -10283,7 +10283,7 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>1203643</v>
+        <v>1000000</v>
       </c>
       <c r="R166" t="n">
         <v>0</v>
@@ -10316,7 +10316,7 @@
       </c>
       <c r="J167" t="inlineStr">
         <is>
-          <t>OLHOS D´AGUA DO OESTE A SANTA LUZIA DA SERRA - CÓRREGO SÃO BARTOLOMEU</t>
+          <t>MGC-267 (CORDISLÂNDIA A CARVALHÓPOLIS, PONTE SOBRE O RIO SAPUCAÍ -  LOTE 01)</t>
         </is>
       </c>
       <c r="K167" t="inlineStr">
@@ -10340,7 +10340,7 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>730000</v>
+        <v>1203643</v>
       </c>
       <c r="R167" t="n">
         <v>0</v>
@@ -10373,7 +10373,7 @@
       </c>
       <c r="J168" t="inlineStr">
         <is>
-          <t>PASSARELA MG-010 (CIDADE ADMINISTRATIVA)</t>
+          <t>OLHOS D´AGUA DO OESTE A SANTA LUZIA DA SERRA - CÓRREGO SÃO BARTOLOMEU</t>
         </is>
       </c>
       <c r="K168" t="inlineStr">
@@ -10397,7 +10397,7 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>66619</v>
+        <v>730000</v>
       </c>
       <c r="R168" t="n">
         <v>0</v>
@@ -10430,7 +10430,7 @@
       </c>
       <c r="J169" t="inlineStr">
         <is>
-          <t>PONTE CÓRREGO PERUAÇU, TRECHO CÔNEGO MARINHO - MIRAVÂNIA (RESERVA XACRIABÁ)</t>
+          <t>PASSARELA MG-010 (CIDADE ADMINISTRATIVA)</t>
         </is>
       </c>
       <c r="K169" t="inlineStr">
@@ -10454,7 +10454,7 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>901000</v>
+        <v>66619</v>
       </c>
       <c r="R169" t="n">
         <v>0</v>
@@ -10487,7 +10487,7 @@
       </c>
       <c r="J170" t="inlineStr">
         <is>
-          <t>PONTE CÓRREGO RIBEIRÃO, TRECHO ENTR. BR-040 - PORTO DIAMANTE</t>
+          <t>PONTE CÓRREGO PERUAÇU, TRECHO CÔNEGO MARINHO - MIRAVÂNIA (RESERVA XACRIABÁ)</t>
         </is>
       </c>
       <c r="K170" t="inlineStr">
@@ -10511,7 +10511,7 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>100000</v>
+        <v>901000</v>
       </c>
       <c r="R170" t="n">
         <v>0</v>
@@ -10544,7 +10544,7 @@
       </c>
       <c r="J171" t="inlineStr">
         <is>
-          <t>PONTE SOBRE O EXTRAVASOR DA CEMIG, TRECHO JANUÁRIA - RIO PARDO - PANDEIROS, NA MGC-479</t>
+          <t>PONTE CÓRREGO RIBEIRÃO, TRECHO ENTR. BR-040 - PORTO DIAMANTE</t>
         </is>
       </c>
       <c r="K171" t="inlineStr">
@@ -10568,7 +10568,7 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>170000</v>
+        <v>100000</v>
       </c>
       <c r="R171" t="n">
         <v>0</v>
@@ -10601,7 +10601,7 @@
       </c>
       <c r="J172" t="inlineStr">
         <is>
-          <t>PONTE SOBRE O RIBEIRÃO MATA BOI NA RODOVIA MG-414, TRECHO ARAGUARI (DISTRITO DE AMANHECE) - DIVISA MG/GO</t>
+          <t>PONTE SOBRE O EXTRAVASOR DA CEMIG, TRECHO JANUÁRIA - RIO PARDO - PANDEIROS, NA MGC-479</t>
         </is>
       </c>
       <c r="K172" t="inlineStr">
@@ -10625,7 +10625,7 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>2940000</v>
+        <v>170000</v>
       </c>
       <c r="R172" t="n">
         <v>0</v>
@@ -10658,7 +10658,7 @@
       </c>
       <c r="J173" t="inlineStr">
         <is>
-          <t>PONTE SOBRE O RIBEIRÃO PANDEIROS, TRECHO JANUÁRIA - RIO PARDO - PANDEIROS, NA MGC-479</t>
+          <t>PONTE SOBRE O RIBEIRÃO MATA BOI NA RODOVIA MG-414, TRECHO ARAGUARI (DISTRITO DE AMANHECE) - DIVISA MG/GO</t>
         </is>
       </c>
       <c r="K173" t="inlineStr">
@@ -10682,7 +10682,7 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>810000</v>
+        <v>2940000</v>
       </c>
       <c r="R173" t="n">
         <v>0</v>
@@ -10715,7 +10715,7 @@
       </c>
       <c r="J174" t="inlineStr">
         <is>
-          <t>PONTE SOBRE O RIO ARAGUARI (TROCA DOS APARELHOS DE DO 1º E 5º VÃOS), TRECHO ENTR. MG-190 - ZELÂNDIA (USINA SANTA JULIANA), DIMENSÕES 130,00X12,20M, RODOVIA AMG-0730</t>
+          <t>PONTE SOBRE O RIBEIRÃO PANDEIROS, TRECHO JANUÁRIA - RIO PARDO - PANDEIROS, NA MGC-479</t>
         </is>
       </c>
       <c r="K174" t="inlineStr">
@@ -10739,7 +10739,7 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>542000</v>
+        <v>810000</v>
       </c>
       <c r="R174" t="n">
         <v>0</v>
@@ -10772,7 +10772,7 @@
       </c>
       <c r="J175" t="inlineStr">
         <is>
-          <t>PONTE SOBRE O RIO CORRENTE -  MG-460, NO TRECHO DE MUNHOZ - TOLEDO ( E SEMI-INTEGRADA)</t>
+          <t>PONTE SOBRE O RIO ARAGUARI (TROCA DOS APARELHOS DE DO 1º E 5º VÃOS), TRECHO ENTR. MG-190 - ZELÂNDIA (USINA SANTA JULIANA), DIMENSÕES 130,00X12,20M, RODOVIA AMG-0730</t>
         </is>
       </c>
       <c r="K175" t="inlineStr">
@@ -10796,7 +10796,7 @@
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>2163814</v>
+        <v>542000</v>
       </c>
       <c r="R175" t="n">
         <v>0</v>
@@ -10829,7 +10829,7 @@
       </c>
       <c r="J176" t="inlineStr">
         <is>
-          <t>PONTE SOBRE O RIO SÃO FRANCISCO - ENTR. MGC-135 (MANGA) ¿ PORTO DE MATIAS CARDOSO, NA RODOVIA MG-401</t>
+          <t>PONTE SOBRE O RIO CORRENTE -  MG-460, NO TRECHO DE MUNHOZ - TOLEDO ( E SEMI-INTEGRADA)</t>
         </is>
       </c>
       <c r="K176" t="inlineStr">
@@ -10853,7 +10853,7 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>25000000</v>
+        <v>2163814</v>
       </c>
       <c r="R176" t="n">
         <v>0</v>
@@ -10886,7 +10886,7 @@
       </c>
       <c r="J177" t="inlineStr">
         <is>
-          <t>PONTES SOBRE OS RIOS SUAÇUI PEQUENO I E II, TRECHO PEÇANHA - COROACI, NA MG-314</t>
+          <t>PONTE SOBRE O RIO SÃO FRANCISCO - ENTR. MGC-135 (MANGA) ¿ PORTO DE MATIAS CARDOSO, NA RODOVIA MG-401</t>
         </is>
       </c>
       <c r="K177" t="inlineStr">
@@ -10910,7 +10910,7 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>500000</v>
+        <v>25000000</v>
       </c>
       <c r="R177" t="n">
         <v>0</v>
@@ -10943,7 +10943,7 @@
       </c>
       <c r="J178" t="inlineStr">
         <is>
-          <t>RECUPERAÇÃO DA PONTE S/ O RIO JEQUITINHONHA- DIAMANTINA - COUTO MAGALHÃES.</t>
+          <t>PONTES SOBRE OS RIOS SUAÇUI PEQUENO I E II, TRECHO PEÇANHA - COROACI, NA MG-314</t>
         </is>
       </c>
       <c r="K178" t="inlineStr">
@@ -10967,7 +10967,7 @@
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>1382535</v>
+        <v>500000</v>
       </c>
       <c r="R178" t="n">
         <v>0</v>
@@ -11000,7 +11000,7 @@
       </c>
       <c r="J179" t="inlineStr">
         <is>
-          <t>RECUPERAÇÃO ESTRUTURAL DA PONTE SOBRE O RIO PARACATU, TRECHO JOÃO PINHEIRO - BRASÍLÂNDIA DE MINAS, NA MG-181</t>
+          <t>RECUPERAÇÃO DA PONTE S/ O RIO JEQUITINHONHA- DIAMANTINA - COUTO MAGALHÃES.</t>
         </is>
       </c>
       <c r="K179" t="inlineStr">
@@ -11024,7 +11024,7 @@
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>1000000</v>
+        <v>1382535</v>
       </c>
       <c r="R179" t="n">
         <v>0</v>
@@ -11057,7 +11057,7 @@
       </c>
       <c r="J180" t="inlineStr">
         <is>
-          <t>RECUPERAÇÃO ESTRUTURAL DA PONTE SOBRE O RIO PARACATU, TRECHO JOÃO PINHEIRO (ENTR. MG-408) - BRASÍLÂNDIA DE MINAS, NA MG-181</t>
+          <t>RECUPERAÇÃO ESTRUTURAL DA PONTE SOBRE O RIO PARACATU, TRECHO JOÃO PINHEIRO - BRASÍLÂNDIA DE MINAS, NA MG-181</t>
         </is>
       </c>
       <c r="K180" t="inlineStr">
@@ -11081,7 +11081,7 @@
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>900000</v>
+        <v>1000000</v>
       </c>
       <c r="R180" t="n">
         <v>0</v>
@@ -11114,7 +11114,7 @@
       </c>
       <c r="J181" t="inlineStr">
         <is>
-          <t>REFORÇO DA FUNDAÇÃO DA PONTE SOBRE O RIBEIRÃO DAS ARARAS I, TRECHO GUANHÃES - SÃO PEDRO DO SUAÇUÍ, NA CMG-120</t>
+          <t>RECUPERAÇÃO ESTRUTURAL DA PONTE SOBRE O RIO PARACATU, TRECHO JOÃO PINHEIRO (ENTR. MG-408) - BRASÍLÂNDIA DE MINAS, NA MG-181</t>
         </is>
       </c>
       <c r="K181" t="inlineStr">
@@ -11138,7 +11138,7 @@
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>168000</v>
+        <v>900000</v>
       </c>
       <c r="R181" t="n">
         <v>0</v>
@@ -11171,7 +11171,7 @@
       </c>
       <c r="J182" t="inlineStr">
         <is>
-          <t>REFORÇO DA FUNDAÇÃO DA PONTE SOBRE O RIBEIRÃO MACAÚBAS, TRECHO SANTA LUZIA - JABOTICATUBAS, MG-020</t>
+          <t>REFORÇO DA FUNDAÇÃO DA PONTE SOBRE O RIBEIRÃO DAS ARARAS I, TRECHO GUANHÃES - SÃO PEDRO DO SUAÇUÍ, NA CMG-120</t>
         </is>
       </c>
       <c r="K182" t="inlineStr">
@@ -11195,7 +11195,7 @@
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>249000</v>
+        <v>168000</v>
       </c>
       <c r="R182" t="n">
         <v>0</v>
@@ -11228,7 +11228,7 @@
       </c>
       <c r="J183" t="inlineStr">
         <is>
-          <t>REFORÇO DA FUNDAÇÃO DO VIADUTO II NA PISTA DIREITA DA INTERSEÇÃO 3 (ACESSO AO INHOTIM, ESTACA 138)</t>
+          <t>REFORÇO DA FUNDAÇÃO DA PONTE SOBRE O RIBEIRÃO MACAÚBAS, TRECHO SANTA LUZIA - JABOTICATUBAS, MG-020</t>
         </is>
       </c>
       <c r="K183" t="inlineStr">
@@ -11252,7 +11252,7 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>705000</v>
+        <v>249000</v>
       </c>
       <c r="R183" t="n">
         <v>0</v>
@@ -11285,7 +11285,7 @@
       </c>
       <c r="J184" t="inlineStr">
         <is>
-          <t>REFORÇO DE FUNDAÇÃO CÓRREGO DOIDOS, TRECHO SÃO FRANCISCO DE PAULA - ENTR. BR-354</t>
+          <t>REFORÇO DA FUNDAÇÃO DO VIADUTO II NA PISTA DIREITA DA INTERSEÇÃO 3 (ACESSO AO INHOTIM, ESTACA 138)</t>
         </is>
       </c>
       <c r="K184" t="inlineStr">
@@ -11309,7 +11309,7 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>58800</v>
+        <v>705000</v>
       </c>
       <c r="R184" t="n">
         <v>0</v>
@@ -11342,7 +11342,7 @@
       </c>
       <c r="J185" t="inlineStr">
         <is>
-          <t>REFORÇO NA FUNDAÇÃO DA PONTE SOBRE O RIO VERMELHO, TRECHO SANTA BÁRBARA - CATAS ALTAS, NA MG-129</t>
+          <t>REFORÇO DE FUNDAÇÃO CÓRREGO DOIDOS, TRECHO SÃO FRANCISCO DE PAULA - ENTR. BR-354</t>
         </is>
       </c>
       <c r="K185" t="inlineStr">
@@ -11366,7 +11366,7 @@
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>725000</v>
+        <v>58800</v>
       </c>
       <c r="R185" t="n">
         <v>0</v>
@@ -11386,7 +11386,7 @@
         <v>81</v>
       </c>
       <c r="E186" t="n">
-        <v>4275</v>
+        <v>4272</v>
       </c>
       <c r="F186" t="n">
         <v>1</v>
@@ -11399,7 +11399,7 @@
       </c>
       <c r="J186" t="inlineStr">
         <is>
-          <t>PAVIMENTAÇÃO MG-326 (PONTE NOVA A BARRA LONGA)</t>
+          <t>REFORÇO NA FUNDAÇÃO DA PONTE SOBRE O RIO VERMELHO, TRECHO SANTA BÁRBARA - CATAS ALTAS, NA MG-129</t>
         </is>
       </c>
       <c r="K186" t="inlineStr">
@@ -11423,10 +11423,10 @@
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>0</v>
+        <v>725000</v>
       </c>
       <c r="R186" t="n">
-        <v>82286728</v>
+        <v>0</v>
       </c>
     </row>
     <row r="187">
@@ -11456,7 +11456,7 @@
       </c>
       <c r="J187" t="inlineStr">
         <is>
-          <t>PAVIMENTAÇÃO DA MG-314 (ENTR. MG-416 (PEÇANHA) A LMG-744 (COROACI) ENTR. VIRGOLÂNDIA)</t>
+          <t>PAVIMENTAÇÃO MG-326 (PONTE NOVA A BARRA LONGA)</t>
         </is>
       </c>
       <c r="K187" t="inlineStr">
@@ -11483,7 +11483,7 @@
         <v>0</v>
       </c>
       <c r="R187" t="n">
-        <v>22137718</v>
+        <v>82286728</v>
       </c>
     </row>
     <row r="188">
@@ -11513,7 +11513,7 @@
       </c>
       <c r="J188" t="inlineStr">
         <is>
-          <t>PAVIMENTAÇÃO DA RODOVIA MUNICIPAL (SANTA RITA DO ITUETO A ENTR. BR-259 (RESPLENDOR))</t>
+          <t>PAVIMENTAÇÃO DA MG-314 (ENTR. MG-416 (PEÇANHA) A LMG-744 (COROACI) ENTR. VIRGOLÂNDIA)</t>
         </is>
       </c>
       <c r="K188" t="inlineStr">
@@ -11540,7 +11540,7 @@
         <v>0</v>
       </c>
       <c r="R188" t="n">
-        <v>21757581</v>
+        <v>22137718</v>
       </c>
     </row>
     <row r="189">
@@ -11570,7 +11570,7 @@
       </c>
       <c r="J189" t="inlineStr">
         <is>
-          <t>RODOVIA MG-010, TRECHO CONCEIÇÃO DO MATO DENTRO - SERRO (DISTRITO DE MATO GROSSO), COM EXTENSÃO DE 21,80 KM</t>
+          <t>PAVIMENTAÇÃO DA RODOVIA MUNICIPAL (SANTA RITA DO ITUETO A ENTR. BR-259 (RESPLENDOR))</t>
         </is>
       </c>
       <c r="K189" t="inlineStr">
@@ -11597,7 +11597,7 @@
         <v>0</v>
       </c>
       <c r="R189" t="n">
-        <v>8036364</v>
+        <v>21757581</v>
       </c>
     </row>
     <row r="190">
@@ -11627,7 +11627,7 @@
       </c>
       <c r="J190" t="inlineStr">
         <is>
-          <t>TRECHO ENTRº LMG-690 (PARACATU) - ENTRº ENTRE RIBEIROS (DISTRITO) - ENTRº MG-181 (ESTACA 1250 A 2000)</t>
+          <t>RODOVIA MG-010, TRECHO CONCEIÇÃO DO MATO DENTRO - SERRO (DISTRITO DE MATO GROSSO), COM EXTENSÃO DE 21,80 KM</t>
         </is>
       </c>
       <c r="K190" t="inlineStr">
@@ -11654,7 +11654,7 @@
         <v>0</v>
       </c>
       <c r="R190" t="n">
-        <v>14063636</v>
+        <v>8036364</v>
       </c>
     </row>
     <row r="191">
@@ -11684,7 +11684,7 @@
       </c>
       <c r="J191" t="inlineStr">
         <is>
-          <t>RODOVIA MG-10 - TRECHO CONCEIÇÃO DO MATO DENTRO - SERRO (DISTRITO DE MATO GROSSO), COM EXTENSÃO DE 22,50 KM</t>
+          <t>TRECHO ENTRº LMG-690 (PARACATU) - ENTRº ENTRE RIBEIROS (DISTRITO) - ENTRº MG-181 (ESTACA 1250 A 2000)</t>
         </is>
       </c>
       <c r="K191" t="inlineStr">
@@ -11711,7 +11711,7 @@
         <v>0</v>
       </c>
       <c r="R191" t="n">
-        <v>8100000</v>
+        <v>14063636</v>
       </c>
     </row>
     <row r="192">
@@ -11741,7 +11741,7 @@
       </c>
       <c r="J192" t="inlineStr">
         <is>
-          <t>MELHORAMENTO E PAVIMENTAÇÃO DO CONTORNO DE ANDRADAS</t>
+          <t>RODOVIA MG-10 - TRECHO CONCEIÇÃO DO MATO DENTRO - SERRO (DISTRITO DE MATO GROSSO), COM EXTENSÃO DE 22,50 KM</t>
         </is>
       </c>
       <c r="K192" t="inlineStr">
@@ -11768,7 +11768,7 @@
         <v>0</v>
       </c>
       <c r="R192" t="n">
-        <v>4804860</v>
+        <v>8100000</v>
       </c>
     </row>
     <row r="193">
@@ -11798,7 +11798,7 @@
       </c>
       <c r="J193" t="inlineStr">
         <is>
-          <t>EMPREENDIMENTO EM DEFINIÇÃO JUNTO AO BANCO DO BRASIL - CONTRATO DE FINANCIAMENTO Nº 20/00020-0 (PDMG)</t>
+          <t>MELHORAMENTO E PAVIMENTAÇÃO DO CONTORNO DE ANDRADAS</t>
         </is>
       </c>
       <c r="K193" t="inlineStr">
@@ -11825,7 +11825,7 @@
         <v>0</v>
       </c>
       <c r="R193" t="n">
-        <v>6000001</v>
+        <v>4804860</v>
       </c>
     </row>
     <row r="194">
@@ -11855,7 +11855,7 @@
       </c>
       <c r="J194" t="inlineStr">
         <is>
-          <t>COMPLEMENTAÇÃO LMG-680, TRECHO PARACATU (ENTR. LMG-690) - ENTR. ENTRE RIBEIROS - ENTR. MG-181 - (LOTE 1), SEGMENTO 1 (0 A 835), 16,70 KM E SEGMENTO 2 (835 A 1250), 8,30 KM</t>
+          <t>EMPREENDIMENTO EM DEFINIÇÃO JUNTO AO BANCO DO BRASIL - CONTRATO DE FINANCIAMENTO Nº 20/00020-0 (PDMG)</t>
         </is>
       </c>
       <c r="K194" t="inlineStr">
@@ -11879,10 +11879,10 @@
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>11326937</v>
+        <v>0</v>
       </c>
       <c r="R194" t="n">
-        <v>0</v>
+        <v>6000001</v>
       </c>
     </row>
     <row r="195">
@@ -11912,7 +11912,7 @@
       </c>
       <c r="J195" t="inlineStr">
         <is>
-          <t>COMPLEMENTAÇÃO LMG-680, TRECHO PARACATU (ENTR. LMG-690) - ENTR. ENTRE RIBEIROS - ENTR. MG-181 - ESTACA 2550 A 3281</t>
+          <t>COMPLEMENTAÇÃO LMG-680, TRECHO PARACATU (ENTR. LMG-690) - ENTR. ENTRE RIBEIROS - ENTR. MG-181 - (LOTE 1), SEGMENTO 1 (0 A 835), 16,70 KM E SEGMENTO 2 (835 A 1250), 8,30 KM</t>
         </is>
       </c>
       <c r="K195" t="inlineStr">
@@ -11936,7 +11936,7 @@
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>19000000</v>
+        <v>11326937</v>
       </c>
       <c r="R195" t="n">
         <v>0</v>
@@ -11969,7 +11969,7 @@
       </c>
       <c r="J196" t="inlineStr">
         <is>
-          <t>COMPLEMENTO S JANUÁRIA - PANDEIROS, NA RODOVIA MGC-479</t>
+          <t>COMPLEMENTAÇÃO LMG-680, TRECHO PARACATU (ENTR. LMG-690) - ENTR. ENTRE RIBEIROS - ENTR. MG-181 - ESTACA 2550 A 3281</t>
         </is>
       </c>
       <c r="K196" t="inlineStr">
@@ -11993,7 +11993,7 @@
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>74941120</v>
+        <v>19000000</v>
       </c>
       <c r="R196" t="n">
         <v>0</v>
@@ -12026,7 +12026,7 @@
       </c>
       <c r="J197" t="inlineStr">
         <is>
-          <t>CONTORNO DE ANDRADAS (COMPLEMENTAÇÃO) - LOTE 01</t>
+          <t>COMPLEMENTO S JANUÁRIA - PANDEIROS, NA RODOVIA MGC-479</t>
         </is>
       </c>
       <c r="K197" t="inlineStr">
@@ -12050,7 +12050,7 @@
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>38460000</v>
+        <v>74941120</v>
       </c>
       <c r="R197" t="n">
         <v>0</v>
@@ -12083,7 +12083,7 @@
       </c>
       <c r="J198" t="inlineStr">
         <is>
-          <t>ENTR. MG-181 (BRASILÂNDIA DE MINAS) - ENTR. BR-365 (BURITIZEIRO), NA MG-408 - LOTE 01</t>
+          <t>CONTORNO DE ANDRADAS (COMPLEMENTAÇÃO) - LOTE 01</t>
         </is>
       </c>
       <c r="K198" t="inlineStr">
@@ -12107,7 +12107,7 @@
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>1000000</v>
+        <v>38460000</v>
       </c>
       <c r="R198" t="n">
         <v>0</v>
@@ -12140,7 +12140,7 @@
       </c>
       <c r="J199" t="inlineStr">
         <is>
-          <t>IBERTIOGA - PIEDADE DO RIO GRANDE, NA RODOVIA MG-338</t>
+          <t>ENTR. MG-181 (BRASILÂNDIA DE MINAS) - ENTR. BR-365 (BURITIZEIRO), NA MG-408 - LOTE 01</t>
         </is>
       </c>
       <c r="K199" t="inlineStr">
@@ -12164,7 +12164,7 @@
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>7000000</v>
+        <v>1000000</v>
       </c>
       <c r="R199" t="n">
         <v>0</v>
@@ -12197,7 +12197,7 @@
       </c>
       <c r="J200" t="inlineStr">
         <is>
-          <t>INTERSEÇÃO DE ACESSO A COUTO DE MAGALHÃES DE MINAS, NA MGC-367</t>
+          <t>IBERTIOGA - PIEDADE DO RIO GRANDE, NA RODOVIA MG-338</t>
         </is>
       </c>
       <c r="K200" t="inlineStr">
@@ -12221,7 +12221,7 @@
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>1000000</v>
+        <v>7000000</v>
       </c>
       <c r="R200" t="n">
         <v>0</v>
@@ -12254,7 +12254,7 @@
       </c>
       <c r="J201" t="inlineStr">
         <is>
-          <t>ITAPAGIPE - ENTR. BR-364 (CAMPINA VERDE), RODOVIA MGC-154</t>
+          <t>INTERSEÇÃO DE ACESSO A COUTO DE MAGALHÃES DE MINAS, NA MGC-367</t>
         </is>
       </c>
       <c r="K201" t="inlineStr">
@@ -12278,7 +12278,7 @@
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>6121131</v>
+        <v>1000000</v>
       </c>
       <c r="R201" t="n">
         <v>0</v>
@@ -12311,7 +12311,7 @@
       </c>
       <c r="J202" t="inlineStr">
         <is>
-          <t>MG-631 - SÃO JOÃO DA PONTE A CAPITÃO ENÉAS</t>
+          <t>ITAPAGIPE - ENTR. BR-364 (CAMPINA VERDE), RODOVIA MGC-154</t>
         </is>
       </c>
       <c r="K202" t="inlineStr">
@@ -12335,7 +12335,7 @@
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>1000000</v>
+        <v>6121131</v>
       </c>
       <c r="R202" t="n">
         <v>0</v>
@@ -12368,7 +12368,7 @@
       </c>
       <c r="J203" t="inlineStr">
         <is>
-          <t>MELHORAMENTO E PAVIMENTAÇÃO DA RODOVIA LMG-706, SEGMENTO 01: ENTR. BR-040 - VARIANTE (PONTE RIO ESCURO); SEGMENTO 02: VAZAMOR - VAZANTE; SEGMENTO 03: CONTORNO DE VAZANTE - ENTR. BR-354</t>
+          <t>MG-631 - SÃO JOÃO DA PONTE A CAPITÃO ENÉAS</t>
         </is>
       </c>
       <c r="K203" t="inlineStr">
@@ -12425,7 +12425,7 @@
       </c>
       <c r="J204" t="inlineStr">
         <is>
-          <t>ACESSO AO PRESÍDIO DE ITURAMA</t>
+          <t>MELHORAMENTO E PAVIMENTAÇÃO DA RODOVIA LMG-706, SEGMENTO 01: ENTR. BR-040 - VARIANTE (PONTE RIO ESCURO); SEGMENTO 02: VAZAMOR - VAZANTE; SEGMENTO 03: CONTORNO DE VAZANTE - ENTR. BR-354</t>
         </is>
       </c>
       <c r="K204" t="inlineStr">
@@ -12482,7 +12482,7 @@
       </c>
       <c r="J205" t="inlineStr">
         <is>
-          <t>MONTE CARMELO (ENTR. MG-190) - ENTR. LMG-742 (CHAPADA DE MINAS P/ GRUPIARA), NA LMG-746 - LOTE 01 9,50 KM</t>
+          <t>ACESSO AO PRESÍDIO DE ITURAMA</t>
         </is>
       </c>
       <c r="K205" t="inlineStr">
@@ -12539,7 +12539,7 @@
       </c>
       <c r="J206" t="inlineStr">
         <is>
-          <t>MONTE CARMELO A CHAPADA DE MINAS - LOTE 2</t>
+          <t>MONTE CARMELO (ENTR. MG-190) - ENTR. LMG-742 (CHAPADA DE MINAS P/ GRUPIARA), NA LMG-746 - LOTE 01 9,50 KM</t>
         </is>
       </c>
       <c r="K206" t="inlineStr">
@@ -12596,7 +12596,7 @@
       </c>
       <c r="J207" t="inlineStr">
         <is>
-          <t>NATALÂNDIA - ENTR. BR-251, NA LMG-622</t>
+          <t>MONTE CARMELO A CHAPADA DE MINAS - LOTE 2</t>
         </is>
       </c>
       <c r="K207" t="inlineStr">
@@ -12653,7 +12653,7 @@
       </c>
       <c r="J208" t="inlineStr">
         <is>
-          <t>PEÇANHA (ENTR. MG-416) - LMG-744 (COROACI), NA MG-314</t>
+          <t>NATALÂNDIA - ENTR. BR-251, NA LMG-622</t>
         </is>
       </c>
       <c r="K208" t="inlineStr">
@@ -12677,7 +12677,7 @@
         </is>
       </c>
       <c r="Q208" t="n">
-        <v>431808</v>
+        <v>1000000</v>
       </c>
       <c r="R208" t="n">
         <v>0</v>
@@ -12710,7 +12710,7 @@
       </c>
       <c r="J209" t="inlineStr">
         <is>
-          <t>PEDRA AZUL (ENTR. MG-105) - DISTRITO DE PEDRA GRANDE - ALMENARA, MG-251/MG-406, LOTE 01 35 KM</t>
+          <t>PEÇANHA (ENTR. MG-416) - LMG-744 (COROACI), NA MG-314</t>
         </is>
       </c>
       <c r="K209" t="inlineStr">
@@ -12734,7 +12734,7 @@
         </is>
       </c>
       <c r="Q209" t="n">
-        <v>1000000</v>
+        <v>431808</v>
       </c>
       <c r="R209" t="n">
         <v>0</v>
@@ -12767,7 +12767,7 @@
       </c>
       <c r="J210" t="inlineStr">
         <is>
-          <t>PEDRA BONITA - ENTR. BR-116 E INTERSEÇÃO ENTR. BR-116 (COMPLEMENTAÇÃO), RODOVIA LMG-840</t>
+          <t>PEDRA AZUL (ENTR. MG-105) - DISTRITO DE PEDRA GRANDE - ALMENARA, MG-251/MG-406, LOTE 01 35 KM</t>
         </is>
       </c>
       <c r="K210" t="inlineStr">
@@ -12824,7 +12824,7 @@
       </c>
       <c r="J211" t="inlineStr">
         <is>
-          <t>PRESIDENTE OLEGÁRIO - GALENA, NA LMG-726</t>
+          <t>PEDRA BONITA - ENTR. BR-116 E INTERSEÇÃO ENTR. BR-116 (COMPLEMENTAÇÃO), RODOVIA LMG-840</t>
         </is>
       </c>
       <c r="K211" t="inlineStr">
@@ -12881,7 +12881,7 @@
       </c>
       <c r="J212" t="inlineStr">
         <is>
-          <t>SANTA RITA DO ITUETO - ENTR. BR-259 (RESPLENDOR) (COMPLEMENTAÇÃO), MUNICIPAL AMG-2320</t>
+          <t>PRESIDENTE OLEGÁRIO - GALENA, NA LMG-726</t>
         </is>
       </c>
       <c r="K212" t="inlineStr">
@@ -12905,7 +12905,7 @@
         </is>
       </c>
       <c r="Q212" t="n">
-        <v>14356788</v>
+        <v>1000000</v>
       </c>
       <c r="R212" t="n">
         <v>0</v>
@@ -12938,7 +12938,7 @@
       </c>
       <c r="J213" t="inlineStr">
         <is>
-          <t>SÃO DOMINGOS DO PRATA - DOM SILVÉRIO, NA MGC-120</t>
+          <t>SANTA RITA DO ITUETO - ENTR. BR-259 (RESPLENDOR) (COMPLEMENTAÇÃO), MUNICIPAL AMG-2320</t>
         </is>
       </c>
       <c r="K213" t="inlineStr">
@@ -12962,7 +12962,7 @@
         </is>
       </c>
       <c r="Q213" t="n">
-        <v>100000</v>
+        <v>14356788</v>
       </c>
       <c r="R213" t="n">
         <v>0</v>
@@ -12995,7 +12995,7 @@
       </c>
       <c r="J214" t="inlineStr">
         <is>
-          <t>UNAÍ (ENTR. BR-251) - PARACATU (ENTR. BR-040) (ESTRADA DO MUNDO NOVO), NA LMG-658 - LOTE 01</t>
+          <t>SÃO DOMINGOS DO PRATA - DOM SILVÉRIO, NA MGC-120</t>
         </is>
       </c>
       <c r="K214" t="inlineStr">
@@ -13019,7 +13019,7 @@
         </is>
       </c>
       <c r="Q214" t="n">
-        <v>1000000</v>
+        <v>100000</v>
       </c>
       <c r="R214" t="n">
         <v>0</v>
@@ -13052,7 +13052,7 @@
       </c>
       <c r="J215" t="inlineStr">
         <is>
-          <t>ARAÇAÍ - SETE LAGOAS, RODOVIA MUNICIPAL</t>
+          <t>UNAÍ (ENTR. BR-251) - PARACATU (ENTR. BR-040) (ESTRADA DO MUNDO NOVO), NA LMG-658 - LOTE 01</t>
         </is>
       </c>
       <c r="K215" t="inlineStr">
@@ -13076,7 +13076,7 @@
         </is>
       </c>
       <c r="Q215" t="n">
-        <v>35359852</v>
+        <v>1000000</v>
       </c>
       <c r="R215" t="n">
         <v>0</v>
@@ -13109,7 +13109,7 @@
       </c>
       <c r="J216" t="inlineStr">
         <is>
-          <t>ARAGUARI (DISTRITO DE AMANHECE) - DIVISA MG/GO, NA MG-414</t>
+          <t>ARAÇAÍ - SETE LAGOAS, RODOVIA MUNICIPAL</t>
         </is>
       </c>
       <c r="K216" t="inlineStr">
@@ -13133,7 +13133,7 @@
         </is>
       </c>
       <c r="Q216" t="n">
-        <v>29030000</v>
+        <v>35359852</v>
       </c>
       <c r="R216" t="n">
         <v>0</v>
@@ -13166,7 +13166,7 @@
       </c>
       <c r="J217" t="inlineStr">
         <is>
-          <t>CAMPO VERDE (DISTRITO E NOVORIZONTE) - FRUTA DE LEITE, NA LMG-626 (LOTE 01 TSD)</t>
+          <t>ARAGUARI (DISTRITO DE AMANHECE) - DIVISA MG/GO, NA MG-414</t>
         </is>
       </c>
       <c r="K217" t="inlineStr">
@@ -13190,7 +13190,7 @@
         </is>
       </c>
       <c r="Q217" t="n">
-        <v>1000000</v>
+        <v>29030000</v>
       </c>
       <c r="R217" t="n">
         <v>0</v>
@@ -13223,7 +13223,7 @@
       </c>
       <c r="J218" t="inlineStr">
         <is>
-          <t>JABOTICATUBAS - LAGOA SANTA, RODOVIA MUNICIPAL - LOTE 01</t>
+          <t>CAMPO VERDE (DISTRITO E NOVORIZONTE) - FRUTA DE LEITE, NA LMG-626 (LOTE 01 TSD)</t>
         </is>
       </c>
       <c r="K218" t="inlineStr">
@@ -13247,7 +13247,7 @@
         </is>
       </c>
       <c r="Q218" t="n">
-        <v>3541727</v>
+        <v>1000000</v>
       </c>
       <c r="R218" t="n">
         <v>0</v>
@@ -13280,7 +13280,7 @@
       </c>
       <c r="J219" t="inlineStr">
         <is>
-          <t xml:space="preserve">LMG-629 (RIO PARDO DE MINAS A ENTRº LMG-635) - LOTE 2 </t>
+          <t>JABOTICATUBAS - LAGOA SANTA, RODOVIA MUNICIPAL - LOTE 01</t>
         </is>
       </c>
       <c r="K219" t="inlineStr">
@@ -13304,7 +13304,7 @@
         </is>
       </c>
       <c r="Q219" t="n">
-        <v>31280000</v>
+        <v>3541727</v>
       </c>
       <c r="R219" t="n">
         <v>0</v>
@@ -13324,7 +13324,7 @@
         <v>81</v>
       </c>
       <c r="E220" t="n">
-        <v>4287</v>
+        <v>4275</v>
       </c>
       <c r="F220" t="n">
         <v>1</v>
@@ -13337,7 +13337,7 @@
       </c>
       <c r="J220" t="inlineStr">
         <is>
-          <t>Empreendimentos do Acordo Judicial do Rio Doce</t>
+          <t xml:space="preserve">LMG-629 (RIO PARDO DE MINAS A ENTRº LMG-635) - LOTE 2 </t>
         </is>
       </c>
       <c r="K220" t="inlineStr">
@@ -13361,7 +13361,7 @@
         </is>
       </c>
       <c r="Q220" t="n">
-        <v>1000</v>
+        <v>31280000</v>
       </c>
       <c r="R220" t="n">
         <v>0</v>
@@ -13381,7 +13381,7 @@
         <v>81</v>
       </c>
       <c r="E221" t="n">
-        <v>4289</v>
+        <v>4287</v>
       </c>
       <c r="F221" t="n">
         <v>1</v>
@@ -13394,7 +13394,7 @@
       </c>
       <c r="J221" t="inlineStr">
         <is>
-          <t>Empreendimentos do Acordo Judicial de Brumadinho</t>
+          <t>Empreendimentos do Acordo Judicial do Rio Doce</t>
         </is>
       </c>
       <c r="K221" t="inlineStr">
@@ -13438,7 +13438,7 @@
         <v>81</v>
       </c>
       <c r="E222" t="n">
-        <v>4293</v>
+        <v>4289</v>
       </c>
       <c r="F222" t="n">
         <v>1</v>
@@ -13451,7 +13451,7 @@
       </c>
       <c r="J222" t="inlineStr">
         <is>
-          <t>PROGRAMA DE MICRORREVESTIMENTO ASFÁLTICO</t>
+          <t>Empreendimentos do Acordo Judicial de Brumadinho</t>
         </is>
       </c>
       <c r="K222" t="inlineStr">
@@ -13475,7 +13475,7 @@
         </is>
       </c>
       <c r="Q222" t="n">
-        <v>10000000</v>
+        <v>1000</v>
       </c>
       <c r="R222" t="n">
         <v>0</v>
@@ -13508,7 +13508,7 @@
       </c>
       <c r="J223" t="inlineStr">
         <is>
-          <t>REALINHAMENTO DE PREÇOS DO FORNECIMENTO DO MATERIAL BETUMINOSO</t>
+          <t>PROGRAMA DE MICRORREVESTIMENTO ASFÁLTICO</t>
         </is>
       </c>
       <c r="K223" t="inlineStr">
@@ -13532,7 +13532,7 @@
         </is>
       </c>
       <c r="Q223" t="n">
-        <v>1406178</v>
+        <v>10000000</v>
       </c>
       <c r="R223" t="n">
         <v>0</v>
@@ -13565,7 +13565,7 @@
       </c>
       <c r="J224" t="inlineStr">
         <is>
-          <t>04ª URG BARBACENA</t>
+          <t>REALINHAMENTO DE PREÇOS DO FORNECIMENTO DO MATERIAL BETUMINOSO</t>
         </is>
       </c>
       <c r="K224" t="inlineStr">
@@ -13589,10 +13589,10 @@
         </is>
       </c>
       <c r="Q224" t="n">
-        <v>0</v>
+        <v>1406178</v>
       </c>
       <c r="R224" t="n">
-        <v>12870000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="225">
@@ -13622,7 +13622,7 @@
       </c>
       <c r="J225" t="inlineStr">
         <is>
-          <t>20ª URG FORMIGA</t>
+          <t>04ª URG BARBACENA</t>
         </is>
       </c>
       <c r="K225" t="inlineStr">
@@ -13679,7 +13679,7 @@
       </c>
       <c r="J226" t="inlineStr">
         <is>
-          <t>28ª URG TEÓFILO OTONI</t>
+          <t>20ª URG FORMIGA</t>
         </is>
       </c>
       <c r="K226" t="inlineStr">
@@ -13706,7 +13706,7 @@
         <v>0</v>
       </c>
       <c r="R226" t="n">
-        <v>9575065</v>
+        <v>12870000</v>
       </c>
     </row>
     <row r="227">
@@ -13736,7 +13736,7 @@
       </c>
       <c r="J227" t="inlineStr">
         <is>
-          <t>30ª URG JUIZ DE FORA</t>
+          <t>28ª URG TEÓFILO OTONI</t>
         </is>
       </c>
       <c r="K227" t="inlineStr">
@@ -13763,7 +13763,7 @@
         <v>0</v>
       </c>
       <c r="R227" t="n">
-        <v>12375000</v>
+        <v>9575065</v>
       </c>
     </row>
     <row r="228">
@@ -13793,7 +13793,7 @@
       </c>
       <c r="J228" t="inlineStr">
         <is>
-          <t>01ª URG BELO HORIZONTE - SUL</t>
+          <t>30ª URG JUIZ DE FORA</t>
         </is>
       </c>
       <c r="K228" t="inlineStr">
@@ -13820,7 +13820,7 @@
         <v>0</v>
       </c>
       <c r="R228" t="n">
-        <v>14850000</v>
+        <v>12375000</v>
       </c>
     </row>
     <row r="229">
@@ -13850,7 +13850,7 @@
       </c>
       <c r="J229" t="inlineStr">
         <is>
-          <t>01ª URG BELO HORIZONTE - NORTE</t>
+          <t>01ª URG BELO HORIZONTE - SUL</t>
         </is>
       </c>
       <c r="K229" t="inlineStr">
@@ -13907,7 +13907,7 @@
       </c>
       <c r="J230" t="inlineStr">
         <is>
-          <t>31ª URG ITUIUTABA</t>
+          <t>01ª URG BELO HORIZONTE - NORTE</t>
         </is>
       </c>
       <c r="K230" t="inlineStr">
@@ -13934,7 +13934,7 @@
         <v>0</v>
       </c>
       <c r="R230" t="n">
-        <v>9900000</v>
+        <v>14850000</v>
       </c>
     </row>
     <row r="231">
@@ -13964,7 +13964,7 @@
       </c>
       <c r="J231" t="inlineStr">
         <is>
-          <t>CONSERVAÇÃO DA MALHA VIÁRIA DAS 40ª URG`S</t>
+          <t>31ª URG ITUIUTABA</t>
         </is>
       </c>
       <c r="K231" t="inlineStr">
@@ -13988,10 +13988,10 @@
         </is>
       </c>
       <c r="Q231" t="n">
-        <v>654124898</v>
+        <v>0</v>
       </c>
       <c r="R231" t="n">
-        <v>0</v>
+        <v>9900000</v>
       </c>
     </row>
     <row r="232">
@@ -14021,7 +14021,7 @@
       </c>
       <c r="J232" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE EMPRESA PARA EXECUÇÃO DE SERVIÇOS DE NATUREZA CONTÍNUA DE SINALIZAÇÃO VIÁRIA VERTICAL, HORIZONTAL E DISPOSITIVOS AUXILIARES, EM REGIME DE EMPREITADA POR PREÇO UNITÁRIO, COM FORNECIMENTO DE MATERIAIS, UTILIZAÇÃO DE EQUIPAMENTOS E MÃO-DE</t>
+          <t>CONSERVAÇÃO DA MALHA VIÁRIA DAS 40ª URG`S</t>
         </is>
       </c>
       <c r="K232" t="inlineStr">
@@ -14045,7 +14045,7 @@
         </is>
       </c>
       <c r="Q232" t="n">
-        <v>30767861</v>
+        <v>654124898</v>
       </c>
       <c r="R232" t="n">
         <v>0</v>
@@ -14078,7 +14078,7 @@
       </c>
       <c r="J233" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO LINHA VERDE E COMPLEXO CIDADE ADMINISTRATIVA</t>
+          <t>CONTRATAÇÃO DE EMPRESA PARA EXECUÇÃO DE SERVIÇOS DE NATUREZA CONTÍNUA DE SINALIZAÇÃO VIÁRIA VERTICAL, HORIZONTAL E DISPOSITIVOS AUXILIARES, EM REGIME DE EMPREITADA POR PREÇO UNITÁRIO, COM FORNECIMENTO DE MATERIAIS, UTILIZAÇÃO DE EQUIPAMENTOS E MÃO-DE</t>
         </is>
       </c>
       <c r="K233" t="inlineStr">
@@ -14102,7 +14102,7 @@
         </is>
       </c>
       <c r="Q233" t="n">
-        <v>19976964</v>
+        <v>30767861</v>
       </c>
       <c r="R233" t="n">
         <v>0</v>
@@ -14135,7 +14135,7 @@
       </c>
       <c r="J234" t="inlineStr">
         <is>
-          <t>SINALIZAÇÃO VIÁRIA VERTICAL, HORIZONTAL E DISPOSITIVOS AUXILIARES, COM FORNECIMENTO DE MATERIAIS, UTILIZAÇÃO DE EQUIPAMENTOS E MÃO-DE-OBRA ESPECIALIZADA - LOTE 1</t>
+          <t>MANUTENÇÃO LINHA VERDE E COMPLEXO CIDADE ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="K234" t="inlineStr">
@@ -14159,7 +14159,7 @@
         </is>
       </c>
       <c r="Q234" t="n">
-        <v>12895888</v>
+        <v>19976964</v>
       </c>
       <c r="R234" t="n">
         <v>0</v>
@@ -14192,7 +14192,7 @@
       </c>
       <c r="J235" t="inlineStr">
         <is>
-          <t>SINALIZAÇÃO VIÁRIA VERTICAL, HORIZONTAL E DISPOSITIVOS AUXILIARES, COM FORNECIMENTO DE MATERIAIS, UTILIZAÇÃO DE EQUIPAMENTOS E MÃO-DE-OBRA ESPECIALIZADA - LOTE 2</t>
+          <t>SINALIZAÇÃO VIÁRIA VERTICAL, HORIZONTAL E DISPOSITIVOS AUXILIARES, COM FORNECIMENTO DE MATERIAIS, UTILIZAÇÃO DE EQUIPAMENTOS E MÃO-DE-OBRA ESPECIALIZADA - LOTE 1</t>
         </is>
       </c>
       <c r="K235" t="inlineStr">
@@ -14216,7 +14216,7 @@
         </is>
       </c>
       <c r="Q235" t="n">
-        <v>11846334</v>
+        <v>12895888</v>
       </c>
       <c r="R235" t="n">
         <v>0</v>
@@ -14249,7 +14249,7 @@
       </c>
       <c r="J236" t="inlineStr">
         <is>
-          <t>SINALIZAÇÃO VIÁRIA VERTICAL, HORIZONTAL E DISPOSITIVOS AUXILIARES, COM FORNECIMENTO DE MATERIAIS, UTILIZAÇÃO DE EQUIPAMENTOS E MÃO-DE-OBRA ESPECIALIZADA - LOTE 3</t>
+          <t>SINALIZAÇÃO VIÁRIA VERTICAL, HORIZONTAL E DISPOSITIVOS AUXILIARES, COM FORNECIMENTO DE MATERIAIS, UTILIZAÇÃO DE EQUIPAMENTOS E MÃO-DE-OBRA ESPECIALIZADA - LOTE 2</t>
         </is>
       </c>
       <c r="K236" t="inlineStr">
@@ -14273,7 +14273,7 @@
         </is>
       </c>
       <c r="Q236" t="n">
-        <v>15201174</v>
+        <v>11846334</v>
       </c>
       <c r="R236" t="n">
         <v>0</v>
@@ -14306,7 +14306,7 @@
       </c>
       <c r="J237" t="inlineStr">
         <is>
-          <t>SINALIZAÇÃO VIÁRIA VERTICAL, HORIZONTAL E DISPOSITIVOS AUXILIARES, COM FORNECIMENTO DE MATERIAIS, UTILIZAÇÃO DE EQUIPAMENTOS E MÃO-DE-OBRA ESPECIALIZADA - LOTE 4</t>
+          <t>SINALIZAÇÃO VIÁRIA VERTICAL, HORIZONTAL E DISPOSITIVOS AUXILIARES, COM FORNECIMENTO DE MATERIAIS, UTILIZAÇÃO DE EQUIPAMENTOS E MÃO-DE-OBRA ESPECIALIZADA - LOTE 3</t>
         </is>
       </c>
       <c r="K237" t="inlineStr">
@@ -14330,7 +14330,7 @@
         </is>
       </c>
       <c r="Q237" t="n">
-        <v>12921920</v>
+        <v>15201174</v>
       </c>
       <c r="R237" t="n">
         <v>0</v>
@@ -14350,7 +14350,7 @@
         <v>81</v>
       </c>
       <c r="E238" t="n">
-        <v>4385</v>
+        <v>4293</v>
       </c>
       <c r="F238" t="n">
         <v>1</v>
@@ -14363,7 +14363,7 @@
       </c>
       <c r="J238" t="inlineStr">
         <is>
-          <t>RECUPERAÇÃO FUNCIONAL MG-232 (BRAÚNAS (DIV. 40ª/ 2ª) - IPATINGA)</t>
+          <t>SINALIZAÇÃO VIÁRIA VERTICAL, HORIZONTAL E DISPOSITIVOS AUXILIARES, COM FORNECIMENTO DE MATERIAIS, UTILIZAÇÃO DE EQUIPAMENTOS E MÃO-DE-OBRA ESPECIALIZADA - LOTE 4</t>
         </is>
       </c>
       <c r="K238" t="inlineStr">
@@ -14387,7 +14387,7 @@
         </is>
       </c>
       <c r="Q238" t="n">
-        <v>6382601</v>
+        <v>12921920</v>
       </c>
       <c r="R238" t="n">
         <v>0</v>
@@ -14420,7 +14420,7 @@
       </c>
       <c r="J239" t="inlineStr">
         <is>
-          <t>RECUPERAÇÃO FUNCIONAL MGC-259 ( SABINÓPOLIS - SERRO, GUANHÃES - SABINÓPOLIS E ALVORADA MINAS - SERRO) *</t>
+          <t>RECUPERAÇÃO FUNCIONAL MG-232 (BRAÚNAS (DIV. 40ª/ 2ª) - IPATINGA)</t>
         </is>
       </c>
       <c r="K239" t="inlineStr">
@@ -14444,7 +14444,7 @@
         </is>
       </c>
       <c r="Q239" t="n">
-        <v>30000000</v>
+        <v>6382601</v>
       </c>
       <c r="R239" t="n">
         <v>0</v>
@@ -14477,7 +14477,7 @@
       </c>
       <c r="J240" t="inlineStr">
         <is>
-          <t>RECUPERAÇÃO FUNCIONAL MGC-455 (PIRAJUBA - ENTRº BR-364 (PLANURA)</t>
+          <t>RECUPERAÇÃO FUNCIONAL MGC-259 ( SABINÓPOLIS - SERRO, GUANHÃES - SABINÓPOLIS E ALVORADA MINAS - SERRO) *</t>
         </is>
       </c>
       <c r="K240" t="inlineStr">
@@ -14501,7 +14501,7 @@
         </is>
       </c>
       <c r="Q240" t="n">
-        <v>4000000</v>
+        <v>30000000</v>
       </c>
       <c r="R240" t="n">
         <v>0</v>
@@ -14518,10 +14518,10 @@
         <v>782</v>
       </c>
       <c r="D241" t="n">
-        <v>139</v>
+        <v>81</v>
       </c>
       <c r="E241" t="n">
-        <v>4280</v>
+        <v>4385</v>
       </c>
       <c r="F241" t="n">
         <v>1</v>
@@ -14534,7 +14534,7 @@
       </c>
       <c r="J241" t="inlineStr">
         <is>
-          <t>PONTO CRÍTICO: ENTRº BR-040 (BARREIRA DOTRIUNFO) - ENTRº MG-353 (GOIANÁ)</t>
+          <t>RECUPERAÇÃO FUNCIONAL MGC-455 (PIRAJUBA - ENTRº BR-364 (PLANURA)</t>
         </is>
       </c>
       <c r="K241" t="inlineStr">
@@ -14591,7 +14591,7 @@
       </c>
       <c r="J242" t="inlineStr">
         <is>
-          <t>PONTO CRÍTICO: ENTRº MGC-265 (RIO POMBA) - PONTE RIO POMBA</t>
+          <t>PONTO CRÍTICO: ENTRº BR-040 (BARREIRA DOTRIUNFO) - ENTRº MG-353 (GOIANÁ)</t>
         </is>
       </c>
       <c r="K242" t="inlineStr">
@@ -14615,7 +14615,7 @@
         </is>
       </c>
       <c r="Q242" t="n">
-        <v>470000</v>
+        <v>4000000</v>
       </c>
       <c r="R242" t="n">
         <v>0</v>
@@ -14648,7 +14648,7 @@
       </c>
       <c r="J243" t="inlineStr">
         <is>
-          <t>PONTO CRÍTICO: ENTRº P/ MARIA DA FÉ - INÍCIO DO PERÍMETRO URBANO DE ITAJUBÁ (2  PONTOS)</t>
+          <t>PONTO CRÍTICO: ENTRº MGC-265 (RIO POMBA) - PONTE RIO POMBA</t>
         </is>
       </c>
       <c r="K243" t="inlineStr">
@@ -14672,7 +14672,7 @@
         </is>
       </c>
       <c r="Q243" t="n">
-        <v>4000000</v>
+        <v>470000</v>
       </c>
       <c r="R243" t="n">
         <v>0</v>
@@ -14705,7 +14705,7 @@
       </c>
       <c r="J244" t="inlineStr">
         <is>
-          <t>PONTO CRÍTICO: PALMÓPOLIS - RIO DO PRADO (6 PONTOS)/ PONTE SOBRE O RIBEIRÃO JOSÉ FERREIRA (1 PONTO)</t>
+          <t>PONTO CRÍTICO: ENTRº P/ MARIA DA FÉ - INÍCIO DO PERÍMETRO URBANO DE ITAJUBÁ (2  PONTOS)</t>
         </is>
       </c>
       <c r="K244" t="inlineStr">
@@ -14729,7 +14729,7 @@
         </is>
       </c>
       <c r="Q244" t="n">
-        <v>1000000</v>
+        <v>4000000</v>
       </c>
       <c r="R244" t="n">
         <v>0</v>
@@ -14762,7 +14762,7 @@
       </c>
       <c r="J245" t="inlineStr">
         <is>
-          <t>PONTO CRÍTICO: RODEIRO - ENTRº MG-285</t>
+          <t>PONTO CRÍTICO: PALMÓPOLIS - RIO DO PRADO (6 PONTOS)/ PONTE SOBRE O RIBEIRÃO JOSÉ FERREIRA (1 PONTO)</t>
         </is>
       </c>
       <c r="K245" t="inlineStr">
@@ -14786,7 +14786,7 @@
         </is>
       </c>
       <c r="Q245" t="n">
-        <v>420000</v>
+        <v>1000000</v>
       </c>
       <c r="R245" t="n">
         <v>0</v>
@@ -14819,7 +14819,7 @@
       </c>
       <c r="J246" t="inlineStr">
         <is>
-          <t>PONTO CRÍTICO: SABARÁ-CAETÉ (3 PONTOS)</t>
+          <t>PONTO CRÍTICO: RODEIRO - ENTRº MG-285</t>
         </is>
       </c>
       <c r="K246" t="inlineStr">
@@ -14843,7 +14843,7 @@
         </is>
       </c>
       <c r="Q246" t="n">
-        <v>790000</v>
+        <v>420000</v>
       </c>
       <c r="R246" t="n">
         <v>0</v>
@@ -14851,19 +14851,19 @@
     </row>
     <row r="247">
       <c r="A247" t="n">
-        <v>2311</v>
+        <v>2301</v>
       </c>
       <c r="B247" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="C247" t="n">
-        <v>363</v>
+        <v>782</v>
       </c>
       <c r="D247" t="n">
-        <v>7</v>
+        <v>139</v>
       </c>
       <c r="E247" t="n">
-        <v>4006</v>
+        <v>4280</v>
       </c>
       <c r="F247" t="n">
         <v>1</v>
@@ -14876,39 +14876,31 @@
       </c>
       <c r="J247" t="inlineStr">
         <is>
-          <t>Construção da escola do Brasil Profissionalizado no município de Unaí-MG</t>
+          <t>PONTO CRÍTICO: SABARÁ-CAETÉ (3 PONTOS)</t>
         </is>
       </c>
       <c r="K247" t="inlineStr">
         <is>
-          <t>PARALISADO</t>
-        </is>
-      </c>
-      <c r="L247" t="inlineStr">
-        <is>
-          <t>METRO QUADRADO</t>
-        </is>
-      </c>
-      <c r="M247" t="n">
-        <v>5000</v>
+          <t>INICIANDO</t>
+        </is>
       </c>
       <c r="N247" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="O247" t="inlineStr">
         <is>
-          <t>Região Intermediária de Patos de Minas</t>
+          <t>Estadual</t>
         </is>
       </c>
       <c r="P247" t="inlineStr">
         <is>
-          <t>UNAÍ</t>
+          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
         </is>
       </c>
       <c r="Q247" t="n">
-        <v>5000000</v>
+        <v>790000</v>
       </c>
       <c r="R247" t="n">
         <v>0</v>
@@ -14916,19 +14908,19 @@
     </row>
     <row r="248">
       <c r="A248" t="n">
-        <v>2321</v>
+        <v>2311</v>
       </c>
       <c r="B248" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C248" t="n">
-        <v>302</v>
+        <v>363</v>
       </c>
       <c r="D248" t="n">
-        <v>87</v>
+        <v>7</v>
       </c>
       <c r="E248" t="n">
-        <v>4222</v>
+        <v>4006</v>
       </c>
       <c r="F248" t="n">
         <v>1</v>
@@ -14941,31 +14933,39 @@
       </c>
       <c r="J248" t="inlineStr">
         <is>
-          <t xml:space="preserve">Projetos em unidade diversas </t>
+          <t>Construção da escola do Brasil Profissionalizado no município de Unaí-MG</t>
         </is>
       </c>
       <c r="K248" t="inlineStr">
         <is>
-          <t>EXECUÇÃO</t>
-        </is>
+          <t>PARALISADO</t>
+        </is>
+      </c>
+      <c r="L248" t="inlineStr">
+        <is>
+          <t>METRO QUADRADO</t>
+        </is>
+      </c>
+      <c r="M248" t="n">
+        <v>5000</v>
       </c>
       <c r="N248" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="O248" t="inlineStr">
         <is>
-          <t>Região Intermediária de Belo Horizonte</t>
+          <t>Região Intermediária de Patos de Minas</t>
         </is>
       </c>
       <c r="P248" t="inlineStr">
         <is>
-          <t>BELO HORIZONTE</t>
+          <t>UNAÍ</t>
         </is>
       </c>
       <c r="Q248" t="n">
-        <v>800291</v>
+        <v>5000000</v>
       </c>
       <c r="R248" t="n">
         <v>0</v>
@@ -15018,11 +15018,11 @@
       </c>
       <c r="P249" t="inlineStr">
         <is>
-          <t>BETIM</t>
+          <t>BELO HORIZONTE</t>
         </is>
       </c>
       <c r="Q249" t="n">
-        <v>174673</v>
+        <v>800291</v>
       </c>
       <c r="R249" t="n">
         <v>0</v>
@@ -15053,17 +15053,14 @@
       <c r="H250" t="n">
         <v>249</v>
       </c>
-      <c r="I250" t="n">
-        <v>11877</v>
-      </c>
       <c r="J250" t="inlineStr">
         <is>
-          <t>Contrato a obra de reforma e ampliação</t>
+          <t xml:space="preserve">Projetos em unidade diversas </t>
         </is>
       </c>
       <c r="K250" t="inlineStr">
         <is>
-          <t>INICIANDO</t>
+          <t>EXECUÇÃO</t>
         </is>
       </c>
       <c r="N250" t="inlineStr">
@@ -15073,16 +15070,16 @@
       </c>
       <c r="O250" t="inlineStr">
         <is>
-          <t>Região Intermediária de Barbacena</t>
+          <t>Região Intermediária de Belo Horizonte</t>
         </is>
       </c>
       <c r="P250" t="inlineStr">
         <is>
-          <t>SÃO JOÃO DEL REI</t>
+          <t>BETIM</t>
         </is>
       </c>
       <c r="Q250" t="n">
-        <v>1088908</v>
+        <v>174673</v>
       </c>
       <c r="R250" t="n">
         <v>0</v>
@@ -15090,19 +15087,19 @@
     </row>
     <row r="251">
       <c r="A251" t="n">
-        <v>2361</v>
+        <v>2321</v>
       </c>
       <c r="B251" t="n">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="C251" t="n">
-        <v>846</v>
+        <v>302</v>
       </c>
       <c r="D251" t="n">
-        <v>705</v>
+        <v>87</v>
       </c>
       <c r="E251" t="n">
-        <v>7004</v>
+        <v>4222</v>
       </c>
       <c r="F251" t="n">
         <v>1</v>
@@ -15113,9 +15110,12 @@
       <c r="H251" t="n">
         <v>250</v>
       </c>
+      <c r="I251" t="n">
+        <v>11877</v>
+      </c>
       <c r="J251" t="inlineStr">
         <is>
-          <t>Possível adequação da sede</t>
+          <t>Contrato a obra de reforma e ampliação</t>
         </is>
       </c>
       <c r="K251" t="inlineStr">
@@ -15127,6 +15127,22 @@
         <is>
           <t>Não</t>
         </is>
+      </c>
+      <c r="O251" t="inlineStr">
+        <is>
+          <t>Região Intermediária de Barbacena</t>
+        </is>
+      </c>
+      <c r="P251" t="inlineStr">
+        <is>
+          <t>SÃO JOÃO DEL REI</t>
+        </is>
+      </c>
+      <c r="Q251" t="n">
+        <v>1088908</v>
+      </c>
+      <c r="R251" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="252">
@@ -15134,16 +15150,16 @@
         <v>2361</v>
       </c>
       <c r="B252" t="n">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="C252" t="n">
-        <v>274</v>
+        <v>846</v>
       </c>
       <c r="D252" t="n">
-        <v>766</v>
+        <v>705</v>
       </c>
       <c r="E252" t="n">
-        <v>2113</v>
+        <v>7004</v>
       </c>
       <c r="F252" t="n">
         <v>1</v>
@@ -15181,10 +15197,10 @@
         <v>274</v>
       </c>
       <c r="D253" t="n">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="E253" t="n">
-        <v>2114</v>
+        <v>2113</v>
       </c>
       <c r="F253" t="n">
         <v>1</v>
@@ -15197,7 +15213,7 @@
       </c>
       <c r="J253" t="inlineStr">
         <is>
-          <t>Possível obras de adequação da sede.</t>
+          <t>Possível adequação da sede</t>
         </is>
       </c>
       <c r="K253" t="inlineStr">
@@ -15209,39 +15225,23 @@
         <is>
           <t>Não</t>
         </is>
-      </c>
-      <c r="O253" t="inlineStr">
-        <is>
-          <t>Região Intermediária de Belo Horizonte</t>
-        </is>
-      </c>
-      <c r="P253" t="inlineStr">
-        <is>
-          <t>BELO HORIZONTE</t>
-        </is>
-      </c>
-      <c r="Q253" t="n">
-        <v>0</v>
-      </c>
-      <c r="R253" t="n">
-        <v>2754406</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="n">
-        <v>2371</v>
+        <v>2361</v>
       </c>
       <c r="B254" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="C254" t="n">
-        <v>609</v>
+        <v>274</v>
       </c>
       <c r="D254" t="n">
-        <v>78</v>
+        <v>767</v>
       </c>
       <c r="E254" t="n">
-        <v>4238</v>
+        <v>2114</v>
       </c>
       <c r="F254" t="n">
         <v>1</v>
@@ -15254,7 +15254,7 @@
       </c>
       <c r="J254" t="inlineStr">
         <is>
-          <t>Reestruturação física e ampliação do Laboratório de Química Agropecuária do Instituto Mineiro de Agropecuária - IMA</t>
+          <t>Possível obras de adequação da sede.</t>
         </is>
       </c>
       <c r="K254" t="inlineStr">
@@ -15278,27 +15278,27 @@
         </is>
       </c>
       <c r="Q254" t="n">
-        <v>8311374</v>
+        <v>0</v>
       </c>
       <c r="R254" t="n">
-        <v>0</v>
+        <v>2754406</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="n">
-        <v>2421</v>
+        <v>2371</v>
       </c>
       <c r="B255" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="C255" t="n">
-        <v>544</v>
+        <v>609</v>
       </c>
       <c r="D255" t="n">
-        <v>101</v>
+        <v>78</v>
       </c>
       <c r="E255" t="n">
-        <v>1016</v>
+        <v>4238</v>
       </c>
       <c r="F255" t="n">
         <v>1</v>
@@ -15311,7 +15311,7 @@
       </c>
       <c r="J255" t="inlineStr">
         <is>
-          <t>Perfuração de Sistemas de Abastecimento de Agua conforme demanda dos municípios atendidos pelo IDENE</t>
+          <t>Reestruturação física e ampliação do Laboratório de Química Agropecuária do Instituto Mineiro de Agropecuária - IMA</t>
         </is>
       </c>
       <c r="K255" t="inlineStr">
@@ -15326,16 +15326,16 @@
       </c>
       <c r="O255" t="inlineStr">
         <is>
-          <t>Região Intermediária de Montes Claros</t>
+          <t>Região Intermediária de Belo Horizonte</t>
         </is>
       </c>
       <c r="P255" t="inlineStr">
         <is>
-          <t>MONTES CLAROS</t>
+          <t>BELO HORIZONTE</t>
         </is>
       </c>
       <c r="Q255" t="n">
-        <v>477508</v>
+        <v>8311374</v>
       </c>
       <c r="R255" t="n">
         <v>0</v>
@@ -15343,19 +15343,19 @@
     </row>
     <row r="256">
       <c r="A256" t="n">
-        <v>3051</v>
+        <v>2421</v>
       </c>
       <c r="B256" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C256" t="n">
-        <v>364</v>
+        <v>544</v>
       </c>
       <c r="D256" t="n">
-        <v>15</v>
+        <v>101</v>
       </c>
       <c r="E256" t="n">
-        <v>4016</v>
+        <v>1016</v>
       </c>
       <c r="F256" t="n">
         <v>1</v>
@@ -15368,7 +15368,7 @@
       </c>
       <c r="J256" t="inlineStr">
         <is>
-          <t>Instalações do curso de Agropecuária de Precisão, com 1.070 m² de área total, além de 5 unidades de tratamento de águas residuárias.</t>
+          <t>Perfuração de Sistemas de Abastecimento de Agua conforme demanda dos municípios atendidos pelo IDENE</t>
         </is>
       </c>
       <c r="K256" t="inlineStr">
@@ -15383,16 +15383,16 @@
       </c>
       <c r="O256" t="inlineStr">
         <is>
-          <t>Estadual</t>
+          <t>Região Intermediária de Montes Claros</t>
         </is>
       </c>
       <c r="P256" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
+          <t>MONTES CLAROS</t>
         </is>
       </c>
       <c r="Q256" t="n">
-        <v>4825656</v>
+        <v>477508</v>
       </c>
       <c r="R256" t="n">
         <v>0</v>
@@ -15425,7 +15425,7 @@
       </c>
       <c r="J257" t="inlineStr">
         <is>
-          <t>Construção de novas instalações no Instituto Tecnológico de Agropecuária de Pitangui - ITAP, totalizando 3.214 m², para salas de aula, plantas-piloto de produção e laboratórios de apoio.</t>
+          <t>Instalações do curso de Agropecuária de Precisão, com 1.070 m² de área total, além de 5 unidades de tratamento de águas residuárias.</t>
         </is>
       </c>
       <c r="K257" t="inlineStr">
@@ -15449,7 +15449,7 @@
         </is>
       </c>
       <c r="Q257" t="n">
-        <v>12649000</v>
+        <v>4825656</v>
       </c>
       <c r="R257" t="n">
         <v>0</v>
@@ -15482,7 +15482,7 @@
       </c>
       <c r="J258" t="inlineStr">
         <is>
-          <t xml:space="preserve">Reforma do edifício histórico do Instituto de Laticínios Cândido Tostes, localizado no município dde juiz de Fora. </t>
+          <t>Construção de novas instalações no Instituto Tecnológico de Agropecuária de Pitangui - ITAP, totalizando 3.214 m², para salas de aula, plantas-piloto de produção e laboratórios de apoio.</t>
         </is>
       </c>
       <c r="K258" t="inlineStr">
@@ -15506,7 +15506,7 @@
         </is>
       </c>
       <c r="Q258" t="n">
-        <v>3715000</v>
+        <v>12649000</v>
       </c>
       <c r="R258" t="n">
         <v>0</v>
@@ -15517,16 +15517,16 @@
         <v>3051</v>
       </c>
       <c r="B259" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="C259" t="n">
-        <v>571</v>
+        <v>364</v>
       </c>
       <c r="D259" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E259" t="n">
-        <v>4018</v>
+        <v>4016</v>
       </c>
       <c r="F259" t="n">
         <v>1</v>
@@ -15539,7 +15539,7 @@
       </c>
       <c r="J259" t="inlineStr">
         <is>
-          <t>Melhoria na infraestrutura das unidades de pesquisa.</t>
+          <t xml:space="preserve">Reforma do edifício histórico do Instituto de Laticínios Cândido Tostes, localizado no município dde juiz de Fora. </t>
         </is>
       </c>
       <c r="K259" t="inlineStr">
@@ -15563,27 +15563,27 @@
         </is>
       </c>
       <c r="Q259" t="n">
-        <v>0</v>
+        <v>3715000</v>
       </c>
       <c r="R259" t="n">
-        <v>250000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="n">
-        <v>4031</v>
+        <v>3051</v>
       </c>
       <c r="B260" t="n">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="C260" t="n">
-        <v>61</v>
+        <v>571</v>
       </c>
       <c r="D260" t="n">
-        <v>706</v>
+        <v>16</v>
       </c>
       <c r="E260" t="n">
-        <v>2091</v>
+        <v>4018</v>
       </c>
       <c r="F260" t="n">
         <v>1</v>
@@ -15594,47 +15594,36 @@
       <c r="H260" t="n">
         <v>259</v>
       </c>
-      <c r="I260" t="n">
-        <v>12054</v>
-      </c>
       <c r="J260" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Construção do novo prédio do Fórum da Comarca de Betim/MG</t>
+          <t>Melhoria na infraestrutura das unidades de pesquisa.</t>
         </is>
       </c>
       <c r="K260" t="inlineStr">
         <is>
-          <t>EXECUÇÃO</t>
-        </is>
-      </c>
-      <c r="L260" t="inlineStr">
-        <is>
-          <t>UNIDADE</t>
-        </is>
-      </c>
-      <c r="M260" t="n">
-        <v>1</v>
+          <t>INICIANDO</t>
+        </is>
       </c>
       <c r="N260" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="O260" t="inlineStr">
         <is>
-          <t>Região Intermediária de Belo Horizonte</t>
+          <t>Estadual</t>
         </is>
       </c>
       <c r="P260" t="inlineStr">
         <is>
-          <t>BETIM</t>
+          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
         </is>
       </c>
       <c r="Q260" t="n">
         <v>0</v>
       </c>
       <c r="R260" t="n">
-        <v>11016496</v>
+        <v>250000</v>
       </c>
     </row>
     <row r="261">
@@ -15663,11 +15652,11 @@
         <v>260</v>
       </c>
       <c r="I261" t="n">
-        <v>12806</v>
+        <v>12054</v>
       </c>
       <c r="J261" t="inlineStr">
         <is>
-          <t>Campo Belo/MG - Construção do novo Fórum da Comarca de Campo Belo</t>
+          <t xml:space="preserve"> Construção do novo prédio do Fórum da Comarca de Betim/MG</t>
         </is>
       </c>
       <c r="K261" t="inlineStr">
@@ -15690,19 +15679,19 @@
       </c>
       <c r="O261" t="inlineStr">
         <is>
-          <t>Região Intermediária de Varginha</t>
+          <t>Região Intermediária de Belo Horizonte</t>
         </is>
       </c>
       <c r="P261" t="inlineStr">
         <is>
-          <t>CAMPO BELO</t>
+          <t>BETIM</t>
         </is>
       </c>
       <c r="Q261" t="n">
         <v>0</v>
       </c>
       <c r="R261" t="n">
-        <v>19994210</v>
+        <v>11016496</v>
       </c>
     </row>
     <row r="262">
@@ -15731,11 +15720,11 @@
         <v>261</v>
       </c>
       <c r="I262" t="n">
-        <v>12638</v>
+        <v>12806</v>
       </c>
       <c r="J262" t="inlineStr">
         <is>
-          <t>Obra de construção do novo Fórum da Comarca de Carangola.</t>
+          <t>Campo Belo/MG - Construção do novo Fórum da Comarca de Campo Belo</t>
         </is>
       </c>
       <c r="K262" t="inlineStr">
@@ -15758,19 +15747,19 @@
       </c>
       <c r="O262" t="inlineStr">
         <is>
-          <t>Região Intermediária de Juíz de Fora</t>
+          <t>Região Intermediária de Varginha</t>
         </is>
       </c>
       <c r="P262" t="inlineStr">
         <is>
-          <t>CARANGOLA</t>
+          <t>CAMPO BELO</t>
         </is>
       </c>
       <c r="Q262" t="n">
         <v>0</v>
       </c>
       <c r="R262" t="n">
-        <v>12843388</v>
+        <v>19994210</v>
       </c>
     </row>
     <row r="263">
@@ -15799,11 +15788,11 @@
         <v>262</v>
       </c>
       <c r="I263" t="n">
-        <v>12400</v>
+        <v>12638</v>
       </c>
       <c r="J263" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Contrato a execução da obra de reforma e ampliação do Fórum da Comarca de Ipatinga/MG</t>
+          <t>Obra de construção do novo Fórum da Comarca de Carangola.</t>
         </is>
       </c>
       <c r="K263" t="inlineStr">
@@ -15826,19 +15815,19 @@
       </c>
       <c r="O263" t="inlineStr">
         <is>
-          <t>Região Intermediária de Ipatinga</t>
+          <t>Região Intermediária de Juíz de Fora</t>
         </is>
       </c>
       <c r="P263" t="inlineStr">
         <is>
-          <t>IPATINGA</t>
+          <t>CARANGOLA</t>
         </is>
       </c>
       <c r="Q263" t="n">
         <v>0</v>
       </c>
       <c r="R263" t="n">
-        <v>18849069</v>
+        <v>12843388</v>
       </c>
     </row>
     <row r="264">
@@ -15867,11 +15856,11 @@
         <v>263</v>
       </c>
       <c r="I264" t="n">
-        <v>12288</v>
+        <v>12400</v>
       </c>
       <c r="J264" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Reforma e Ampliação do Fórum da Comarca de Monte Belo/MG</t>
+          <t xml:space="preserve"> Contrato a execução da obra de reforma e ampliação do Fórum da Comarca de Ipatinga/MG</t>
         </is>
       </c>
       <c r="K264" t="inlineStr">
@@ -15894,19 +15883,19 @@
       </c>
       <c r="O264" t="inlineStr">
         <is>
-          <t>Região Intermediária de Varginha</t>
+          <t>Região Intermediária de Ipatinga</t>
         </is>
       </c>
       <c r="P264" t="inlineStr">
         <is>
-          <t>MONTE BELO</t>
+          <t>IPATINGA</t>
         </is>
       </c>
       <c r="Q264" t="n">
         <v>0</v>
       </c>
       <c r="R264" t="n">
-        <v>1950000</v>
+        <v>18849069</v>
       </c>
     </row>
     <row r="265">
@@ -15935,11 +15924,11 @@
         <v>264</v>
       </c>
       <c r="I265" t="n">
-        <v>12816</v>
+        <v>12288</v>
       </c>
       <c r="J265" t="inlineStr">
         <is>
-          <t>Obra de construção do novo Fórum da Comarca de Pirapora/MG</t>
+          <t xml:space="preserve"> Reforma e Ampliação do Fórum da Comarca de Monte Belo/MG</t>
         </is>
       </c>
       <c r="K265" t="inlineStr">
@@ -15962,19 +15951,19 @@
       </c>
       <c r="O265" t="inlineStr">
         <is>
-          <t>Região Intermediária de Montes Claros</t>
+          <t>Região Intermediária de Varginha</t>
         </is>
       </c>
       <c r="P265" t="inlineStr">
         <is>
-          <t>PIRAPORA</t>
+          <t>MONTE BELO</t>
         </is>
       </c>
       <c r="Q265" t="n">
         <v>0</v>
       </c>
       <c r="R265" t="n">
-        <v>22776109</v>
+        <v>1950000</v>
       </c>
     </row>
     <row r="266">
@@ -16003,11 +15992,11 @@
         <v>265</v>
       </c>
       <c r="I266" t="n">
-        <v>12781</v>
+        <v>12816</v>
       </c>
       <c r="J266" t="inlineStr">
         <is>
-          <t>Construção do novo fórum da Comarca de São Gonçalo do Sapucaí/MG</t>
+          <t>Obra de construção do novo Fórum da Comarca de Pirapora/MG</t>
         </is>
       </c>
       <c r="K266" t="inlineStr">
@@ -16030,19 +16019,19 @@
       </c>
       <c r="O266" t="inlineStr">
         <is>
-          <t>Região Intermediária de Varginha</t>
+          <t>Região Intermediária de Montes Claros</t>
         </is>
       </c>
       <c r="P266" t="inlineStr">
         <is>
-          <t>SÃO GONÇALO DO SAPUCAÍ</t>
+          <t>PIRAPORA</t>
         </is>
       </c>
       <c r="Q266" t="n">
         <v>0</v>
       </c>
       <c r="R266" t="n">
-        <v>14670005</v>
+        <v>22776109</v>
       </c>
     </row>
     <row r="267">
@@ -16071,11 +16060,11 @@
         <v>266</v>
       </c>
       <c r="I267" t="n">
-        <v>12799</v>
+        <v>12781</v>
       </c>
       <c r="J267" t="inlineStr">
         <is>
-          <t xml:space="preserve">Construção do novo Fórum da Comarca de Timóteo/MG </t>
+          <t>Construção do novo fórum da Comarca de São Gonçalo do Sapucaí/MG</t>
         </is>
       </c>
       <c r="K267" t="inlineStr">
@@ -16098,19 +16087,19 @@
       </c>
       <c r="O267" t="inlineStr">
         <is>
-          <t>Região Intermediária de Ipatinga</t>
+          <t>Região Intermediária de Varginha</t>
         </is>
       </c>
       <c r="P267" t="inlineStr">
         <is>
-          <t>TIMÓTEO</t>
+          <t>SÃO GONÇALO DO SAPUCAÍ</t>
         </is>
       </c>
       <c r="Q267" t="n">
         <v>0</v>
       </c>
       <c r="R267" t="n">
-        <v>19506288</v>
+        <v>14670005</v>
       </c>
     </row>
     <row r="268">
@@ -16139,16 +16128,16 @@
         <v>267</v>
       </c>
       <c r="I268" t="n">
-        <v>12833</v>
+        <v>12799</v>
       </c>
       <c r="J268" t="inlineStr">
         <is>
-          <t>Obra de construção do novo Fórum da Comarca de Rio Novo.</t>
+          <t xml:space="preserve">Construção do novo Fórum da Comarca de Timóteo/MG </t>
         </is>
       </c>
       <c r="K268" t="inlineStr">
         <is>
-          <t>INICIANDO</t>
+          <t>EXECUÇÃO</t>
         </is>
       </c>
       <c r="L268" t="inlineStr">
@@ -16166,19 +16155,19 @@
       </c>
       <c r="O268" t="inlineStr">
         <is>
-          <t>Região Intermediária de Juíz de Fora</t>
+          <t>Região Intermediária de Ipatinga</t>
         </is>
       </c>
       <c r="P268" t="inlineStr">
         <is>
-          <t>RIO NOVO</t>
+          <t>TIMÓTEO</t>
         </is>
       </c>
       <c r="Q268" t="n">
         <v>0</v>
       </c>
       <c r="R268" t="n">
-        <v>4976096</v>
+        <v>19506288</v>
       </c>
     </row>
     <row r="269">
@@ -16207,11 +16196,11 @@
         <v>268</v>
       </c>
       <c r="I269" t="n">
-        <v>12629</v>
+        <v>12833</v>
       </c>
       <c r="J269" t="inlineStr">
         <is>
-          <t>Obra de construção do novo Fórum da Comarca de Luz.</t>
+          <t>Obra de construção do novo Fórum da Comarca de Rio Novo.</t>
         </is>
       </c>
       <c r="K269" t="inlineStr">
@@ -16234,19 +16223,19 @@
       </c>
       <c r="O269" t="inlineStr">
         <is>
-          <t>Região Intermediária de Divinópolis</t>
+          <t>Região Intermediária de Juíz de Fora</t>
         </is>
       </c>
       <c r="P269" t="inlineStr">
         <is>
-          <t>LUZ</t>
+          <t>RIO NOVO</t>
         </is>
       </c>
       <c r="Q269" t="n">
         <v>0</v>
       </c>
       <c r="R269" t="n">
-        <v>7654409</v>
+        <v>4976096</v>
       </c>
     </row>
     <row r="270">
@@ -16275,16 +16264,16 @@
         <v>269</v>
       </c>
       <c r="I270" t="n">
-        <v>12607</v>
+        <v>12629</v>
       </c>
       <c r="J270" t="inlineStr">
         <is>
-          <t>Reforma e ampliação do Fórum da Comarca de Sete Lagoas/MG.</t>
+          <t>Obra de construção do novo Fórum da Comarca de Luz.</t>
         </is>
       </c>
       <c r="K270" t="inlineStr">
         <is>
-          <t>EXECUÇÃO</t>
+          <t>INICIANDO</t>
         </is>
       </c>
       <c r="L270" t="inlineStr">
@@ -16302,19 +16291,19 @@
       </c>
       <c r="O270" t="inlineStr">
         <is>
-          <t>Região Intermediária de Belo Horizonte</t>
+          <t>Região Intermediária de Divinópolis</t>
         </is>
       </c>
       <c r="P270" t="inlineStr">
         <is>
-          <t>SETE LAGOAS</t>
+          <t>LUZ</t>
         </is>
       </c>
       <c r="Q270" t="n">
         <v>0</v>
       </c>
       <c r="R270" t="n">
-        <v>32235085</v>
+        <v>7654409</v>
       </c>
     </row>
     <row r="271">
@@ -16343,11 +16332,11 @@
         <v>270</v>
       </c>
       <c r="I271" t="n">
-        <v>12639</v>
+        <v>12607</v>
       </c>
       <c r="J271" t="inlineStr">
         <is>
-          <t>Obra de construção do novo Fórum da Comarca de Três Pontas</t>
+          <t>Reforma e ampliação do Fórum da Comarca de Sete Lagoas/MG.</t>
         </is>
       </c>
       <c r="K271" t="inlineStr">
@@ -16370,19 +16359,19 @@
       </c>
       <c r="O271" t="inlineStr">
         <is>
-          <t>Região Intermediária de Varginha</t>
+          <t>Região Intermediária de Belo Horizonte</t>
         </is>
       </c>
       <c r="P271" t="inlineStr">
         <is>
-          <t>TRÊS PONTAS</t>
+          <t>SETE LAGOAS</t>
         </is>
       </c>
       <c r="Q271" t="n">
         <v>0</v>
       </c>
       <c r="R271" t="n">
-        <v>9489687</v>
+        <v>32235085</v>
       </c>
     </row>
     <row r="272">
@@ -16411,16 +16400,16 @@
         <v>271</v>
       </c>
       <c r="I272" t="n">
-        <v>11547</v>
+        <v>12639</v>
       </c>
       <c r="J272" t="inlineStr">
         <is>
-          <t>RETOMADA DA OBRA DE CONSTRUÇÃO DO NOVO PRÉDIO DO FÓRUM DA COMARCA DE ITAJUBÁ/MG</t>
+          <t>Obra de construção do novo Fórum da Comarca de Três Pontas</t>
         </is>
       </c>
       <c r="K272" t="inlineStr">
         <is>
-          <t>INICIANDO</t>
+          <t>EXECUÇÃO</t>
         </is>
       </c>
       <c r="L272" t="inlineStr">
@@ -16438,19 +16427,19 @@
       </c>
       <c r="O272" t="inlineStr">
         <is>
-          <t>Região Intermediária de Pouso Alegre</t>
+          <t>Região Intermediária de Varginha</t>
         </is>
       </c>
       <c r="P272" t="inlineStr">
         <is>
-          <t>ITAJUBÁ</t>
+          <t>TRÊS PONTAS</t>
         </is>
       </c>
       <c r="Q272" t="n">
         <v>0</v>
       </c>
       <c r="R272" t="n">
-        <v>9366263</v>
+        <v>9489687</v>
       </c>
     </row>
     <row r="273">
@@ -16479,11 +16468,11 @@
         <v>272</v>
       </c>
       <c r="I273" t="n">
-        <v>12856</v>
+        <v>11547</v>
       </c>
       <c r="J273" t="inlineStr">
         <is>
-          <t>Retomada da obra de construção do novo Fórum da Comarca de Poços de Caldas.</t>
+          <t>RETOMADA DA OBRA DE CONSTRUÇÃO DO NOVO PRÉDIO DO FÓRUM DA COMARCA DE ITAJUBÁ/MG</t>
         </is>
       </c>
       <c r="K273" t="inlineStr">
@@ -16511,14 +16500,14 @@
       </c>
       <c r="P273" t="inlineStr">
         <is>
-          <t>POÇOS DE CALDAS</t>
+          <t>ITAJUBÁ</t>
         </is>
       </c>
       <c r="Q273" t="n">
         <v>0</v>
       </c>
       <c r="R273" t="n">
-        <v>11009635</v>
+        <v>9366263</v>
       </c>
     </row>
     <row r="274">
@@ -16547,11 +16536,11 @@
         <v>273</v>
       </c>
       <c r="I274" t="n">
-        <v>12344</v>
+        <v>12856</v>
       </c>
       <c r="J274" t="inlineStr">
         <is>
-          <t>Construção do novo prédio do Fórum da Comarca de Camanducaia/MG</t>
+          <t>Retomada da obra de construção do novo Fórum da Comarca de Poços de Caldas.</t>
         </is>
       </c>
       <c r="K274" t="inlineStr">
@@ -16579,14 +16568,14 @@
       </c>
       <c r="P274" t="inlineStr">
         <is>
-          <t>CAMANDUCAIA</t>
+          <t>POÇOS DE CALDAS</t>
         </is>
       </c>
       <c r="Q274" t="n">
         <v>0</v>
       </c>
       <c r="R274" t="n">
-        <v>4627222</v>
+        <v>11009635</v>
       </c>
     </row>
     <row r="275">
@@ -16614,9 +16603,12 @@
       <c r="H275" t="n">
         <v>274</v>
       </c>
+      <c r="I275" t="n">
+        <v>12344</v>
+      </c>
       <c r="J275" t="inlineStr">
         <is>
-          <t>Obra de construção do novo Fórum da Comarca de São João do Paraíso</t>
+          <t>Construção do novo prédio do Fórum da Comarca de Camanducaia/MG</t>
         </is>
       </c>
       <c r="K275" t="inlineStr">
@@ -16639,19 +16631,19 @@
       </c>
       <c r="O275" t="inlineStr">
         <is>
-          <t>Região Intermediária de Montes Claros</t>
+          <t>Região Intermediária de Pouso Alegre</t>
         </is>
       </c>
       <c r="P275" t="inlineStr">
         <is>
-          <t>SÃO JOÃO DO PARAÍSO</t>
+          <t>CAMANDUCAIA</t>
         </is>
       </c>
       <c r="Q275" t="n">
         <v>0</v>
       </c>
       <c r="R275" t="n">
-        <v>7290196</v>
+        <v>4627222</v>
       </c>
     </row>
     <row r="276">
@@ -16681,7 +16673,7 @@
       </c>
       <c r="J276" t="inlineStr">
         <is>
-          <t>Implantação do Fórum Digital no município de Brasilândia de Minas</t>
+          <t>Obra de construção do novo Fórum da Comarca de São João do Paraíso</t>
         </is>
       </c>
       <c r="K276" t="inlineStr">
@@ -16704,19 +16696,19 @@
       </c>
       <c r="O276" t="inlineStr">
         <is>
-          <t>Região Intermediária de Patos de Minas</t>
+          <t>Região Intermediária de Montes Claros</t>
         </is>
       </c>
       <c r="P276" t="inlineStr">
         <is>
-          <t>BRASILÂNDIA DE MINAS</t>
+          <t>SÃO JOÃO DO PARAÍSO</t>
         </is>
       </c>
       <c r="Q276" t="n">
         <v>0</v>
       </c>
       <c r="R276" t="n">
-        <v>1373680</v>
+        <v>7290196</v>
       </c>
     </row>
     <row r="277">
@@ -16746,7 +16738,7 @@
       </c>
       <c r="J277" t="inlineStr">
         <is>
-          <t>Implantação do Fórum Digital no município de São Gonçalo do Abaeté</t>
+          <t>Implantação do Fórum Digital no município de Brasilândia de Minas</t>
         </is>
       </c>
       <c r="K277" t="inlineStr">
@@ -16774,7 +16766,7 @@
       </c>
       <c r="P277" t="inlineStr">
         <is>
-          <t>SÃO GONÇALO DO ABAETÉ</t>
+          <t>BRASILÂNDIA DE MINAS</t>
         </is>
       </c>
       <c r="Q277" t="n">
@@ -16811,7 +16803,7 @@
       </c>
       <c r="J278" t="inlineStr">
         <is>
-          <t>Implantação do Fórum Digital no município de Ponto Chique</t>
+          <t>Implantação do Fórum Digital no município de São Gonçalo do Abaeté</t>
         </is>
       </c>
       <c r="K278" t="inlineStr">
@@ -16834,19 +16826,19 @@
       </c>
       <c r="O278" t="inlineStr">
         <is>
-          <t>Região Intermediária de Montes Claros</t>
+          <t>Região Intermediária de Patos de Minas</t>
         </is>
       </c>
       <c r="P278" t="inlineStr">
         <is>
-          <t>PONTO CHIQUE</t>
+          <t>SÃO GONÇALO DO ABAETÉ</t>
         </is>
       </c>
       <c r="Q278" t="n">
         <v>0</v>
       </c>
       <c r="R278" t="n">
-        <v>1760000</v>
+        <v>1373680</v>
       </c>
     </row>
     <row r="279">
@@ -16874,17 +16866,14 @@
       <c r="H279" t="n">
         <v>278</v>
       </c>
-      <c r="I279" t="n">
-        <v>12627</v>
-      </c>
       <c r="J279" t="inlineStr">
         <is>
-          <t>Execução da 4ª (quarta) parcela da reforma parcial do Edifício-Sede do TRIBUNAL.</t>
+          <t>Implantação do Fórum Digital no município de Ponto Chique</t>
         </is>
       </c>
       <c r="K279" t="inlineStr">
         <is>
-          <t>EXECUÇÃO</t>
+          <t>INICIANDO</t>
         </is>
       </c>
       <c r="L279" t="inlineStr">
@@ -16902,19 +16891,19 @@
       </c>
       <c r="O279" t="inlineStr">
         <is>
-          <t>Região Intermediária de Belo Horizonte</t>
+          <t>Região Intermediária de Montes Claros</t>
         </is>
       </c>
       <c r="P279" t="inlineStr">
         <is>
-          <t>BELO HORIZONTE</t>
+          <t>PONTO CHIQUE</t>
         </is>
       </c>
       <c r="Q279" t="n">
         <v>0</v>
       </c>
       <c r="R279" t="n">
-        <v>38084213</v>
+        <v>1760000</v>
       </c>
     </row>
     <row r="280">
@@ -16943,11 +16932,11 @@
         <v>279</v>
       </c>
       <c r="I280" t="n">
-        <v>12146</v>
+        <v>12627</v>
       </c>
       <c r="J280" t="inlineStr">
         <is>
-          <t>Reforma geral do Fórum Lafayette, em Belo Horizonte/MG</t>
+          <t>Execução da 4ª (quarta) parcela da reforma parcial do Edifício-Sede do TRIBUNAL.</t>
         </is>
       </c>
       <c r="K280" t="inlineStr">
@@ -16982,7 +16971,7 @@
         <v>0</v>
       </c>
       <c r="R280" t="n">
-        <v>135013067</v>
+        <v>38084213</v>
       </c>
     </row>
     <row r="281">
@@ -17011,11 +17000,11 @@
         <v>280</v>
       </c>
       <c r="I281" t="n">
-        <v>12703</v>
+        <v>12146</v>
       </c>
       <c r="J281" t="inlineStr">
         <is>
-          <t>Cincão - Reforma parcial para adequações da estrutura física dos Armazéns 6, 7 e 8, Galpão 2, Arquivo Central e Permanente</t>
+          <t>Reforma geral do Fórum Lafayette, em Belo Horizonte/MG</t>
         </is>
       </c>
       <c r="K281" t="inlineStr">
@@ -17050,7 +17039,7 @@
         <v>0</v>
       </c>
       <c r="R281" t="n">
-        <v>1052449</v>
+        <v>135013067</v>
       </c>
     </row>
     <row r="282">
@@ -17078,14 +17067,17 @@
       <c r="H282" t="n">
         <v>281</v>
       </c>
+      <c r="I282" t="n">
+        <v>12703</v>
+      </c>
       <c r="J282" t="inlineStr">
         <is>
-          <t>Obra de construção do novo Fórum da Comarca de Monte Alegre de Minas</t>
+          <t>Cincão - Reforma parcial para adequações da estrutura física dos Armazéns 6, 7 e 8, Galpão 2, Arquivo Central e Permanente</t>
         </is>
       </c>
       <c r="K282" t="inlineStr">
         <is>
-          <t>INICIANDO</t>
+          <t>EXECUÇÃO</t>
         </is>
       </c>
       <c r="L282" t="inlineStr">
@@ -17103,36 +17095,36 @@
       </c>
       <c r="O282" t="inlineStr">
         <is>
-          <t>Região Intermediária de Uberlândia</t>
+          <t>Região Intermediária de Belo Horizonte</t>
         </is>
       </c>
       <c r="P282" t="inlineStr">
         <is>
-          <t>MONTE ALEGRE DE MINAS</t>
+          <t>BELO HORIZONTE</t>
         </is>
       </c>
       <c r="Q282" t="n">
         <v>0</v>
       </c>
       <c r="R282" t="n">
-        <v>6139672</v>
+        <v>1052449</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="n">
-        <v>5011</v>
+        <v>4031</v>
       </c>
       <c r="B283" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C283" t="n">
-        <v>122</v>
+        <v>61</v>
       </c>
       <c r="D283" t="n">
-        <v>133</v>
+        <v>706</v>
       </c>
       <c r="E283" t="n">
-        <v>3017</v>
+        <v>2091</v>
       </c>
       <c r="F283" t="n">
         <v>1</v>
@@ -17145,7 +17137,7 @@
       </c>
       <c r="J283" t="inlineStr">
         <is>
-          <t>CENTRO DE CULTURA PRESIDENTE ITAMAR FRANCO</t>
+          <t>Obra de construção do novo Fórum da Comarca de Monte Alegre de Minas</t>
         </is>
       </c>
       <c r="K283" t="inlineStr">
@@ -17153,43 +17145,51 @@
           <t>INICIANDO</t>
         </is>
       </c>
+      <c r="L283" t="inlineStr">
+        <is>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="M283" t="n">
+        <v>1</v>
+      </c>
       <c r="N283" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="O283" t="inlineStr">
         <is>
-          <t>Estadual</t>
+          <t>Região Intermediária de Uberlândia</t>
         </is>
       </c>
       <c r="P283" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
+          <t>MONTE ALEGRE DE MINAS</t>
         </is>
       </c>
       <c r="Q283" t="n">
         <v>0</v>
       </c>
       <c r="R283" t="n">
-        <v>800000</v>
+        <v>6139672</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="n">
-        <v>5031</v>
+        <v>5011</v>
       </c>
       <c r="B284" t="n">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="C284" t="n">
-        <v>572</v>
+        <v>122</v>
       </c>
       <c r="D284" t="n">
         <v>133</v>
       </c>
       <c r="E284" t="n">
-        <v>3015</v>
+        <v>3017</v>
       </c>
       <c r="F284" t="n">
         <v>1</v>
@@ -17202,7 +17202,7 @@
       </c>
       <c r="J284" t="inlineStr">
         <is>
-          <t>BALNEÁRIO ÁGUAS SANTAS - TIRADENTES/MG | BARREIO DE ARAXÁ</t>
+          <t>CENTRO DE CULTURA PRESIDENTE ITAMAR FRANCO</t>
         </is>
       </c>
       <c r="K284" t="inlineStr">
@@ -17229,24 +17229,24 @@
         <v>0</v>
       </c>
       <c r="R284" t="n">
-        <v>4782988</v>
+        <v>800000</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="n">
-        <v>5141</v>
+        <v>5031</v>
       </c>
       <c r="B285" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="C285" t="n">
-        <v>126</v>
+        <v>572</v>
       </c>
       <c r="D285" t="n">
-        <v>30</v>
+        <v>133</v>
       </c>
       <c r="E285" t="n">
-        <v>6006</v>
+        <v>3015</v>
       </c>
       <c r="F285" t="n">
         <v>1</v>
@@ -17259,7 +17259,7 @@
       </c>
       <c r="J285" t="inlineStr">
         <is>
-          <t>ELABORAÇÃO E EXECUÇÃO DE PROJETOS RELACIONADOS À REFORMA, MODERNIZAÇÃO E ADEQUAÇÃO DAS INSTALAÇÕES PREDIAIS DA COMPANHIA.</t>
+          <t>BALNEÁRIO ÁGUAS SANTAS - TIRADENTES/MG | BARREIO DE ARAXÁ</t>
         </is>
       </c>
       <c r="K285" t="inlineStr">
@@ -17286,24 +17286,24 @@
         <v>0</v>
       </c>
       <c r="R285" t="n">
-        <v>16317109</v>
+        <v>4782988</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="n">
-        <v>5251</v>
+        <v>5141</v>
       </c>
       <c r="B286" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="C286" t="n">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="D286" t="n">
-        <v>133</v>
+        <v>30</v>
       </c>
       <c r="E286" t="n">
-        <v>3018</v>
+        <v>6006</v>
       </c>
       <c r="F286" t="n">
         <v>1</v>
@@ -17316,12 +17316,12 @@
       </c>
       <c r="J286" t="inlineStr">
         <is>
-          <t>Projeto de Expansão</t>
+          <t>ELABORAÇÃO E EXECUÇÃO DE PROJETOS RELACIONADOS À REFORMA, MODERNIZAÇÃO E ADEQUAÇÃO DAS INSTALAÇÕES PREDIAIS DA COMPANHIA.</t>
         </is>
       </c>
       <c r="K286" t="inlineStr">
         <is>
-          <t>EXECUÇÃO</t>
+          <t>INICIANDO</t>
         </is>
       </c>
       <c r="N286" t="inlineStr">
@@ -17331,36 +17331,36 @@
       </c>
       <c r="O286" t="inlineStr">
         <is>
-          <t>Região Intermediária de Belo Horizonte</t>
+          <t>Estadual</t>
         </is>
       </c>
       <c r="P286" t="inlineStr">
         <is>
-          <t>BELO HORIZONTE</t>
+          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
         </is>
       </c>
       <c r="Q286" t="n">
         <v>0</v>
       </c>
       <c r="R286" t="n">
-        <v>457766318</v>
+        <v>16317109</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="n">
-        <v>5391</v>
+        <v>5251</v>
       </c>
       <c r="B287" t="n">
         <v>25</v>
       </c>
       <c r="C287" t="n">
-        <v>752</v>
+        <v>121</v>
       </c>
       <c r="D287" t="n">
-        <v>92</v>
+        <v>133</v>
       </c>
       <c r="E287" t="n">
-        <v>3004</v>
+        <v>3018</v>
       </c>
       <c r="F287" t="n">
         <v>1</v>
@@ -17373,12 +17373,12 @@
       </c>
       <c r="J287" t="inlineStr">
         <is>
-          <t xml:space="preserve">Expansão e Aquisição do Sistema de Transmissão </t>
+          <t>Projeto de Expansão</t>
         </is>
       </c>
       <c r="K287" t="inlineStr">
         <is>
-          <t>INICIANDO</t>
+          <t>EXECUÇÃO</t>
         </is>
       </c>
       <c r="N287" t="inlineStr">
@@ -17393,14 +17393,14 @@
       </c>
       <c r="P287" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE BELO HORIZONTE</t>
+          <t>BELO HORIZONTE</t>
         </is>
       </c>
       <c r="Q287" t="n">
         <v>0</v>
       </c>
       <c r="R287" t="n">
-        <v>92004926</v>
+        <v>457766318</v>
       </c>
     </row>
     <row r="288">
@@ -17445,19 +17445,19 @@
       </c>
       <c r="O288" t="inlineStr">
         <is>
-          <t>Região Intermediária de Montes Claros</t>
+          <t>Região Intermediária de Belo Horizonte</t>
         </is>
       </c>
       <c r="P288" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE MONTES CLAROS</t>
+          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE BELO HORIZONTE</t>
         </is>
       </c>
       <c r="Q288" t="n">
         <v>0</v>
       </c>
       <c r="R288" t="n">
-        <v>10705994</v>
+        <v>92004926</v>
       </c>
     </row>
     <row r="289">
@@ -17502,19 +17502,19 @@
       </c>
       <c r="O289" t="inlineStr">
         <is>
-          <t>Região Intermediária de Juíz de Fora</t>
+          <t>Região Intermediária de Montes Claros</t>
         </is>
       </c>
       <c r="P289" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE JUÍZ DE FORA</t>
+          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE MONTES CLAROS</t>
         </is>
       </c>
       <c r="Q289" t="n">
         <v>0</v>
       </c>
       <c r="R289" t="n">
-        <v>10464844</v>
+        <v>10705994</v>
       </c>
     </row>
     <row r="290">
@@ -17559,19 +17559,19 @@
       </c>
       <c r="O290" t="inlineStr">
         <is>
-          <t>Região Intermediária de Uberlândia</t>
+          <t>Região Intermediária de Juíz de Fora</t>
         </is>
       </c>
       <c r="P290" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE UBERLÂNDIA</t>
+          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE JUÍZ DE FORA</t>
         </is>
       </c>
       <c r="Q290" t="n">
         <v>0</v>
       </c>
       <c r="R290" t="n">
-        <v>2098278</v>
+        <v>10464844</v>
       </c>
     </row>
     <row r="291">
@@ -17616,19 +17616,19 @@
       </c>
       <c r="O291" t="inlineStr">
         <is>
-          <t>Estadual</t>
+          <t>Região Intermediária de Uberlândia</t>
         </is>
       </c>
       <c r="P291" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
+          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE UBERLÂNDIA</t>
         </is>
       </c>
       <c r="Q291" t="n">
         <v>0</v>
       </c>
       <c r="R291" t="n">
-        <v>96721858</v>
+        <v>2098278</v>
       </c>
     </row>
     <row r="292">
@@ -17673,19 +17673,19 @@
       </c>
       <c r="O292" t="inlineStr">
         <is>
-          <t>Região Intermediária de Uberaba</t>
+          <t>Estadual</t>
         </is>
       </c>
       <c r="P292" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE UBERABA</t>
+          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
         </is>
       </c>
       <c r="Q292" t="n">
         <v>0</v>
       </c>
       <c r="R292" t="n">
-        <v>16415074</v>
+        <v>96721858</v>
       </c>
     </row>
     <row r="293">
@@ -17730,19 +17730,19 @@
       </c>
       <c r="O293" t="inlineStr">
         <is>
-          <t>Região Intermediária de Ipatinga</t>
+          <t>Região Intermediária de Uberaba</t>
         </is>
       </c>
       <c r="P293" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE IPATINGA</t>
+          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE UBERABA</t>
         </is>
       </c>
       <c r="Q293" t="n">
         <v>0</v>
       </c>
       <c r="R293" t="n">
-        <v>1</v>
+        <v>16415074</v>
       </c>
     </row>
     <row r="294">
@@ -17759,7 +17759,7 @@
         <v>92</v>
       </c>
       <c r="E294" t="n">
-        <v>3005</v>
+        <v>3004</v>
       </c>
       <c r="F294" t="n">
         <v>1</v>
@@ -17772,7 +17772,7 @@
       </c>
       <c r="J294" t="inlineStr">
         <is>
-          <t>Reformas de Subestações e Linhas de Transmissão</t>
+          <t xml:space="preserve">Expansão e Aquisição do Sistema de Transmissão </t>
         </is>
       </c>
       <c r="K294" t="inlineStr">
@@ -17787,19 +17787,19 @@
       </c>
       <c r="O294" t="inlineStr">
         <is>
-          <t>Região Intermediária de Belo Horizonte</t>
+          <t>Região Intermediária de Ipatinga</t>
         </is>
       </c>
       <c r="P294" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE BELO HORIZONTE</t>
+          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE IPATINGA</t>
         </is>
       </c>
       <c r="Q294" t="n">
         <v>0</v>
       </c>
       <c r="R294" t="n">
-        <v>126817302</v>
+        <v>1</v>
       </c>
     </row>
     <row r="295">
@@ -17844,19 +17844,19 @@
       </c>
       <c r="O295" t="inlineStr">
         <is>
-          <t>Região Intermediária de Montes Claros</t>
+          <t>Região Intermediária de Belo Horizonte</t>
         </is>
       </c>
       <c r="P295" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE MONTES CLAROS</t>
+          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE BELO HORIZONTE</t>
         </is>
       </c>
       <c r="Q295" t="n">
         <v>0</v>
       </c>
       <c r="R295" t="n">
-        <v>16058991</v>
+        <v>126817302</v>
       </c>
     </row>
     <row r="296">
@@ -17901,19 +17901,19 @@
       </c>
       <c r="O296" t="inlineStr">
         <is>
-          <t>Região Intermediária de Juíz de Fora</t>
+          <t>Região Intermediária de Montes Claros</t>
         </is>
       </c>
       <c r="P296" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE JUÍZ DE FORA</t>
+          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE MONTES CLAROS</t>
         </is>
       </c>
       <c r="Q296" t="n">
         <v>0</v>
       </c>
       <c r="R296" t="n">
-        <v>65795530</v>
+        <v>16058991</v>
       </c>
     </row>
     <row r="297">
@@ -17958,19 +17958,19 @@
       </c>
       <c r="O297" t="inlineStr">
         <is>
-          <t>Região Intermediária de Uberlândia</t>
+          <t>Região Intermediária de Juíz de Fora</t>
         </is>
       </c>
       <c r="P297" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE UBERLÂNDIA</t>
+          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE JUÍZ DE FORA</t>
         </is>
       </c>
       <c r="Q297" t="n">
         <v>0</v>
       </c>
       <c r="R297" t="n">
-        <v>44156794</v>
+        <v>65795530</v>
       </c>
     </row>
     <row r="298">
@@ -18015,19 +18015,19 @@
       </c>
       <c r="O298" t="inlineStr">
         <is>
-          <t>Estadual</t>
+          <t>Região Intermediária de Uberlândia</t>
         </is>
       </c>
       <c r="P298" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
+          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE UBERLÂNDIA</t>
         </is>
       </c>
       <c r="Q298" t="n">
         <v>0</v>
       </c>
       <c r="R298" t="n">
-        <v>140716908</v>
+        <v>44156794</v>
       </c>
     </row>
     <row r="299">
@@ -18072,19 +18072,19 @@
       </c>
       <c r="O299" t="inlineStr">
         <is>
-          <t>Região Intermediária de Ipatinga</t>
+          <t>Estadual</t>
         </is>
       </c>
       <c r="P299" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE IPATINGA</t>
+          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
         </is>
       </c>
       <c r="Q299" t="n">
         <v>0</v>
       </c>
       <c r="R299" t="n">
-        <v>8715687</v>
+        <v>140716908</v>
       </c>
     </row>
     <row r="300">
@@ -18129,19 +18129,19 @@
       </c>
       <c r="O300" t="inlineStr">
         <is>
-          <t>Região Intermediária de Uberaba</t>
+          <t>Região Intermediária de Ipatinga</t>
         </is>
       </c>
       <c r="P300" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE UBERABA</t>
+          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE IPATINGA</t>
         </is>
       </c>
       <c r="Q300" t="n">
         <v>0</v>
       </c>
       <c r="R300" t="n">
-        <v>24622611</v>
+        <v>8715687</v>
       </c>
     </row>
     <row r="301">
@@ -18155,10 +18155,10 @@
         <v>752</v>
       </c>
       <c r="D301" t="n">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E301" t="n">
-        <v>3001</v>
+        <v>3005</v>
       </c>
       <c r="F301" t="n">
         <v>1</v>
@@ -18171,33 +18171,90 @@
       </c>
       <c r="J301" t="inlineStr">
         <is>
+          <t>Reformas de Subestações e Linhas de Transmissão</t>
+        </is>
+      </c>
+      <c r="K301" t="inlineStr">
+        <is>
+          <t>INICIANDO</t>
+        </is>
+      </c>
+      <c r="N301" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="O301" t="inlineStr">
+        <is>
+          <t>Região Intermediária de Uberaba</t>
+        </is>
+      </c>
+      <c r="P301" t="inlineStr">
+        <is>
+          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE UBERABA</t>
+        </is>
+      </c>
+      <c r="Q301" t="n">
+        <v>0</v>
+      </c>
+      <c r="R301" t="n">
+        <v>24622611</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="n">
+        <v>5391</v>
+      </c>
+      <c r="B302" t="n">
+        <v>25</v>
+      </c>
+      <c r="C302" t="n">
+        <v>752</v>
+      </c>
+      <c r="D302" t="n">
+        <v>94</v>
+      </c>
+      <c r="E302" t="n">
+        <v>3001</v>
+      </c>
+      <c r="F302" t="n">
+        <v>1</v>
+      </c>
+      <c r="G302" t="n">
+        <v>0</v>
+      </c>
+      <c r="H302" t="n">
+        <v>301</v>
+      </c>
+      <c r="J302" t="inlineStr">
+        <is>
           <t>Expansão do Sistema de Geração</t>
         </is>
       </c>
-      <c r="K301" t="inlineStr">
-        <is>
-          <t>INICIANDO</t>
-        </is>
-      </c>
-      <c r="N301" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="O301" t="inlineStr">
+      <c r="K302" t="inlineStr">
+        <is>
+          <t>INICIANDO</t>
+        </is>
+      </c>
+      <c r="N302" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="O302" t="inlineStr">
         <is>
           <t>Estadual</t>
         </is>
       </c>
-      <c r="P301" t="inlineStr">
+      <c r="P302" t="inlineStr">
         <is>
           <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
         </is>
       </c>
-      <c r="Q301" t="n">
-        <v>0</v>
-      </c>
-      <c r="R301" t="n">
+      <c r="Q302" t="n">
+        <v>0</v>
+      </c>
+      <c r="R302" t="n">
         <v>1</v>
       </c>
     </row>
